--- a/docs/rewards/Rewards_HLRD_LLRD.xlsx
+++ b/docs/rewards/Rewards_HLRD_LLRD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MansiGupta\myworld\life-experiences-webpage\docs\rewards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A893EF0D-AA5E-4F5D-B325-99D66C9D751E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB280F5A-D1F4-46B2-B499-1968F1052134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2935" uniqueCount="1180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2935" uniqueCount="1179">
   <si>
     <t>Rewards Microfrontend: HLRD and LLRD workbook</t>
   </si>
@@ -207,66 +207,66 @@
     <t>Tiles &amp; areas: User-managed tiles and areas (create, edit, reorder, delete); empty start with an optional starter set</t>
   </si>
   <si>
+    <t>Built &amp; tested</t>
+  </si>
+  <si>
+    <t>Must</t>
+  </si>
+  <si>
+    <t>HLR-2</t>
+  </si>
+  <si>
+    <t>Task management: Create, prioritise, filter, change status/frequency/relevance</t>
+  </si>
+  <si>
+    <t>HLR-3</t>
+  </si>
+  <si>
+    <t>Completion &amp; streaks: Log completions with note/backfill; activity log; current/best streak</t>
+  </si>
+  <si>
+    <t>HLR-4</t>
+  </si>
+  <si>
+    <t>Rewards: Create, tag, progress, auto-unlock, claim</t>
+  </si>
+  <si>
+    <t>HLR-5</t>
+  </si>
+  <si>
+    <t>Insights dashboard: Aggregates, filters, cached reads, claim from dashboard</t>
+  </si>
+  <si>
+    <t>HLR-6</t>
+  </si>
+  <si>
+    <t>AI task suggestions: Photos → suggestions → decisions → tasks; non-blocking</t>
+  </si>
+  <si>
+    <t>Planned</t>
+  </si>
+  <si>
+    <t>HLR-7</t>
+  </si>
+  <si>
+    <t>Module composition: Independently delivered MFE with host fallback</t>
+  </si>
+  <si>
+    <t>HLR-8</t>
+  </si>
+  <si>
+    <t>API (BFF): Versionable, documented, client-shaped API with demo auth</t>
+  </si>
+  <si>
+    <t>HLR-9</t>
+  </si>
+  <si>
+    <t>Reward scope and matching: Rewards live in the same tiles and areas as tasks; tasks are matched to rewards inside that scope (selected tasks, or all tasks in scope); existing rewards migrated without data loss</t>
+  </si>
+  <si>
     <t>Next</t>
   </si>
   <si>
-    <t>Must</t>
-  </si>
-  <si>
-    <t>HLR-2</t>
-  </si>
-  <si>
-    <t>Task management: Create, prioritise, filter, change status/frequency/relevance</t>
-  </si>
-  <si>
-    <t>Built &amp; tested</t>
-  </si>
-  <si>
-    <t>HLR-3</t>
-  </si>
-  <si>
-    <t>Completion &amp; streaks: Log completions with note/backfill; activity log; current/best streak</t>
-  </si>
-  <si>
-    <t>HLR-4</t>
-  </si>
-  <si>
-    <t>Rewards: Create, tag, progress, auto-unlock, claim</t>
-  </si>
-  <si>
-    <t>HLR-5</t>
-  </si>
-  <si>
-    <t>Insights dashboard: Aggregates, filters, cached reads, claim from dashboard</t>
-  </si>
-  <si>
-    <t>HLR-6</t>
-  </si>
-  <si>
-    <t>AI task suggestions: Photos → suggestions → decisions → tasks; non-blocking</t>
-  </si>
-  <si>
-    <t>Planned</t>
-  </si>
-  <si>
-    <t>HLR-7</t>
-  </si>
-  <si>
-    <t>Module composition: Independently delivered MFE with host fallback</t>
-  </si>
-  <si>
-    <t>HLR-8</t>
-  </si>
-  <si>
-    <t>API (BFF): Versionable, documented, client-shaped API with demo auth</t>
-  </si>
-  <si>
-    <t>HLR-9</t>
-  </si>
-  <si>
-    <t>Reward scope and matching: Rewards live in the same tiles and areas as tasks; tasks are matched to rewards inside that scope (selected tasks, or all tasks in scope); existing rewards migrated without data loss</t>
-  </si>
-  <si>
     <t>HLR-10</t>
   </si>
   <si>
@@ -2013,15 +2013,15 @@
     <t>User-managed tiles (CRUD), no seeding, optional starter set (HLR-1 update)</t>
   </si>
   <si>
+    <t>T3d</t>
+  </si>
+  <si>
+    <t>Notes, contacts and files on tiles and areas (HLR-10)</t>
+  </si>
+  <si>
     <t>⏳ next</t>
   </si>
   <si>
-    <t>T3d</t>
-  </si>
-  <si>
-    <t>Notes, contacts and files on tiles and areas (HLR-10)</t>
-  </si>
-  <si>
     <t>T3e</t>
   </si>
   <si>
@@ -2136,9 +2136,6 @@
     <t>LLR-1.x</t>
   </si>
   <si>
-    <t>🟡 areas ✅, tiles CRUD ⏳ next</t>
-  </si>
-  <si>
     <t>Task management</t>
   </si>
   <si>
@@ -2910,7 +2907,10 @@
     <t>🟡</t>
   </si>
   <si>
-    <t>User-managed tiles (HLR-1 update) ⏳ next</t>
+    <t>User-managed tiles (HLR-1 update) ✅</t>
+  </si>
+  <si>
+    <t>✅ (up/down; drag on wide screens later)</t>
   </si>
   <si>
     <t>AC-1.7 to 1.12</t>
@@ -3153,13 +3153,13 @@
     <t>Tiles</t>
   </si>
   <si>
-    <t>Tiles: icon, name, area count, active task count; ⏳ "+ New tile"; ⏳ search box (LLR-10.9)</t>
-  </si>
-  <si>
-    <t>loading, error+retry; ⏳ empty: "Create your first tile" + "Add suggested tiles"</t>
-  </si>
-  <si>
-    <t>open tile; ⏳ create, edit, reorder, delete tile</t>
+    <t>Tiles: icon, name, area count, active task count; "Edit tiles" mode (↑ ↓ ✎ 🗑, "+ New tile", "Add suggested tiles"); ⏳ search box (LLR-10.9)</t>
+  </si>
+  <si>
+    <t>loading, error+retry; empty: "Create your first tile" + "Add suggested tiles"</t>
+  </si>
+  <si>
+    <t>open tile; create, edit, reorder, delete tile (typed-name dialog)</t>
   </si>
   <si>
     <t>Tile (category)</t>
@@ -3171,7 +3171,7 @@
     <t>loading, error, empty ("No areas yet"), not found</t>
   </si>
   <si>
-    <t>add, rename (inline), delete (confirm) area; ⏳ edit or delete this tile; ⏳ tile-level notes, contacts, files</t>
+    <t>add, rename (inline), reorder (↑ ↓), delete (confirm) area; edit or delete this tile; ⏳ tile-level notes, contacts, files</t>
   </si>
   <si>
     <t>⏳ Notes &amp; contacts (tab on tile and area)</t>
@@ -3435,10 +3435,7 @@
     <t>LLR-1.1 (superseded)</t>
   </si>
   <si>
-    <t>lifespan seed, GET /categories</t>
-  </si>
-  <si>
-    <t>test_seeded_tiles_and_sub_tiles (to be replaced by the LLR-1.7 tests)</t>
+    <t>replaced by test_starter_set_contents and the LLR-1.7 tests</t>
   </si>
   <si>
     <t>LLR-1.3–1.5</t>
@@ -3456,7 +3453,7 @@
     <t>/categories*</t>
   </si>
   <si>
-    <t>⏳ planned: test_fresh_database_has_no_tiles, test_starter_set_is_idempotent, test_tile_crud_and_unique_names, test_delete_tile_snapshots_and_cascades, test_upgrade_keeps_existing_tiles</t>
+    <t>test_fresh_database_has_no_tiles, test_starter_set_is_idempotent, test_starter_set_fills_in_missing_areas_only, test_tile_crud_and_unique_names, test_new_tile_ids_stay_unique, test_reorder_tiles_and_areas, test_delete_tile_needs_typed_name_snapshots_and_cascades, test_restart_never_reseeds, test_upgrade_keeps_existing_tiles</t>
   </si>
   <si>
     <t>LLR-12.1–12.9; BR-R27–R30; LLR-8.13</t>
@@ -4144,60 +4141,60 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>742</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>743</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>457</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>745</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>746</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>747</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>749</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>747</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>752</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>753</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>464</v>
@@ -4218,12 +4215,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -4244,119 +4241,119 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>757</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>758</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>759</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>761</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>762</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>762</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>764</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>762</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>765</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>767</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>762</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>762</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
+        <v>768</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>769</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>762</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>770</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="42" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>772</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>762</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>762</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>774</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>765</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>776</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>765</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>777</v>
       </c>
     </row>
   </sheetData>
@@ -4374,67 +4371,67 @@
   <sheetData>
     <row r="1" spans="1:1" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="42" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="28" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="56" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="70" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="56" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
   </sheetData>
@@ -4454,12 +4451,12 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -4467,10 +4464,10 @@
         <v>466</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>793</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>794</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>27</v>
@@ -4478,357 +4475,357 @@
     </row>
     <row r="5" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>795</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>796</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>797</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="42" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>799</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>800</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>801</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>803</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>804</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>805</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>807</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>808</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>809</v>
-      </c>
       <c r="D8" s="7" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>810</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>811</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>812</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>814</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>815</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="D10" s="7" t="s">
         <v>816</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>818</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>820</v>
-      </c>
       <c r="D11" s="7" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="7" t="s">
         <v>823</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>827</v>
-      </c>
       <c r="D13" s="7" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>830</v>
-      </c>
       <c r="D14" s="7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="42" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>831</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>833</v>
-      </c>
       <c r="D15" s="7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="42" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>834</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>835</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>836</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>838</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>839</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>840</v>
-      </c>
       <c r="D17" s="7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="42" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>841</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>842</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>843</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>845</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>846</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>847</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="42" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>849</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>850</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>851</v>
-      </c>
       <c r="D20" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>852</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>853</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>854</v>
-      </c>
       <c r="D21" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>855</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>856</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>857</v>
-      </c>
       <c r="D22" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="42" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>858</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>859</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>860</v>
-      </c>
       <c r="D23" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="42" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
+        <v>860</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>861</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>862</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>863</v>
-      </c>
       <c r="D24" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>864</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="7" t="s">
         <v>865</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>866</v>
-      </c>
       <c r="D25" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>867</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="C26" s="7" t="s">
         <v>868</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="7" t="s">
         <v>869</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>871</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="C27" s="7" t="s">
         <v>872</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>873</v>
-      </c>
       <c r="D27" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
+        <v>873</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>874</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>875</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="D28" s="7" t="s">
         <v>876</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
+        <v>877</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="C29" s="7" t="s">
         <v>879</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>880</v>
-      </c>
       <c r="D29" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="13" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -4836,24 +4833,24 @@
         <v>466</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
+        <v>883</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>884</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="C33" s="7" t="s">
         <v>885</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>886</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>464</v>
@@ -4861,86 +4858,86 @@
     </row>
     <row r="34" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>887</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="C34" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>888</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>886</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>890</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="C35" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>891</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>886</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>893</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="C36" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>894</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>886</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>896</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="C37" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>897</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>886</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
+        <v>898</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>899</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="C38" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>900</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>886</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>902</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="C39" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>903</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>886</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -4961,43 +4958,43 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>906</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>907</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>908</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>910</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>912</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
+        <v>913</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>914</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>915</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>691</v>
@@ -5011,27 +5008,27 @@
         <v>631</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>915</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>916</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>917</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
+        <v>917</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>919</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>920</v>
-      </c>
       <c r="D7" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -5039,55 +5036,55 @@
         <v>544</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>921</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>922</v>
-      </c>
       <c r="D8" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>583</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
+        <v>924</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>925</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>926</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="D10" s="7" t="s">
         <v>927</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
+        <v>928</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>929</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>930</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>931</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -5095,13 +5092,13 @@
         <v>547</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>932</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>934</v>
-      </c>
       <c r="D12" s="7" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" x14ac:dyDescent="0.35">
@@ -5109,27 +5106,27 @@
         <v>627</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>935</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>936</v>
-      </c>
       <c r="D13" s="7" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
+        <v>936</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>937</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>938</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>939</v>
-      </c>
       <c r="D14" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -5140,10 +5137,10 @@
         <v>603</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -5154,24 +5151,24 @@
         <v>464</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
+        <v>941</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>942</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>943</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>944</v>
-      </c>
       <c r="D17" s="7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -5179,13 +5176,13 @@
         <v>611</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>945</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>946</v>
-      </c>
       <c r="D18" s="7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -5199,17 +5196,17 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="70" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="41" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -5231,7 +5228,7 @@
         <v>95</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -5242,7 +5239,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -5286,12 +5283,12 @@
         <v>107</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -5313,7 +5310,7 @@
         <v>109</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="56" x14ac:dyDescent="0.35">
@@ -5324,7 +5321,7 @@
         <v>111</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -5335,7 +5332,7 @@
         <v>113</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -5346,7 +5343,7 @@
         <v>115</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -5357,7 +5354,7 @@
         <v>117</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>652</v>
+        <v>951</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -5368,7 +5365,7 @@
         <v>119</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -5379,7 +5376,7 @@
         <v>121</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -5472,7 +5469,7 @@
         <v>125</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
@@ -5527,7 +5524,7 @@
         <v>135</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -5607,7 +5604,7 @@
         <v>143</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -5673,7 +5670,7 @@
         <v>155</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -5808,7 +5805,7 @@
         <v>161</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -5863,7 +5860,7 @@
         <v>171</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -6175,7 +6172,7 @@
         <v>195</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -6186,7 +6183,7 @@
         <v>197</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
@@ -6197,7 +6194,7 @@
         <v>199</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -6208,7 +6205,7 @@
         <v>201</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
@@ -6219,7 +6216,7 @@
         <v>203</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -6230,7 +6227,7 @@
         <v>205</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
@@ -6241,7 +6238,7 @@
         <v>207</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
@@ -6397,7 +6394,7 @@
         <v>235</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
@@ -6419,7 +6416,7 @@
         <v>239</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
@@ -6430,7 +6427,7 @@
         <v>241</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -6452,7 +6449,7 @@
         <v>245</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
@@ -6463,7 +6460,7 @@
         <v>247</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -6589,7 +6586,7 @@
         <v>267</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="56" x14ac:dyDescent="0.35">
@@ -6600,7 +6597,7 @@
         <v>271</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="70" x14ac:dyDescent="0.35">
@@ -6611,7 +6608,7 @@
         <v>273</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="56" x14ac:dyDescent="0.35">
@@ -6622,7 +6619,7 @@
         <v>269</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -6659,7 +6656,7 @@
         <v>275</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -6670,7 +6667,7 @@
         <v>277</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="56" x14ac:dyDescent="0.35">
@@ -6681,7 +6678,7 @@
         <v>279</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -6692,7 +6689,7 @@
         <v>281</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -6703,7 +6700,7 @@
         <v>283</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -6714,7 +6711,7 @@
         <v>285</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="56" x14ac:dyDescent="0.35">
@@ -6725,7 +6722,7 @@
         <v>287</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -6736,7 +6733,7 @@
         <v>289</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="56" x14ac:dyDescent="0.35">
@@ -6747,7 +6744,7 @@
         <v>291</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -6758,7 +6755,7 @@
         <v>293</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -6769,7 +6766,7 @@
         <v>295</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -6780,7 +6777,7 @@
         <v>297</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -6905,7 +6902,7 @@
         <v>299</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -6916,7 +6913,7 @@
         <v>301</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -6927,7 +6924,7 @@
         <v>303</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="56" x14ac:dyDescent="0.35">
@@ -6938,7 +6935,7 @@
         <v>305</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -6949,7 +6946,7 @@
         <v>307</v>
       </c>
       <c r="C226" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -6960,7 +6957,7 @@
         <v>309</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="56" x14ac:dyDescent="0.35">
@@ -6971,7 +6968,7 @@
         <v>311</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="56" x14ac:dyDescent="0.35">
@@ -6982,7 +6979,7 @@
         <v>313</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -6993,7 +6990,7 @@
         <v>315</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -7004,7 +7001,7 @@
         <v>317</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -7015,7 +7012,7 @@
         <v>319</v>
       </c>
       <c r="C232" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -7026,7 +7023,7 @@
         <v>321</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -7037,7 +7034,7 @@
         <v>323</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -7167,7 +7164,7 @@
         <v>325</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -7178,7 +7175,7 @@
         <v>327</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -7189,7 +7186,7 @@
         <v>329</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="56" x14ac:dyDescent="0.35">
@@ -7200,7 +7197,7 @@
         <v>331</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="56" x14ac:dyDescent="0.35">
@@ -7211,7 +7208,7 @@
         <v>333</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -7222,7 +7219,7 @@
         <v>335</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="42" x14ac:dyDescent="0.35">
@@ -7233,7 +7230,7 @@
         <v>337</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -7244,7 +7241,7 @@
         <v>339</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -7255,7 +7252,7 @@
         <v>341</v>
       </c>
       <c r="C266" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -8072,7 +8069,7 @@
         <v>53</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>51</v>
@@ -8088,17 +8085,17 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>51</v>
@@ -8114,17 +8111,17 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>51</v>
@@ -8140,17 +8137,17 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>51</v>
@@ -8166,17 +8163,17 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>63</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -8192,17 +8189,17 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>51</v>
@@ -8218,17 +8215,17 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>51</v>
@@ -8244,17 +8241,17 @@
     </row>
     <row r="18" spans="1:10" ht="42" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>51</v>
@@ -8280,7 +8277,7 @@
         <v>71</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>51</v>
@@ -8306,7 +8303,7 @@
         <v>73</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>51</v>
@@ -8332,7 +8329,7 @@
         <v>75</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>51</v>
@@ -8612,7 +8609,7 @@
         <v>101</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>51</v>
@@ -8640,7 +8637,7 @@
         <v>103</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>51</v>
@@ -8668,7 +8665,7 @@
         <v>105</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>51</v>
@@ -8920,7 +8917,7 @@
         <v>123</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>51</v>
@@ -8976,7 +8973,7 @@
         <v>127</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>51</v>
@@ -9004,7 +9001,7 @@
         <v>129</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>51</v>
@@ -9032,7 +9029,7 @@
         <v>131</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>51</v>
@@ -9060,7 +9057,7 @@
         <v>133</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>51</v>
@@ -9116,7 +9113,7 @@
         <v>137</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>51</v>
@@ -9144,7 +9141,7 @@
         <v>139</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>51</v>
@@ -9166,13 +9163,13 @@
         <v>94</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>51</v>
@@ -9194,7 +9191,7 @@
         <v>94</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>143</v>
@@ -9222,13 +9219,13 @@
         <v>94</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>145</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>51</v>
@@ -9250,13 +9247,13 @@
         <v>94</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>147</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>51</v>
@@ -9278,13 +9275,13 @@
         <v>94</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>149</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>51</v>
@@ -9306,13 +9303,13 @@
         <v>94</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>151</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>51</v>
@@ -9334,13 +9331,13 @@
         <v>94</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>153</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>51</v>
@@ -9362,7 +9359,7 @@
         <v>94</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>155</v>
@@ -9390,13 +9387,13 @@
         <v>94</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>157</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>51</v>
@@ -9418,13 +9415,13 @@
         <v>94</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>159</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>51</v>
@@ -9446,7 +9443,7 @@
         <v>94</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>161</v>
@@ -9474,13 +9471,13 @@
         <v>94</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>163</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>51</v>
@@ -9502,13 +9499,13 @@
         <v>94</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>165</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>51</v>
@@ -9530,13 +9527,13 @@
         <v>94</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>167</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>51</v>
@@ -9558,13 +9555,13 @@
         <v>94</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>169</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>51</v>
@@ -9586,7 +9583,7 @@
         <v>94</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>171</v>
@@ -9614,13 +9611,13 @@
         <v>94</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>173</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>51</v>
@@ -9642,13 +9639,13 @@
         <v>94</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>175</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>51</v>
@@ -9670,13 +9667,13 @@
         <v>94</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>177</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>51</v>
@@ -9698,13 +9695,13 @@
         <v>94</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>179</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>51</v>
@@ -9726,13 +9723,13 @@
         <v>94</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>181</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>51</v>
@@ -9754,13 +9751,13 @@
         <v>94</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>183</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>51</v>
@@ -9782,13 +9779,13 @@
         <v>94</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>185</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>51</v>
@@ -9810,13 +9807,13 @@
         <v>94</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>187</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>51</v>
@@ -9838,13 +9835,13 @@
         <v>94</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>189</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>51</v>
@@ -9866,13 +9863,13 @@
         <v>94</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>191</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>51</v>
@@ -9894,13 +9891,13 @@
         <v>94</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>193</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>51</v>
@@ -9922,7 +9919,7 @@
         <v>94</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>195</v>
@@ -9950,7 +9947,7 @@
         <v>94</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>197</v>
@@ -9978,7 +9975,7 @@
         <v>94</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>199</v>
@@ -10006,7 +10003,7 @@
         <v>94</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>201</v>
@@ -10034,7 +10031,7 @@
         <v>94</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>203</v>
@@ -10062,7 +10059,7 @@
         <v>94</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>205</v>
@@ -10090,7 +10087,7 @@
         <v>94</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>207</v>
@@ -10118,13 +10115,13 @@
         <v>94</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>209</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>51</v>
@@ -10146,13 +10143,13 @@
         <v>94</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>211</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>51</v>
@@ -10174,13 +10171,13 @@
         <v>94</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>213</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>51</v>
@@ -10202,13 +10199,13 @@
         <v>94</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>215</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>31</v>
@@ -10230,13 +10227,13 @@
         <v>94</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>217</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>31</v>
@@ -10258,13 +10255,13 @@
         <v>94</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>219</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>31</v>
@@ -10286,13 +10283,13 @@
         <v>94</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>221</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -10314,13 +10311,13 @@
         <v>94</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>223</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>31</v>
@@ -10342,13 +10339,13 @@
         <v>94</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>225</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -10370,13 +10367,13 @@
         <v>94</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>227</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>31</v>
@@ -10398,13 +10395,13 @@
         <v>94</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>229</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>31</v>
@@ -10426,13 +10423,13 @@
         <v>94</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>231</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>31</v>
@@ -10454,13 +10451,13 @@
         <v>94</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>233</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>51</v>
@@ -10482,7 +10479,7 @@
         <v>94</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>235</v>
@@ -10510,7 +10507,7 @@
         <v>94</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>237</v>
@@ -10538,7 +10535,7 @@
         <v>94</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>239</v>
@@ -10566,7 +10563,7 @@
         <v>94</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>241</v>
@@ -10594,13 +10591,13 @@
         <v>94</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>243</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>51</v>
@@ -10622,7 +10619,7 @@
         <v>94</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>245</v>
@@ -10650,7 +10647,7 @@
         <v>94</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>247</v>
@@ -10678,13 +10675,13 @@
         <v>94</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>249</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>51</v>
@@ -10706,13 +10703,13 @@
         <v>94</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>251</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>51</v>
@@ -10734,13 +10731,13 @@
         <v>94</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>253</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>51</v>
@@ -10762,13 +10759,13 @@
         <v>94</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>255</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>51</v>
@@ -10790,13 +10787,13 @@
         <v>94</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>257</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>51</v>
@@ -10818,13 +10815,13 @@
         <v>94</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>259</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>51</v>
@@ -10846,13 +10843,13 @@
         <v>94</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>261</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>51</v>
@@ -10874,13 +10871,13 @@
         <v>94</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>263</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>51</v>
@@ -10902,13 +10899,13 @@
         <v>94</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D113" s="8" t="s">
         <v>265</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>51</v>
@@ -10964,7 +10961,7 @@
         <v>269</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>51</v>
@@ -10992,7 +10989,7 @@
         <v>271</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>51</v>
@@ -11020,7 +11017,7 @@
         <v>273</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>51</v>
@@ -11048,7 +11045,7 @@
         <v>275</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>51</v>
@@ -11076,7 +11073,7 @@
         <v>277</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>51</v>
@@ -11104,7 +11101,7 @@
         <v>279</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>51</v>
@@ -11132,7 +11129,7 @@
         <v>281</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>51</v>
@@ -11160,7 +11157,7 @@
         <v>283</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>51</v>
@@ -11188,7 +11185,7 @@
         <v>285</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>51</v>
@@ -11216,7 +11213,7 @@
         <v>287</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>51</v>
@@ -11244,7 +11241,7 @@
         <v>289</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>51</v>
@@ -11272,7 +11269,7 @@
         <v>291</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>51</v>
@@ -11300,7 +11297,7 @@
         <v>293</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>51</v>
@@ -11328,7 +11325,7 @@
         <v>295</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>51</v>
@@ -11356,7 +11353,7 @@
         <v>297</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>51</v>
@@ -11384,7 +11381,7 @@
         <v>299</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>51</v>
@@ -11412,7 +11409,7 @@
         <v>301</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>51</v>
@@ -11440,7 +11437,7 @@
         <v>303</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>51</v>
@@ -11468,7 +11465,7 @@
         <v>305</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>51</v>
@@ -11496,7 +11493,7 @@
         <v>307</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>51</v>
@@ -11524,7 +11521,7 @@
         <v>309</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>51</v>
@@ -11552,7 +11549,7 @@
         <v>311</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>51</v>
@@ -11580,7 +11577,7 @@
         <v>313</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>51</v>
@@ -11608,7 +11605,7 @@
         <v>315</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>51</v>
@@ -11636,7 +11633,7 @@
         <v>317</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>51</v>
@@ -11664,7 +11661,7 @@
         <v>319</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>51</v>
@@ -11692,7 +11689,7 @@
         <v>321</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>51</v>
@@ -11720,7 +11717,7 @@
         <v>323</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>51</v>
@@ -11748,7 +11745,7 @@
         <v>325</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>51</v>
@@ -11776,7 +11773,7 @@
         <v>327</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>51</v>
@@ -11804,7 +11801,7 @@
         <v>329</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>51</v>
@@ -11832,7 +11829,7 @@
         <v>331</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>51</v>
@@ -11860,7 +11857,7 @@
         <v>333</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>51</v>
@@ -11888,7 +11885,7 @@
         <v>335</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>51</v>
@@ -11916,7 +11913,7 @@
         <v>337</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>51</v>
@@ -11944,7 +11941,7 @@
         <v>339</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>51</v>
@@ -11972,7 +11969,7 @@
         <v>341</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>51</v>
@@ -11994,13 +11991,13 @@
         <v>343</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D152" s="8" t="s">
         <v>344</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>51</v>
@@ -12022,13 +12019,13 @@
         <v>343</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>346</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>51</v>
@@ -12050,13 +12047,13 @@
         <v>343</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>348</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>51</v>
@@ -12078,13 +12075,13 @@
         <v>343</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>350</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>51</v>
@@ -12106,13 +12103,13 @@
         <v>343</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>352</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>51</v>
@@ -12134,13 +12131,13 @@
         <v>343</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>354</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>51</v>
@@ -12162,13 +12159,13 @@
         <v>343</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D158" s="8" t="s">
         <v>356</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>51</v>
@@ -12190,13 +12187,13 @@
         <v>343</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D159" s="8" t="s">
         <v>358</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>51</v>
@@ -12218,13 +12215,13 @@
         <v>343</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D160" s="8" t="s">
         <v>360</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>51</v>
@@ -12246,13 +12243,13 @@
         <v>343</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D161" s="8" t="s">
         <v>362</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>51</v>
@@ -12274,13 +12271,13 @@
         <v>343</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D162" s="8" t="s">
         <v>364</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>51</v>
@@ -12302,13 +12299,13 @@
         <v>343</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D163" s="8" t="s">
         <v>366</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>51</v>
@@ -12330,13 +12327,13 @@
         <v>343</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>368</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>51</v>
@@ -12358,13 +12355,13 @@
         <v>343</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D165" s="8" t="s">
         <v>370</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>51</v>
@@ -12386,13 +12383,13 @@
         <v>343</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D166" s="8" t="s">
         <v>372</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>51</v>
@@ -12414,13 +12411,13 @@
         <v>343</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D167" s="8" t="s">
         <v>374</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>51</v>
@@ -12532,7 +12529,7 @@
         <v>382</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>51</v>
@@ -12560,7 +12557,7 @@
         <v>384</v>
       </c>
       <c r="E172" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>51</v>
@@ -12588,7 +12585,7 @@
         <v>386</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>51</v>
@@ -12616,7 +12613,7 @@
         <v>388</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>51</v>
@@ -12644,7 +12641,7 @@
         <v>390</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>51</v>
@@ -12672,7 +12669,7 @@
         <v>392</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>51</v>
@@ -12700,7 +12697,7 @@
         <v>394</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>51</v>
@@ -12728,7 +12725,7 @@
         <v>396</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>51</v>
@@ -12756,7 +12753,7 @@
         <v>398</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>51</v>
@@ -12784,7 +12781,7 @@
         <v>400</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>51</v>
@@ -12812,7 +12809,7 @@
         <v>402</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>51</v>
@@ -12840,7 +12837,7 @@
         <v>405</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>51</v>
@@ -12868,7 +12865,7 @@
         <v>408</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>51</v>
@@ -12896,7 +12893,7 @@
         <v>410</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>51</v>
@@ -12924,7 +12921,7 @@
         <v>412</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>51</v>
@@ -12952,7 +12949,7 @@
         <v>414</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>51</v>
@@ -12980,7 +12977,7 @@
         <v>416</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>51</v>
@@ -13008,7 +13005,7 @@
         <v>418</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>51</v>
@@ -13036,7 +13033,7 @@
         <v>420</v>
       </c>
       <c r="E189" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>51</v>
@@ -13064,7 +13061,7 @@
         <v>422</v>
       </c>
       <c r="E190" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>51</v>
@@ -13092,7 +13089,7 @@
         <v>424</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>51</v>
@@ -13120,7 +13117,7 @@
         <v>426</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>51</v>
@@ -13164,7 +13161,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1123</v>
@@ -13178,109 +13175,109 @@
         <v>1125</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>1126</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>1128</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>1129</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
         <v>1130</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="42" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="B6" s="7" t="s">
         <v>1131</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>1132</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="56" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>1134</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>1135</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="70" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>1137</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>1138</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="56" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>1140</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>1141</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>1143</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>1144</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>1146</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>1147</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>1149</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>1150</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>1152</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -13288,10 +13285,10 @@
         <v>357</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -13302,18 +13299,18 @@
         <v>464</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>1156</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>1157</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -13321,65 +13318,65 @@
         <v>248</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>1159</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>464</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>661</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>1165</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>1167</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>1169</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>1170</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -13387,32 +13384,32 @@
         <v>188</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>1172</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="56" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>1175</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>1177</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="7" t="s">
         <v>1178</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>1179</v>
       </c>
     </row>
   </sheetData>
@@ -13453,16 +13450,16 @@
         <v>431</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>432</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>433</v>
@@ -13482,7 +13479,7 @@
       </c>
       <c r="D5" s="7">
         <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A5,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E5" s="7">
         <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A5,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
@@ -13490,7 +13487,7 @@
       </c>
       <c r="F5" s="7">
         <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A5,'Requirements Register'!$E$5:$E$392,"Next")</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7">
         <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A5,'Requirements Register'!$E$5:$E$392,"Planned")</f>
@@ -13498,7 +13495,7 @@
       </c>
       <c r="H5" s="9">
         <f t="shared" ref="H5:H17" si="0">IF(C5=0,"-",(D5+E5)/C5)</f>
-        <v>0.29411764705882354</v>
+        <v>0.94117647058823528</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -13536,7 +13533,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="7" t="str">
         <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A7,'Requirements Register'!$A$5:$A$392,0)),"")</f>
@@ -13569,7 +13566,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="7" t="str">
         <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A8,'Requirements Register'!$A$5:$A$392,0)),"")</f>
@@ -13602,7 +13599,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B9" s="7" t="str">
         <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A9,'Requirements Register'!$A$5:$A$392,0)),"")</f>
@@ -13635,7 +13632,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="7" t="str">
         <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A10,'Requirements Register'!$A$5:$A$392,0)),"")</f>
@@ -13668,7 +13665,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="7" t="str">
         <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A11,'Requirements Register'!$A$5:$A$392,0)),"")</f>
@@ -13701,7 +13698,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" s="7" t="str">
         <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A12,'Requirements Register'!$A$5:$A$392,0)),"")</f>
@@ -13734,7 +13731,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B13" s="7" t="str">
         <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A13,'Requirements Register'!$A$5:$A$392,0)),"")</f>
@@ -13875,7 +13872,7 @@
       </c>
       <c r="D17" s="10">
         <f>SUM(D5:D16)</f>
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E17" s="10">
         <f>SUM(E5:E16)</f>
@@ -13883,7 +13880,7 @@
       </c>
       <c r="F17" s="10">
         <f>SUM(F5:F16)</f>
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G17" s="10">
         <f>SUM(G5:G16)</f>
@@ -13891,7 +13888,7 @@
       </c>
       <c r="H17" s="11">
         <f t="shared" si="0"/>
-        <v>0.43137254901960786</v>
+        <v>0.50326797385620914</v>
       </c>
     </row>
   </sheetData>
@@ -14854,18 +14851,18 @@
         <v>651</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>654</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="28" x14ac:dyDescent="0.35">
@@ -14876,7 +14873,7 @@
         <v>656</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -14887,7 +14884,7 @@
         <v>658</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
@@ -15016,7 +15013,7 @@
     <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="3" width="70" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20" x14ac:dyDescent="0.4">
@@ -15131,7 +15128,7 @@
         <v>692</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>693</v>
+        <v>639</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -15139,13 +15136,13 @@
         <v>52</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>694</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>695</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>696</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>639</v>
@@ -15153,16 +15150,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>697</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>698</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>699</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>639</v>
@@ -15170,16 +15167,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>547</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>700</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>701</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>639</v>
@@ -15187,19 +15184,19 @@
     </row>
     <row r="17" spans="1:5" ht="42" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>702</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>703</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>704</v>
-      </c>
       <c r="E17" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="42" x14ac:dyDescent="0.35">
@@ -15207,16 +15204,16 @@
         <v>70</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>705</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>707</v>
-      </c>
       <c r="E18" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="56" x14ac:dyDescent="0.35">
@@ -15224,16 +15221,16 @@
         <v>72</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>708</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>710</v>
-      </c>
       <c r="E19" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="42" x14ac:dyDescent="0.35">
@@ -15241,30 +15238,30 @@
         <v>74</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>710</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="D20" s="7" t="s">
         <v>712</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>713</v>
-      </c>
       <c r="E20" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>715</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>716</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>639</v>
@@ -15272,16 +15269,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>717</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>718</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>719</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>661</v>
@@ -15289,16 +15286,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>721</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>722</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>639</v>
@@ -15306,16 +15303,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>722</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>723</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>724</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>725</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>639</v>
@@ -15323,7 +15320,7 @@
     </row>
     <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="13" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -15331,7 +15328,7 @@
         <v>18</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>21</v>
@@ -15342,10 +15339,10 @@
         <v>76</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>728</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -15356,7 +15353,7 @@
         <v>556</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="28" x14ac:dyDescent="0.35">
@@ -15364,10 +15361,10 @@
         <v>83</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>731</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -15375,10 +15372,10 @@
         <v>85</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>732</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>733</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -15386,10 +15383,10 @@
         <v>87</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>735</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -15397,10 +15394,10 @@
         <v>89</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>737</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -15408,10 +15405,10 @@
         <v>91</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>739</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>740</v>
       </c>
     </row>
   </sheetData>

--- a/docs/rewards/Rewards_HLRD_LLRD.xlsx
+++ b/docs/rewards/Rewards_HLRD_LLRD.xlsx
@@ -1129,7 +1129,7 @@
     <col width="37" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Before HLR-9 build</t>
+          <t>Built with "no" (HLR-9); revisit after real use</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>Reward scope and matching (HLR-9) ⏳ next</t>
+          <t>Reward scope and matching (HLR-9) ✅</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Each reward card shows its scope as a breadcrumb (e.g. "Household › Kitchen" or "Fun") and its match mode. The rewards list can be filtered by tile and by area, in addition to status</t>
+          <t>Each reward card shows its scope as a breadcrumb (e.g. "Household › Kitchen" or "Fun") and its match mode. The Rewards tab is navigated like the Areas tab: tile cards (with active / to-claim / claimed counts) → a tile (its whole-tile rewards, then one row per area) → an area (its rewards, plus whole-tile rewards that also count there). Each level filters by status and has + New reward preset to that tile or area</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4365,12 +4365,12 @@
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>Reward create/update accept categoryId (required on create), areaId (optional) and match (selected | all_in_scope); reward responses include scope {categoryId, categoryName, areaId, areaName}, match and needsTile</t>
+          <t>Reward create/update accept categoryId (required on create), areaId (optional; null = whole tile) and matchMode (selected | all); update also accepts untagOutside (narrowing answers 409 listing the tasks until it's true). Reward responses include categoryId, categoryName, categoryIcon, areaId, areaName, matchMode, needsTile and matchedTaskCount</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
         <is>
-          <t>⏳ (HLR-9)</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>⏳ (HLR-9)</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Each reward card shows its scope as a breadcrumb (e.g. "Household › Kitchen" or "Fun") and its match mode. The rewards list can be filtered by tile and by area, in addition to status</t>
+          <t>Each reward card shows its scope as a breadcrumb (e.g. "Household › Kitchen" or "Fun") and its match mode. The Rewards tab is navigated like the Areas tab: tile cards (with active / to-claim / claimed counts) → a tile (its whole-tile rewards, then one row per area) → an area (its rewards, plus whole-tile rewards that also count there). Each level filters by status and has + New reward preset to that tile or area</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Reward create/update accept categoryId (required on create), areaId (optional) and match (selected | all_in_scope); reward responses include scope {categoryId, categoryName, areaId, areaName}, match and needsTile</t>
+          <t>Reward create/update accept categoryId (required on create), areaId (optional; null = whole tile) and matchMode (selected | all); update also accepts untagOutside (narrowing answers 409 listing the tasks until it's true). Reward responses include categoryId, categoryName, categoryIcon, areaId, areaName, matchMode, needsTile and matchedTaskCount</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F163" s="8" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F165" s="8" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F166" s="8" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F167" s="8" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>⏳ planned: test_reward_scope_validation, test_tagging_outside_scope_rejected, test_narrowing_scope_untags</t>
+          <t>test_reward_scope_validation, test_tagging_outside_scope_rejected, test_narrowing_scope_untags</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>⏳ planned: test_all_in_scope_counts_untagged_and_new_tasks, test_other_tile_never_counts</t>
+          <t>test_all_in_scope_counts_untagged_and_new_tasks, test_other_tile_never_counts</t>
         </is>
       </c>
     </row>
@@ -14987,7 +14987,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>⏳ planned: test_area_lists_matching_rewards, test_task_detail_lists_matching_rewards</t>
+          <t>test_area_lists_matching_rewards, test_task_detail_lists_matching_rewards</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>⏳ planned: test_deleting_area_widens_reward_scope</t>
+          <t>test_deleting_area_widens_reward_scope</t>
         </is>
       </c>
     </row>
@@ -15033,12 +15033,12 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>migration 0002_reward_scope</t>
+          <t>migration 0003_reward_scope</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>⏳ planned: test_migration_infers_scope_and_keeps_data (runs against a pre-migration fixture database)</t>
+          <t>test_migration_infers_scope_and_keeps_data (runs against a database at 0002_details), test_needs_a_tile_reward_must_pick_one_first, test_claimed_reward_without_a_tile_can_still_get_one</t>
         </is>
       </c>
     </row>
@@ -17035,12 +17035,12 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Reward scope and matching (HLR-9), shipped as the first data-preserving migration</t>
+          <t>Reward scope and matching (HLR-9), shipped as a data-preserving migration (0003_reward_scope)</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>⏳ next, after T3a</t>
+          <t>✅ (branch)</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/docs/rewards/Rewards_HLRD_LLRD.xlsx
+++ b/docs/rewards/Rewards_HLRD_LLRD.xlsx
@@ -29,7 +29,7 @@
     <sheet name="LLRD 7. Traceability matrix" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements Register'!$A$4:$J$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements Register'!$A$4:$J$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-29 from docs/rewards/HLRD.md and docs/rewards/LLRD.md.</t>
+          <t>Generated 2026-09-30 from docs/rewards/HLRD.md and docs/rewards/LLRD.md.</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C280"/>
+  <dimension ref="A1:C281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -2835,121 +2835,121 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>LLR-2.10</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Edit a task from task detail (✎): title and notes. Delete a task (🗑) after a confirmation that names its completion count; its completions and reward tags go with it, the rewards themselves stay (DELETE /tasks/{id})</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>AC-2.3</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>• *Given* a low-priority task created before a high-priority one *when* the list loads *then* the high one is first.</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="13" t="inlineStr">
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>AC-2.4</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>• *Given* one task is archived *when* filtering status = active *then* only the other task shows.</t>
         </is>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>LLR-3 Completion, activity log and streaks (HLR-3)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>LLR-3.1</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Complete an active task, optionally with a note (≤ 1000) and a time (completedAt). If no time is given, the time is now</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.2</t>
+          <t>LLR-3.1</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>The UI offers *Now*, *Yesterday* and *2 days ago* (same time of day)</t>
+          <t>Complete an active task, optionally with a note (≤ 1000) and a time (completedAt). If no time is given, the time is now</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.3</t>
+          <t>LLR-3.2</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>A completion more than 1 minute in the future is rejected (422)</t>
+          <t>Logging uses a month calendar: days the task was done are marked (with a count when more than once), today is outlined, future days are disabled, and ‹ › move between months. Tap a day, adjust the time (defaults to now), add an optional note and log. A time later than now is clamped to now</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.4</t>
+          <t>LLR-3.3</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Completing a one-off task sets it to done. Further completions are rejected (409)</t>
+          <t>A completion more than 1 minute in the future is rejected (422)</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -2961,12 +2961,12 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.5</t>
+          <t>LLR-3.4</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Completing a done or archived task is rejected with a message naming its status (409)</t>
+          <t>Completing a one-off task sets it to done. Further completions are rejected (409)</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -2978,12 +2978,12 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.6</t>
+          <t>LLR-3.5</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>The activity log lists completions newest first, with local date/time and note</t>
+          <t>Completing a done or archived task is rejected with a message naming its status (409)</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -2995,12 +2995,12 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.7</t>
+          <t>LLR-3.6</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Each task shows completion count, current streak, best streak and last completion time</t>
+          <t>The activity log lists completions newest first, with local date/time and note</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -3012,199 +3012,199 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
+          <t>LLR-3.7</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Each task shows completion count, current streak, best streak and last completion time</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
           <t>LLR-3.8</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>The area list offers a one-tap ✓ complete (now) for active tasks</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
     </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Business rules: streaks</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>BR-R1</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>A period is a local calendar day (daily) or a Monday–Sunday week (weekly) in BFF_TIMEZONE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>BR-R2</t>
+          <t>BR-R1</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Several completions in one period count once towards the streak (they all count towards completion count)</t>
+          <t>A period is a local calendar day (daily) or a Monday–Sunday week (weekly) in BFF_TIMEZONE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>BR-R3</t>
+          <t>BR-R2</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Best streak = longest run of consecutive periods with ≥ 1 completion</t>
+          <t>Several completions in one period count once towards the streak (they all count towards completion count)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>BR-R4</t>
+          <t>BR-R3</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Current streak = the run ending at the latest completed period, if that period is the current or the previous one; otherwise 0</t>
+          <t>Best streak = longest run of consecutive periods with ≥ 1 completion</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>BR-R5</t>
+          <t>BR-R4</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>One-off tasks: streak = 1 once completed, else 0 (not shown as an active streak)</t>
+          <t>Current streak = the run ending at the latest completed period, if that period is the current or the previous one; otherwise 0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
+          <t>BR-R5</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>One-off tasks: streak = 1 once completed, else 0 (not shown as an active streak)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
           <t>BR-R6</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>Streaks are derived from the activity log on every read (never stored)</t>
         </is>
       </c>
     </row>
-    <row r="73"/>
-    <row r="74">
-      <c r="A74" s="13" t="inlineStr">
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>AC-3 (streak)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* a daily task *when* completed yesterday and then today *then* current = 2 and best = 2.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the same task completed again today *then* current stays 2 and completion count becomes 3.</t>
+          <t>• *Given* a daily task *when* completed yesterday and then today *then* current = 2 and best = 2.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>• *Given* last completion 2 days ago (none yesterday) *then* current = 0 and best keeps its value.</t>
+          <t>• *Given* the same task completed again today *then* current stays 2 and completion count becomes 3.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
+          <t>• *Given* last completion 2 days ago (none yesterday) *then* current = 0 and best keeps its value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
           <t>• *Given* a weekly task done this Monday and last Sunday *then* current = 2 (different weeks).</t>
         </is>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" s="13" t="inlineStr">
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
         <is>
           <t>LLR-4 Rewards (HLR-4)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>LLR-4.1</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Create a reward: title (1–200, required), description (≤ 2000), image URL (≤ 500, optional), rule type (completions or streak), threshold N (1–365), tagged tasks (optional)</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.2</t>
+          <t>LLR-4.1</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Tag or untag tasks as a full replacement of the set. Unknown task ids are rejected (422)</t>
+          <t>Create a reward: title (1–200, required), description (≤ 2000), image URL (≤ 500, optional), rule type (completions or streak), threshold N (1–365), tagged tasks (optional)</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -3216,46 +3216,46 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.3</t>
+          <t>LLR-4.2</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Tag a task to a locked reward from the task detail screen</t>
+          <t>Tag or untag tasks as a full replacement of the set. Unknown task ids are rejected (422)</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.4</t>
+          <t>LLR-4.3</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Show each reward's rule text, progress (current / target, %), status and tagged tasks</t>
+          <t>Tag a task to a locked reward from the task detail screen</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.5</t>
+          <t>LLR-4.4</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Filter the rewards list by status</t>
+          <t>Show each reward's rule text, progress (current / target, %), status and tagged tasks</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -3267,12 +3267,12 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.6</t>
+          <t>LLR-4.5</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Claim is only possible when the status is unlocked. Claiming a locked reward is rejected (409). Claiming an already claimed reward changes nothing</t>
+          <t>Filter the rewards list by status</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -3284,12 +3284,12 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.7</t>
+          <t>LLR-4.6</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>When a completion unlocks a reward, the completion response includes it and the UI shows a celebration toast</t>
+          <t>Claim is only possible when the status is unlocked. Claiming a locked reward is rejected (409). Claiming an already claimed reward changes nothing</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -3301,71 +3301,71 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
+          <t>LLR-4.7</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>When a completion unlocks a reward, the completion response includes it and the UI shows a celebration toast</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
           <t>LLR-4.8</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>Editing a reward's tasks is only offered while it's locked</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91">
-      <c r="A91" s="13" t="inlineStr">
-        <is>
-          <t>Reward scope and matching (HLR-9) ✅</t>
-        </is>
-      </c>
-    </row>
+    <row r="91"/>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>Rewards, areas and links (HLR-9, revised 2026-09-30) ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>LLR-4.9</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>Every reward has a scope from the same taxonomy as tasks: a tile (required: Career/Office/Work, Household or Fun) and optionally one area of that tile (e.g. Household › Kitchen). Creating a reward without a tile is rejected (422); an area from another tile is rejected (422)</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.10</t>
+          <t>LLR-4.9</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>Every reward has a match mode: *Selected tasks* (default; the user tags specific tasks) or *All tasks in scope* (every non-archived task in the scope counts automatically, including tasks created later)</t>
+          <t>Rewards stand alone. A reward needs only a title and N (default 5); a note and picture link are optional. It can optionally be kept in an area (to organise it; its tile comes from the area), but that never limits which tasks it can be linked to</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
@@ -3377,12 +3377,12 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.11</t>
+          <t>LLR-4.10</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>In *Selected tasks* mode, only tasks inside the reward's scope can be tagged. Tagging a task outside it is rejected (422) with a message naming the task and the scope</t>
+          <t>Links are many-to-many and unrestricted: any task (from any tile or area) can be linked to any reward; one task can count for several rewards. Unlock rule for now: task count, the linked tasks done N times in total. (Older rewards that counted "all tasks in an area" keep working)</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -3394,12 +3394,12 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.12</t>
+          <t>LLR-4.11</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>The reward form picks tile, then area (optional, "Whole tile" default), then match mode. The task picker lists only tasks in that scope, grouped by area</t>
+          <t>Linking twice is harmless; unlinking an unlocked or claimed reward doesn't lock it again (BR-R10); deleting a task, area or tile removes only its links, and rewards stay. Deleting a tile does delete rewards kept in it (BR-R18)</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
@@ -3411,12 +3411,12 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.13</t>
+          <t>LLR-4.12</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Each reward card shows its scope as a breadcrumb (e.g. "Household › Kitchen" or "Fun") and its match mode. The Rewards tab is navigated like the Areas tab: tile cards (with active / to-claim / claimed counts) → a tile (its whole-tile rewards, then one row per area) → an area (its rewards, plus whole-tile rewards that also count there). Each level filters by status and has + New reward preset to that tile or area</t>
+          <t>The Link screen (#/rewards/link, top menu *Link*) lists all tasks (grouped by tile › area, with how often each was done and how many rewards it counts for) and all rewards (with area, N and status), each searchable. Pick a task and a reward, then Link (or Unlink if they already are). *Current links* lists each linked reward with its tasks, each with ✕ to unlink. Opens with a task or reward already picked from the task or reward screens</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -3428,12 +3428,12 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.14</t>
+          <t>LLR-4.13</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>The area screen shows "Rewards you can earn here": locked or unlocked rewards whose scope is this area or this area's whole tile, with progress</t>
+          <t>The top menu is Tiles | Tasks | Rewards | Link. *Tasks* lists every task grouped by tile › area (status filter, default Active; search; each row shows frequency, completions, streak 🔥 and rewards 🎁, with a quick ✓). *Rewards* lists every reward grouped by the area it's kept in (tile › area order, *Not in an area* last; status filter; search; + New with an optional area). The Link screen's two lists use the same grouping. A tile shows only its areas; an area has tabs Tasks | Rewards | Notes &amp; contacts, and its Rewards tab lists and adds the rewards kept there but doesn't link tasks</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
@@ -3445,12 +3445,12 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.15</t>
+          <t>LLR-4.14</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>On task detail, "Tag to a reward" offers only locked *Selected tasks* rewards whose scope contains the task. Rewards that match the task automatically (*All tasks in scope*) are listed with the label "Counts automatically"</t>
+          <t>A reward's screen (#/rewards/r/{id}) shows its rule, progress and linked tasks (✕ to unlink), *+ Link tasks* (Link screen with this reward picked), *Claim 🎁* when unlocked, and ✎ / 🗑 to edit (title, N while locked, area, note, picture) or delete it (tasks and history stay)</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -3462,12 +3462,12 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.16</t>
+          <t>LLR-4.15</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Scope and match mode can be changed only while the reward is locked. Narrowing the scope removes tags that fall outside it, after the user confirms; the confirmation lists the tasks that will be untagged</t>
+          <t>On task detail, the *Rewards* card lists the rewards the task counts for (links to each reward) and *+ Link to a reward* opens the Link screen with this task picked</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.17</t>
+          <t>LLR-4.16</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Deleting an area doesn't delete rewards scoped to it: they widen to the area's tile (area cleared) and keep their status, rule and remaining tags. Renaming an area changes nothing</t>
+          <t>N can be changed only while the reward is locked; lowering it re-checks the rule at once. A reward whose linked tasks already meet N unlocks as soon as it's linked</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
@@ -3496,307 +3496,307 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
+          <t>LLR-4.17</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Moving a reward to another area, or out of any area, never changes its links</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
           <t>LLR-4.18</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>Existing rewards are migrated without data loss (schema migration with automatic pre-upgrade backup): if all tagged tasks share one area, scope = that area; else if they share one tile, scope = that tile; otherwise (no tags, or tags across tiles) the reward keeps its tags and is marked *Needs a tile* until the user picks one. No reward, tag, completion or status is deleted</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
-    <row r="103"/>
-    <row r="104">
-      <c r="A104" s="13" t="inlineStr">
+    <row r="104"/>
+    <row r="105">
+      <c r="A105" s="13" t="inlineStr">
         <is>
           <t>Business rules: rewards</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="7" t="inlineStr">
-        <is>
-          <t>BR-R7</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>*Completions* rule progress = total completions of all tagged tasks (all-time)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>BR-R8</t>
+          <t>BR-R7</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>*Streak* rule progress = the highest current streak among tagged tasks</t>
+          <t>*Completions* rule progress = total completions of all tagged tasks (all-time)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>BR-R9</t>
+          <t>BR-R8</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>The unlock check runs on task completion, reward creation, reward update and tag change</t>
+          <t>*Streak* rule progress = the highest current streak among tagged tasks</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>BR-R10</t>
+          <t>BR-R9</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>Status flow locked → unlocked → claimed only; there's no path back</t>
+          <t>The unlock check runs on task completion, reward creation, reward update and tag change</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>BR-R11</t>
+          <t>BR-R10</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>Unlocked and claimed rewards always show 100 %</t>
+          <t>Status flow locked → unlocked → claimed only; there's no path back</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>BR-R12</t>
+          <t>BR-R11</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Scope containment. A task is in a reward's scope when the task's area belongs to the reward's tile and, if the reward has an area, the task's area *is* that area</t>
+          <t>Unlocked and claimed rewards always show 100 %</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>BR-R13</t>
+          <t>BR-R12</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>Matched tasks. *Selected tasks*: the tagged tasks (all in scope). *All tasks in scope*: every task in scope whose status isn't archived. BR-R7 and BR-R8 compute progress over the matched tasks</t>
+          <t>Scope containment. A task is in a reward's scope when the task's area belongs to the reward's tile and, if the reward has an area, the task's area *is* that area</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>BR-R14</t>
+          <t>BR-R13</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>In *All tasks in scope* mode, tags are ignored for progress (they're kept, so switching back to *Selected tasks* restores them)</t>
+          <t>Matched tasks. *Selected tasks*: the tagged tasks (all in scope). *All tasks in scope*: every task in scope whose status isn't archived. BR-R7 and BR-R8 compute progress over the matched tasks</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>BR-R15</t>
+          <t>BR-R14</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>The unlock check (BR-R9) on completion evaluates every locked reward that matches the completed task, whether tagged or by scope</t>
+          <t>In *All tasks in scope* mode, tags are ignored for progress (they're kept, so switching back to *Selected tasks* restores them)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
+          <t>BR-R15</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>The unlock check (BR-R9) on completion evaluates every locked reward that matches the completed task, whether tagged or by scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
           <t>BR-R16</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B116" s="7" t="inlineStr">
         <is>
           <t>A reward marked *Needs a tile* (LLR-4.18) still shows progress from its tags, but can't be edited until a tile is chosen. It never unlocks from tasks outside the tile the user then picks</t>
         </is>
       </c>
     </row>
-    <row r="116"/>
-    <row r="117">
-      <c r="A117" s="13" t="inlineStr">
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" s="13" t="inlineStr">
         <is>
           <t>AC-4b (scope and matching)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* a reward scoped to Household › Kitchen *when* the user tries to tag the Laundry task *then* it's rejected: "“Wash whites” isn't in Household › Kitchen" (422).</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a reward "Weekend brunch" scoped to Household with *All tasks in scope*, 3 completions *when* the user completes any Household task (Kitchen or Laundry) *then* progress counts it without tagging. A Career task never counts.</t>
+          <t>• *Given* a reward scoped to Household › Kitchen *when* the user tries to tag the Laundry task *then* it's rejected: "“Wash whites” isn't in Household › Kitchen" (422).</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a new Kitchen task is created after the reward *when* it's completed *then* it counts towards the Household reward immediately.</t>
+          <t>• *Given* a reward "Weekend brunch" scoped to Household with *All tasks in scope*, 3 completions *when* the user completes any Household task (Kitchen or Laundry) *then* progress counts it without tagging. A Career task never counts.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the Kitchen area screen *then* "Rewards you can earn here" lists rewards scoped to Household › Kitchen and to Household, not Fun or Household › Laundry.</t>
+          <t>• *Given* a new Kitchen task is created after the reward *when* it's completed *then* it counts towards the Household reward immediately.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>• *Given* an existing reward tagged only to Kitchen tasks *when* the migration runs *then* its scope becomes Household › Kitchen, and its tags, progress and status are unchanged.</t>
+          <t>• *Given* the Kitchen area screen *then* "Rewards you can earn here" lists rewards scoped to Household › Kitchen and to Household, not Fun or Household › Laundry.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
+          <t>• *Given* an existing reward tagged only to Kitchen tasks *when* the migration runs *then* its scope becomes Household › Kitchen, and its tags, progress and status are unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
           <t>• *Given* the Kitchen area is deleted *then* a reward scoped to Household › Kitchen becomes scoped to Household and keeps its status.</t>
         </is>
       </c>
     </row>
-    <row r="124"/>
-    <row r="125">
-      <c r="A125" s="13" t="inlineStr">
+    <row r="125"/>
+    <row r="126">
+      <c r="A126" s="13" t="inlineStr">
         <is>
           <t>AC-4 (demo flow)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* a task with 2 completions and a locked "3 completions" reward *when* the reward is tagged to the task *then* progress = 2/3 (67 %).</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>• *When* the task is completed once more *then* the response lists the reward as unlocked and the UI shows "🎉 Reward unlocked: &lt;title&gt;".</t>
+          <t>• *Given* a task with 2 completions and a locked "3 completions" reward *when* the reward is tagged to the task *then* progress = 2/3 (67 %).</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
+          <t>• *When* the task is completed once more *then* the response lists the reward as unlocked and the UI shows "🎉 Reward unlocked: &lt;title&gt;".</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
           <t>• *When* the user claims it *then* the status is claimed and claimedAt is set.</t>
         </is>
       </c>
     </row>
-    <row r="129"/>
-    <row r="130">
-      <c r="A130" s="13" t="inlineStr">
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="13" t="inlineStr">
         <is>
           <t>LLR-5 Insights dashboard (HLR-5)</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B131" s="6" t="inlineStr">
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr">
+      <c r="C132" s="6" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>LLR-5.1</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>Reads only GET /dashboard/summary; never the database</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.2</t>
+          <t>LLR-5.1</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>KPIs: completions (window), active tasks, active streaks, unlocked + claimed rewards, AI acceptance rate (— when undefined)</t>
+          <t>Reads only GET /dashboard/summary; never the database</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.3</t>
+          <t>LLR-5.2</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>Charts: completions by tile, by area (filterable by tile) and per day (empty days shown as gaps). Hover tooltips on every mark</t>
+          <t>KPIs: completions (window), active tasks, active streaks, unlocked + claimed rewards, AI acceptance rate (— when undefined)</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
@@ -3808,12 +3808,12 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.4</t>
+          <t>LLR-5.3</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>Tables: active streaks (filterable by tile); reward progress with a progress bar</t>
+          <t>Charts: completions by tile, by area (filterable by tile) and per day (empty days shown as gaps). Hover tooltips on every mark</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
@@ -3825,12 +3825,12 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.5</t>
+          <t>LLR-5.4</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>Filters: window (7/30/90 days/all time) and tile. They survive reruns (session_state)</t>
+          <t>Tables: active streaks (filterable by tile); reward progress with a progress bar</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
@@ -3842,12 +3842,12 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.6</t>
+          <t>LLR-5.5</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>Responses are cached 30 s per window. *Refresh now* clears the cache</t>
+          <t>Filters: window (7/30/90 days/all time) and tile. They survive reruns (session_state)</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
@@ -3859,12 +3859,12 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.7</t>
+          <t>LLR-5.6</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>Unlocked rewards can be claimed from the dashboard. After claiming, the cache is cleared and the page shows fresh data</t>
+          <t>Responses are cached 30 s per window. *Refresh now* clears the cache</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
@@ -3876,12 +3876,12 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.8</t>
+          <t>LLR-5.7</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>If the BFF is unreachable, show the error and *Try again* (no stack traces)</t>
+          <t>Unlocked rewards can be claimed from the dashboard. After claiming, the cache is cleared and the page shows fresh data</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
@@ -3893,29 +3893,29 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.9</t>
+          <t>LLR-5.8</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>Streaks and rewards ignore the window; completion aggregates respect it</t>
+          <t>If the BFF is unreachable, show the error and *Try again* (no stack traces)</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.10</t>
+          <t>LLR-5.9</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>Summary payload is flat snake_case records; React endpoints are camelCase (per-client shaping)</t>
+          <t>Streaks and rewards ignore the window; completion aggregates respect it</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
@@ -3927,250 +3927,250 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
+          <t>LLR-5.10</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>Summary payload is flat snake_case records; React endpoints are camelCase (per-client shaping)</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
           <t>LLR-5.11</t>
         </is>
       </c>
-      <c r="B142" s="7" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t>Reward progress rows include the reward's tile and area; the dashboard's tile filter applies to rewards as well as completions and streaks</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>⏳ (HLR-9)</t>
         </is>
       </c>
     </row>
-    <row r="143"/>
-    <row r="144">
-      <c r="A144" s="13" t="inlineStr">
+    <row r="144"/>
+    <row r="145">
+      <c r="A145" s="13" t="inlineStr">
         <is>
           <t>LLR-6 AI task suggestions (HLR-6) ⏳</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="6" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>Requirement</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>LLR-6.1</t>
-        </is>
-      </c>
-      <c r="B146" s="7" t="inlineStr">
-        <is>
-          <t>Attach 1–5 photos per run to an area (JPEG/PNG/WebP, ≤ 5 MB each; type checked by content, not extension)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.2</t>
+          <t>LLR-6.1</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>Photos are stored privately with random names and are never publicly addressable</t>
+          <t>Attach 1–5 photos per run to an area (JPEG/PNG/WebP, ≤ 5 MB each; type checked by content, not extension)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.3</t>
+          <t>LLR-6.2</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>Starting a suggestion run returns immediately (202) with a run id; the UI shows a loading state</t>
+          <t>Photos are stored privately with random names and are never publicly addressable</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.4</t>
+          <t>LLR-6.3</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>While a run is in progress, the manual *Add a task* form stays fully usable</t>
+          <t>Starting a suggestion run returns immediately (202) with a run id; the UI shows a loading state</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.5</t>
+          <t>LLR-6.4</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>Each suggestion has a title (≤ 200), why (≤ 500), priority and frequency, validated against a strict schema</t>
+          <t>While a run is in progress, the manual *Add a task* form stays fully usable</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.6</t>
+          <t>LLR-6.5</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>The user marks each suggestion Relevant / Not relevant / Ignore. Relevant creates a task with source = ai. A decision is final (409 on re-decide)</t>
+          <t>Each suggestion has a title (≤ 200), why (≤ 500), priority and frequency, validated against a strict schema</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.7</t>
+          <t>LLR-6.6</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>On timeout (30 s), invalid output or missing API key: retry once where sensible, then show "AI suggestions unavailable, add tasks manually". The page never breaks</t>
+          <t>The user marks each suggestion Relevant / Not relevant / Ignore. Relevant creates a task with source = ai. A decision is final (409 on re-decide)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.8</t>
+          <t>LLR-6.7</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>The API key exists only in BFF environment variables</t>
+          <t>On timeout (30 s), invalid output or missing API key: retry once where sensible, then show "AI suggestions unavailable, add tasks manually". The page never breaks</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
+          <t>LLR-6.8</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>The API key exists only in BFF environment variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
           <t>LLR-6.9</t>
         </is>
       </c>
-      <c r="B154" s="7" t="inlineStr">
+      <c r="B155" s="7" t="inlineStr">
         <is>
           <t>Decisions feed the dashboard acceptance rate (relevant ÷ decided)</t>
         </is>
       </c>
     </row>
-    <row r="155"/>
-    <row r="156">
-      <c r="A156" s="13" t="inlineStr">
+    <row r="156"/>
+    <row r="157">
+      <c r="A157" s="13" t="inlineStr">
         <is>
           <t>LLR-7 Module composition (HLR-7)</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="6" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B157" s="6" t="inlineStr">
+      <c r="B158" s="6" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C157" s="6" t="inlineStr">
+      <c r="C158" s="6" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="7" t="inlineStr">
-        <is>
-          <t>LLR-7.1</t>
-        </is>
-      </c>
-      <c r="B158" s="7" t="inlineStr">
-        <is>
-          <t>The MFE is built separately and exposes ./RewardsApp via remoteEntry.js</t>
-        </is>
-      </c>
-      <c r="C158" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.2</t>
+          <t>LLR-7.1</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>The host mounts it on #/rewards and every #/rewards/*. The nav item stays active on sub-routes</t>
+          <t>The MFE is built separately and exposes ./RewardsApp via remoteEntry.js</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.3</t>
+          <t>LLR-7.2</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>Host and remote share one React instance; the remote bundles no React</t>
+          <t>The host mounts it on #/rewards and every #/rewards/*. The nav item stays active on sub-routes</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>🟡 (verified in browser)</t>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.4</t>
+          <t>LLR-7.3</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>If the remote fails to load, the host shows "Rewards is unavailable right now" and a reload button. Other pages are unaffected</t>
+          <t>Host and remote share one React instance; the remote bundles no React</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>🟡 (verified in browser)</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.5</t>
+          <t>LLR-7.4</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>MFE styles are scoped (.rw-app) and don't alter host styles</t>
+          <t>If the remote fails to load, the host shows "Rewards is unavailable right now" and a reload button. Other pages are unaffected</t>
         </is>
       </c>
       <c r="C162" s="7" t="inlineStr">
@@ -4182,105 +4182,105 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.6</t>
+          <t>LLR-7.5</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>The remote URL is configurable per environment (VITE_REWARDS_REMOTE_URL)</t>
+          <t>MFE styles are scoped (.rw-app) and don't alter host styles</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.7</t>
+          <t>LLR-7.6</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
         <is>
-          <t>The MFE runs standalone for development (npm run dev)</t>
+          <t>The remote URL is configurable per environment (VITE_REWARDS_REMOTE_URL)</t>
         </is>
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
+          <t>LLR-7.7</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>The MFE runs standalone for development (npm run dev)</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
           <t>LLR-7.8</t>
         </is>
       </c>
-      <c r="B165" s="7" t="inlineStr">
+      <c r="B166" s="7" t="inlineStr">
         <is>
           <t>Every screen has loading, error (with retry) and empty states</t>
         </is>
       </c>
-      <c r="C165" s="7" t="inlineStr">
+      <c r="C166" s="7" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
     </row>
-    <row r="166"/>
-    <row r="167">
-      <c r="A167" s="13" t="inlineStr">
+    <row r="167"/>
+    <row r="168">
+      <c r="A168" s="13" t="inlineStr">
         <is>
           <t>LLR-8 BFF API (HLR-8)</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="6" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B168" s="6" t="inlineStr">
+      <c r="B169" s="6" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C168" s="6" t="inlineStr">
+      <c r="C169" s="6" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t>LLR-8.1</t>
-        </is>
-      </c>
-      <c r="B169" s="7" t="inlineStr">
-        <is>
-          <t>Every endpoint except /health needs Authorization: Bearer &lt;demo token&gt;; otherwise 401</t>
-        </is>
-      </c>
-      <c r="C169" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.2</t>
+          <t>LLR-8.1</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>CORS allows only the configured origins</t>
+          <t>Every endpoint except /health needs Authorization: Bearer &lt;demo token&gt;; otherwise 401</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
@@ -4292,12 +4292,12 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.3</t>
+          <t>LLR-8.2</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>OpenAPI documentation is served at /docs</t>
+          <t>CORS allows only the configured origins</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
@@ -4309,12 +4309,12 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.4</t>
+          <t>LLR-8.3</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t>Errors use {detail} with status codes 401, 404, 409 and 422 as catalogued in LLD §3.3</t>
+          <t>OpenAPI documentation is served at /docs</t>
         </is>
       </c>
       <c r="C172" s="7" t="inlineStr">
@@ -4326,12 +4326,12 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.5</t>
+          <t>LLR-8.4</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>Request bodies accept camelCase or snake_case. React responses are camelCase; dashboard responses are snake_case</t>
+          <t>Errors use {detail} with status codes 401, 404, 409 and 422 as catalogued in LLD §3.3</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
@@ -4343,12 +4343,12 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.6</t>
+          <t>LLR-8.5</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
         <is>
-          <t>Timestamps are ISO-8601 UTC in responses</t>
+          <t>Request bodies accept camelCase or snake_case. React responses are camelCase; dashboard responses are snake_case</t>
         </is>
       </c>
       <c r="C174" s="7" t="inlineStr">
@@ -4360,12 +4360,12 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.7</t>
+          <t>LLR-8.6</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>Reward create/update accept categoryId (required on create), areaId (optional; null = whole tile) and matchMode (selected | all); update also accepts untagOutside (narrowing answers 409 listing the tasks until it's true). Reward responses include categoryId, categoryName, categoryIcon, areaId, areaName, matchMode, needsTile and matchedTaskCount</t>
+          <t>Timestamps are ISO-8601 UTC in responses</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
@@ -4377,12 +4377,12 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.8</t>
+          <t>LLR-8.7</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>GET /rewards accepts categoryId and areaId filters. GET /areas/{id}/rewards returns the rewards that match that area (LLR-4.14). Task detail's rewards lists every reward matching the task, with how it matches (tagged or scope)</t>
+          <t>POST /rewards needs only title (optional threshold = N, default 5, areaId, description, imageUrl, taskIds). GET /rewards (?status=, ?areaId=), GET / PATCH / DELETE /rewards/{id} (PATCH edits title, N, note, picture, areaId or null). POST / DELETE /rewards/{id}/tasks/{taskId} link and unlink one task; PUT /rewards/{id}/tasks replaces all links. Responses include the optional categoryId, categoryName, categoryIcon, areaId, areaName, plus tasks, connected and matchedTaskCount</t>
         </is>
       </c>
       <c r="C176" s="7" t="inlineStr">
@@ -4394,12 +4394,12 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.9</t>
+          <t>LLR-8.8</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>Schema changes are applied by versioned migrations on startup, never by dropping and recreating tables; a backup of the database file is written before each upgrade (Q14)</t>
+          <t>Task detail's rewards lists every reward the task counts for, with how (tagged = linked, or scope for older all-tasks-in-an-area rewards)</t>
         </is>
       </c>
       <c r="C177" s="7" t="inlineStr">
@@ -4411,12 +4411,12 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.10</t>
+          <t>LLR-8.9</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>Tile endpoints: POST /categories, PATCH /categories/{id} (name, icon), DELETE /categories/{id}, PUT /categories/order and PUT /categories/{id}/areas/order, POST /categories/starter (LLR-1.8, returns what was added)</t>
+          <t>Schema changes are applied by versioned migrations on startup, never by dropping and recreating tables; a backup of the database file is written before each upgrade (Q14)</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
@@ -4428,29 +4428,29 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.12</t>
+          <t>LLR-8.10</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>Task create/update accept isMilestone, visibility (announced | silent), dueAt (ISO date-time, optional) and targetDays (optional); GET /areas/{id}/tasks adds filters milestone=true and due=overdue|today|week and sort=due. Responses served without the passcode omit silent tasks entirely (BR-R23)</t>
+          <t>Tile endpoints: POST /categories, PATCH /categories/{id} (name, icon), DELETE /categories/{id}, PUT /categories/order and PUT /categories/{id}/areas/order, POST /categories/starter (LLR-1.8, returns what was added)</t>
         </is>
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.13</t>
+          <t>LLR-8.12</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>Rewards accept status: "idea" on create (rule, threshold and tile then optional), forWhom, visibility, link, seenAt (where seen) and a cover image; POST /rewards/{id}/activate (rule, threshold, tile, tasks) turns an idea into a locked reward; POST /rewards/{id}/close with outcome (bought | dropped); GET /rewards filters status=idea|closed and forWhom=</t>
+          <t>Task create/update accept isMilestone, visibility (announced | silent), dueAt (ISO date-time, optional) and targetDays (optional); GET /areas/{id}/tasks adds filters milestone=true and due=overdue|today|week and sort=due. Responses served without the passcode omit silent tasks entirely (BR-R23)</t>
         </is>
       </c>
       <c r="C180" s="7" t="inlineStr">
@@ -4462,86 +4462,86 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
+          <t>LLR-8.13</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>Rewards accept status: "idea" on create (rule, threshold and tile then optional), forWhom, visibility, link, seenAt (where seen) and a cover image; POST /rewards/{id}/activate (rule, threshold, tile, tasks) turns an idea into a locked reward; POST /rewards/{id}/close with outcome (bought | dropped); GET /rewards filters status=idea|closed and forWhom=</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>⏳ next</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
           <t>LLR-8.11</t>
         </is>
       </c>
-      <c r="B181" s="7" t="inlineStr">
+      <c r="B182" s="7" t="inlineStr">
         <is>
           <t>Details endpoints for both owners (/categories/{id} and /areas/{id}): …/details (grouped by topic), …/notes, …/contacts, …/files (multipart upload); PATCH/DELETE on /notes/{id}, /contacts/{id}, /files/{id}; GET /files/{id}/download; GET /search?q=</t>
         </is>
       </c>
-      <c r="C181" s="7" t="inlineStr">
+      <c r="C182" s="7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
-    <row r="182"/>
-    <row r="183">
-      <c r="A183" s="13" t="inlineStr">
+    <row r="183"/>
+    <row r="184">
+      <c r="A184" s="13" t="inlineStr">
         <is>
           <t>LLR-10 Notes, contacts and files (HLR-10) ✅</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="12" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="12" t="inlineStr">
         <is>
           <t>Each tile and each area has a *Notes &amp; contacts* section (Q16, Q18). Every note, contact and file can carry an optional topic (e.g. "Bosch Dishwasher", "Pest Control") that groups related items.</t>
         </is>
       </c>
     </row>
-    <row r="185"/>
-    <row r="186">
-      <c r="A186" s="13" t="inlineStr">
+    <row r="186"/>
+    <row r="187">
+      <c r="A187" s="13" t="inlineStr">
         <is>
           <t>LLR-10 Notes, contacts and files (HLR-10) ✅</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="6" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="7" t="inlineStr">
-        <is>
-          <t>LLR-10.1</t>
-        </is>
-      </c>
-      <c r="B188" s="7" t="inlineStr">
-        <is>
-          <t>The tile screen and the area screen each have a Notes &amp; contacts tab next to their main content. It lists topics as groups (items without a topic under "General"), each showing its contacts, files and notes</t>
-        </is>
-      </c>
-      <c r="C188" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.2</t>
+          <t>LLR-10.1</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
         <is>
-          <t>Topic is free text (1–60 characters), optional, and offers existing topics from the same tile or area as suggestions, so "Bosch Dishwasher" isn't typed three different ways</t>
+          <t>The area screen has a Notes &amp; contacts tab (tiles no longer have their own tabs; older tile-level items stay stored and searchable) next to their main content. It lists topics as groups (items without a topic under "General"), each showing its contacts, files and notes</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
@@ -4553,12 +4553,12 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.3</t>
+          <t>LLR-10.2</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>Contact: name (required, 1–80); organisation or brand (e.g. Bosch, Kent, IFB, LG); role (*Customer care*, *Service executive*, *Technician*, *Vendor or shop*, *Other*); up to 3 phone numbers with labels (mobile, toll-free, WhatsApp); email; website; last visit or contact date; notes (≤ 1000); topic</t>
+          <t>Topic is free text (1–60 characters), optional, and offers existing topics from the same tile or area as suggestions, so "Bosch Dishwasher" isn't typed three different ways</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
@@ -4570,12 +4570,12 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.4</t>
+          <t>LLR-10.3</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
         <is>
-          <t>Phone numbers are stored as entered and shown with actions: Call (tel:), WhatsApp (wa.me, for numbers marked WhatsApp) and Copy. Email gets Email (mailto:). All actions are one tap on a phone</t>
+          <t>Contact: name (required, 1–80); organisation or brand (e.g. Bosch, Kent, IFB, LG); role (*Customer care*, *Service executive*, *Technician*, *Vendor or shop*, *Other*); up to 3 phone numbers with labels (mobile, toll-free, WhatsApp); email; website; last visit or contact date; notes (≤ 1000); topic</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
@@ -4587,12 +4587,12 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.5</t>
+          <t>LLR-10.4</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t>Past executives: within a topic, contacts with the role *Service executive* or *Technician* are listed newest last-visit first. The topic header shows the last executive (name, date, call button)</t>
+          <t>Phone numbers are stored as entered and shown with actions: Call (tel:), WhatsApp (wa.me, for numbers marked WhatsApp) and Copy. Email gets Email (mailto:). All actions are one tap on a phone</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
@@ -4604,12 +4604,12 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.6</t>
+          <t>LLR-10.5</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
         <is>
-          <t>Note: text 1–5000 characters, optional title and topic; shows created and last-edited time; newest first</t>
+          <t>Past executives: within a topic, contacts with the role *Service executive* or *Technician* are listed newest last-visit first. The topic header shows the last executive (name, date, call button)</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
@@ -4621,12 +4621,12 @@
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.7</t>
+          <t>LLR-10.6</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
         <is>
-          <t>File (bills, invoices, warranty cards, manuals): PDF, JPG, PNG, WebP or HEIC, up to 10 MB each, checked by content; title (required), optional date, amount (₹) and topic. Files open in the browser or download; images show a thumbnail</t>
+          <t>Note: text 1–5000 characters, optional title and topic; shows created and last-edited time; newest first</t>
         </is>
       </c>
       <c r="C194" s="7" t="inlineStr">
@@ -4638,12 +4638,12 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.8</t>
+          <t>LLR-10.7</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
         <is>
-          <t>Notes, contacts and files can be edited and deleted (with confirmation), and moved between topics by editing the topic</t>
+          <t>File (bills, invoices, warranty cards, manuals): PDF, JPG, PNG, WebP or HEIC, up to 10 MB each, checked by content; title (required), optional date, amount (₹) and topic. Files open in the browser or download; images show a thumbnail</t>
         </is>
       </c>
       <c r="C195" s="7" t="inlineStr">
@@ -4655,12 +4655,12 @@
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.9</t>
+          <t>LLR-10.8</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
         <is>
-          <t>Search across every tile and area by contact name, organisation, topic, phone digits (spaces and dashes ignored), note text and file title. Results show where each hit lives (e.g. "Household › Kitchen › Bosch Dishwasher") and link to it</t>
+          <t>Notes, contacts and files can be edited and deleted (with confirmation), and moved between topics by editing the topic</t>
         </is>
       </c>
       <c r="C196" s="7" t="inlineStr">
@@ -4672,12 +4672,12 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.10</t>
+          <t>LLR-10.9</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
         <is>
-          <t>Deleting an area or tile deletes its notes, contacts and files, and the confirmation counts them (LLR-1.12). Stored files are removed only after the database change commits</t>
+          <t>Search across every tile and area by contact name, organisation, topic, phone digits (spaces and dashes ignored), note text and file title. Results show where each hit lives (e.g. "Household › Kitchen › Bosch Dishwasher") and link to it</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr">
@@ -4689,12 +4689,12 @@
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.11</t>
+          <t>LLR-10.10</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
         <is>
-          <t>Visibility follows the rewards setting (Q17): readable in the read-only view when public reads are on; creating, editing, deleting and uploading need the owner passcode</t>
+          <t>Deleting an area or tile deletes its notes, contacts and files, and the confirmation counts them (LLR-1.12). Stored files are removed only after the database change commits</t>
         </is>
       </c>
       <c r="C198" s="7" t="inlineStr">
@@ -4706,216 +4706,216 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
+          <t>LLR-10.11</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>Visibility follows the rewards setting (Q17): readable in the read-only view when public reads are on; creating, editing, deleting and uploading need the owner passcode</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
           <t>LLR-10.12</t>
         </is>
       </c>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="B200" s="7" t="inlineStr">
         <is>
           <t>The JSON export (app.backup) includes notes and contacts, and lists files by title and stored name; the server backup covers the files folder as well as the database</t>
         </is>
       </c>
-      <c r="C199" s="7" t="inlineStr">
+      <c r="C200" s="7" t="inlineStr">
         <is>
           <t>🟡 export built; server backup of the files folder comes with hosting</t>
         </is>
       </c>
     </row>
-    <row r="200"/>
-    <row r="201">
-      <c r="A201" s="13" t="inlineStr">
+    <row r="201"/>
+    <row r="202">
+      <c r="A202" s="13" t="inlineStr">
         <is>
           <t>Business rules: tiles and details</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="6" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B202" s="6" t="inlineStr">
+      <c r="B203" s="6" t="inlineStr">
         <is>
           <t>Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="7" t="inlineStr">
-        <is>
-          <t>BR-R17</t>
-        </is>
-      </c>
-      <c r="B203" s="7" t="inlineStr">
-        <is>
-          <t>Tile names are unique ignoring case; area names are unique within their tile ignoring case</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>BR-R18</t>
+          <t>BR-R17</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
         <is>
-          <t>Deleting a tile removes everything under it (areas, tasks, completions, rewards scoped to it, notes, contacts, files) in one transaction, after a database snapshot is saved to data/backups/</t>
+          <t>Tile names are unique ignoring case; area names are unique within their tile ignoring case</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>BR-R19</t>
+          <t>BR-R18</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
         <is>
-          <t>The starter set only adds tiles and areas whose names are missing; it never renames, merges or deletes</t>
+          <t>Deleting a tile removes everything under it (areas, tasks, completions, rewards scoped to it, notes, contacts, files) in one transaction, after a database snapshot is saved to data/backups/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>BR-R20</t>
+          <t>BR-R19</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
         <is>
-          <t>Details belong to exactly one owner: a tile or an area. Moving an area to another tile isn't supported, so details never change tile</t>
+          <t>The starter set only adds tiles and areas whose names are missing; it never renames, merges or deletes</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
+          <t>BR-R20</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>Details belong to exactly one owner: a tile or an area. Moving an area to another tile isn't supported, so details never change tile</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
           <t>BR-R21</t>
         </is>
       </c>
-      <c r="B207" s="7" t="inlineStr">
+      <c r="B208" s="7" t="inlineStr">
         <is>
           <t>The "last executive" of a topic is the *Service executive* or *Technician* contact in that topic with the latest last-visit date; contacts without a date come after dated ones</t>
         </is>
       </c>
     </row>
-    <row r="208"/>
-    <row r="209">
-      <c r="A209" s="13" t="inlineStr">
+    <row r="209"/>
+    <row r="210">
+      <c r="A210" s="13" t="inlineStr">
         <is>
           <t>AC-10 (your examples)</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* Household › Kitchen *when* the user adds contacts "Bosch Customer Care" (Customer care, toll-free number) and "Ramesh" (Service executive, last visit 12 Aug 2026), both with topic "Bosch Dishwasher", uploads the installation bill and adds a note "Filter cleaned; next service due in 6 months" *then* the Bosch Dishwasher topic shows all four, with Ramesh as the last executive.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a topic "Kent Water Purifier" with executives visiting in March and August *then* the August executive is shown as the last executive, and both appear under past executives.</t>
+          <t>• *Given* Household › Kitchen *when* the user adds contacts "Bosch Customer Care" (Customer care, toll-free number) and "Ramesh" (Service executive, last visit 12 Aug 2026), both with topic "Bosch Dishwasher", uploads the installation bill and adds a note "Filter cleaned; next service due in 6 months" *then* the Bosch Dishwasher topic shows all four, with Ramesh as the last executive.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>• *Given* "IFB Washing Machine" (Laundry), "LG Fridge" (Kitchen) and "Pigeon Net" (Balcony) contacts *when* the user searches "IFB" *then* the result shows "Household › Laundry › IFB Washing Machine".</t>
+          <t>• *Given* a topic "Kent Water Purifier" with executives visiting in March and August *then* the August executive is shown as the last executive, and both appear under past executives.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>• *Given* Household (tile level) with topic "Pest Control" *then* its last executive shows on the Household tile's Notes &amp; contacts tab, not under any area.</t>
+          <t>• *Given* "IFB Washing Machine" (Laundry), "LG Fridge" (Kitchen) and "Pigeon Net" (Balcony) contacts *when* the user searches "IFB" *then* the result shows "Household › Laundry › IFB Washing Machine".</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a saved number "98450 12345" *when* the user searches "9845012345" *then* the contact is found, and tapping Call on a phone dials it.</t>
+          <t>• *Given* Household (tile level) with topic "Pest Control" *then* its last executive shows on the Household tile's Notes &amp; contacts tab, not under any area.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
+          <t>• *Given* a saved number "98450 12345" *when* the user searches "9845012345" *then* the contact is found, and tapping Call on a phone dials it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
           <t>• *Given* the read-only view (no passcode) *then* notes, contacts and files are visible, but the add, edit, delete and upload controls are hidden (Q17).</t>
         </is>
       </c>
     </row>
-    <row r="216"/>
-    <row r="217">
-      <c r="A217" s="13" t="inlineStr">
+    <row r="217"/>
+    <row r="218">
+      <c r="A218" s="13" t="inlineStr">
         <is>
           <t>LLR-11 Task planning and visibility (HLR-11) ⏳ next</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="12" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="12" t="inlineStr">
         <is>
           <t>Four new, optional task attributes (Q19 to Q22). They sit under More options in the add form, so adding a quick task on a phone stays one field and one tap.</t>
         </is>
       </c>
     </row>
-    <row r="219"/>
-    <row r="220">
-      <c r="A220" s="13" t="inlineStr">
+    <row r="220"/>
+    <row r="221">
+      <c r="A221" s="13" t="inlineStr">
         <is>
           <t>LLR-11 Task planning and visibility (HLR-11) ⏳ next</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="6" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B221" s="6" t="inlineStr">
+      <c r="B222" s="6" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C221" s="6" t="inlineStr">
+      <c r="C222" s="6" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="7" t="inlineStr">
-        <is>
-          <t>LLR-11.1</t>
-        </is>
-      </c>
-      <c r="B222" s="7" t="inlineStr">
-        <is>
-          <t>Milestone: yes/no (default no), set when creating or editing a task</t>
-        </is>
-      </c>
-      <c r="C222" s="7" t="inlineStr">
-        <is>
-          <t>⏳ next</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.2</t>
+          <t>LLR-11.1</t>
         </is>
       </c>
       <c r="B223" s="7" t="inlineStr">
         <is>
-          <t>Milestones show a 🏁 badge on task rows and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
+          <t>Milestone: yes/no (default no), set when creating or editing a task</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
@@ -4927,12 +4927,12 @@
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.3</t>
+          <t>LLR-11.2</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
         <is>
-          <t>Completing an announced milestone shows the milestone celebration: a larger, longer celebration than a normal completion (respects reduced motion), with its own share prompt</t>
+          <t>Milestones show a 🏁 badge on task rows and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
         </is>
       </c>
       <c r="C224" s="7" t="inlineStr">
@@ -4944,12 +4944,12 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.4</t>
+          <t>LLR-11.3</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
         <is>
-          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task it matches has at least one completion (BR-R25). Creating one that matches no milestone task is rejected (422)</t>
+          <t>Completing an announced milestone shows the milestone celebration: a larger, longer celebration than a normal completion (respects reduced motion), with its own share prompt</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
@@ -4961,12 +4961,12 @@
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.5</t>
+          <t>LLR-11.4</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
         <is>
-          <t>Announce or keep silent: each task is *Announced* (default) or *Silent*, set when creating or editing it (Q20, Q22)</t>
+          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task it matches has at least one completion (BR-R25). Creating one that matches no milestone task is rejected (422)</t>
         </is>
       </c>
       <c r="C226" s="7" t="inlineStr">
@@ -4978,12 +4978,12 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.6</t>
+          <t>LLR-11.5</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
         <is>
-          <t>Silent tasks and their completions never appear in anything served without the owner passcode: lists, counts, streaks, activity, dashboard aggregates or reward task lists (BR-R23). With the passcode they're shown with a 🔕 marker</t>
+          <t>Announce or keep silent: each task is *Announced* (default) or *Silent*, set when creating or editing it (Q20, Q22)</t>
         </is>
       </c>
       <c r="C227" s="7" t="inlineStr">
@@ -4995,12 +4995,12 @@
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.7</t>
+          <t>LLR-11.6</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
         <is>
-          <t>Completing an announced task shows the celebration toast and a Share on WhatsApp prompt (prefilled text, e.g. "Done: Wipe counters 🔥 3-day streak"). Completing a silent task shows only a quiet "Logged" confirmation, with no share prompt (BR-R24)</t>
+          <t>Silent tasks and their completions never appear in anything served without the owner passcode: lists, counts, streaks, activity, dashboard aggregates or reward task lists (BR-R23). With the passcode they're shown with a 🔕 marker</t>
         </is>
       </c>
       <c r="C228" s="7" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.8</t>
+          <t>LLR-11.7</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
         <is>
-          <t>Due date and time (optional): a local date and time, stored in UTC. Tasks show a chip: *Overdue* (red), *Due today*, *Due in N days* (within 7 days) or the date. The area list can be filtered by *Overdue*, *Due today* and *Due this week*, and sorted by due date</t>
+          <t>Completing an announced task shows the celebration toast and a Share on WhatsApp prompt (prefilled text, e.g. "Done: Wipe counters 🔥 3-day streak"). Completing a silent task shows only a quiet "Logged" confirmation, with no share prompt (BR-R24)</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
@@ -5029,12 +5029,12 @@
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.9</t>
+          <t>LLR-11.8</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
         <is>
-          <t>Days to complete (optional): a whole number from 1 to 3650, shown as "Planned: N days". Task detail also shows "Day X of N", counted from the task's creation date</t>
+          <t>Due date and time (optional): a local date and time, stored in UTC. Tasks show a chip: *Overdue* (red), *Due today*, *Due in N days* (within 7 days) or the date. The area list can be filtered by *Overdue*, *Due today* and *Due this week*, and sorted by due date</t>
         </is>
       </c>
       <c r="C230" s="7" t="inlineStr">
@@ -5046,12 +5046,12 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.10</t>
+          <t>LLR-11.9</t>
         </is>
       </c>
       <c r="B231" s="7" t="inlineStr">
         <is>
-          <t>Due date and days to complete are independent: changing one never changes the other, and they may disagree (Q21, BR-R26)</t>
+          <t>Days to complete (optional): a whole number from 1 to 3650, shown as "Planned: N days". Task detail also shows "Day X of N", counted from the task's creation date</t>
         </is>
       </c>
       <c r="C231" s="7" t="inlineStr">
@@ -5063,12 +5063,12 @@
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.11</t>
+          <t>LLR-11.10</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
         <is>
-          <t>All four attributes can be edited on task detail at any time. A due date in the past is allowed (the task is simply overdue)</t>
+          <t>Due date and days to complete are independent: changing one never changes the other, and they may disagree (Q21, BR-R26)</t>
         </is>
       </c>
       <c r="C232" s="7" t="inlineStr">
@@ -5080,12 +5080,12 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.12</t>
+          <t>LLR-11.11</t>
         </is>
       </c>
       <c r="B233" s="7" t="inlineStr">
         <is>
-          <t>Existing tasks are migrated without data loss: milestone = no, visibility = announced, no due date, no days to complete. Nothing else changes</t>
+          <t>All four attributes can be edited on task detail at any time. A due date in the past is allowed (the task is simply overdue)</t>
         </is>
       </c>
       <c r="C233" s="7" t="inlineStr">
@@ -5097,223 +5097,223 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
+          <t>LLR-11.12</t>
+        </is>
+      </c>
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t>Existing tasks are migrated without data loss: milestone = no, visibility = announced, no due date, no days to complete. Nothing else changes</t>
+        </is>
+      </c>
+      <c r="C234" s="7" t="inlineStr">
+        <is>
+          <t>⏳ next</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="7" t="inlineStr">
+        <is>
           <t>LLR-11.13</t>
         </is>
       </c>
-      <c r="B234" s="7" t="inlineStr">
+      <c r="B235" s="7" t="inlineStr">
         <is>
           <t>The dashboard adds an Overdue KPI and the *Milestones* table (LLR-11.2); the owner-only dashboard includes silent tasks, marked 🔕</t>
         </is>
       </c>
-      <c r="C234" s="7" t="inlineStr">
+      <c r="C235" s="7" t="inlineStr">
         <is>
           <t>⏳ next</t>
         </is>
       </c>
     </row>
-    <row r="235"/>
-    <row r="236">
-      <c r="A236" s="13" t="inlineStr">
+    <row r="236"/>
+    <row r="237">
+      <c r="A237" s="13" t="inlineStr">
         <is>
           <t>Business rules: task planning and visibility</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="6" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B237" s="6" t="inlineStr">
+      <c r="B238" s="6" t="inlineStr">
         <is>
           <t>Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="7" t="inlineStr">
-        <is>
-          <t>BR-R22</t>
-        </is>
-      </c>
-      <c r="B238" s="7" t="inlineStr">
-        <is>
-          <t>A task is overdue when it's active, has a due date, and the due date is before now. Done and archived tasks are never overdue</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>BR-R23</t>
+          <t>BR-R22</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
         <is>
-          <t>Silent means invisible without the passcode: silent tasks, their completions, streaks and activity are excluded from every response to a caller without the owner passcode, including counts and aggregates, so their existence can't be inferred</t>
+          <t>A task is overdue when it's active, has a due date, and the due date is before now. Done and archived tasks are never overdue</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>BR-R24</t>
+          <t>BR-R23</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
         <is>
-          <t>Celebrations and share prompts happen only for announced tasks. A reward unlocked by a silent task's completion is unlocked quietly (no share prompt); the reward itself stays visible</t>
+          <t>Silent means invisible without the passcode: silent tasks, their completions, streaks and activity are excluded from every response to a caller without the owner passcode, including counts and aggregates, so their existence can't be inferred</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>BR-R25</t>
+          <t>BR-R24</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
         <is>
-          <t>A Milestone completed reward unlocks when every milestone task it matches (tagged, or in scope with *All tasks in scope*) has ≥ 1 completion. Non-milestone tasks tagged to it don't count. Progress = milestones completed ÷ milestones matched</t>
+          <t>Celebrations and share prompts happen only for announced tasks. A reward unlocked by a silent task's completion is unlocked quietly (no share prompt); the reward itself stays visible</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
+          <t>BR-R25</t>
+        </is>
+      </c>
+      <c r="B242" s="7" t="inlineStr">
+        <is>
+          <t>A Milestone completed reward unlocks when every milestone task it matches (tagged, or in scope with *All tasks in scope*) has ≥ 1 completion. Non-milestone tasks tagged to it don't count. Progress = milestones completed ÷ milestones matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="7" t="inlineStr">
+        <is>
           <t>BR-R26</t>
         </is>
       </c>
-      <c r="B242" s="7" t="inlineStr">
+      <c r="B243" s="7" t="inlineStr">
         <is>
           <t>Due date and days to complete are never derived from each other or from the frequency</t>
         </is>
       </c>
     </row>
-    <row r="243"/>
-    <row r="244">
-      <c r="A244" s="13" t="inlineStr">
+    <row r="244"/>
+    <row r="245">
+      <c r="A245" s="13" t="inlineStr">
         <is>
           <t>AC-11 (your examples)</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* the add form *when* the user opens More options, ticks Milestone, sets due "31 Oct 2026, 6:00 pm" and days to complete "30" *then* the task shows 🏁, "Due 31 Oct" and "Planned: 30 days", and task detail shows "Day 1 of 30".</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a reward "New laptop bag" with the rule Milestone completed tagged to the milestone "Finish React course" *when* that task is completed *then* the reward unlocks and the milestone celebration plays.</t>
+          <t>• *Given* the add form *when* the user opens More options, ticks Milestone, sets due "31 Oct 2026, 6:00 pm" and days to complete "30" *then* the task shows 🏁, "Due 31 Oct" and "Planned: 30 days", and task detail shows "Day 1 of 30".</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>• *Given* two milestone tasks tagged to one milestone reward *when* only one is completed *then* progress shows 1 of 2 and it stays locked (BR-R25, O7).</t>
+          <t>• *Given* a reward "New laptop bag" with the rule Milestone completed tagged to the milestone "Finish React course" *when* that task is completed *then* the reward unlocks and the milestone celebration plays.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a silent task "Therapy session" *when* a visitor opens the read-only view *then* it isn't listed, the area's active count doesn't include it, and dashboard totals exclude it; with the passcode it's shown with 🔕.</t>
+          <t>• *Given* two milestone tasks tagged to one milestone reward *when* only one is completed *then* progress shows 1 of 2 and it stays locked (BR-R25, O7).</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the user completes a silent task *then* only "Logged" appears: no toast and no share prompt.</t>
+          <t>• *Given* a silent task "Therapy session" *when* a visitor opens the read-only view *then* it isn't listed, the area's active count doesn't include it, and dashboard totals exclude it; with the passcode it's shown with 🔕.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a task due yesterday that's still active *then* it shows *Overdue*; when it's completed or archived the chip disappears.</t>
+          <t>• *Given* the user completes a silent task *then* only "Logged" appears: no toast and no share prompt.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
+          <t>• *Given* a task due yesterday that's still active *then* it shows *Overdue*; when it's completed or archived the chip disappears.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="7" t="inlineStr">
+        <is>
           <t>• *Given* a task with due date 10 Oct and days to complete 30 *when* the due date is moved to 20 Oct *then* days to complete stays 30.</t>
         </is>
       </c>
     </row>
-    <row r="252"/>
-    <row r="253">
-      <c r="A253" s="13" t="inlineStr">
+    <row r="253"/>
+    <row r="254">
+      <c r="A254" s="13" t="inlineStr">
         <is>
           <t>LLR-12 Reward ideas and wishlist (HLR-12) ⏳ next</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="12" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="12" t="inlineStr">
         <is>
           <t>A reward can start life as an idea: something you might get later, captured before any rule or task exists (Q23).</t>
         </is>
       </c>
     </row>
-    <row r="255"/>
-    <row r="256">
-      <c r="A256" s="13" t="inlineStr">
+    <row r="256"/>
+    <row r="257">
+      <c r="A257" s="13" t="inlineStr">
         <is>
           <t>LLR-12 Reward ideas and wishlist (HLR-12) ⏳ next</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="6" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B257" s="6" t="inlineStr">
+      <c r="B258" s="6" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C257" s="6" t="inlineStr">
+      <c r="C258" s="6" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="7" t="inlineStr">
-        <is>
-          <t>LLR-12.1</t>
-        </is>
-      </c>
-      <c r="B258" s="7" t="inlineStr">
-        <is>
-          <t>Quick capture: a "+ Idea" button on the Rewards tab and on every tile and area screen opens a short form: title (required, 1–200), then optional for whom, notes (≤ 2000), link (URL), cover photo (camera or gallery, via the file rules of LLR-10.7), where seen (e.g. "City library") and tile/area. Saving needs only the title</t>
-        </is>
-      </c>
-      <c r="C258" s="7" t="inlineStr">
-        <is>
-          <t>⏳ next</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.2</t>
+          <t>LLR-12.1</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
         <is>
-          <t>For whom on every reward and idea: free text (1–40) with suggestions from earlier entries; default "Me" (Q25)</t>
+          <t>Quick capture: a "+ Idea" button on the Rewards tab and on every tile and area screen opens a short form: title (required, 1–200), then optional for whom, notes (≤ 2000), link (URL), cover photo (camera or gallery, via the file rules of LLR-10.7), where seen (e.g. "City library") and tile/area. Saving needs only the title</t>
         </is>
       </c>
       <c r="C259" s="7" t="inlineStr">
@@ -5325,12 +5325,12 @@
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.3</t>
+          <t>LLR-12.2</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
         <is>
-          <t>Ideas have status Idea: no rule, no progress and no tasks, and they never unlock or appear in progress counts (BR-R27)</t>
+          <t>For whom on every reward and idea: free text (1–40) with suggestions from earlier entries; default "Me" (Q25)</t>
         </is>
       </c>
       <c r="C260" s="7" t="inlineStr">
@@ -5342,12 +5342,12 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.4</t>
+          <t>LLR-12.3</t>
         </is>
       </c>
       <c r="B261" s="7" t="inlineStr">
         <is>
-          <t>The Rewards tab has an Ideas filter (and *Closed* for bought or dropped ideas), and can be filtered by for whom, e.g. "Shiragi's ideas and rewards". Tile and area screens list their ideas under "Rewards you can earn here" in a separate *Ideas* group</t>
+          <t>Ideas have status Idea: no rule, no progress and no tasks, and they never unlock or appear in progress counts (BR-R27)</t>
         </is>
       </c>
       <c r="C261" s="7" t="inlineStr">
@@ -5359,12 +5359,12 @@
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.5</t>
+          <t>LLR-12.4</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
         <is>
-          <t>Turn into a reward: from an idea, add a rule (N completions, streak of N or milestone completed), a threshold, a tile (and optional area) and tasks. It becomes a normal *locked* reward, keeping its title, photo, link, notes and for whom; the unlock check runs straight away (BR-R28)</t>
+          <t>The Rewards tab has an Ideas filter (and *Closed* for bought or dropped ideas), and can be filtered by for whom, e.g. "Shiragi's ideas and rewards". Tile and area screens list their ideas under "Rewards you can earn here" in a separate *Ideas* group</t>
         </is>
       </c>
       <c r="C262" s="7" t="inlineStr">
@@ -5376,12 +5376,12 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.6</t>
+          <t>LLR-12.5</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
         <is>
-          <t>Close an idea as *Bought* (got it without a rule) or *Dropped* (no longer wanted). Closed ideas leave the Ideas list, stay under *Closed* with the date and outcome, and can be reopened (BR-R29)</t>
+          <t>Turn into a reward: from an idea, add a rule (N completions, streak of N or milestone completed), a threshold, a tile (and optional area) and tasks. It becomes a normal *locked* reward, keeping its title, photo, link, notes and for whom; the unlock check runs straight away (BR-R28)</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
@@ -5393,12 +5393,12 @@
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.7</t>
+          <t>LLR-12.6</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
         <is>
-          <t>Ideas are Silent by default (hidden from the read-only view) and can be switched to *Announced*; ordinary rewards default to *Announced*. Visibility follows the silent rules of BR-R23 (Q24)</t>
+          <t>Close an idea as *Bought* (got it without a rule) or *Dropped* (no longer wanted). Closed ideas leave the Ideas list, stay under *Closed* with the date and outcome, and can be reopened (BR-R29)</t>
         </is>
       </c>
       <c r="C264" s="7" t="inlineStr">
@@ -5410,12 +5410,12 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.8</t>
+          <t>LLR-12.7</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
         <is>
-          <t>Ideas are included in search (LLR-10.9) by title, notes, for whom and where seen</t>
+          <t>Ideas are Silent by default (hidden from the read-only view) and can be switched to *Announced*; ordinary rewards default to *Announced*. Visibility follows the silent rules of BR-R23 (Q24)</t>
         </is>
       </c>
       <c r="C265" s="7" t="inlineStr">
@@ -5427,126 +5427,143 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
+          <t>LLR-12.8</t>
+        </is>
+      </c>
+      <c r="B266" s="7" t="inlineStr">
+        <is>
+          <t>Ideas are included in search (LLR-10.9) by title, notes, for whom and where seen</t>
+        </is>
+      </c>
+      <c r="C266" s="7" t="inlineStr">
+        <is>
+          <t>⏳ next</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="7" t="inlineStr">
+        <is>
           <t>LLR-12.9</t>
         </is>
       </c>
-      <c r="B266" s="7" t="inlineStr">
+      <c r="B267" s="7" t="inlineStr">
         <is>
           <t>Existing rewards are migrated without data loss: for whom = "Me", visibility = announced; their status, rule, tasks and progress are unchanged</t>
         </is>
       </c>
-      <c r="C266" s="7" t="inlineStr">
+      <c r="C267" s="7" t="inlineStr">
         <is>
           <t>⏳ next</t>
         </is>
       </c>
     </row>
-    <row r="267"/>
-    <row r="268">
-      <c r="A268" s="13" t="inlineStr">
+    <row r="268"/>
+    <row r="269">
+      <c r="A269" s="13" t="inlineStr">
         <is>
           <t>Business rules: ideas</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="6" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="7" t="inlineStr">
-        <is>
-          <t>BR-R27</t>
-        </is>
-      </c>
-      <c r="B270" s="7" t="inlineStr">
-        <is>
-          <t>An *Idea* has no rule and no progress. It can't unlock or be claimed, and it isn't counted in reward totals or progress on the dashboard (the dashboard shows an *Ideas* count per person)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>BR-R28</t>
+          <t>BR-R27</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
         <is>
-          <t>Turning an idea into a reward requires a rule, a threshold (except *milestone completed*) and a tile (LLR-4.9); the idea's id is kept, so links and photos stay attached</t>
+          <t>An *Idea* has no rule and no progress. It can't unlock or be claimed, and it isn't counted in reward totals or progress on the dashboard (the dashboard shows an *Ideas* count per person)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>BR-R29</t>
+          <t>BR-R28</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
         <is>
-          <t>Closing is only for ideas; a reward that already has a rule is claimed, not closed. Reopening a closed idea returns it to *Idea*</t>
+          <t>Turning an idea into a reward requires a rule, a threshold (except *milestone completed*) and a tile (LLR-4.9); the idea's id is kept, so links and photos stay attached</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
+          <t>BR-R29</t>
+        </is>
+      </c>
+      <c r="B273" s="7" t="inlineStr">
+        <is>
+          <t>Closing is only for ideas; a reward that already has a rule is claimed, not closed. Reopening a closed idea returns it to *Idea*</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="7" t="inlineStr">
+        <is>
           <t>BR-R30</t>
         </is>
       </c>
-      <c r="B273" s="7" t="inlineStr">
+      <c r="B274" s="7" t="inlineStr">
         <is>
           <t>*For whom* is a label: it groups and filters rewards, but never changes who can see or edit them (visibility rules decide that)</t>
         </is>
       </c>
     </row>
-    <row r="274"/>
-    <row r="275">
-      <c r="A275" s="13" t="inlineStr">
+    <row r="275"/>
+    <row r="276">
+      <c r="A276" s="13" t="inlineStr">
         <is>
           <t>AC-12 (your example)</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* the user is at the library *when* they tap "+ Idea", type "101 Hilarious Jokes", choose for whom "Shiragi", take a photo of the cover and save *then* it appears under Rewards › Ideas with the photo, for "Shiragi", saved in under 10 seconds on a phone.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the idea *when* a visitor opens the read-only view *then* it isn't shown (silent by default); with the passcode it's listed with 🔕.</t>
+          <t>• *Given* the user is at the library *when* they tap "+ Idea", type "101 Hilarious Jokes", choose for whom "Shiragi", take a photo of the cover and save *then* it appears under Rewards › Ideas with the photo, for "Shiragi", saved in under 10 seconds on a phone.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the idea *when* the user turns it into a reward for Household › Books with the rule "streak of 7" tagged to Shiragi's task "Read 20 minutes" *then* it's a locked reward at 0 %, still with its photo, link and for whom "Shiragi".</t>
+          <t>• *Given* the idea *when* a visitor opens the read-only view *then* it isn't shown (silent by default); with the passcode it's listed with 🔕.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the user simply buys the book *when* they close the idea as *Bought* *then* it moves to *Closed* with today's date.</t>
+          <t>• *Given* the idea *when* the user turns it into a reward for Household › Books with the rule "streak of 7" tagged to Shiragi's task "Read 20 minutes" *then* it's a locked reward at 0 %, still with its photo, link and for whom "Shiragi".</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* the user simply buys the book *when* they close the idea as *Bought* *then* it moves to *Closed* with today's date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="7" t="inlineStr">
         <is>
           <t>• *Given* the Rewards tab filtered to "Shiragi" *then* only her ideas and rewards are shown.</t>
         </is>
@@ -6331,7 +6348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J192"/>
+  <dimension ref="A1:J193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8371,7 +8388,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.1</t>
+          <t>LLR-2.10</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -8381,12 +8398,12 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-2</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Complete an active task, optionally with a note (≤ 1000) and a time (completedAt). If no time is given, the time is now</t>
+          <t>Edit a task from task detail (✎): title and notes. Delete a task (🗑) after a confirmation that names its completion count; its completions and reward tags go with it, the rewards themselves stay (DELETE /tasks/{id})</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -8415,7 +8432,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.2</t>
+          <t>LLR-3.1</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -8430,12 +8447,12 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>The UI offers *Now*, *Yesterday* and *2 days ago* (same time of day)</t>
+          <t>Complete an active task, optionally with a note (≤ 1000) and a time (completedAt). If no time is given, the time is now</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -8459,7 +8476,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.3</t>
+          <t>LLR-3.2</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -8474,12 +8491,12 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>A completion more than 1 minute in the future is rejected (422)</t>
+          <t>Logging uses a month calendar: days the task was done are marked (with a count when more than once), today is outlined, future days are disabled, and ‹ › move between months. Tap a day, adjust the time (defaults to now), add an optional note and log. A time later than now is clamped to now</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -8503,7 +8520,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.4</t>
+          <t>LLR-3.3</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -8518,7 +8535,7 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Completing a one-off task sets it to done. Further completions are rejected (409)</t>
+          <t>A completion more than 1 minute in the future is rejected (422)</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -8547,7 +8564,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.5</t>
+          <t>LLR-3.4</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -8562,7 +8579,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Completing a done or archived task is rejected with a message naming its status (409)</t>
+          <t>Completing a one-off task sets it to done. Further completions are rejected (409)</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -8591,7 +8608,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.6</t>
+          <t>LLR-3.5</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -8606,7 +8623,7 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>The activity log lists completions newest first, with local date/time and note</t>
+          <t>Completing a done or archived task is rejected with a message naming its status (409)</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -8635,7 +8652,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.7</t>
+          <t>LLR-3.6</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -8650,7 +8667,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Each task shows completion count, current streak, best streak and last completion time</t>
+          <t>The activity log lists completions newest first, with local date/time and note</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -8679,7 +8696,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.8</t>
+          <t>LLR-3.7</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -8694,12 +8711,12 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>The area list offers a one-tap ✓ complete (now) for active tasks</t>
+          <t>Each task shows completion count, current streak, best streak and last completion time</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -8723,7 +8740,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.1</t>
+          <t>LLR-3.8</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -8733,17 +8750,17 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Create a reward: title (1–200, required), description (≤ 2000), image URL (≤ 500, optional), rule type (completions or streak), threshold N (1–365), tagged tasks (optional)</t>
+          <t>The area list offers a one-tap ✓ complete (now) for active tasks</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -8767,7 +8784,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.2</t>
+          <t>LLR-4.1</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -8782,7 +8799,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Tag or untag tasks as a full replacement of the set. Unknown task ids are rejected (422)</t>
+          <t>Create a reward: title (1–200, required), description (≤ 2000), image URL (≤ 500, optional), rule type (completions or streak), threshold N (1–365), tagged tasks (optional)</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
@@ -8811,7 +8828,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.3</t>
+          <t>LLR-4.2</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -8826,12 +8843,12 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Tag a task to a locked reward from the task detail screen</t>
+          <t>Tag or untag tasks as a full replacement of the set. Unknown task ids are rejected (422)</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -8855,7 +8872,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.4</t>
+          <t>LLR-4.3</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -8870,12 +8887,12 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Show each reward's rule text, progress (current / target, %), status and tagged tasks</t>
+          <t>Tag a task to a locked reward from the task detail screen</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -8899,7 +8916,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.5</t>
+          <t>LLR-4.4</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -8914,7 +8931,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Filter the rewards list by status</t>
+          <t>Show each reward's rule text, progress (current / target, %), status and tagged tasks</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -8943,7 +8960,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.6</t>
+          <t>LLR-4.5</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -8958,7 +8975,7 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Claim is only possible when the status is unlocked. Claiming a locked reward is rejected (409). Claiming an already claimed reward changes nothing</t>
+          <t>Filter the rewards list by status</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -8987,7 +9004,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.7</t>
+          <t>LLR-4.6</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -9002,7 +9019,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>When a completion unlocks a reward, the completion response includes it and the UI shows a celebration toast</t>
+          <t>Claim is only possible when the status is unlocked. Claiming a locked reward is rejected (409). Claiming an already claimed reward changes nothing</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -9031,7 +9048,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.8</t>
+          <t>LLR-4.7</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -9046,12 +9063,12 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Editing a reward's tasks is only offered while it's locked</t>
+          <t>When a completion unlocks a reward, the completion response includes it and the UI shows a celebration toast</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -9075,7 +9092,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.9</t>
+          <t>LLR-4.8</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -9085,17 +9102,17 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Every reward has a scope from the same taxonomy as tasks: a tile (required: Career/Office/Work, Household or Fun) and optionally one area of that tile (e.g. Household › Kitchen). Creating a reward without a tile is rejected (422); an area from another tile is rejected (422)</t>
+          <t>Editing a reward's tasks is only offered while it's locked</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -9119,7 +9136,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.10</t>
+          <t>LLR-4.9</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -9134,7 +9151,7 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Every reward has a match mode: *Selected tasks* (default; the user tags specific tasks) or *All tasks in scope* (every non-archived task in the scope counts automatically, including tasks created later)</t>
+          <t>Rewards stand alone. A reward needs only a title and N (default 5); a note and picture link are optional. It can optionally be kept in an area (to organise it; its tile comes from the area), but that never limits which tasks it can be linked to</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -9163,7 +9180,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.11</t>
+          <t>LLR-4.10</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -9178,7 +9195,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>In *Selected tasks* mode, only tasks inside the reward's scope can be tagged. Tagging a task outside it is rejected (422) with a message naming the task and the scope</t>
+          <t>Links are many-to-many and unrestricted: any task (from any tile or area) can be linked to any reward; one task can count for several rewards. Unlock rule for now: task count, the linked tasks done N times in total. (Older rewards that counted "all tasks in an area" keep working)</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -9207,7 +9224,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.12</t>
+          <t>LLR-4.11</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -9222,7 +9239,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>The reward form picks tile, then area (optional, "Whole tile" default), then match mode. The task picker lists only tasks in that scope, grouped by area</t>
+          <t>Linking twice is harmless; unlinking an unlocked or claimed reward doesn't lock it again (BR-R10); deleting a task, area or tile removes only its links, and rewards stay. Deleting a tile does delete rewards kept in it (BR-R18)</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -9251,7 +9268,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.13</t>
+          <t>LLR-4.12</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -9266,7 +9283,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Each reward card shows its scope as a breadcrumb (e.g. "Household › Kitchen" or "Fun") and its match mode. The Rewards tab is navigated like the Areas tab: tile cards (with active / to-claim / claimed counts) → a tile (its whole-tile rewards, then one row per area) → an area (its rewards, plus whole-tile rewards that also count there). Each level filters by status and has + New reward preset to that tile or area</t>
+          <t>The Link screen (#/rewards/link, top menu *Link*) lists all tasks (grouped by tile › area, with how often each was done and how many rewards it counts for) and all rewards (with area, N and status), each searchable. Pick a task and a reward, then Link (or Unlink if they already are). *Current links* lists each linked reward with its tasks, each with ✕ to unlink. Opens with a task or reward already picked from the task or reward screens</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -9295,7 +9312,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.14</t>
+          <t>LLR-4.13</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -9310,7 +9327,7 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>The area screen shows "Rewards you can earn here": locked or unlocked rewards whose scope is this area or this area's whole tile, with progress</t>
+          <t>The top menu is Tiles | Tasks | Rewards | Link. *Tasks* lists every task grouped by tile › area (status filter, default Active; search; each row shows frequency, completions, streak 🔥 and rewards 🎁, with a quick ✓). *Rewards* lists every reward grouped by the area it's kept in (tile › area order, *Not in an area* last; status filter; search; + New with an optional area). The Link screen's two lists use the same grouping. A tile shows only its areas; an area has tabs Tasks | Rewards | Notes &amp; contacts, and its Rewards tab lists and adds the rewards kept there but doesn't link tasks</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
@@ -9339,7 +9356,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.15</t>
+          <t>LLR-4.14</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -9354,7 +9371,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>On task detail, "Tag to a reward" offers only locked *Selected tasks* rewards whose scope contains the task. Rewards that match the task automatically (*All tasks in scope*) are listed with the label "Counts automatically"</t>
+          <t>A reward's screen (#/rewards/r/{id}) shows its rule, progress and linked tasks (✕ to unlink), *+ Link tasks* (Link screen with this reward picked), *Claim 🎁* when unlocked, and ✎ / 🗑 to edit (title, N while locked, area, note, picture) or delete it (tasks and history stay)</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -9383,7 +9400,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.16</t>
+          <t>LLR-4.15</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9398,7 +9415,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Scope and match mode can be changed only while the reward is locked. Narrowing the scope removes tags that fall outside it, after the user confirms; the confirmation lists the tasks that will be untagged</t>
+          <t>On task detail, the *Rewards* card lists the rewards the task counts for (links to each reward) and *+ Link to a reward* opens the Link screen with this task picked</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -9427,7 +9444,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.17</t>
+          <t>LLR-4.16</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -9442,7 +9459,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Deleting an area doesn't delete rewards scoped to it: they widen to the area's tile (area cleared) and keep their status, rule and remaining tags. Renaming an area changes nothing</t>
+          <t>N can be changed only while the reward is locked; lowering it re-checks the rule at once. A reward whose linked tasks already meet N unlocks as soon as it's linked</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -9471,7 +9488,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.18</t>
+          <t>LLR-4.17</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9486,7 +9503,7 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Existing rewards are migrated without data loss (schema migration with automatic pre-upgrade backup): if all tagged tasks share one area, scope = that area; else if they share one tile, scope = that tile; otherwise (no tags, or tags across tiles) the reward keeps its tags and is marked *Needs a tile* until the user picks one. No reward, tag, completion or status is deleted</t>
+          <t>Moving a reward to another area, or out of any area, never changes its links</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -9515,7 +9532,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.1</t>
+          <t>LLR-4.18</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -9525,12 +9542,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>HLR-5</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Reads only GET /dashboard/summary; never the database</t>
+          <t>Existing rewards are migrated without data loss (schema migration with automatic pre-upgrade backup): if all tagged tasks share one area, scope = that area; else if they share one tile, scope = that tile; otherwise (no tags, or tags across tiles) the reward keeps its tags and is marked *Needs a tile* until the user picks one. No reward, tag, completion or status is deleted</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -9559,7 +9576,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.2</t>
+          <t>LLR-5.1</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9574,12 +9591,12 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>KPIs: completions (window), active tasks, active streaks, unlocked + claimed rewards, AI acceptance rate (— when undefined)</t>
+          <t>Reads only GET /dashboard/summary; never the database</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -9603,7 +9620,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.3</t>
+          <t>LLR-5.2</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -9618,7 +9635,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Charts: completions by tile, by area (filterable by tile) and per day (empty days shown as gaps). Hover tooltips on every mark</t>
+          <t>KPIs: completions (window), active tasks, active streaks, unlocked + claimed rewards, AI acceptance rate (— when undefined)</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -9647,7 +9664,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.4</t>
+          <t>LLR-5.3</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9662,7 +9679,7 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Tables: active streaks (filterable by tile); reward progress with a progress bar</t>
+          <t>Charts: completions by tile, by area (filterable by tile) and per day (empty days shown as gaps). Hover tooltips on every mark</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -9691,7 +9708,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.5</t>
+          <t>LLR-5.4</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -9706,7 +9723,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Filters: window (7/30/90 days/all time) and tile. They survive reruns (session_state)</t>
+          <t>Tables: active streaks (filterable by tile); reward progress with a progress bar</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -9735,7 +9752,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.6</t>
+          <t>LLR-5.5</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -9750,7 +9767,7 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Responses are cached 30 s per window. *Refresh now* clears the cache</t>
+          <t>Filters: window (7/30/90 days/all time) and tile. They survive reruns (session_state)</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -9779,7 +9796,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.7</t>
+          <t>LLR-5.6</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -9794,7 +9811,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Unlocked rewards can be claimed from the dashboard. After claiming, the cache is cleared and the page shows fresh data</t>
+          <t>Responses are cached 30 s per window. *Refresh now* clears the cache</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -9823,7 +9840,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.8</t>
+          <t>LLR-5.7</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -9838,7 +9855,7 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>If the BFF is unreachable, show the error and *Try again* (no stack traces)</t>
+          <t>Unlocked rewards can be claimed from the dashboard. After claiming, the cache is cleared and the page shows fresh data</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -9867,7 +9884,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.9</t>
+          <t>LLR-5.8</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -9882,12 +9899,12 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Streaks and rewards ignore the window; completion aggregates respect it</t>
+          <t>If the BFF is unreachable, show the error and *Try again* (no stack traces)</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -9911,7 +9928,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.10</t>
+          <t>LLR-5.9</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -9926,7 +9943,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Summary payload is flat snake_case records; React endpoints are camelCase (per-client shaping)</t>
+          <t>Streaks and rewards ignore the window; completion aggregates respect it</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -9955,7 +9972,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.11</t>
+          <t>LLR-5.10</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -9970,12 +9987,12 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Reward progress rows include the reward's tile and area; the dashboard's tile filter applies to rewards as well as completions and streaks</t>
+          <t>Summary payload is flat snake_case records; React endpoints are camelCase (per-client shaping)</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -9999,7 +10016,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.1</t>
+          <t>LLR-5.11</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -10009,22 +10026,22 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>HLR-6</t>
+          <t>HLR-5</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Attach 1–5 photos per run to an area (JPEG/PNG/WebP, ≤ 5 MB each; type checked by content, not extension)</t>
+          <t>Reward progress rows include the reward's tile and area; the dashboard's tile filter applies to rewards as well as completions and streaks</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
@@ -10043,7 +10060,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.2</t>
+          <t>LLR-6.1</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -10058,7 +10075,7 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Photos are stored privately with random names and are never publicly addressable</t>
+          <t>Attach 1–5 photos per run to an area (JPEG/PNG/WebP, ≤ 5 MB each; type checked by content, not extension)</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -10087,7 +10104,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.3</t>
+          <t>LLR-6.2</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -10102,7 +10119,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Starting a suggestion run returns immediately (202) with a run id; the UI shows a loading state</t>
+          <t>Photos are stored privately with random names and are never publicly addressable</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -10131,7 +10148,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.4</t>
+          <t>LLR-6.3</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -10146,7 +10163,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>While a run is in progress, the manual *Add a task* form stays fully usable</t>
+          <t>Starting a suggestion run returns immediately (202) with a run id; the UI shows a loading state</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -10175,7 +10192,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.5</t>
+          <t>LLR-6.4</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -10190,7 +10207,7 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Each suggestion has a title (≤ 200), why (≤ 500), priority and frequency, validated against a strict schema</t>
+          <t>While a run is in progress, the manual *Add a task* form stays fully usable</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -10219,7 +10236,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.6</t>
+          <t>LLR-6.5</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -10234,7 +10251,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>The user marks each suggestion Relevant / Not relevant / Ignore. Relevant creates a task with source = ai. A decision is final (409 on re-decide)</t>
+          <t>Each suggestion has a title (≤ 200), why (≤ 500), priority and frequency, validated against a strict schema</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -10263,7 +10280,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.7</t>
+          <t>LLR-6.6</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10278,7 +10295,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>On timeout (30 s), invalid output or missing API key: retry once where sensible, then show "AI suggestions unavailable, add tasks manually". The page never breaks</t>
+          <t>The user marks each suggestion Relevant / Not relevant / Ignore. Relevant creates a task with source = ai. A decision is final (409 on re-decide)</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -10307,7 +10324,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.8</t>
+          <t>LLR-6.7</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -10322,7 +10339,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>The API key exists only in BFF environment variables</t>
+          <t>On timeout (30 s), invalid output or missing API key: retry once where sensible, then show "AI suggestions unavailable, add tasks manually". The page never breaks</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -10351,7 +10368,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.9</t>
+          <t>LLR-6.8</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -10366,7 +10383,7 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Decisions feed the dashboard acceptance rate (relevant ÷ decided)</t>
+          <t>The API key exists only in BFF environment variables</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -10395,7 +10412,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.1</t>
+          <t>LLR-6.9</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -10405,22 +10422,22 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>HLR-7</t>
+          <t>HLR-6</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>The MFE is built separately and exposes ./RewardsApp via remoteEntry.js</t>
+          <t>Decisions feed the dashboard acceptance rate (relevant ÷ decided)</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -10439,7 +10456,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.2</t>
+          <t>LLR-7.1</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -10454,12 +10471,12 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>The host mounts it on #/rewards and every #/rewards/*. The nav item stays active on sub-routes</t>
+          <t>The MFE is built separately and exposes ./RewardsApp via remoteEntry.js</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -10483,7 +10500,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.3</t>
+          <t>LLR-7.2</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -10498,7 +10515,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Host and remote share one React instance; the remote bundles no React</t>
+          <t>The host mounts it on #/rewards and every #/rewards/*. The nav item stays active on sub-routes</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -10527,7 +10544,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.4</t>
+          <t>LLR-7.3</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -10542,7 +10559,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>If the remote fails to load, the host shows "Rewards is unavailable right now" and a reload button. Other pages are unaffected</t>
+          <t>Host and remote share one React instance; the remote bundles no React</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -10571,7 +10588,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.5</t>
+          <t>LLR-7.4</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -10586,7 +10603,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>MFE styles are scoped (.rw-app) and don't alter host styles</t>
+          <t>If the remote fails to load, the host shows "Rewards is unavailable right now" and a reload button. Other pages are unaffected</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -10615,7 +10632,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.6</t>
+          <t>LLR-7.5</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -10630,12 +10647,12 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>The remote URL is configurable per environment (VITE_REWARDS_REMOTE_URL)</t>
+          <t>MFE styles are scoped (.rw-app) and don't alter host styles</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
@@ -10659,7 +10676,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.7</t>
+          <t>LLR-7.6</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -10674,12 +10691,12 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>The MFE runs standalone for development (npm run dev)</t>
+          <t>The remote URL is configurable per environment (VITE_REWARDS_REMOTE_URL)</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -10703,7 +10720,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.8</t>
+          <t>LLR-7.7</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -10718,7 +10735,7 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Every screen has loading, error (with retry) and empty states</t>
+          <t>The MFE runs standalone for development (npm run dev)</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -10747,7 +10764,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.1</t>
+          <t>LLR-7.8</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -10757,17 +10774,17 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>HLR-8</t>
+          <t>HLR-7</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Every endpoint except /health needs Authorization: Bearer &lt;demo token&gt;; otherwise 401</t>
+          <t>Every screen has loading, error (with retry) and empty states</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
@@ -10791,7 +10808,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.2</t>
+          <t>LLR-8.1</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -10806,7 +10823,7 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>CORS allows only the configured origins</t>
+          <t>Every endpoint except /health needs Authorization: Bearer &lt;demo token&gt;; otherwise 401</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -10835,7 +10852,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.3</t>
+          <t>LLR-8.2</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -10850,7 +10867,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>OpenAPI documentation is served at /docs</t>
+          <t>CORS allows only the configured origins</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -10879,7 +10896,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.4</t>
+          <t>LLR-8.3</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -10894,7 +10911,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Errors use {detail} with status codes 401, 404, 409 and 422 as catalogued in LLD §3.3</t>
+          <t>OpenAPI documentation is served at /docs</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -10923,7 +10940,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.5</t>
+          <t>LLR-8.4</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -10938,7 +10955,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Request bodies accept camelCase or snake_case. React responses are camelCase; dashboard responses are snake_case</t>
+          <t>Errors use {detail} with status codes 401, 404, 409 and 422 as catalogued in LLD §3.3</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -10967,7 +10984,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.6</t>
+          <t>LLR-8.5</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -10982,7 +10999,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Timestamps are ISO-8601 UTC in responses</t>
+          <t>Request bodies accept camelCase or snake_case. React responses are camelCase; dashboard responses are snake_case</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -11011,7 +11028,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.7</t>
+          <t>LLR-8.6</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -11021,12 +11038,12 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-8</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Reward create/update accept categoryId (required on create), areaId (optional; null = whole tile) and matchMode (selected | all); update also accepts untagOutside (narrowing answers 409 listing the tasks until it's true). Reward responses include categoryId, categoryName, categoryIcon, areaId, areaName, matchMode, needsTile and matchedTaskCount</t>
+          <t>Timestamps are ISO-8601 UTC in responses</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -11055,7 +11072,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.8</t>
+          <t>LLR-8.7</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -11070,7 +11087,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>GET /rewards accepts categoryId and areaId filters. GET /areas/{id}/rewards returns the rewards that match that area (LLR-4.14). Task detail's rewards lists every reward matching the task, with how it matches (tagged or scope)</t>
+          <t>POST /rewards needs only title (optional threshold = N, default 5, areaId, description, imageUrl, taskIds). GET /rewards (?status=, ?areaId=), GET / PATCH / DELETE /rewards/{id} (PATCH edits title, N, note, picture, areaId or null). POST / DELETE /rewards/{id}/tasks/{taskId} link and unlink one task; PUT /rewards/{id}/tasks replaces all links. Responses include the optional categoryId, categoryName, categoryIcon, areaId, areaName, plus tasks, connected and matchedTaskCount</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -11099,7 +11116,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.9</t>
+          <t>LLR-8.8</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -11109,12 +11126,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>HLR-8</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Schema changes are applied by versioned migrations on startup, never by dropping and recreating tables; a backup of the database file is written before each upgrade (Q14)</t>
+          <t>Task detail's rewards lists every reward the task counts for, with how (tagged = linked, or scope for older all-tasks-in-an-area rewards)</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -11143,7 +11160,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.10</t>
+          <t>LLR-8.9</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -11153,12 +11170,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>HLR-1</t>
+          <t>HLR-8</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Tile endpoints: POST /categories, PATCH /categories/{id} (name, icon), DELETE /categories/{id}, PUT /categories/order and PUT /categories/{id}/areas/order, POST /categories/starter (LLR-1.8, returns what was added)</t>
+          <t>Schema changes are applied by versioned migrations on startup, never by dropping and recreating tables; a backup of the database file is written before each upgrade (Q14)</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -11187,7 +11204,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.11</t>
+          <t>LLR-8.10</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -11197,12 +11214,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-1</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Details endpoints for both owners (/categories/{id} and /areas/{id}): …/details (grouped by topic), …/notes, …/contacts, …/files (multipart upload); PATCH/DELETE on /notes/{id}, /contacts/{id}, /files/{id}; GET /files/{id}/download; GET /search?q=</t>
+          <t>Tile endpoints: POST /categories, PATCH /categories/{id} (name, icon), DELETE /categories/{id}, PUT /categories/order and PUT /categories/{id}/areas/order, POST /categories/starter (LLR-1.8, returns what was added)</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -11231,7 +11248,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.12</t>
+          <t>LLR-8.11</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -11241,17 +11258,17 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Task create/update accept isMilestone, visibility (announced | silent), dueAt (ISO date-time, optional) and targetDays (optional); GET /areas/{id}/tasks adds filters milestone=true and due=overdue|today|week and sort=due. Responses served without the passcode omit silent tasks entirely (BR-R23)</t>
+          <t>Details endpoints for both owners (/categories/{id} and /areas/{id}): …/details (grouped by topic), …/notes, …/contacts, …/files (multipart upload); PATCH/DELETE on /notes/{id}, /contacts/{id}, /files/{id}; GET /files/{id}/download; GET /search?q=</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -11275,7 +11292,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.13</t>
+          <t>LLR-8.12</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -11285,12 +11302,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Rewards accept status: "idea" on create (rule, threshold and tile then optional), forWhom, visibility, link, seenAt (where seen) and a cover image; POST /rewards/{id}/activate (rule, threshold, tile, tasks) turns an idea into a locked reward; POST /rewards/{id}/close with outcome (bought | dropped); GET /rewards filters status=idea|closed and forWhom=</t>
+          <t>Task create/update accept isMilestone, visibility (announced | silent), dueAt (ISO date-time, optional) and targetDays (optional); GET /areas/{id}/tasks adds filters milestone=true and due=overdue|today|week and sort=due. Responses served without the passcode omit silent tasks entirely (BR-R23)</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -11319,7 +11336,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.1</t>
+          <t>LLR-8.13</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -11329,17 +11346,17 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>The tile screen and the area screen each have a Notes &amp; contacts tab next to their main content. It lists topics as groups (items without a topic under "General"), each showing its contacts, files and notes</t>
+          <t>Rewards accept status: "idea" on create (rule, threshold and tile then optional), forWhom, visibility, link, seenAt (where seen) and a cover image; POST /rewards/{id}/activate (rule, threshold, tile, tasks) turns an idea into a locked reward; POST /rewards/{id}/close with outcome (bought | dropped); GET /rewards filters status=idea|closed and forWhom=</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -11363,7 +11380,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.2</t>
+          <t>LLR-10.1</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -11378,7 +11395,7 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Topic is free text (1–60 characters), optional, and offers existing topics from the same tile or area as suggestions, so "Bosch Dishwasher" isn't typed three different ways</t>
+          <t>The area screen has a Notes &amp; contacts tab (tiles no longer have their own tabs; older tile-level items stay stored and searchable) next to their main content. It lists topics as groups (items without a topic under "General"), each showing its contacts, files and notes</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -11407,7 +11424,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.3</t>
+          <t>LLR-10.2</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -11422,7 +11439,7 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Contact: name (required, 1–80); organisation or brand (e.g. Bosch, Kent, IFB, LG); role (*Customer care*, *Service executive*, *Technician*, *Vendor or shop*, *Other*); up to 3 phone numbers with labels (mobile, toll-free, WhatsApp); email; website; last visit or contact date; notes (≤ 1000); topic</t>
+          <t>Topic is free text (1–60 characters), optional, and offers existing topics from the same tile or area as suggestions, so "Bosch Dishwasher" isn't typed three different ways</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -11451,7 +11468,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.4</t>
+          <t>LLR-10.3</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -11466,7 +11483,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Phone numbers are stored as entered and shown with actions: Call (tel:), WhatsApp (wa.me, for numbers marked WhatsApp) and Copy. Email gets Email (mailto:). All actions are one tap on a phone</t>
+          <t>Contact: name (required, 1–80); organisation or brand (e.g. Bosch, Kent, IFB, LG); role (*Customer care*, *Service executive*, *Technician*, *Vendor or shop*, *Other*); up to 3 phone numbers with labels (mobile, toll-free, WhatsApp); email; website; last visit or contact date; notes (≤ 1000); topic</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -11495,7 +11512,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.5</t>
+          <t>LLR-10.4</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -11510,7 +11527,7 @@
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Past executives: within a topic, contacts with the role *Service executive* or *Technician* are listed newest last-visit first. The topic header shows the last executive (name, date, call button)</t>
+          <t>Phone numbers are stored as entered and shown with actions: Call (tel:), WhatsApp (wa.me, for numbers marked WhatsApp) and Copy. Email gets Email (mailto:). All actions are one tap on a phone</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
@@ -11539,7 +11556,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.6</t>
+          <t>LLR-10.5</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -11554,7 +11571,7 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Note: text 1–5000 characters, optional title and topic; shows created and last-edited time; newest first</t>
+          <t>Past executives: within a topic, contacts with the role *Service executive* or *Technician* are listed newest last-visit first. The topic header shows the last executive (name, date, call button)</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -11583,7 +11600,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.7</t>
+          <t>LLR-10.6</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -11598,7 +11615,7 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>File (bills, invoices, warranty cards, manuals): PDF, JPG, PNG, WebP or HEIC, up to 10 MB each, checked by content; title (required), optional date, amount (₹) and topic. Files open in the browser or download; images show a thumbnail</t>
+          <t>Note: text 1–5000 characters, optional title and topic; shows created and last-edited time; newest first</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
@@ -11627,7 +11644,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.8</t>
+          <t>LLR-10.7</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -11642,7 +11659,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Notes, contacts and files can be edited and deleted (with confirmation), and moved between topics by editing the topic</t>
+          <t>File (bills, invoices, warranty cards, manuals): PDF, JPG, PNG, WebP or HEIC, up to 10 MB each, checked by content; title (required), optional date, amount (₹) and topic. Files open in the browser or download; images show a thumbnail</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -11671,7 +11688,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.9</t>
+          <t>LLR-10.8</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -11686,7 +11703,7 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Search across every tile and area by contact name, organisation, topic, phone digits (spaces and dashes ignored), note text and file title. Results show where each hit lives (e.g. "Household › Kitchen › Bosch Dishwasher") and link to it</t>
+          <t>Notes, contacts and files can be edited and deleted (with confirmation), and moved between topics by editing the topic</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
@@ -11715,7 +11732,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.10</t>
+          <t>LLR-10.9</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -11730,7 +11747,7 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Deleting an area or tile deletes its notes, contacts and files, and the confirmation counts them (LLR-1.12). Stored files are removed only after the database change commits</t>
+          <t>Search across every tile and area by contact name, organisation, topic, phone digits (spaces and dashes ignored), note text and file title. Results show where each hit lives (e.g. "Household › Kitchen › Bosch Dishwasher") and link to it</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -11759,7 +11776,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.11</t>
+          <t>LLR-10.10</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -11774,7 +11791,7 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Visibility follows the rewards setting (Q17): readable in the read-only view when public reads are on; creating, editing, deleting and uploading need the owner passcode</t>
+          <t>Deleting an area or tile deletes its notes, contacts and files, and the confirmation counts them (LLR-1.12). Stored files are removed only after the database change commits</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
@@ -11803,7 +11820,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.12</t>
+          <t>LLR-10.11</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -11818,12 +11835,12 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>The JSON export (app.backup) includes notes and contacts, and lists files by title and stored name; the server backup covers the files folder as well as the database</t>
+          <t>Visibility follows the rewards setting (Q17): readable in the read-only view when public reads are on; creating, editing, deleting and uploading need the owner passcode</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr">
@@ -11847,7 +11864,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.1</t>
+          <t>LLR-10.12</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -11857,17 +11874,17 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Milestone: yes/no (default no), set when creating or editing a task</t>
+          <t>The JSON export (app.backup) includes notes and contacts, and lists files by title and stored name; the server backup covers the files folder as well as the database</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
@@ -11891,7 +11908,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.2</t>
+          <t>LLR-11.1</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -11906,7 +11923,7 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>Milestones show a 🏁 badge on task rows and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
+          <t>Milestone: yes/no (default no), set when creating or editing a task</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -11935,7 +11952,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.3</t>
+          <t>LLR-11.2</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -11950,7 +11967,7 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Completing an announced milestone shows the milestone celebration: a larger, longer celebration than a normal completion (respects reduced motion), with its own share prompt</t>
+          <t>Milestones show a 🏁 badge on task rows and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
@@ -11979,7 +11996,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.4</t>
+          <t>LLR-11.3</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -11994,7 +12011,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task it matches has at least one completion (BR-R25). Creating one that matches no milestone task is rejected (422)</t>
+          <t>Completing an announced milestone shows the milestone celebration: a larger, longer celebration than a normal completion (respects reduced motion), with its own share prompt</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -12023,7 +12040,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.5</t>
+          <t>LLR-11.4</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -12038,7 +12055,7 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Announce or keep silent: each task is *Announced* (default) or *Silent*, set when creating or editing it (Q20, Q22)</t>
+          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task it matches has at least one completion (BR-R25). Creating one that matches no milestone task is rejected (422)</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
@@ -12067,7 +12084,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.6</t>
+          <t>LLR-11.5</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -12082,7 +12099,7 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Silent tasks and their completions never appear in anything served without the owner passcode: lists, counts, streaks, activity, dashboard aggregates or reward task lists (BR-R23). With the passcode they're shown with a 🔕 marker</t>
+          <t>Announce or keep silent: each task is *Announced* (default) or *Silent*, set when creating or editing it (Q20, Q22)</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -12111,7 +12128,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.7</t>
+          <t>LLR-11.6</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -12126,7 +12143,7 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Completing an announced task shows the celebration toast and a Share on WhatsApp prompt (prefilled text, e.g. "Done: Wipe counters 🔥 3-day streak"). Completing a silent task shows only a quiet "Logged" confirmation, with no share prompt (BR-R24)</t>
+          <t>Silent tasks and their completions never appear in anything served without the owner passcode: lists, counts, streaks, activity, dashboard aggregates or reward task lists (BR-R23). With the passcode they're shown with a 🔕 marker</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
@@ -12155,7 +12172,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.8</t>
+          <t>LLR-11.7</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -12170,7 +12187,7 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Due date and time (optional): a local date and time, stored in UTC. Tasks show a chip: *Overdue* (red), *Due today*, *Due in N days* (within 7 days) or the date. The area list can be filtered by *Overdue*, *Due today* and *Due this week*, and sorted by due date</t>
+          <t>Completing an announced task shows the celebration toast and a Share on WhatsApp prompt (prefilled text, e.g. "Done: Wipe counters 🔥 3-day streak"). Completing a silent task shows only a quiet "Logged" confirmation, with no share prompt (BR-R24)</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -12199,7 +12216,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.9</t>
+          <t>LLR-11.8</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -12214,7 +12231,7 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Days to complete (optional): a whole number from 1 to 3650, shown as "Planned: N days". Task detail also shows "Day X of N", counted from the task's creation date</t>
+          <t>Due date and time (optional): a local date and time, stored in UTC. Tasks show a chip: *Overdue* (red), *Due today*, *Due in N days* (within 7 days) or the date. The area list can be filtered by *Overdue*, *Due today* and *Due this week*, and sorted by due date</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
@@ -12243,7 +12260,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.10</t>
+          <t>LLR-11.9</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -12258,7 +12275,7 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Due date and days to complete are independent: changing one never changes the other, and they may disagree (Q21, BR-R26)</t>
+          <t>Days to complete (optional): a whole number from 1 to 3650, shown as "Planned: N days". Task detail also shows "Day X of N", counted from the task's creation date</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -12287,7 +12304,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.11</t>
+          <t>LLR-11.10</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -12302,7 +12319,7 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>All four attributes can be edited on task detail at any time. A due date in the past is allowed (the task is simply overdue)</t>
+          <t>Due date and days to complete are independent: changing one never changes the other, and they may disagree (Q21, BR-R26)</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -12331,7 +12348,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.12</t>
+          <t>LLR-11.11</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -12346,7 +12363,7 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Existing tasks are migrated without data loss: milestone = no, visibility = announced, no due date, no days to complete. Nothing else changes</t>
+          <t>All four attributes can be edited on task detail at any time. A due date in the past is allowed (the task is simply overdue)</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -12375,7 +12392,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.13</t>
+          <t>LLR-11.12</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -12390,7 +12407,7 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>The dashboard adds an Overdue KPI and the *Milestones* table (LLR-11.2); the owner-only dashboard includes silent tasks, marked 🔕</t>
+          <t>Existing tasks are migrated without data loss: milestone = no, visibility = announced, no due date, no days to complete. Nothing else changes</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
@@ -12419,7 +12436,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.1</t>
+          <t>LLR-11.13</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -12429,12 +12446,12 @@
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>Quick capture: a "+ Idea" button on the Rewards tab and on every tile and area screen opens a short form: title (required, 1–200), then optional for whom, notes (≤ 2000), link (URL), cover photo (camera or gallery, via the file rules of LLR-10.7), where seen (e.g. "City library") and tile/area. Saving needs only the title</t>
+          <t>The dashboard adds an Overdue KPI and the *Milestones* table (LLR-11.2); the owner-only dashboard includes silent tasks, marked 🔕</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -12463,7 +12480,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.2</t>
+          <t>LLR-12.1</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -12478,7 +12495,7 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>For whom on every reward and idea: free text (1–40) with suggestions from earlier entries; default "Me" (Q25)</t>
+          <t>Quick capture: a "+ Idea" button on the Rewards tab and on every tile and area screen opens a short form: title (required, 1–200), then optional for whom, notes (≤ 2000), link (URL), cover photo (camera or gallery, via the file rules of LLR-10.7), where seen (e.g. "City library") and tile/area. Saving needs only the title</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
@@ -12507,7 +12524,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.3</t>
+          <t>LLR-12.2</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -12522,7 +12539,7 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Ideas have status Idea: no rule, no progress and no tasks, and they never unlock or appear in progress counts (BR-R27)</t>
+          <t>For whom on every reward and idea: free text (1–40) with suggestions from earlier entries; default "Me" (Q25)</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -12551,7 +12568,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.4</t>
+          <t>LLR-12.3</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -12566,7 +12583,7 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>The Rewards tab has an Ideas filter (and *Closed* for bought or dropped ideas), and can be filtered by for whom, e.g. "Shiragi's ideas and rewards". Tile and area screens list their ideas under "Rewards you can earn here" in a separate *Ideas* group</t>
+          <t>Ideas have status Idea: no rule, no progress and no tasks, and they never unlock or appear in progress counts (BR-R27)</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
@@ -12595,7 +12612,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.5</t>
+          <t>LLR-12.4</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -12610,7 +12627,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>Turn into a reward: from an idea, add a rule (N completions, streak of N or milestone completed), a threshold, a tile (and optional area) and tasks. It becomes a normal *locked* reward, keeping its title, photo, link, notes and for whom; the unlock check runs straight away (BR-R28)</t>
+          <t>The Rewards tab has an Ideas filter (and *Closed* for bought or dropped ideas), and can be filtered by for whom, e.g. "Shiragi's ideas and rewards". Tile and area screens list their ideas under "Rewards you can earn here" in a separate *Ideas* group</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -12639,7 +12656,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.6</t>
+          <t>LLR-12.5</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -12654,7 +12671,7 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Close an idea as *Bought* (got it without a rule) or *Dropped* (no longer wanted). Closed ideas leave the Ideas list, stay under *Closed* with the date and outcome, and can be reopened (BR-R29)</t>
+          <t>Turn into a reward: from an idea, add a rule (N completions, streak of N or milestone completed), a threshold, a tile (and optional area) and tasks. It becomes a normal *locked* reward, keeping its title, photo, link, notes and for whom; the unlock check runs straight away (BR-R28)</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
@@ -12683,7 +12700,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.7</t>
+          <t>LLR-12.6</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -12698,7 +12715,7 @@
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Ideas are Silent by default (hidden from the read-only view) and can be switched to *Announced*; ordinary rewards default to *Announced*. Visibility follows the silent rules of BR-R23 (Q24)</t>
+          <t>Close an idea as *Bought* (got it without a rule) or *Dropped* (no longer wanted). Closed ideas leave the Ideas list, stay under *Closed* with the date and outcome, and can be reopened (BR-R29)</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -12727,7 +12744,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.8</t>
+          <t>LLR-12.7</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -12742,7 +12759,7 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Ideas are included in search (LLR-10.9) by title, notes, for whom and where seen</t>
+          <t>Ideas are Silent by default (hidden from the read-only view) and can be switched to *Announced*; ordinary rewards default to *Announced*. Visibility follows the silent rules of BR-R23 (Q24)</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
@@ -12771,7 +12788,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.9</t>
+          <t>LLR-12.8</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -12786,7 +12803,7 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>Existing rewards are migrated without data loss: for whom = "Me", visibility = announced; their status, rule, tasks and progress are unchanged</t>
+          <t>Ideas are included in search (LLR-10.9) by title, notes, for whom and where seen</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -12815,27 +12832,27 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>BR-R1</t>
+          <t>LLR-12.9</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>A period is a local calendar day (daily) or a Monday–Sunday week (weekly) in BFF_TIMEZONE</t>
+          <t>Existing rewards are migrated without data loss: for whom = "Me", visibility = announced; their status, rule, tasks and progress are unchanged</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
@@ -12859,7 +12876,7 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>BR-R2</t>
+          <t>BR-R1</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -12874,7 +12891,7 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>Several completions in one period count once towards the streak (they all count towards completion count)</t>
+          <t>A period is a local calendar day (daily) or a Monday–Sunday week (weekly) in BFF_TIMEZONE</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -12903,7 +12920,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>BR-R3</t>
+          <t>BR-R2</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -12918,7 +12935,7 @@
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Best streak = longest run of consecutive periods with ≥ 1 completion</t>
+          <t>Several completions in one period count once towards the streak (they all count towards completion count)</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
@@ -12947,7 +12964,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>BR-R4</t>
+          <t>BR-R3</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -12962,7 +12979,7 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>Current streak = the run ending at the latest completed period, if that period is the current or the previous one; otherwise 0</t>
+          <t>Best streak = longest run of consecutive periods with ≥ 1 completion</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -12991,7 +13008,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>BR-R5</t>
+          <t>BR-R4</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -13006,7 +13023,7 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>One-off tasks: streak = 1 once completed, else 0 (not shown as an active streak)</t>
+          <t>Current streak = the run ending at the latest completed period, if that period is the current or the previous one; otherwise 0</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
@@ -13035,7 +13052,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>BR-R6</t>
+          <t>BR-R5</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -13050,7 +13067,7 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Streaks are derived from the activity log on every read (never stored)</t>
+          <t>One-off tasks: streak = 1 once completed, else 0 (not shown as an active streak)</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -13079,7 +13096,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>BR-R7</t>
+          <t>BR-R6</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -13089,12 +13106,12 @@
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>*Completions* rule progress = total completions of all tagged tasks (all-time)</t>
+          <t>Streaks are derived from the activity log on every read (never stored)</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
@@ -13123,7 +13140,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>BR-R8</t>
+          <t>BR-R7</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -13138,7 +13155,7 @@
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>*Streak* rule progress = the highest current streak among tagged tasks</t>
+          <t>*Completions* rule progress = total completions of all tagged tasks (all-time)</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -13167,7 +13184,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>BR-R9</t>
+          <t>BR-R8</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -13182,7 +13199,7 @@
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>The unlock check runs on task completion, reward creation, reward update and tag change</t>
+          <t>*Streak* rule progress = the highest current streak among tagged tasks</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
@@ -13211,7 +13228,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>BR-R10</t>
+          <t>BR-R9</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -13226,7 +13243,7 @@
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>Status flow locked → unlocked → claimed only; there's no path back</t>
+          <t>The unlock check runs on task completion, reward creation, reward update and tag change</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -13255,7 +13272,7 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>BR-R11</t>
+          <t>BR-R10</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -13270,7 +13287,7 @@
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Unlocked and claimed rewards always show 100 %</t>
+          <t>Status flow locked → unlocked → claimed only; there's no path back</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
@@ -13299,7 +13316,7 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>BR-R12</t>
+          <t>BR-R11</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -13309,12 +13326,12 @@
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>Scope containment. A task is in a reward's scope when the task's area belongs to the reward's tile and, if the reward has an area, the task's area *is* that area</t>
+          <t>Unlocked and claimed rewards always show 100 %</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -13343,7 +13360,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>BR-R13</t>
+          <t>BR-R12</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -13358,7 +13375,7 @@
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Matched tasks. *Selected tasks*: the tagged tasks (all in scope). *All tasks in scope*: every task in scope whose status isn't archived. BR-R7 and BR-R8 compute progress over the matched tasks</t>
+          <t>Scope containment. A task is in a reward's scope when the task's area belongs to the reward's tile and, if the reward has an area, the task's area *is* that area</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
@@ -13387,7 +13404,7 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>BR-R14</t>
+          <t>BR-R13</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -13402,7 +13419,7 @@
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>In *All tasks in scope* mode, tags are ignored for progress (they're kept, so switching back to *Selected tasks* restores them)</t>
+          <t>Matched tasks. *Selected tasks*: the tagged tasks (all in scope). *All tasks in scope*: every task in scope whose status isn't archived. BR-R7 and BR-R8 compute progress over the matched tasks</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -13431,7 +13448,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>BR-R15</t>
+          <t>BR-R14</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -13446,7 +13463,7 @@
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>The unlock check (BR-R9) on completion evaluates every locked reward that matches the completed task, whether tagged or by scope</t>
+          <t>In *All tasks in scope* mode, tags are ignored for progress (they're kept, so switching back to *Selected tasks* restores them)</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
@@ -13475,7 +13492,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>BR-R16</t>
+          <t>BR-R15</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -13490,7 +13507,7 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>A reward marked *Needs a tile* (LLR-4.18) still shows progress from its tags, but can't be edited until a tile is chosen. It never unlocks from tasks outside the tile the user then picks</t>
+          <t>The unlock check (BR-R9) on completion evaluates every locked reward that matches the completed task, whether tagged or by scope</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -13519,7 +13536,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>BR-R17</t>
+          <t>BR-R16</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -13529,12 +13546,12 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>HLR-1</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Tile names are unique ignoring case; area names are unique within their tile ignoring case</t>
+          <t>A reward marked *Needs a tile* (LLR-4.18) still shows progress from its tags, but can't be edited until a tile is chosen. It never unlocks from tasks outside the tile the user then picks</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
@@ -13563,7 +13580,7 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>BR-R18</t>
+          <t>BR-R17</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -13578,7 +13595,7 @@
       </c>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t>Deleting a tile removes everything under it (areas, tasks, completions, rewards scoped to it, notes, contacts, files) in one transaction, after a database snapshot is saved to data/backups/</t>
+          <t>Tile names are unique ignoring case; area names are unique within their tile ignoring case</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -13607,7 +13624,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>BR-R19</t>
+          <t>BR-R18</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -13622,7 +13639,7 @@
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>The starter set only adds tiles and areas whose names are missing; it never renames, merges or deletes</t>
+          <t>Deleting a tile removes everything under it (areas, tasks, completions, rewards scoped to it, notes, contacts, files) in one transaction, after a database snapshot is saved to data/backups/</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
@@ -13651,7 +13668,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>BR-R20</t>
+          <t>BR-R19</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -13661,12 +13678,12 @@
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-1</t>
         </is>
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>Details belong to exactly one owner: a tile or an area. Moving an area to another tile isn't supported, so details never change tile</t>
+          <t>The starter set only adds tiles and areas whose names are missing; it never renames, merges or deletes</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -13695,7 +13712,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>BR-R21</t>
+          <t>BR-R20</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -13710,7 +13727,7 @@
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>The "last executive" of a topic is the *Service executive* or *Technician* contact in that topic with the latest last-visit date; contacts without a date come after dated ones</t>
+          <t>Details belong to exactly one owner: a tile or an area. Moving an area to another tile isn't supported, so details never change tile</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
@@ -13739,7 +13756,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>BR-R22</t>
+          <t>BR-R21</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -13749,17 +13766,17 @@
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>A task is overdue when it's active, has a due date, and the due date is before now. Done and archived tasks are never overdue</t>
+          <t>The "last executive" of a topic is the *Service executive* or *Technician* contact in that topic with the latest last-visit date; contacts without a date come after dated ones</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr">
@@ -13783,7 +13800,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>BR-R23</t>
+          <t>BR-R22</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -13798,7 +13815,7 @@
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Silent means invisible without the passcode: silent tasks, their completions, streaks and activity are excluded from every response to a caller without the owner passcode, including counts and aggregates, so their existence can't be inferred</t>
+          <t>A task is overdue when it's active, has a due date, and the due date is before now. Done and archived tasks are never overdue</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
@@ -13827,7 +13844,7 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>BR-R24</t>
+          <t>BR-R23</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -13842,7 +13859,7 @@
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>Celebrations and share prompts happen only for announced tasks. A reward unlocked by a silent task's completion is unlocked quietly (no share prompt); the reward itself stays visible</t>
+          <t>Silent means invisible without the passcode: silent tasks, their completions, streaks and activity are excluded from every response to a caller without the owner passcode, including counts and aggregates, so their existence can't be inferred</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -13871,7 +13888,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>BR-R25</t>
+          <t>BR-R24</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -13886,7 +13903,7 @@
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>A Milestone completed reward unlocks when every milestone task it matches (tagged, or in scope with *All tasks in scope*) has ≥ 1 completion. Non-milestone tasks tagged to it don't count. Progress = milestones completed ÷ milestones matched</t>
+          <t>Celebrations and share prompts happen only for announced tasks. A reward unlocked by a silent task's completion is unlocked quietly (no share prompt); the reward itself stays visible</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
@@ -13915,7 +13932,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>BR-R26</t>
+          <t>BR-R25</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -13930,7 +13947,7 @@
       </c>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t>Due date and days to complete are never derived from each other or from the frequency</t>
+          <t>A Milestone completed reward unlocks when every milestone task it matches (tagged, or in scope with *All tasks in scope*) has ≥ 1 completion. Non-milestone tasks tagged to it don't count. Progress = milestones completed ÷ milestones matched</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -13959,7 +13976,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>BR-R27</t>
+          <t>BR-R26</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -13969,12 +13986,12 @@
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>An *Idea* has no rule and no progress. It can't unlock or be claimed, and it isn't counted in reward totals or progress on the dashboard (the dashboard shows an *Ideas* count per person)</t>
+          <t>Due date and days to complete are never derived from each other or from the frequency</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
@@ -14003,7 +14020,7 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>BR-R28</t>
+          <t>BR-R27</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -14018,7 +14035,7 @@
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>Turning an idea into a reward requires a rule, a threshold (except *milestone completed*) and a tile (LLR-4.9); the idea's id is kept, so links and photos stay attached</t>
+          <t>An *Idea* has no rule and no progress. It can't unlock or be claimed, and it isn't counted in reward totals or progress on the dashboard (the dashboard shows an *Ideas* count per person)</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -14047,7 +14064,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>BR-R29</t>
+          <t>BR-R28</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -14062,7 +14079,7 @@
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>Closing is only for ideas; a reward that already has a rule is claimed, not closed. Reopening a closed idea returns it to *Idea*</t>
+          <t>Turning an idea into a reward requires a rule, a threshold (except *milestone completed*) and a tile (LLR-4.9); the idea's id is kept, so links and photos stay attached</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
@@ -14091,7 +14108,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>BR-R30</t>
+          <t>BR-R29</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -14106,7 +14123,7 @@
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>*For whom* is a label: it groups and filters rewards, but never changes who can see or edit them (visibility rules decide that)</t>
+          <t>Closing is only for ideas; a reward that already has a rule is claimed, not closed. Reopening a closed idea returns it to *Idea*</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -14135,27 +14152,27 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>NFR-D1</t>
+          <t>BR-R30</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C182" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Remote exposed chunk ≤ 50 KB gzip (now ~11 KB)</t>
+          <t>*For whom* is a label: it groups and filters rewards, but never changes who can see or edit them (visibility rules decide that)</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr">
@@ -14172,14 +14189,14 @@
       <c r="I182" s="8" t="inlineStr"/>
       <c r="J182" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>NFR-D2</t>
+          <t>NFR-D1</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
@@ -14194,7 +14211,7 @@
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>Remote load after navigating to #/rewards ≤ 500 ms locally (measured ~36 ms client-side nav, ~275 ms cold)</t>
+          <t>Remote exposed chunk ≤ 50 KB gzip (now ~11 KB)</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -14223,7 +14240,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>NFR-D3</t>
+          <t>NFR-D2</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
@@ -14238,7 +14255,7 @@
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Dashboard issues ≤ 1 BFF read per window per 30 s</t>
+          <t>Remote load after navigating to #/rewards ≤ 500 ms locally (measured ~36 ms client-side nav, ~275 ms cold)</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
@@ -14267,7 +14284,7 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>NFR-D4</t>
+          <t>NFR-D3</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
@@ -14282,7 +14299,7 @@
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>No horizontal scroll at 375 px width</t>
+          <t>Dashboard issues ≤ 1 BFF read per window per 30 s</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -14311,7 +14328,7 @@
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>NFR-D5</t>
+          <t>NFR-D4</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -14326,7 +14343,7 @@
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Stats for N tasks use one activity query (no N+1)</t>
+          <t>No horizontal scroll at 375 px width</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
@@ -14355,7 +14372,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>NFR-D6</t>
+          <t>NFR-D5</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -14370,7 +14387,7 @@
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>Every business rule BR-R1…R30 has ≥ 1 automated test</t>
+          <t>Stats for N tasks use one activity query (no N+1)</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -14399,7 +14416,7 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>NFR-D7</t>
+          <t>NFR-D6</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -14414,7 +14431,7 @@
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>Naive datetimes never reach storage</t>
+          <t>Every business rule BR-R1…R30 has ≥ 1 automated test</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
@@ -14443,7 +14460,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>NFR-D8</t>
+          <t>NFR-D7</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -14458,7 +14475,7 @@
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>No schema change may delete or rewrite existing rows except as specified (LLR-4.18); every migration has an upgrade test run against a copy of a pre-migration database</t>
+          <t>Naive datetimes never reach storage</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -14487,7 +14504,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>NFR-D9</t>
+          <t>NFR-D8</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -14502,12 +14519,12 @@
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>Uploaded files are stored outside any public web folder with random names, served only through the BFF, and count against a 2 GB soft limit on the droplet (warning shown); moving to object storage later changes no requirement</t>
+          <t>No schema change may delete or rewrite existing rows except as specified (LLR-4.18); every migration has an upgrade test run against a copy of a pre-migration database</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F190" s="8" t="inlineStr">
@@ -14531,7 +14548,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>NFR-D10</t>
+          <t>NFR-D9</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -14546,7 +14563,7 @@
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>Search over notes, contacts and files returns in ≤ 300 ms for 5,000 items</t>
+          <t>Uploaded files are stored outside any public web folder with random names, served only through the BFF, and count against a 2 GB soft limit on the droplet (warning shown); moving to object storage later changes no requirement</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -14575,7 +14592,7 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>NFR-D11</t>
+          <t>NFR-D10</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -14590,7 +14607,7 @@
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>Every read endpoint has a test that a silent task leaves no trace (item, count or aggregate) in its response without the passcode</t>
+          <t>Search over notes, contacts and files returns in ≤ 300 ms for 5,000 items</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
@@ -14616,13 +14633,57 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D11</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C193" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D193" s="8" t="inlineStr">
+        <is>
+          <t>Every read endpoint has a test that a silent task leaves no trace (item, count or aggregate) in its response without the passcode</t>
+        </is>
+      </c>
+      <c r="E193" s="8" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G193" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H193" s="8" t="inlineStr"/>
+      <c r="I193" s="8" t="inlineStr"/>
+      <c r="J193" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J192"/>
+  <autoFilter ref="A4:J193"/>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E392" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E393" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Built &amp; tested,Built (manual test),Planned,Next,Out of scope"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F392" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F393" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Must,Should,Could,Won't (now)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14636,7 +14697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14790,58 +14851,58 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.1, 3.6, 3.7; BR-R2–R4</t>
+          <t>LLR-2.10</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/complete, GET /tasks/{id}/activity, GET /tasks/{id}</t>
+          <t>PATCH /tasks/{id}, DELETE /tasks/{id}</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>test_completions_build_streak_and_activity_log, test_daily_streak, test_weekly_streak</t>
+          <t>test_edit_and_delete_task</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.3–3.5; BR-R4, R5</t>
+          <t>LLR-3.1, 3.6, 3.7; BR-R2–R4</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/complete</t>
+          <t>POST /tasks/{id}/complete, GET /tasks/{id}/activity, GET /tasks/{id}</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>test_completion_rules, test_one_off_streak_is_done_or_not</t>
+          <t>test_completions_build_streak_and_activity_log, test_daily_streak, test_weekly_streak</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.1, 4.2, 4.6, 4.7; BR-R7, R9, R10</t>
+          <t>LLR-3.3–3.5; BR-R4, R5</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>/rewards*</t>
+          <t>POST /tasks/{id}/complete</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>test_reward_unlocks_on_completion_count_then_claim, test_reward_already_met_unlocks_on_create_and_rejects_unknown_tasks, test_completions_rule_progress</t>
+          <t>test_completion_rules, test_one_off_streak_is_done_or_not</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>BR-R8</t>
+          <t>LLR-4.1, 4.2, 4.6, 4.7; BR-R7, R9, R10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -14851,194 +14912,160 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>test_streak_reward_uses_best_current_streak_across_tasks, test_streak_rule_progress</t>
+          <t>test_reward_unlocks_on_completion_count_then_claim, test_reward_already_met_unlocks_on_create_and_rejects_unknown_tasks, test_completions_rule_progress</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>BR-R11</t>
+          <t>BR-R8</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/rewards*</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>test_unlocked_reward_stays_complete_after_streak_breaks</t>
+          <t>test_streak_reward_uses_best_current_streak_across_tasks, test_streak_rule_progress</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.1, 5.9, 5.10</t>
+          <t>BR-R11</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>GET /dashboard/summary</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>test_dashboard_summary_is_flat_snake_case</t>
+          <t>test_unlocked_reward_stays_complete_after_streak_breaks</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.1</t>
+          <t>LLR-5.1, 5.9, 5.10</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>GET /dashboard/summary</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>test_requires_demo_token</t>
+          <t>test_dashboard_summary_is_flat_snake_case</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.x, 5.2–5.8</t>
+          <t>LLR-8.1</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>all</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Manual E2E (browser, 375 px); planned Playwright smoke</t>
+          <t>test_requires_demo_token</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.x</t>
+          <t>LLR-7.x, 5.2–5.8</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>planned: adapter tests with FakeVisionAdapter, fallback tests</t>
+          <t>Manual E2E (browser, 375 px); planned Playwright smoke</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.9–4.11, 4.16; BR-R12</t>
+          <t>LLR-6.x</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>POST/PATCH /rewards, PUT /rewards/{id}/tasks</t>
+          <t>⏳</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>test_reward_scope_validation, test_tagging_outside_scope_rejected, test_narrowing_scope_untags</t>
+          <t>planned: adapter tests with FakeVisionAdapter, fallback tests</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.10; BR-R13–R15</t>
+          <t>LLR-4.9–4.17; LLR-8.7, 8.8</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/complete</t>
+          <t>/rewards*, /rewards/{id}/tasks/{taskId}</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>test_all_in_scope_counts_untagged_and_new_tasks, test_other_tile_never_counts</t>
+          <t>test_reward_needs_only_a_title, test_area_rewards_are_kept_in_an_area_but_link_anywhere, test_link_any_task_to_any_reward, test_linked_task_counts_unlock_the_reward, test_linking_tasks_already_done_enough_unlocks_immediately, test_rewards_outlive_tiles_areas_and_tasks, test_delete_reward_keeps_tasks, test_older_all_tasks_in_area_rewards_keep_counting</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.14, 4.15; LLR-8.8</t>
+          <t>LLR-8.9; NFR-D8</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>GET /areas/{id}/rewards, GET /tasks/{id}</t>
+          <t>startup migrations, app.backup</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>test_area_lists_matching_rewards, test_task_detail_lists_matching_rewards</t>
+          <t>test_models_match_migrations, test_pre_migration_database_is_stamped_not_rebuilt, test_migrate_is_idempotent, test_export_import_round_trip, test_import_refuses_non_empty_target_without_replace</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.17</t>
+          <t>LLR-4.18; BR-R16</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>DELETE /areas/{id}</t>
+          <t>migration 0003_reward_scope</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>test_deleting_area_widens_reward_scope</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>LLR-8.9; NFR-D8</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>startup migrations, app.backup</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>test_models_match_migrations, test_pre_migration_database_is_stamped_not_rebuilt, test_migrate_is_idempotent, test_export_import_round_trip, test_import_refuses_non_empty_target_without_replace</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>LLR-4.18; BR-R16</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>migration 0003_reward_scope</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>test_migration_infers_scope_and_keeps_data (runs against a database at 0002_details), test_needs_a_tile_reward_must_pick_one_first, test_claimed_reward_without_a_tile_can_still_get_one</t>
+          <t>test_migration_infers_scope_and_keeps_data (runs against a database at 0002_details)</t>
         </is>
       </c>
     </row>
@@ -15129,27 +15156,27 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A5,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A5,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A5)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A5)</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A5,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A5,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A5,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A5,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A5,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A5,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A5,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A5,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H5" s="9">
@@ -15164,27 +15191,27 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A6,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A6,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A6)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A6)</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A6,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A6,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A6,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A6,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A6,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A6,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A6,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A6,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H6" s="9">
@@ -15199,27 +15226,27 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A7,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A7,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C7" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A7)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A7)</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A7,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A7,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A7,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A7,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A7,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A7,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A7,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A7,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H7" s="9">
@@ -15234,27 +15261,27 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A8,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A8,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C8" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A8)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A8,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A8,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A8,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A8,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A8,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A8,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A8,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A8,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H8" s="9">
@@ -15269,27 +15296,27 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A9,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A9,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C9" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A9)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A9,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A9,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A9,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A9,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A9,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A9,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A9,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A9,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H9" s="9">
@@ -15304,27 +15331,27 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A10,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A10,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A10)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A10,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A10,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A10,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A10,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A10,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A10,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A10,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A10,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H10" s="9">
@@ -15339,27 +15366,27 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A11,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A11,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A11)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A11,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A11,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A11,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A11,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A11,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A11,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A11,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A11,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H11" s="9">
@@ -15374,27 +15401,27 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A12,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A12,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A12)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A12,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A12,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A12,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A12,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A12,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A12,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A12,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A12,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H12" s="9">
@@ -15409,27 +15436,27 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A13,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A13,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A13)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A13,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A13,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A13,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A13,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A13,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A13,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A13,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A13,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H13" s="9">
@@ -15444,27 +15471,27 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A14,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A14,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A14)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A14,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A14,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A14,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A14,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A14,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A14,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A14,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A14,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H14" s="9">
@@ -15479,27 +15506,27 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A15,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A15,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C15" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A15)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A15)</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A15,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A15,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A15,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A15,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A15,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A15,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A15,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A15,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H15" s="9">
@@ -15514,27 +15541,27 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$392,MATCH(A16,'Requirements Register'!$A$5:$A$392,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A16,'Requirements Register'!$A$5:$A$393,0)),"")</f>
         <v/>
       </c>
       <c r="C16" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$392,A16)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A16)</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A16,'Requirements Register'!$E$5:$E$392,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A16,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A16,'Requirements Register'!$E$5:$E$392,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A16,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A16,'Requirements Register'!$E$5:$E$392,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A16,'Requirements Register'!$E$5:$E$393,"Next")</f>
         <v/>
       </c>
       <c r="G16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$392,A16,'Requirements Register'!$E$5:$E$392,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A16,'Requirements Register'!$E$5:$E$393,"Planned")</f>
         <v/>
       </c>
       <c r="H16" s="9">

--- a/docs/rewards/Rewards_HLRD_LLRD.xlsx
+++ b/docs/rewards/Rewards_HLRD_LLRD.xlsx
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Before HLR-11 build</t>
+          <t>Built with all (HLR-11); revisit after real use</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅ (hiding silent tasks from visitors comes with the passcode)</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>LLR-11 Task planning and visibility (HLR-11) ⏳ next</t>
+          <t>LLR-11 Task planning and visibility (HLR-11) ✅</t>
         </is>
       </c>
     </row>
@@ -4886,7 +4886,7 @@
     <row r="221">
       <c r="A221" s="13" t="inlineStr">
         <is>
-          <t>LLR-11 Task planning and visibility (HLR-11) ⏳ next</t>
+          <t>LLR-11 Task planning and visibility (HLR-11) ✅</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="C223" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4932,12 +4932,12 @@
       </c>
       <c r="B224" s="7" t="inlineStr">
         <is>
-          <t>Milestones show a 🏁 badge on task rows and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
+          <t>Milestones show a 🏁 badge on task rows (area list, Tasks list, Link screen) and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
         </is>
       </c>
       <c r="C224" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C225" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4966,12 +4966,12 @@
       </c>
       <c r="B226" s="7" t="inlineStr">
         <is>
-          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task it matches has at least one completion (BR-R25). Creating one that matches no milestone task is rejected (422)</t>
+          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task linked to it has at least one completion (BR-R25). With no milestone linked yet it shows 0 of 0 and never unlocks (tasks are linked later, on the Link screen)</t>
         </is>
       </c>
       <c r="C226" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="C227" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="C228" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>🟡 🔕 marker and quiet completion built; hiding from visitors comes with the owner passcode (hosting)</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C229" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="C230" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="C231" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="C232" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="C233" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="C234" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="C235" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Milestones show a 🏁 badge on task rows and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
+          <t>Milestones show a 🏁 badge on task rows (area list, Tasks list, Link screen) and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
@@ -12055,12 +12055,12 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task it matches has at least one completion (BR-R25). Creating one that matches no milestone task is rejected (422)</t>
+          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task linked to it has at least one completion (BR-R25). With no milestone linked yet it shows 0 of 0 and never unlocks (tasks are linked later, on the Link screen)</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F175" s="8" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F177" s="8" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr">
@@ -14810,7 +14810,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>⏳ planned: test_task_planning_fields_round_trip, test_overdue_rules, test_milestone_reward_needs_all_milestones, test_silent_tasks_invisible_without_passcode, test_silent_completion_has_no_celebration_flag, test_migration_defaults_existing_tasks</t>
+          <t>test_task_planning_fields_round_trip, test_overdue_rules, test_due_filters_milestones_and_sort, test_milestone_reward_needs_all_milestones, test_dashboard_overdue_and_milestones, test_migration_defaults_existing_tasks; quiet completion and celebrations verified in the browser; ⏳ test_silent_tasks_invisible_without_passcode comes with the passcode</t>
         </is>
       </c>
     </row>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅ (branch; hiding silent tasks from visitors comes with hosting)</t>
         </is>
       </c>
     </row>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/docs/rewards/Rewards_HLRD_LLRD.xlsx
+++ b/docs/rewards/Rewards_HLRD_LLRD.xlsx
@@ -4467,12 +4467,12 @@
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>Rewards accept status: "idea" on create (rule, threshold and tile then optional), forWhom, visibility, link, seenAt (where seen) and a cover image; POST /rewards/{id}/activate (rule, threshold, tile, tasks) turns an idea into a locked reward; POST /rewards/{id}/close with outcome (bought | dropped); GET /rewards filters status=idea|closed and forWhom=</t>
+          <t>POST /rewards accepts status: "idea", forWhom, visibility, link and whereSeen; POST /rewards/{id}/activate (ruleType, threshold), /close (outcome: bought | dropped) and /reopen; PUT / DELETE /rewards/{id}/cover (multipart photo; served by a signed link like files); GET /rewards filters status=idea|closed and forWhom=; GET /rewards-people lists everyone for suggestions; ideas can't be linked or claimed (409)</t>
         </is>
       </c>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
     <row r="254">
       <c r="A254" s="13" t="inlineStr">
         <is>
-          <t>LLR-12 Reward ideas and wishlist (HLR-12) ⏳ next</t>
+          <t>LLR-12 Reward ideas and wishlist (HLR-12) ✅</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
     <row r="257">
       <c r="A257" s="13" t="inlineStr">
         <is>
-          <t>LLR-12 Reward ideas and wishlist (HLR-12) ⏳ next</t>
+          <t>LLR-12 Reward ideas and wishlist (HLR-12) ✅</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="B259" s="7" t="inlineStr">
         <is>
-          <t>Quick capture: a "+ Idea" button on the Rewards tab and on every tile and area screen opens a short form: title (required, 1–200), then optional for whom, notes (≤ 2000), link (URL), cover photo (camera or gallery, via the file rules of LLR-10.7), where seen (e.g. "City library") and tile/area. Saving needs only the title</t>
+          <t>Quick capture: "💡 + Idea" on the Rewards screen and on every area's Rewards tab opens a short form: title (required), for whom (default Me) and a one-tap cover photo (camera or gallery; JPG, PNG, WebP or HEIC up to 10 MB); *More* adds where seen, link, note and (on the Rewards screen) an optional area. Saving needs only the title</t>
         </is>
       </c>
       <c r="C259" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="C260" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="C261" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="B262" s="7" t="inlineStr">
         <is>
-          <t>The Rewards tab has an Ideas filter (and *Closed* for bought or dropped ideas), and can be filtered by for whom, e.g. "Shiragi's ideas and rewards". Tile and area screens list their ideas under "Rewards you can earn here" in a separate *Ideas* group</t>
+          <t>The Rewards screen filters by status (💡 Ideas, Locked, Unlocked, Claimed, Closed) and by for whom (e.g. *Shiragi*), plus search; closed ideas are hidden unless *Closed* is chosen. An area's Rewards tab lists its ideas with its rewards. Ideas are never offered on the Link screen</t>
         </is>
       </c>
       <c r="C262" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="B263" s="7" t="inlineStr">
         <is>
-          <t>Turn into a reward: from an idea, add a rule (N completions, streak of N or milestone completed), a threshold, a tile (and optional area) and tasks. It becomes a normal *locked* reward, keeping its title, photo, link, notes and for whom; the unlock check runs straight away (BR-R28)</t>
+          <t>Turn into reward: on an idea, pick how it unlocks (task count with N, or milestone completed). It becomes a normal *locked* reward with the same id, keeping title, photo, link, note, where seen, area and for whom; tasks are then linked on the Link screen (BR-R28)</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C264" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="C265" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>🟡 private by default with a 🔕 marker; hiding from visitors comes with the owner passcode (hosting)</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="C266" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="C267" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B272" s="7" t="inlineStr">
         <is>
-          <t>Turning an idea into a reward requires a rule, a threshold (except *milestone completed*) and a tile (LLR-4.9); the idea's id is kept, so links and photos stay attached</t>
+          <t>Turning an idea into a reward requires a rule and a threshold (except *milestone completed*); a tile isn't required since rewards stand alone. The idea's id is kept, so links and photos stay attached</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Rewards accept status: "idea" on create (rule, threshold and tile then optional), forWhom, visibility, link, seenAt (where seen) and a cover image; POST /rewards/{id}/activate (rule, threshold, tile, tasks) turns an idea into a locked reward; POST /rewards/{id}/close with outcome (bought | dropped); GET /rewards filters status=idea|closed and forWhom=</t>
+          <t>POST /rewards accepts status: "idea", forWhom, visibility, link and whereSeen; POST /rewards/{id}/activate (ruleType, threshold), /close (outcome: bought | dropped) and /reopen; PUT / DELETE /rewards/{id}/cover (multipart photo; served by a signed link like files); GET /rewards filters status=idea|closed and forWhom=; GET /rewards-people lists everyone for suggestions; ideas can't be linked or claimed (409)</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Quick capture: a "+ Idea" button on the Rewards tab and on every tile and area screen opens a short form: title (required, 1–200), then optional for whom, notes (≤ 2000), link (URL), cover photo (camera or gallery, via the file rules of LLR-10.7), where seen (e.g. "City library") and tile/area. Saving needs only the title</t>
+          <t>Quick capture: "💡 + Idea" on the Rewards screen and on every area's Rewards tab opens a short form: title (required), for whom (default Me) and a one-tap cover photo (camera or gallery; JPG, PNG, WebP or HEIC up to 10 MB); *More* adds where seen, link, note and (on the Rewards screen) an optional area. Saving needs only the title</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>The Rewards tab has an Ideas filter (and *Closed* for bought or dropped ideas), and can be filtered by for whom, e.g. "Shiragi's ideas and rewards". Tile and area screens list their ideas under "Rewards you can earn here" in a separate *Ideas* group</t>
+          <t>The Rewards screen filters by status (💡 Ideas, Locked, Unlocked, Claimed, Closed) and by for whom (e.g. *Shiragi*), plus search; closed ideas are hidden unless *Closed* is chosen. An area's Rewards tab lists its ideas with its rewards. Ideas are never offered on the Link screen</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
@@ -12671,12 +12671,12 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Turn into a reward: from an idea, add a rule (N completions, streak of N or milestone completed), a threshold, a tile (and optional area) and tasks. It becomes a normal *locked* reward, keeping its title, photo, link, notes and for whom; the unlock check runs straight away (BR-R28)</t>
+          <t>Turn into reward: on an idea, pick how it unlocks (task count with N, or milestone completed). It becomes a normal *locked* reward with the same id, keeping title, photo, link, note, where seen, area and for whom; tasks are then linked on the Link screen (BR-R28)</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F179" s="8" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>Turning an idea into a reward requires a rule, a threshold (except *milestone completed*) and a tile (LLR-4.9); the idea's id is kept, so links and photos stay attached</t>
+          <t>Turning an idea into a reward requires a rule and a threshold (except *milestone completed*); a tile isn't required since rewards stand alone. The idea's id is kept, so links and photos stay attached</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F180" s="8" t="inlineStr">
@@ -14128,7 +14128,7 @@
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F181" s="8" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>⏳ planned: test_idea_needs_only_title, test_idea_never_unlocks_or_counts, test_activate_idea_keeps_details_and_evaluates, test_close_and_reopen_idea, test_ideas_silent_by_default, test_filter_by_for_whom, test_migration_defaults_existing_rewards</t>
+          <t>test_idea_needs_only_title, test_ideas_silent_by_default, test_idea_never_unlocks_or_counts, test_activate_idea_keeps_details_and_evaluates, test_close_and_reopen_idea, test_filter_by_for_whom, test_cover_photo_signed_link_and_cleanup, test_ideas_in_search, test_migration_defaults_existing_rewards</t>
         </is>
       </c>
     </row>
@@ -17135,7 +17135,7 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅ (branch; hiding private ideas from visitors comes with hosting)</t>
         </is>
       </c>
     </row>
@@ -17693,7 +17693,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>⏳ next</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/docs/rewards/Rewards_HLRD_LLRD.xlsx
+++ b/docs/rewards/Rewards_HLRD_LLRD.xlsx
@@ -29,7 +29,7 @@
     <sheet name="LLRD 7. Traceability matrix" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements Register'!$A$4:$J$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements Register'!$A$4:$J$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-30 from docs/rewards/HLRD.md and docs/rewards/LLRD.md.</t>
+          <t>Generated 2026-10-02 from docs/rewards/HLRD.md and docs/rewards/LLRD.md.</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1109,6 +1109,13 @@
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>• (HLR-12) At the library, capture the idea "101 Hilarious Jokes" for Shiragi with a cover photo in two taps; later turn it into a reward that unlocks when Shiragi's "Read 20 minutes" task reaches a 7-day streak. The idea stays hidden from the read-only view until then.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>• (HLR-13) Career / Office / Work has areas switched off: opening it shows its tasks straight away ("Connect with Amex Project - BA", "Learning", …), and a new task is added right there with no area to pick.</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C281"/>
+  <dimension ref="A1:C305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -5566,6 +5573,250 @@
       <c r="A281" s="7" t="inlineStr">
         <is>
           <t>• *Given* the Rewards tab filtered to "Shiragi" *then* only her ideas and rewards are shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282"/>
+    <row r="283">
+      <c r="A283" s="13" t="inlineStr">
+        <is>
+          <t>LLR-13 Tiles without areas (HLR-13) ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="12" t="inlineStr">
+        <is>
+          <t>Some tiles have no natural sub-areas (D15). Such a tile holds its tasks, rewards and notes directly. Internally it keeps exactly one hidden area, so tasks, completions, rewards and notes work unchanged; every screen shows the tile in its place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285"/>
+    <row r="286">
+      <c r="A286" s="13" t="inlineStr">
+        <is>
+          <t>LLR-13 Tiles without areas (HLR-13) ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B287" s="6" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C287" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.1</t>
+        </is>
+      </c>
+      <c r="B288" s="7" t="inlineStr">
+        <is>
+          <t>The tile form (new tile and ✎ edit) has a Use areas switch, on by default. POST /categories and PATCH /categories/{id} accept useAreas; every tile in GET /categories returns useAreas, and each area returns hidden</t>
+        </is>
+      </c>
+      <c r="C288" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.2</t>
+        </is>
+      </c>
+      <c r="B289" s="7" t="inlineStr">
+        <is>
+          <t>Switching areas off is only possible while the tile has no areas; otherwise the switch is disabled with "move or delete its N areas first" and the API answers 409 (BR-R31)</t>
+        </is>
+      </c>
+      <c r="C289" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.3</t>
+        </is>
+      </c>
+      <c r="B290" s="7" t="inlineStr">
+        <is>
+          <t>A tile without areas opens straight to Tasks | Rewards | Notes &amp; contacts at #/rewards/c/{tile} (/rewards, /details), with the tile's name, icon and its ✎ / 🗑 buttons. Old links to its hidden area open the tile instead</t>
+        </is>
+      </c>
+      <c r="C290" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.4</t>
+        </is>
+      </c>
+      <c r="B291" s="7" t="inlineStr">
+        <is>
+          <t>Tiles screen shows "N active tasks" without an area count; the Tasks, Rewards and Link screens, area pickers, search results and the dashboard show such tasks and rewards under the tile name alone (e.g. "💼 Career / Office / Work", never "› General")</t>
+        </is>
+      </c>
+      <c r="C291" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.5</t>
+        </is>
+      </c>
+      <c r="B292" s="7" t="inlineStr">
+        <is>
+          <t>No areas can be added to, and the hidden area can't be renamed or deleted on, a tile without areas (409); the starter set never adds areas to it</t>
+        </is>
+      </c>
+      <c r="C292" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.6</t>
+        </is>
+      </c>
+      <c r="B293" s="7" t="inlineStr">
+        <is>
+          <t>Switching areas back on: if the tile holds anything, its hidden area becomes a normal area called General with everything in it; if it's empty, it simply goes</t>
+        </is>
+      </c>
+      <c r="C293" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.7</t>
+        </is>
+      </c>
+      <c r="B294" s="7" t="inlineStr">
+        <is>
+          <t>Move a task: the task's edit form has a *Tile or area* picker (PATCH /tasks/{id} with areaId). Completions, streaks and reward links move with it</t>
+        </is>
+      </c>
+      <c r="C294" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.8</t>
+        </is>
+      </c>
+      <c r="B295" s="7" t="inlineStr">
+        <is>
+          <t>Existing data is kept: migration 0006_tile_without_areas adds areas.hidden (false for every existing area), with a backup first</t>
+        </is>
+      </c>
+      <c r="C295" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="296"/>
+    <row r="297">
+      <c r="A297" s="13" t="inlineStr">
+        <is>
+          <t>Business rules: tiles without areas</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="7" t="inlineStr">
+        <is>
+          <t>BR-R31</t>
+        </is>
+      </c>
+      <c r="B299" s="7" t="inlineStr">
+        <is>
+          <t>A tile either uses areas or holds everything itself, never both. Areas can only be switched off on a tile with no areas, so nothing is hidden or lost by the switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="300"/>
+    <row r="301">
+      <c r="A301" s="13" t="inlineStr">
+        <is>
+          <t>AC-13 (your example)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* Career / Office / Work with areas switched off *when* the user opens it *then* the task list and an *Add a task* form are shown straight away, with no area step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* the Tasks screen *then* those tasks are grouped under "💼 Career / Office / Work", not under an area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* the Fun tile with 2 areas *when* the user edits it *then* *Use areas* can't be switched off and says to move or delete its 2 areas first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* the task "Micro-frontend Rewards Deployment" with 1 completion and a linked reward *when* it's moved to another tile *then* its completion and reward link stay.</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J193"/>
+  <dimension ref="A1:J203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7112,27 +7363,23 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>HNFR-1</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (high level)</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
+          <t>Epic (HLR)</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Usability: Mobile-first; every primary action reachable in ≤ 3 taps from the area screen</t>
+          <t>Tiles without areas: A tile can switch areas off (e.g. Career / Office / Work): it then opens straight to Tasks, Rewards and Notes &amp; contacts, and tasks can be moved between tiles and areas</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -7156,7 +7403,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>HNFR-2</t>
+          <t>HNFR-1</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -7171,7 +7418,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Resilience: No single dependency failure (remote, BFF, AI) blanks the host page</t>
+          <t>Usability: Mobile-first; every primary action reachable in ≤ 3 taps from the area screen</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -7200,7 +7447,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>HNFR-3</t>
+          <t>HNFR-2</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -7215,7 +7462,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Performance: Rewards screen interactive ≤ 2 s on local/broadband; dashboard cached reads</t>
+          <t>Resilience: No single dependency failure (remote, BFF, AI) blanks the host page</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -7244,7 +7491,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>HNFR-4</t>
+          <t>HNFR-3</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -7259,7 +7506,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Security: Secrets server-side only; CORS allow-list; private photo storage</t>
+          <t>Performance: Rewards screen interactive ≤ 2 s on local/broadband; dashboard cached reads</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -7288,7 +7535,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>HNFR-5</t>
+          <t>HNFR-4</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -7303,7 +7550,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Accessibility: WCAG 2.2 AA intent: labels, focus, live regions, contrast, reduced motion</t>
+          <t>Security: Secrets server-side only; CORS allow-list; private photo storage</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -7332,7 +7579,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>HNFR-6</t>
+          <t>HNFR-5</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -7347,7 +7594,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Maintainability: Typed contracts; pure, unit-tested business rules; ≥ 1 test per business rule</t>
+          <t>Accessibility: WCAG 2.2 AA intent: labels, focus, live regions, contrast, reduced motion</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -7376,7 +7623,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>HNFR-7</t>
+          <t>HNFR-6</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -7391,7 +7638,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Portability: HTTP/JSON only between tiers; storage swappable (SQLite → Postgres)</t>
+          <t>Maintainability: Typed contracts; pure, unit-tested business rules; ≥ 1 test per business rule</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -7420,32 +7667,32 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.1</t>
+          <t>HNFR-7</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Functional (LLR)</t>
+          <t>Non-functional (high level)</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>HLR-1</t>
+          <t>Cross-cutting</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Superseded by LLR-1.7 (Q15). Was: on first start the system seeds tiles and areas per Q2</t>
+          <t>Portability: HTTP/JSON only between tiers; storage swappable (SQLite → Postgres)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Out of scope</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -7457,14 +7704,14 @@
       <c r="I29" s="8" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 3. Detailed functional requirements</t>
+          <t>HLRD › 6. High-level requirements</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.2</t>
+          <t>LLR-1.1</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -7479,17 +7726,17 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>The tiles screen shows each tile's icon, name, area count and active task count</t>
+          <t>Superseded by LLR-1.7 (Q15). Was: on first start the system seeds tiles and areas per Q2</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Out of scope</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -7508,7 +7755,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.3</t>
+          <t>LLR-1.2</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -7523,12 +7770,12 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>The user can add an area to a tile. The name is 1–80 characters, trimmed, and unique within the tile ignoring case</t>
+          <t>The tiles screen shows each tile's icon, name, area count and active task count</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -7552,7 +7799,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.4</t>
+          <t>LLR-1.3</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -7567,7 +7814,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>The user can rename an area under the same rules as LLR-1.3</t>
+          <t>The user can add an area to a tile. The name is 1–80 characters, trimmed, and unique within the tile ignoring case</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -7596,7 +7843,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.5</t>
+          <t>LLR-1.4</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -7611,7 +7858,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>The user can delete an area after confirmation. Its tasks, completions, photos and suggestions are removed with it</t>
+          <t>The user can rename an area under the same rules as LLR-1.3</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -7640,7 +7887,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.6</t>
+          <t>LLR-1.5</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -7655,12 +7902,12 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>The confirmation text states how many active tasks will be deleted</t>
+          <t>The user can delete an area after confirmation. Its tasks, completions, photos and suggestions are removed with it</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -7684,7 +7931,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.7</t>
+          <t>LLR-1.6</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -7699,12 +7946,12 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>A new database starts with no tiles. The tiles screen shows "Create your first tile" and an optional Add suggested tiles button. Nothing is seeded automatically</t>
+          <t>The confirmation text states how many active tasks will be deleted</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -7728,7 +7975,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.8</t>
+          <t>LLR-1.7</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -7743,7 +7990,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Add suggested tiles adds the starter set (Career/Office/Work with Learning and Projects; Household with the 13 areas in Q2; Fun with Hobbies and Outings). It only adds tiles and areas whose names don't already exist, so it never duplicates or overwrites anything and can be pressed again safely</t>
+          <t>A new database starts with no tiles. The tiles screen shows "Create your first tile" and an optional Add suggested tiles button. Nothing is seeded automatically</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -7772,7 +8019,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.9</t>
+          <t>LLR-1.8</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -7787,7 +8034,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Create a tile: name 1–40 characters, trimmed, unique ignoring case (409 on duplicate); icon (one emoji, optional, default 📁). New tiles go to the end</t>
+          <t>Add suggested tiles adds the starter set (Career/Office/Work with Learning and Projects; Household with the 13 areas in Q2; Fun with Hobbies and Outings). It only adds tiles and areas whose names don't already exist, so it never duplicates or overwrites anything and can be pressed again safely</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -7816,7 +8063,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.10</t>
+          <t>LLR-1.9</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -7831,7 +8078,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Edit a tile: change its name (same rules) and icon. Areas, tasks, rewards and links keep working, because they refer to the tile's id, not its name</t>
+          <t>Create a tile: name 1–40 characters, trimmed, unique ignoring case (409 on duplicate); icon (one emoji, optional, default 📁). New tiles go to the end</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -7860,7 +8107,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.11</t>
+          <t>LLR-1.10</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -7875,7 +8122,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Reorder tiles, and areas within a tile (move up/down; drag on wider screens). The order is saved and used everywhere, including the dashboard</t>
+          <t>Edit a tile: change its name (same rules) and icon. Areas, tasks, rewards and links keep working, because they refer to the tile's id, not its name</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -7904,7 +8151,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.12</t>
+          <t>LLR-1.11</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -7919,7 +8166,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Delete a tile: the confirmation lists what will be removed (areas, tasks, completions, rewards scoped to it, notes, contacts, files) and requires typing the tile's name. A database snapshot is taken first (BR-R18)</t>
+          <t>Reorder tiles, and areas within a tile (move up/down; drag on wider screens). The order is saved and used everywhere, including the dashboard</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -7948,7 +8195,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>LLR-1.13</t>
+          <t>LLR-1.12</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -7963,7 +8210,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Existing databases keep their current tiles and areas when this ships: the upgrade removes nothing. They become ordinary user-managed tiles that can be edited or deleted</t>
+          <t>Delete a tile: the confirmation lists what will be removed (areas, tasks, completions, rewards scoped to it, notes, contacts, files) and requires typing the tile's name. A database snapshot is taken first (BR-R18)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -7992,7 +8239,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.1</t>
+          <t>LLR-1.13</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -8002,12 +8249,12 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>HLR-2</t>
+          <t>HLR-1</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Create a task with title (1–200 characters, required), notes (≤ 2000), priority (high/medium/low, default medium) and frequency (daily/weekly/one_off, default weekly). Source = manual; status = active; relevance = relevant</t>
+          <t>Existing databases keep their current tiles and areas when this ships: the upgrade removes nothing. They become ordinary user-managed tiles that can be edited or deleted</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -8036,7 +8283,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.2</t>
+          <t>LLR-2.1</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -8051,12 +8298,12 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>After creating a task, the form keeps the chosen priority and frequency for the next entry and clears the title and notes</t>
+          <t>Create a task with title (1–200 characters, required), notes (≤ 2000), priority (high/medium/low, default medium) and frequency (daily/weekly/one_off, default weekly). Source = manual; status = active; relevance = relevant</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -8080,7 +8327,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.3</t>
+          <t>LLR-2.2</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -8095,12 +8342,12 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>An area's task list is sorted by priority (high → low), then by creation time</t>
+          <t>After creating a task, the form keeps the chosen priority and frequency for the next entry and clears the title and notes</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -8124,7 +8371,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.4</t>
+          <t>LLR-2.3</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -8139,7 +8386,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Filter by priority, status and relevance, singly or combined. The default view is status = active</t>
+          <t>An area's task list is sorted by priority (high → low), then by creation time</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -8168,7 +8415,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.5</t>
+          <t>LLR-2.4</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -8183,7 +8430,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Reprioritise from the list (inline select) or from task detail</t>
+          <t>Filter by priority, status and relevance, singly or combined. The default view is status = active</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -8212,7 +8459,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.6</t>
+          <t>LLR-2.5</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -8227,7 +8474,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Change frequency, status (active/done/archived) and relevance from task detail</t>
+          <t>Reprioritise from the list (inline select) or from task detail</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -8256,7 +8503,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.7</t>
+          <t>LLR-2.6</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -8271,12 +8518,12 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>An empty list says "No tasks yet" with the default filter and "No tasks match these filters" otherwise</t>
+          <t>Change frequency, status (active/done/archived) and relevance from task detail</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -8300,7 +8547,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.8</t>
+          <t>LLR-2.7</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -8315,12 +8562,12 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Null values in updates are rejected (422); unknown enum values are rejected (422)</t>
+          <t>An empty list says "No tasks yet" with the default filter and "No tasks match these filters" otherwise</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -8344,7 +8591,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.9</t>
+          <t>LLR-2.8</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -8359,7 +8606,7 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>A cross-area list of active tasks, grouped by area, is available for the reward task picker</t>
+          <t>Null values in updates are rejected (422); unknown enum values are rejected (422)</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -8388,7 +8635,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.10</t>
+          <t>LLR-2.9</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -8403,7 +8650,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Edit a task from task detail (✎): title and notes. Delete a task (🗑) after a confirmation that names its completion count; its completions and reward tags go with it, the rewards themselves stay (DELETE /tasks/{id})</t>
+          <t>A cross-area list of active tasks, grouped by area, is available for the reward task picker</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -8432,7 +8679,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.1</t>
+          <t>LLR-2.10</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -8442,12 +8689,12 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-2</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Complete an active task, optionally with a note (≤ 1000) and a time (completedAt). If no time is given, the time is now</t>
+          <t>Edit a task from task detail (✎): title and notes. Delete a task (🗑) after a confirmation that names its completion count; its completions and reward tags go with it, the rewards themselves stay (DELETE /tasks/{id})</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -8476,7 +8723,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.2</t>
+          <t>LLR-3.1</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -8491,12 +8738,12 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Logging uses a month calendar: days the task was done are marked (with a count when more than once), today is outlined, future days are disabled, and ‹ › move between months. Tap a day, adjust the time (defaults to now), add an optional note and log. A time later than now is clamped to now</t>
+          <t>Complete an active task, optionally with a note (≤ 1000) and a time (completedAt). If no time is given, the time is now</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -8520,7 +8767,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.3</t>
+          <t>LLR-3.2</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -8535,12 +8782,12 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>A completion more than 1 minute in the future is rejected (422)</t>
+          <t>Logging uses a month calendar: days the task was done are marked (with a count when more than once), today is outlined, future days are disabled, and ‹ › move between months. Tap a day, adjust the time (defaults to now), add an optional note and log. A time later than now is clamped to now</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -8564,7 +8811,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.4</t>
+          <t>LLR-3.3</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -8579,7 +8826,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Completing a one-off task sets it to done. Further completions are rejected (409)</t>
+          <t>A completion more than 1 minute in the future is rejected (422)</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -8608,7 +8855,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.5</t>
+          <t>LLR-3.4</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -8623,7 +8870,7 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Completing a done or archived task is rejected with a message naming its status (409)</t>
+          <t>Completing a one-off task sets it to done. Further completions are rejected (409)</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -8652,7 +8899,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.6</t>
+          <t>LLR-3.5</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -8667,7 +8914,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>The activity log lists completions newest first, with local date/time and note</t>
+          <t>Completing a done or archived task is rejected with a message naming its status (409)</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -8696,7 +8943,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.7</t>
+          <t>LLR-3.6</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -8711,7 +8958,7 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Each task shows completion count, current streak, best streak and last completion time</t>
+          <t>The activity log lists completions newest first, with local date/time and note</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -8740,7 +8987,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.8</t>
+          <t>LLR-3.7</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -8755,12 +9002,12 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>The area list offers a one-tap ✓ complete (now) for active tasks</t>
+          <t>Each task shows completion count, current streak, best streak and last completion time</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -8784,7 +9031,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.1</t>
+          <t>LLR-3.8</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -8794,17 +9041,17 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Create a reward: title (1–200, required), description (≤ 2000), image URL (≤ 500, optional), rule type (completions or streak), threshold N (1–365), tagged tasks (optional)</t>
+          <t>The area list offers a one-tap ✓ complete (now) for active tasks</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -8828,7 +9075,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.2</t>
+          <t>LLR-4.1</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -8843,7 +9090,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Tag or untag tasks as a full replacement of the set. Unknown task ids are rejected (422)</t>
+          <t>Create a reward: title (1–200, required), description (≤ 2000), image URL (≤ 500, optional), rule type (completions or streak), threshold N (1–365), tagged tasks (optional)</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -8872,7 +9119,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.3</t>
+          <t>LLR-4.2</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -8887,12 +9134,12 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Tag a task to a locked reward from the task detail screen</t>
+          <t>Tag or untag tasks as a full replacement of the set. Unknown task ids are rejected (422)</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -8916,7 +9163,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.4</t>
+          <t>LLR-4.3</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -8931,12 +9178,12 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Show each reward's rule text, progress (current / target, %), status and tagged tasks</t>
+          <t>Tag a task to a locked reward from the task detail screen</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -8960,7 +9207,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.5</t>
+          <t>LLR-4.4</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -8975,7 +9222,7 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Filter the rewards list by status</t>
+          <t>Show each reward's rule text, progress (current / target, %), status and tagged tasks</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -9004,7 +9251,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.6</t>
+          <t>LLR-4.5</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -9019,7 +9266,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Claim is only possible when the status is unlocked. Claiming a locked reward is rejected (409). Claiming an already claimed reward changes nothing</t>
+          <t>Filter the rewards list by status</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -9048,7 +9295,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.7</t>
+          <t>LLR-4.6</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -9063,7 +9310,7 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>When a completion unlocks a reward, the completion response includes it and the UI shows a celebration toast</t>
+          <t>Claim is only possible when the status is unlocked. Claiming a locked reward is rejected (409). Claiming an already claimed reward changes nothing</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -9092,7 +9339,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.8</t>
+          <t>LLR-4.7</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -9107,12 +9354,12 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Editing a reward's tasks is only offered while it's locked</t>
+          <t>When a completion unlocks a reward, the completion response includes it and the UI shows a celebration toast</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -9136,7 +9383,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.9</t>
+          <t>LLR-4.8</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -9146,17 +9393,17 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Rewards stand alone. A reward needs only a title and N (default 5); a note and picture link are optional. It can optionally be kept in an area (to organise it; its tile comes from the area), but that never limits which tasks it can be linked to</t>
+          <t>Editing a reward's tasks is only offered while it's locked</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -9180,7 +9427,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.10</t>
+          <t>LLR-4.9</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -9195,7 +9442,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Links are many-to-many and unrestricted: any task (from any tile or area) can be linked to any reward; one task can count for several rewards. Unlock rule for now: task count, the linked tasks done N times in total. (Older rewards that counted "all tasks in an area" keep working)</t>
+          <t>Rewards stand alone. A reward needs only a title and N (default 5); a note and picture link are optional. It can optionally be kept in an area (to organise it; its tile comes from the area), but that never limits which tasks it can be linked to</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -9224,7 +9471,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.11</t>
+          <t>LLR-4.10</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -9239,7 +9486,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Linking twice is harmless; unlinking an unlocked or claimed reward doesn't lock it again (BR-R10); deleting a task, area or tile removes only its links, and rewards stay. Deleting a tile does delete rewards kept in it (BR-R18)</t>
+          <t>Links are many-to-many and unrestricted: any task (from any tile or area) can be linked to any reward; one task can count for several rewards. Unlock rule for now: task count, the linked tasks done N times in total. (Older rewards that counted "all tasks in an area" keep working)</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -9268,7 +9515,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.12</t>
+          <t>LLR-4.11</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -9283,7 +9530,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>The Link screen (#/rewards/link, top menu *Link*) lists all tasks (grouped by tile › area, with how often each was done and how many rewards it counts for) and all rewards (with area, N and status), each searchable. Pick a task and a reward, then Link (or Unlink if they already are). *Current links* lists each linked reward with its tasks, each with ✕ to unlink. Opens with a task or reward already picked from the task or reward screens</t>
+          <t>Linking twice is harmless; unlinking an unlocked or claimed reward doesn't lock it again (BR-R10); deleting a task, area or tile removes only its links, and rewards stay. Deleting a tile does delete rewards kept in it (BR-R18)</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -9312,7 +9559,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.13</t>
+          <t>LLR-4.12</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -9327,7 +9574,7 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>The top menu is Tiles | Tasks | Rewards | Link. *Tasks* lists every task grouped by tile › area (status filter, default Active; search; each row shows frequency, completions, streak 🔥 and rewards 🎁, with a quick ✓). *Rewards* lists every reward grouped by the area it's kept in (tile › area order, *Not in an area* last; status filter; search; + New with an optional area). The Link screen's two lists use the same grouping. A tile shows only its areas; an area has tabs Tasks | Rewards | Notes &amp; contacts, and its Rewards tab lists and adds the rewards kept there but doesn't link tasks</t>
+          <t>The Link screen (#/rewards/link, top menu *Link*) lists all tasks (grouped by tile › area, with how often each was done and how many rewards it counts for) and all rewards (with area, N and status), each searchable. Pick a task and a reward, then Link (or Unlink if they already are). *Current links* lists each linked reward with its tasks, each with ✕ to unlink. Opens with a task or reward already picked from the task or reward screens</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
@@ -9356,7 +9603,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.14</t>
+          <t>LLR-4.13</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -9371,7 +9618,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>A reward's screen (#/rewards/r/{id}) shows its rule, progress and linked tasks (✕ to unlink), *+ Link tasks* (Link screen with this reward picked), *Claim 🎁* when unlocked, and ✎ / 🗑 to edit (title, N while locked, area, note, picture) or delete it (tasks and history stay)</t>
+          <t>The top menu is Tiles | Tasks | Rewards | Link. *Tasks* lists every task grouped by tile › area (status filter, default Active; search; each row shows frequency, completions, streak 🔥 and rewards 🎁, with a quick ✓). *Rewards* lists every reward grouped by the area it's kept in (tile › area order, *Not in an area* last; status filter; search; + New with an optional area). The Link screen's two lists use the same grouping. A tile shows only its areas; an area has tabs Tasks | Rewards | Notes &amp; contacts, and its Rewards tab lists and adds the rewards kept there but doesn't link tasks</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -9400,7 +9647,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.15</t>
+          <t>LLR-4.14</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9415,7 +9662,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>On task detail, the *Rewards* card lists the rewards the task counts for (links to each reward) and *+ Link to a reward* opens the Link screen with this task picked</t>
+          <t>A reward's screen (#/rewards/r/{id}) shows its rule, progress and linked tasks (✕ to unlink), *+ Link tasks* (Link screen with this reward picked), *Claim 🎁* when unlocked, and ✎ / 🗑 to edit (title, N while locked, area, note, picture) or delete it (tasks and history stay)</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -9444,7 +9691,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.16</t>
+          <t>LLR-4.15</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -9459,7 +9706,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>N can be changed only while the reward is locked; lowering it re-checks the rule at once. A reward whose linked tasks already meet N unlocks as soon as it's linked</t>
+          <t>On task detail, the *Rewards* card lists the rewards the task counts for (links to each reward) and *+ Link to a reward* opens the Link screen with this task picked</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -9488,7 +9735,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.17</t>
+          <t>LLR-4.16</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9503,7 +9750,7 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Moving a reward to another area, or out of any area, never changes its links</t>
+          <t>N can be changed only while the reward is locked; lowering it re-checks the rule at once. A reward whose linked tasks already meet N unlocks as soon as it's linked</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -9532,7 +9779,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.18</t>
+          <t>LLR-4.17</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -9547,7 +9794,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Existing rewards are migrated without data loss (schema migration with automatic pre-upgrade backup): if all tagged tasks share one area, scope = that area; else if they share one tile, scope = that tile; otherwise (no tags, or tags across tiles) the reward keeps its tags and is marked *Needs a tile* until the user picks one. No reward, tag, completion or status is deleted</t>
+          <t>Moving a reward to another area, or out of any area, never changes its links</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -9576,7 +9823,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.1</t>
+          <t>LLR-4.18</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9586,12 +9833,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>HLR-5</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Reads only GET /dashboard/summary; never the database</t>
+          <t>Existing rewards are migrated without data loss (schema migration with automatic pre-upgrade backup): if all tagged tasks share one area, scope = that area; else if they share one tile, scope = that tile; otherwise (no tags, or tags across tiles) the reward keeps its tags and is marked *Needs a tile* until the user picks one. No reward, tag, completion or status is deleted</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -9620,7 +9867,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.2</t>
+          <t>LLR-5.1</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -9635,12 +9882,12 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>KPIs: completions (window), active tasks, active streaks, unlocked + claimed rewards, AI acceptance rate (— when undefined)</t>
+          <t>Reads only GET /dashboard/summary; never the database</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
@@ -9664,7 +9911,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.3</t>
+          <t>LLR-5.2</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9679,7 +9926,7 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Charts: completions by tile, by area (filterable by tile) and per day (empty days shown as gaps). Hover tooltips on every mark</t>
+          <t>KPIs: completions (window), active tasks, active streaks, unlocked + claimed rewards, AI acceptance rate (— when undefined)</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -9708,7 +9955,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.4</t>
+          <t>LLR-5.3</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -9723,7 +9970,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Tables: active streaks (filterable by tile); reward progress with a progress bar</t>
+          <t>Charts: completions by tile, by area (filterable by tile) and per day (empty days shown as gaps). Hover tooltips on every mark</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -9752,7 +9999,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.5</t>
+          <t>LLR-5.4</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -9767,7 +10014,7 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Filters: window (7/30/90 days/all time) and tile. They survive reruns (session_state)</t>
+          <t>Tables: active streaks (filterable by tile); reward progress with a progress bar</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -9796,7 +10043,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.6</t>
+          <t>LLR-5.5</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -9811,7 +10058,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Responses are cached 30 s per window. *Refresh now* clears the cache</t>
+          <t>Filters: window (7/30/90 days/all time) and tile. They survive reruns (session_state)</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -9840,7 +10087,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.7</t>
+          <t>LLR-5.6</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -9855,7 +10102,7 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Unlocked rewards can be claimed from the dashboard. After claiming, the cache is cleared and the page shows fresh data</t>
+          <t>Responses are cached 30 s per window. *Refresh now* clears the cache</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -9884,7 +10131,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.8</t>
+          <t>LLR-5.7</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -9899,7 +10146,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>If the BFF is unreachable, show the error and *Try again* (no stack traces)</t>
+          <t>Unlocked rewards can be claimed from the dashboard. After claiming, the cache is cleared and the page shows fresh data</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -9928,7 +10175,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.9</t>
+          <t>LLR-5.8</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -9943,12 +10190,12 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Streaks and rewards ignore the window; completion aggregates respect it</t>
+          <t>If the BFF is unreachable, show the error and *Try again* (no stack traces)</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -9972,7 +10219,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.10</t>
+          <t>LLR-5.9</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -9987,7 +10234,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Summary payload is flat snake_case records; React endpoints are camelCase (per-client shaping)</t>
+          <t>Streaks and rewards ignore the window; completion aggregates respect it</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -10016,7 +10263,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.11</t>
+          <t>LLR-5.10</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -10031,12 +10278,12 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Reward progress rows include the reward's tile and area; the dashboard's tile filter applies to rewards as well as completions and streaks</t>
+          <t>Summary payload is flat snake_case records; React endpoints are camelCase (per-client shaping)</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -10060,7 +10307,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.1</t>
+          <t>LLR-5.11</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -10070,22 +10317,22 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>HLR-6</t>
+          <t>HLR-5</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Attach 1–5 photos per run to an area (JPEG/PNG/WebP, ≤ 5 MB each; type checked by content, not extension)</t>
+          <t>Reward progress rows include the reward's tile and area; the dashboard's tile filter applies to rewards as well as completions and streaks</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
@@ -10104,7 +10351,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.2</t>
+          <t>LLR-6.1</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -10119,7 +10366,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Photos are stored privately with random names and are never publicly addressable</t>
+          <t>Attach 1–5 photos per run to an area (JPEG/PNG/WebP, ≤ 5 MB each; type checked by content, not extension)</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -10148,7 +10395,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.3</t>
+          <t>LLR-6.2</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -10163,7 +10410,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Starting a suggestion run returns immediately (202) with a run id; the UI shows a loading state</t>
+          <t>Photos are stored privately with random names and are never publicly addressable</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -10192,7 +10439,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.4</t>
+          <t>LLR-6.3</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -10207,7 +10454,7 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>While a run is in progress, the manual *Add a task* form stays fully usable</t>
+          <t>Starting a suggestion run returns immediately (202) with a run id; the UI shows a loading state</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -10236,7 +10483,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.5</t>
+          <t>LLR-6.4</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -10251,7 +10498,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Each suggestion has a title (≤ 200), why (≤ 500), priority and frequency, validated against a strict schema</t>
+          <t>While a run is in progress, the manual *Add a task* form stays fully usable</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -10280,7 +10527,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.6</t>
+          <t>LLR-6.5</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10295,7 +10542,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>The user marks each suggestion Relevant / Not relevant / Ignore. Relevant creates a task with source = ai. A decision is final (409 on re-decide)</t>
+          <t>Each suggestion has a title (≤ 200), why (≤ 500), priority and frequency, validated against a strict schema</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -10324,7 +10571,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.7</t>
+          <t>LLR-6.6</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -10339,7 +10586,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>On timeout (30 s), invalid output or missing API key: retry once where sensible, then show "AI suggestions unavailable, add tasks manually". The page never breaks</t>
+          <t>The user marks each suggestion Relevant / Not relevant / Ignore. Relevant creates a task with source = ai. A decision is final (409 on re-decide)</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -10368,7 +10615,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.8</t>
+          <t>LLR-6.7</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -10383,7 +10630,7 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>The API key exists only in BFF environment variables</t>
+          <t>On timeout (30 s), invalid output or missing API key: retry once where sensible, then show "AI suggestions unavailable, add tasks manually". The page never breaks</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -10412,7 +10659,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.9</t>
+          <t>LLR-6.8</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -10427,7 +10674,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Decisions feed the dashboard acceptance rate (relevant ÷ decided)</t>
+          <t>The API key exists only in BFF environment variables</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -10456,7 +10703,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.1</t>
+          <t>LLR-6.9</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -10466,22 +10713,22 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>HLR-7</t>
+          <t>HLR-6</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>The MFE is built separately and exposes ./RewardsApp via remoteEntry.js</t>
+          <t>Decisions feed the dashboard acceptance rate (relevant ÷ decided)</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
@@ -10500,7 +10747,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.2</t>
+          <t>LLR-7.1</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -10515,12 +10762,12 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>The host mounts it on #/rewards and every #/rewards/*. The nav item stays active on sub-routes</t>
+          <t>The MFE is built separately and exposes ./RewardsApp via remoteEntry.js</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
@@ -10544,7 +10791,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.3</t>
+          <t>LLR-7.2</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -10559,7 +10806,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Host and remote share one React instance; the remote bundles no React</t>
+          <t>The host mounts it on #/rewards and every #/rewards/*. The nav item stays active on sub-routes</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -10588,7 +10835,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.4</t>
+          <t>LLR-7.3</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -10603,7 +10850,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>If the remote fails to load, the host shows "Rewards is unavailable right now" and a reload button. Other pages are unaffected</t>
+          <t>Host and remote share one React instance; the remote bundles no React</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -10632,7 +10879,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.5</t>
+          <t>LLR-7.4</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -10647,7 +10894,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>MFE styles are scoped (.rw-app) and don't alter host styles</t>
+          <t>If the remote fails to load, the host shows "Rewards is unavailable right now" and a reload button. Other pages are unaffected</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -10676,7 +10923,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.6</t>
+          <t>LLR-7.5</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -10691,12 +10938,12 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>The remote URL is configurable per environment (VITE_REWARDS_REMOTE_URL)</t>
+          <t>MFE styles are scoped (.rw-app) and don't alter host styles</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -10720,7 +10967,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.7</t>
+          <t>LLR-7.6</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -10735,12 +10982,12 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>The MFE runs standalone for development (npm run dev)</t>
+          <t>The remote URL is configurable per environment (VITE_REWARDS_REMOTE_URL)</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
@@ -10764,7 +11011,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.8</t>
+          <t>LLR-7.7</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -10779,7 +11026,7 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Every screen has loading, error (with retry) and empty states</t>
+          <t>The MFE runs standalone for development (npm run dev)</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -10808,7 +11055,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.1</t>
+          <t>LLR-7.8</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -10818,17 +11065,17 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>HLR-8</t>
+          <t>HLR-7</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Every endpoint except /health needs Authorization: Bearer &lt;demo token&gt;; otherwise 401</t>
+          <t>Every screen has loading, error (with retry) and empty states</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
@@ -10852,7 +11099,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.2</t>
+          <t>LLR-8.1</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -10867,7 +11114,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>CORS allows only the configured origins</t>
+          <t>Every endpoint except /health needs Authorization: Bearer &lt;demo token&gt;; otherwise 401</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -10896,7 +11143,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.3</t>
+          <t>LLR-8.2</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -10911,7 +11158,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>OpenAPI documentation is served at /docs</t>
+          <t>CORS allows only the configured origins</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -10940,7 +11187,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.4</t>
+          <t>LLR-8.3</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -10955,7 +11202,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Errors use {detail} with status codes 401, 404, 409 and 422 as catalogued in LLD §3.3</t>
+          <t>OpenAPI documentation is served at /docs</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -10984,7 +11231,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.5</t>
+          <t>LLR-8.4</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -10999,7 +11246,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Request bodies accept camelCase or snake_case. React responses are camelCase; dashboard responses are snake_case</t>
+          <t>Errors use {detail} with status codes 401, 404, 409 and 422 as catalogued in LLD §3.3</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -11028,7 +11275,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.6</t>
+          <t>LLR-8.5</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -11043,7 +11290,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Timestamps are ISO-8601 UTC in responses</t>
+          <t>Request bodies accept camelCase or snake_case. React responses are camelCase; dashboard responses are snake_case</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -11072,7 +11319,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.7</t>
+          <t>LLR-8.6</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -11082,12 +11329,12 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-8</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>POST /rewards needs only title (optional threshold = N, default 5, areaId, description, imageUrl, taskIds). GET /rewards (?status=, ?areaId=), GET / PATCH / DELETE /rewards/{id} (PATCH edits title, N, note, picture, areaId or null). POST / DELETE /rewards/{id}/tasks/{taskId} link and unlink one task; PUT /rewards/{id}/tasks replaces all links. Responses include the optional categoryId, categoryName, categoryIcon, areaId, areaName, plus tasks, connected and matchedTaskCount</t>
+          <t>Timestamps are ISO-8601 UTC in responses</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -11116,7 +11363,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.8</t>
+          <t>LLR-8.7</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -11131,7 +11378,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Task detail's rewards lists every reward the task counts for, with how (tagged = linked, or scope for older all-tasks-in-an-area rewards)</t>
+          <t>POST /rewards needs only title (optional threshold = N, default 5, areaId, description, imageUrl, taskIds). GET /rewards (?status=, ?areaId=), GET / PATCH / DELETE /rewards/{id} (PATCH edits title, N, note, picture, areaId or null). POST / DELETE /rewards/{id}/tasks/{taskId} link and unlink one task; PUT /rewards/{id}/tasks replaces all links. Responses include the optional categoryId, categoryName, categoryIcon, areaId, areaName, plus tasks, connected and matchedTaskCount</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -11160,7 +11407,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.9</t>
+          <t>LLR-8.8</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -11170,12 +11417,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>HLR-8</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Schema changes are applied by versioned migrations on startup, never by dropping and recreating tables; a backup of the database file is written before each upgrade (Q14)</t>
+          <t>Task detail's rewards lists every reward the task counts for, with how (tagged = linked, or scope for older all-tasks-in-an-area rewards)</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -11204,7 +11451,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.10</t>
+          <t>LLR-8.9</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -11214,12 +11461,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>HLR-1</t>
+          <t>HLR-8</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Tile endpoints: POST /categories, PATCH /categories/{id} (name, icon), DELETE /categories/{id}, PUT /categories/order and PUT /categories/{id}/areas/order, POST /categories/starter (LLR-1.8, returns what was added)</t>
+          <t>Schema changes are applied by versioned migrations on startup, never by dropping and recreating tables; a backup of the database file is written before each upgrade (Q14)</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -11248,7 +11495,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.11</t>
+          <t>LLR-8.10</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -11258,12 +11505,12 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-1</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Details endpoints for both owners (/categories/{id} and /areas/{id}): …/details (grouped by topic), …/notes, …/contacts, …/files (multipart upload); PATCH/DELETE on /notes/{id}, /contacts/{id}, /files/{id}; GET /files/{id}/download; GET /search?q=</t>
+          <t>Tile endpoints: POST /categories, PATCH /categories/{id} (name, icon), DELETE /categories/{id}, PUT /categories/order and PUT /categories/{id}/areas/order, POST /categories/starter (LLR-1.8, returns what was added)</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -11292,7 +11539,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.12</t>
+          <t>LLR-8.11</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -11302,12 +11549,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Task create/update accept isMilestone, visibility (announced | silent), dueAt (ISO date-time, optional) and targetDays (optional); GET /areas/{id}/tasks adds filters milestone=true and due=overdue|today|week and sort=due. Responses served without the passcode omit silent tasks entirely (BR-R23)</t>
+          <t>Details endpoints for both owners (/categories/{id} and /areas/{id}): …/details (grouped by topic), …/notes, …/contacts, …/files (multipart upload); PATCH/DELETE on /notes/{id}, /contacts/{id}, /files/{id}; GET /files/{id}/download; GET /search?q=</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -11336,7 +11583,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.13</t>
+          <t>LLR-8.12</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -11346,12 +11593,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>POST /rewards accepts status: "idea", forWhom, visibility, link and whereSeen; POST /rewards/{id}/activate (ruleType, threshold), /close (outcome: bought | dropped) and /reopen; PUT / DELETE /rewards/{id}/cover (multipart photo; served by a signed link like files); GET /rewards filters status=idea|closed and forWhom=; GET /rewards-people lists everyone for suggestions; ideas can't be linked or claimed (409)</t>
+          <t>Task create/update accept isMilestone, visibility (announced | silent), dueAt (ISO date-time, optional) and targetDays (optional); GET /areas/{id}/tasks adds filters milestone=true and due=overdue|today|week and sort=due. Responses served without the passcode omit silent tasks entirely (BR-R23)</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -11380,7 +11627,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.1</t>
+          <t>LLR-8.13</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -11390,12 +11637,12 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>The area screen has a Notes &amp; contacts tab (tiles no longer have their own tabs; older tile-level items stay stored and searchable) next to their main content. It lists topics as groups (items without a topic under "General"), each showing its contacts, files and notes</t>
+          <t>POST /rewards accepts status: "idea", forWhom, visibility, link and whereSeen; POST /rewards/{id}/activate (ruleType, threshold), /close (outcome: bought | dropped) and /reopen; PUT / DELETE /rewards/{id}/cover (multipart photo; served by a signed link like files); GET /rewards filters status=idea|closed and forWhom=; GET /rewards-people lists everyone for suggestions; ideas can't be linked or claimed (409)</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -11424,7 +11671,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.2</t>
+          <t>LLR-10.1</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -11439,7 +11686,7 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Topic is free text (1–60 characters), optional, and offers existing topics from the same tile or area as suggestions, so "Bosch Dishwasher" isn't typed three different ways</t>
+          <t>The area screen has a Notes &amp; contacts tab (tiles no longer have their own tabs; older tile-level items stay stored and searchable) next to their main content. It lists topics as groups (items without a topic under "General"), each showing its contacts, files and notes</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -11468,7 +11715,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.3</t>
+          <t>LLR-10.2</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -11483,7 +11730,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Contact: name (required, 1–80); organisation or brand (e.g. Bosch, Kent, IFB, LG); role (*Customer care*, *Service executive*, *Technician*, *Vendor or shop*, *Other*); up to 3 phone numbers with labels (mobile, toll-free, WhatsApp); email; website; last visit or contact date; notes (≤ 1000); topic</t>
+          <t>Topic is free text (1–60 characters), optional, and offers existing topics from the same tile or area as suggestions, so "Bosch Dishwasher" isn't typed three different ways</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -11512,7 +11759,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.4</t>
+          <t>LLR-10.3</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -11527,7 +11774,7 @@
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Phone numbers are stored as entered and shown with actions: Call (tel:), WhatsApp (wa.me, for numbers marked WhatsApp) and Copy. Email gets Email (mailto:). All actions are one tap on a phone</t>
+          <t>Contact: name (required, 1–80); organisation or brand (e.g. Bosch, Kent, IFB, LG); role (*Customer care*, *Service executive*, *Technician*, *Vendor or shop*, *Other*); up to 3 phone numbers with labels (mobile, toll-free, WhatsApp); email; website; last visit or contact date; notes (≤ 1000); topic</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
@@ -11556,7 +11803,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.5</t>
+          <t>LLR-10.4</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -11571,7 +11818,7 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Past executives: within a topic, contacts with the role *Service executive* or *Technician* are listed newest last-visit first. The topic header shows the last executive (name, date, call button)</t>
+          <t>Phone numbers are stored as entered and shown with actions: Call (tel:), WhatsApp (wa.me, for numbers marked WhatsApp) and Copy. Email gets Email (mailto:). All actions are one tap on a phone</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -11600,7 +11847,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.6</t>
+          <t>LLR-10.5</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -11615,7 +11862,7 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Note: text 1–5000 characters, optional title and topic; shows created and last-edited time; newest first</t>
+          <t>Past executives: within a topic, contacts with the role *Service executive* or *Technician* are listed newest last-visit first. The topic header shows the last executive (name, date, call button)</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
@@ -11644,7 +11891,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.7</t>
+          <t>LLR-10.6</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -11659,7 +11906,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>File (bills, invoices, warranty cards, manuals): PDF, JPG, PNG, WebP or HEIC, up to 10 MB each, checked by content; title (required), optional date, amount (₹) and topic. Files open in the browser or download; images show a thumbnail</t>
+          <t>Note: text 1–5000 characters, optional title and topic; shows created and last-edited time; newest first</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -11688,7 +11935,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.8</t>
+          <t>LLR-10.7</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -11703,7 +11950,7 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Notes, contacts and files can be edited and deleted (with confirmation), and moved between topics by editing the topic</t>
+          <t>File (bills, invoices, warranty cards, manuals): PDF, JPG, PNG, WebP or HEIC, up to 10 MB each, checked by content; title (required), optional date, amount (₹) and topic. Files open in the browser or download; images show a thumbnail</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
@@ -11732,7 +11979,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.9</t>
+          <t>LLR-10.8</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -11747,7 +11994,7 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Search across every tile and area by contact name, organisation, topic, phone digits (spaces and dashes ignored), note text and file title. Results show where each hit lives (e.g. "Household › Kitchen › Bosch Dishwasher") and link to it</t>
+          <t>Notes, contacts and files can be edited and deleted (with confirmation), and moved between topics by editing the topic</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -11776,7 +12023,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.10</t>
+          <t>LLR-10.9</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -11791,7 +12038,7 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Deleting an area or tile deletes its notes, contacts and files, and the confirmation counts them (LLR-1.12). Stored files are removed only after the database change commits</t>
+          <t>Search across every tile and area by contact name, organisation, topic, phone digits (spaces and dashes ignored), note text and file title. Results show where each hit lives (e.g. "Household › Kitchen › Bosch Dishwasher") and link to it</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
@@ -11820,7 +12067,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.11</t>
+          <t>LLR-10.10</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -11835,7 +12082,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>Visibility follows the rewards setting (Q17): readable in the read-only view when public reads are on; creating, editing, deleting and uploading need the owner passcode</t>
+          <t>Deleting an area or tile deletes its notes, contacts and files, and the confirmation counts them (LLR-1.12). Stored files are removed only after the database change commits</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -11864,7 +12111,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.12</t>
+          <t>LLR-10.11</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -11879,12 +12126,12 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>The JSON export (app.backup) includes notes and contacts, and lists files by title and stored name; the server backup covers the files folder as well as the database</t>
+          <t>Visibility follows the rewards setting (Q17): readable in the read-only view when public reads are on; creating, editing, deleting and uploading need the owner passcode</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
@@ -11908,7 +12155,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.1</t>
+          <t>LLR-10.12</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -11918,17 +12165,17 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>Milestone: yes/no (default no), set when creating or editing a task</t>
+          <t>The JSON export (app.backup) includes notes and contacts, and lists files by title and stored name; the server backup covers the files folder as well as the database</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
@@ -11952,7 +12199,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.2</t>
+          <t>LLR-11.1</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -11967,7 +12214,7 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Milestones show a 🏁 badge on task rows (area list, Tasks list, Link screen) and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
+          <t>Milestone: yes/no (default no), set when creating or editing a task</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
@@ -11996,7 +12243,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.3</t>
+          <t>LLR-11.2</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -12011,7 +12258,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Completing an announced milestone shows the milestone celebration: a larger, longer celebration than a normal completion (respects reduced motion), with its own share prompt</t>
+          <t>Milestones show a 🏁 badge on task rows (area list, Tasks list, Link screen) and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -12040,7 +12287,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.4</t>
+          <t>LLR-11.3</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -12055,7 +12302,7 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task linked to it has at least one completion (BR-R25). With no milestone linked yet it shows 0 of 0 and never unlocks (tasks are linked later, on the Link screen)</t>
+          <t>Completing an announced milestone shows the milestone celebration: a larger, longer celebration than a normal completion (respects reduced motion), with its own share prompt</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
@@ -12084,7 +12331,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.5</t>
+          <t>LLR-11.4</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -12099,7 +12346,7 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Announce or keep silent: each task is *Announced* (default) or *Silent*, set when creating or editing it (Q20, Q22)</t>
+          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task linked to it has at least one completion (BR-R25). With no milestone linked yet it shows 0 of 0 and never unlocks (tasks are linked later, on the Link screen)</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -12128,7 +12375,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.6</t>
+          <t>LLR-11.5</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -12143,12 +12390,12 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Silent tasks and their completions never appear in anything served without the owner passcode: lists, counts, streaks, activity, dashboard aggregates or reward task lists (BR-R23). With the passcode they're shown with a 🔕 marker</t>
+          <t>Announce or keep silent: each task is *Announced* (default) or *Silent*, set when creating or editing it (Q20, Q22)</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr">
@@ -12172,7 +12419,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.7</t>
+          <t>LLR-11.6</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -12187,12 +12434,12 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Completing an announced task shows the celebration toast and a Share on WhatsApp prompt (prefilled text, e.g. "Done: Wipe counters 🔥 3-day streak"). Completing a silent task shows only a quiet "Logged" confirmation, with no share prompt (BR-R24)</t>
+          <t>Silent tasks and their completions never appear in anything served without the owner passcode: lists, counts, streaks, activity, dashboard aggregates or reward task lists (BR-R23). With the passcode they're shown with a 🔕 marker</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
@@ -12216,7 +12463,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.8</t>
+          <t>LLR-11.7</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -12231,7 +12478,7 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Due date and time (optional): a local date and time, stored in UTC. Tasks show a chip: *Overdue* (red), *Due today*, *Due in N days* (within 7 days) or the date. The area list can be filtered by *Overdue*, *Due today* and *Due this week*, and sorted by due date</t>
+          <t>Completing an announced task shows the celebration toast and a Share on WhatsApp prompt (prefilled text, e.g. "Done: Wipe counters 🔥 3-day streak"). Completing a silent task shows only a quiet "Logged" confirmation, with no share prompt (BR-R24)</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
@@ -12260,7 +12507,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.9</t>
+          <t>LLR-11.8</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -12275,7 +12522,7 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Days to complete (optional): a whole number from 1 to 3650, shown as "Planned: N days". Task detail also shows "Day X of N", counted from the task's creation date</t>
+          <t>Due date and time (optional): a local date and time, stored in UTC. Tasks show a chip: *Overdue* (red), *Due today*, *Due in N days* (within 7 days) or the date. The area list can be filtered by *Overdue*, *Due today* and *Due this week*, and sorted by due date</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -12304,7 +12551,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.10</t>
+          <t>LLR-11.9</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -12319,7 +12566,7 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Due date and days to complete are independent: changing one never changes the other, and they may disagree (Q21, BR-R26)</t>
+          <t>Days to complete (optional): a whole number from 1 to 3650, shown as "Planned: N days". Task detail also shows "Day X of N", counted from the task's creation date</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -12348,7 +12595,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.11</t>
+          <t>LLR-11.10</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -12363,7 +12610,7 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>All four attributes can be edited on task detail at any time. A due date in the past is allowed (the task is simply overdue)</t>
+          <t>Due date and days to complete are independent: changing one never changes the other, and they may disagree (Q21, BR-R26)</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -12392,7 +12639,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.12</t>
+          <t>LLR-11.11</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -12407,7 +12654,7 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Existing tasks are migrated without data loss: milestone = no, visibility = announced, no due date, no days to complete. Nothing else changes</t>
+          <t>All four attributes can be edited on task detail at any time. A due date in the past is allowed (the task is simply overdue)</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
@@ -12436,7 +12683,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.13</t>
+          <t>LLR-11.12</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -12451,7 +12698,7 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>The dashboard adds an Overdue KPI and the *Milestones* table (LLR-11.2); the owner-only dashboard includes silent tasks, marked 🔕</t>
+          <t>Existing tasks are migrated without data loss: milestone = no, visibility = announced, no due date, no days to complete. Nothing else changes</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -12480,7 +12727,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.1</t>
+          <t>LLR-11.13</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -12490,12 +12737,12 @@
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Quick capture: "💡 + Idea" on the Rewards screen and on every area's Rewards tab opens a short form: title (required), for whom (default Me) and a one-tap cover photo (camera or gallery; JPG, PNG, WebP or HEIC up to 10 MB); *More* adds where seen, link, note and (on the Rewards screen) an optional area. Saving needs only the title</t>
+          <t>The dashboard adds an Overdue KPI and the *Milestones* table (LLR-11.2); the owner-only dashboard includes silent tasks, marked 🔕</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
@@ -12524,7 +12771,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.2</t>
+          <t>LLR-12.1</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -12539,7 +12786,7 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>For whom on every reward and idea: free text (1–40) with suggestions from earlier entries; default "Me" (Q25)</t>
+          <t>Quick capture: "💡 + Idea" on the Rewards screen and on every area's Rewards tab opens a short form: title (required), for whom (default Me) and a one-tap cover photo (camera or gallery; JPG, PNG, WebP or HEIC up to 10 MB); *More* adds where seen, link, note and (on the Rewards screen) an optional area. Saving needs only the title</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -12568,7 +12815,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.3</t>
+          <t>LLR-12.2</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -12583,7 +12830,7 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Ideas have status Idea: no rule, no progress and no tasks, and they never unlock or appear in progress counts (BR-R27)</t>
+          <t>For whom on every reward and idea: free text (1–40) with suggestions from earlier entries; default "Me" (Q25)</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
@@ -12612,7 +12859,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.4</t>
+          <t>LLR-12.3</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -12627,7 +12874,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>The Rewards screen filters by status (💡 Ideas, Locked, Unlocked, Claimed, Closed) and by for whom (e.g. *Shiragi*), plus search; closed ideas are hidden unless *Closed* is chosen. An area's Rewards tab lists its ideas with its rewards. Ideas are never offered on the Link screen</t>
+          <t>Ideas have status Idea: no rule, no progress and no tasks, and they never unlock or appear in progress counts (BR-R27)</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -12656,7 +12903,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.5</t>
+          <t>LLR-12.4</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -12671,7 +12918,7 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Turn into reward: on an idea, pick how it unlocks (task count with N, or milestone completed). It becomes a normal *locked* reward with the same id, keeping title, photo, link, note, where seen, area and for whom; tasks are then linked on the Link screen (BR-R28)</t>
+          <t>The Rewards screen filters by status (💡 Ideas, Locked, Unlocked, Claimed, Closed) and by for whom (e.g. *Shiragi*), plus search; closed ideas are hidden unless *Closed* is chosen. An area's Rewards tab lists its ideas with its rewards. Ideas are never offered on the Link screen</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
@@ -12700,7 +12947,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.6</t>
+          <t>LLR-12.5</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -12715,7 +12962,7 @@
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Close an idea as *Bought* (got it without a rule) or *Dropped* (no longer wanted). Closed ideas leave the Ideas list, stay under *Closed* with the date and outcome, and can be reopened (BR-R29)</t>
+          <t>Turn into reward: on an idea, pick how it unlocks (task count with N, or milestone completed). It becomes a normal *locked* reward with the same id, keeping title, photo, link, note, where seen, area and for whom; tasks are then linked on the Link screen (BR-R28)</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -12744,7 +12991,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.7</t>
+          <t>LLR-12.6</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -12759,12 +13006,12 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Ideas are Silent by default (hidden from the read-only view) and can be switched to *Announced*; ordinary rewards default to *Announced*. Visibility follows the silent rules of BR-R23 (Q24)</t>
+          <t>Close an idea as *Bought* (got it without a rule) or *Dropped* (no longer wanted). Closed ideas leave the Ideas list, stay under *Closed* with the date and outcome, and can be reopened (BR-R29)</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
@@ -12788,7 +13035,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.8</t>
+          <t>LLR-12.7</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -12803,12 +13050,12 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>Ideas are included in search (LLR-10.9) by title, notes, for whom and where seen</t>
+          <t>Ideas are Silent by default (hidden from the read-only view) and can be switched to *Announced*; ordinary rewards default to *Announced*. Visibility follows the silent rules of BR-R23 (Q24)</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
@@ -12832,7 +13079,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.9</t>
+          <t>LLR-12.8</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -12847,7 +13094,7 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Existing rewards are migrated without data loss: for whom = "Me", visibility = announced; their status, rule, tasks and progress are unchanged</t>
+          <t>Ideas are included in search (LLR-10.9) by title, notes, for whom and where seen</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
@@ -12876,22 +13123,22 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>BR-R1</t>
+          <t>LLR-12.9</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>A period is a local calendar day (daily) or a Monday–Sunday week (weekly) in BFF_TIMEZONE</t>
+          <t>Existing rewards are migrated without data loss: for whom = "Me", visibility = announced; their status, rule, tasks and progress are unchanged</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -12920,22 +13167,22 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>BR-R2</t>
+          <t>LLR-13.1</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Several completions in one period count once towards the streak (they all count towards completion count)</t>
+          <t>The tile form (new tile and ✎ edit) has a Use areas switch, on by default. POST /categories and PATCH /categories/{id} accept useAreas; every tile in GET /categories returns useAreas, and each area returns hidden</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
@@ -12964,22 +13211,22 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>BR-R3</t>
+          <t>LLR-13.2</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>Best streak = longest run of consecutive periods with ≥ 1 completion</t>
+          <t>Switching areas off is only possible while the tile has no areas; otherwise the switch is disabled with "move or delete its N areas first" and the API answers 409 (BR-R31)</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -13008,22 +13255,22 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>BR-R4</t>
+          <t>LLR-13.3</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Current streak = the run ending at the latest completed period, if that period is the current or the previous one; otherwise 0</t>
+          <t>A tile without areas opens straight to Tasks | Rewards | Notes &amp; contacts at #/rewards/c/{tile} (/rewards, /details), with the tile's name, icon and its ✎ / 🗑 buttons. Old links to its hidden area open the tile instead</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
@@ -13052,22 +13299,22 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>BR-R5</t>
+          <t>LLR-13.4</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>One-off tasks: streak = 1 once completed, else 0 (not shown as an active streak)</t>
+          <t>Tiles screen shows "N active tasks" without an area count; the Tasks, Rewards and Link screens, area pickers, search results and the dashboard show such tasks and rewards under the tile name alone (e.g. "💼 Career / Office / Work", never "› General")</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -13096,22 +13343,22 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>BR-R6</t>
+          <t>LLR-13.5</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Streaks are derived from the activity log on every read (never stored)</t>
+          <t>No areas can be added to, and the hidden area can't be renamed or deleted on, a tile without areas (409); the starter set never adds areas to it</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
@@ -13140,22 +13387,22 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>BR-R7</t>
+          <t>LLR-13.6</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>*Completions* rule progress = total completions of all tagged tasks (all-time)</t>
+          <t>Switching areas back on: if the tile holds anything, its hidden area becomes a normal area called General with everything in it; if it's empty, it simply goes</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -13184,22 +13431,22 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>BR-R8</t>
+          <t>LLR-13.7</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>*Streak* rule progress = the highest current streak among tagged tasks</t>
+          <t>Move a task: the task's edit form has a *Tile or area* picker (PATCH /tasks/{id} with areaId). Completions, streaks and reward links move with it</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
@@ -13228,22 +13475,22 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>BR-R9</t>
+          <t>LLR-13.8</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>The unlock check runs on task completion, reward creation, reward update and tag change</t>
+          <t>Existing data is kept: migration 0006_tile_without_areas adds areas.hidden (false for every existing area), with a backup first</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -13272,7 +13519,7 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>BR-R10</t>
+          <t>BR-R1</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -13282,12 +13529,12 @@
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Status flow locked → unlocked → claimed only; there's no path back</t>
+          <t>A period is a local calendar day (daily) or a Monday–Sunday week (weekly) in BFF_TIMEZONE</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
@@ -13316,7 +13563,7 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>BR-R11</t>
+          <t>BR-R2</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -13326,12 +13573,12 @@
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>Unlocked and claimed rewards always show 100 %</t>
+          <t>Several completions in one period count once towards the streak (they all count towards completion count)</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -13360,7 +13607,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>BR-R12</t>
+          <t>BR-R3</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -13370,12 +13617,12 @@
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Scope containment. A task is in a reward's scope when the task's area belongs to the reward's tile and, if the reward has an area, the task's area *is* that area</t>
+          <t>Best streak = longest run of consecutive periods with ≥ 1 completion</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
@@ -13404,7 +13651,7 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>BR-R13</t>
+          <t>BR-R4</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -13414,12 +13661,12 @@
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>Matched tasks. *Selected tasks*: the tagged tasks (all in scope). *All tasks in scope*: every task in scope whose status isn't archived. BR-R7 and BR-R8 compute progress over the matched tasks</t>
+          <t>Current streak = the run ending at the latest completed period, if that period is the current or the previous one; otherwise 0</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -13448,7 +13695,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>BR-R14</t>
+          <t>BR-R5</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -13458,12 +13705,12 @@
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>In *All tasks in scope* mode, tags are ignored for progress (they're kept, so switching back to *Selected tasks* restores them)</t>
+          <t>One-off tasks: streak = 1 once completed, else 0 (not shown as an active streak)</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
@@ -13492,7 +13739,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>BR-R15</t>
+          <t>BR-R6</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -13502,12 +13749,12 @@
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>The unlock check (BR-R9) on completion evaluates every locked reward that matches the completed task, whether tagged or by scope</t>
+          <t>Streaks are derived from the activity log on every read (never stored)</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -13536,7 +13783,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>BR-R16</t>
+          <t>BR-R7</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -13546,12 +13793,12 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>A reward marked *Needs a tile* (LLR-4.18) still shows progress from its tags, but can't be edited until a tile is chosen. It never unlocks from tasks outside the tile the user then picks</t>
+          <t>*Completions* rule progress = total completions of all tagged tasks (all-time)</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
@@ -13580,7 +13827,7 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>BR-R17</t>
+          <t>BR-R8</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -13590,12 +13837,12 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>HLR-1</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t>Tile names are unique ignoring case; area names are unique within their tile ignoring case</t>
+          <t>*Streak* rule progress = the highest current streak among tagged tasks</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -13624,7 +13871,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>BR-R18</t>
+          <t>BR-R9</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -13634,12 +13881,12 @@
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>HLR-1</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Deleting a tile removes everything under it (areas, tasks, completions, rewards scoped to it, notes, contacts, files) in one transaction, after a database snapshot is saved to data/backups/</t>
+          <t>The unlock check runs on task completion, reward creation, reward update and tag change</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
@@ -13668,7 +13915,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>BR-R19</t>
+          <t>BR-R10</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -13678,12 +13925,12 @@
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>HLR-1</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>The starter set only adds tiles and areas whose names are missing; it never renames, merges or deletes</t>
+          <t>Status flow locked → unlocked → claimed only; there's no path back</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -13712,7 +13959,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>BR-R20</t>
+          <t>BR-R11</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -13722,12 +13969,12 @@
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Details belong to exactly one owner: a tile or an area. Moving an area to another tile isn't supported, so details never change tile</t>
+          <t>Unlocked and claimed rewards always show 100 %</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
@@ -13756,7 +14003,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>BR-R21</t>
+          <t>BR-R12</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -13766,12 +14013,12 @@
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>The "last executive" of a topic is the *Service executive* or *Technician* contact in that topic with the latest last-visit date; contacts without a date come after dated ones</t>
+          <t>Scope containment. A task is in a reward's scope when the task's area belongs to the reward's tile and, if the reward has an area, the task's area *is* that area</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -13800,7 +14047,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>BR-R22</t>
+          <t>BR-R13</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -13810,12 +14057,12 @@
       </c>
       <c r="C174" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>A task is overdue when it's active, has a due date, and the due date is before now. Done and archived tasks are never overdue</t>
+          <t>Matched tasks. *Selected tasks*: the tagged tasks (all in scope). *All tasks in scope*: every task in scope whose status isn't archived. BR-R7 and BR-R8 compute progress over the matched tasks</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
@@ -13844,7 +14091,7 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>BR-R23</t>
+          <t>BR-R14</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -13854,12 +14101,12 @@
       </c>
       <c r="C175" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>Silent means invisible without the passcode: silent tasks, their completions, streaks and activity are excluded from every response to a caller without the owner passcode, including counts and aggregates, so their existence can't be inferred</t>
+          <t>In *All tasks in scope* mode, tags are ignored for progress (they're kept, so switching back to *Selected tasks* restores them)</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -13888,7 +14135,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>BR-R24</t>
+          <t>BR-R15</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -13898,12 +14145,12 @@
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>Celebrations and share prompts happen only for announced tasks. A reward unlocked by a silent task's completion is unlocked quietly (no share prompt); the reward itself stays visible</t>
+          <t>The unlock check (BR-R9) on completion evaluates every locked reward that matches the completed task, whether tagged or by scope</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
@@ -13932,7 +14179,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>BR-R25</t>
+          <t>BR-R16</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -13942,12 +14189,12 @@
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t>A Milestone completed reward unlocks when every milestone task it matches (tagged, or in scope with *All tasks in scope*) has ≥ 1 completion. Non-milestone tasks tagged to it don't count. Progress = milestones completed ÷ milestones matched</t>
+          <t>A reward marked *Needs a tile* (LLR-4.18) still shows progress from its tags, but can't be edited until a tile is chosen. It never unlocks from tasks outside the tile the user then picks</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -13976,7 +14223,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>BR-R26</t>
+          <t>BR-R17</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -13986,12 +14233,12 @@
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-1</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>Due date and days to complete are never derived from each other or from the frequency</t>
+          <t>Tile names are unique ignoring case; area names are unique within their tile ignoring case</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
@@ -14020,7 +14267,7 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>BR-R27</t>
+          <t>BR-R18</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -14030,12 +14277,12 @@
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-1</t>
         </is>
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>An *Idea* has no rule and no progress. It can't unlock or be claimed, and it isn't counted in reward totals or progress on the dashboard (the dashboard shows an *Ideas* count per person)</t>
+          <t>Deleting a tile removes everything under it (areas, tasks, completions, rewards scoped to it, notes, contacts, files) in one transaction, after a database snapshot is saved to data/backups/</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -14064,7 +14311,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>BR-R28</t>
+          <t>BR-R19</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -14074,12 +14321,12 @@
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-1</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>Turning an idea into a reward requires a rule and a threshold (except *milestone completed*); a tile isn't required since rewards stand alone. The idea's id is kept, so links and photos stay attached</t>
+          <t>The starter set only adds tiles and areas whose names are missing; it never renames, merges or deletes</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
@@ -14108,7 +14355,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>BR-R29</t>
+          <t>BR-R20</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -14118,12 +14365,12 @@
       </c>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>Closing is only for ideas; a reward that already has a rule is claimed, not closed. Reopening a closed idea returns it to *Idea*</t>
+          <t>Details belong to exactly one owner: a tile or an area. Moving an area to another tile isn't supported, so details never change tile</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -14152,7 +14399,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>BR-R30</t>
+          <t>BR-R21</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
@@ -14162,12 +14409,12 @@
       </c>
       <c r="C182" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>*For whom* is a label: it groups and filters rewards, but never changes who can see or edit them (visibility rules decide that)</t>
+          <t>The "last executive" of a topic is the *Service executive* or *Technician* contact in that topic with the latest last-visit date; contacts without a date come after dated ones</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
@@ -14196,22 +14443,22 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>NFR-D1</t>
+          <t>BR-R22</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C183" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>Remote exposed chunk ≤ 50 KB gzip (now ~11 KB)</t>
+          <t>A task is overdue when it's active, has a due date, and the due date is before now. Done and archived tasks are never overdue</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -14233,29 +14480,29 @@
       <c r="I183" s="8" t="inlineStr"/>
       <c r="J183" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>NFR-D2</t>
+          <t>BR-R23</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C184" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Remote load after navigating to #/rewards ≤ 500 ms locally (measured ~36 ms client-side nav, ~275 ms cold)</t>
+          <t>Silent means invisible without the passcode: silent tasks, their completions, streaks and activity are excluded from every response to a caller without the owner passcode, including counts and aggregates, so their existence can't be inferred</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
@@ -14277,29 +14524,29 @@
       <c r="I184" s="8" t="inlineStr"/>
       <c r="J184" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>NFR-D3</t>
+          <t>BR-R24</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C185" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>Dashboard issues ≤ 1 BFF read per window per 30 s</t>
+          <t>Celebrations and share prompts happen only for announced tasks. A reward unlocked by a silent task's completion is unlocked quietly (no share prompt); the reward itself stays visible</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -14321,29 +14568,29 @@
       <c r="I185" s="8" t="inlineStr"/>
       <c r="J185" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>NFR-D4</t>
+          <t>BR-R25</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>No horizontal scroll at 375 px width</t>
+          <t>A Milestone completed reward unlocks when every milestone task it matches (tagged, or in scope with *All tasks in scope*) has ≥ 1 completion. Non-milestone tasks tagged to it don't count. Progress = milestones completed ÷ milestones matched</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
@@ -14365,29 +14612,29 @@
       <c r="I186" s="8" t="inlineStr"/>
       <c r="J186" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>NFR-D5</t>
+          <t>BR-R26</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>Stats for N tasks use one activity query (no N+1)</t>
+          <t>Due date and days to complete are never derived from each other or from the frequency</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -14409,29 +14656,29 @@
       <c r="I187" s="8" t="inlineStr"/>
       <c r="J187" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>NFR-D6</t>
+          <t>BR-R27</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>Every business rule BR-R1…R30 has ≥ 1 automated test</t>
+          <t>An *Idea* has no rule and no progress. It can't unlock or be claimed, and it isn't counted in reward totals or progress on the dashboard (the dashboard shows an *Ideas* count per person)</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
@@ -14453,29 +14700,29 @@
       <c r="I188" s="8" t="inlineStr"/>
       <c r="J188" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>NFR-D7</t>
+          <t>BR-R28</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>Naive datetimes never reach storage</t>
+          <t>Turning an idea into a reward requires a rule and a threshold (except *milestone completed*); a tile isn't required since rewards stand alone. The idea's id is kept, so links and photos stay attached</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -14497,29 +14744,29 @@
       <c r="I189" s="8" t="inlineStr"/>
       <c r="J189" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>NFR-D8</t>
+          <t>BR-R29</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>No schema change may delete or rewrite existing rows except as specified (LLR-4.18); every migration has an upgrade test run against a copy of a pre-migration database</t>
+          <t>Closing is only for ideas; a reward that already has a rule is claimed, not closed. Reopening a closed idea returns it to *Idea*</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
@@ -14541,34 +14788,34 @@
       <c r="I190" s="8" t="inlineStr"/>
       <c r="J190" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>NFR-D9</t>
+          <t>BR-R30</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>Uploaded files are stored outside any public web folder with random names, served only through the BFF, and count against a 2 GB soft limit on the droplet (warning shown); moving to object storage later changes no requirement</t>
+          <t>*For whom* is a label: it groups and filters rewards, but never changes who can see or edit them (visibility rules decide that)</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr">
@@ -14585,34 +14832,34 @@
       <c r="I191" s="8" t="inlineStr"/>
       <c r="J191" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>NFR-D10</t>
+          <t>BR-R31</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>Search over notes, contacts and files returns in ≤ 300 ms for 5,000 items</t>
+          <t>A tile either uses areas or holds everything itself, never both. Areas can only be switched off on a tile with no areas, so nothing is hidden or lost by the switch</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F192" s="8" t="inlineStr">
@@ -14629,14 +14876,14 @@
       <c r="I192" s="8" t="inlineStr"/>
       <c r="J192" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>NFR-D11</t>
+          <t>NFR-D1</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -14651,12 +14898,12 @@
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>Every read endpoint has a test that a silent task leaves no trace (item, count or aggregate) in its response without the passcode</t>
+          <t>Remote exposed chunk ≤ 50 KB gzip (now ~11 KB)</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F193" s="8" t="inlineStr">
@@ -14677,13 +14924,453 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D2</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C194" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D194" s="8" t="inlineStr">
+        <is>
+          <t>Remote load after navigating to #/rewards ≤ 500 ms locally (measured ~36 ms client-side nav, ~275 ms cold)</t>
+        </is>
+      </c>
+      <c r="E194" s="8" t="inlineStr">
+        <is>
+          <t>Built &amp; tested</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G194" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H194" s="8" t="inlineStr"/>
+      <c r="I194" s="8" t="inlineStr"/>
+      <c r="J194" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D3</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D195" s="8" t="inlineStr">
+        <is>
+          <t>Dashboard issues ≤ 1 BFF read per window per 30 s</t>
+        </is>
+      </c>
+      <c r="E195" s="8" t="inlineStr">
+        <is>
+          <t>Built &amp; tested</t>
+        </is>
+      </c>
+      <c r="F195" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G195" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H195" s="8" t="inlineStr"/>
+      <c r="I195" s="8" t="inlineStr"/>
+      <c r="J195" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D4</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C196" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D196" s="8" t="inlineStr">
+        <is>
+          <t>No horizontal scroll at 375 px width</t>
+        </is>
+      </c>
+      <c r="E196" s="8" t="inlineStr">
+        <is>
+          <t>Built &amp; tested</t>
+        </is>
+      </c>
+      <c r="F196" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G196" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H196" s="8" t="inlineStr"/>
+      <c r="I196" s="8" t="inlineStr"/>
+      <c r="J196" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D5</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D197" s="8" t="inlineStr">
+        <is>
+          <t>Stats for N tasks use one activity query (no N+1)</t>
+        </is>
+      </c>
+      <c r="E197" s="8" t="inlineStr">
+        <is>
+          <t>Built &amp; tested</t>
+        </is>
+      </c>
+      <c r="F197" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G197" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H197" s="8" t="inlineStr"/>
+      <c r="I197" s="8" t="inlineStr"/>
+      <c r="J197" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D6</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D198" s="8" t="inlineStr">
+        <is>
+          <t>Every business rule BR-R1…R30 has ≥ 1 automated test</t>
+        </is>
+      </c>
+      <c r="E198" s="8" t="inlineStr">
+        <is>
+          <t>Built &amp; tested</t>
+        </is>
+      </c>
+      <c r="F198" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G198" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H198" s="8" t="inlineStr"/>
+      <c r="I198" s="8" t="inlineStr"/>
+      <c r="J198" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D7</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D199" s="8" t="inlineStr">
+        <is>
+          <t>Naive datetimes never reach storage</t>
+        </is>
+      </c>
+      <c r="E199" s="8" t="inlineStr">
+        <is>
+          <t>Built &amp; tested</t>
+        </is>
+      </c>
+      <c r="F199" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G199" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H199" s="8" t="inlineStr"/>
+      <c r="I199" s="8" t="inlineStr"/>
+      <c r="J199" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D8</t>
+        </is>
+      </c>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D200" s="8" t="inlineStr">
+        <is>
+          <t>No schema change may delete or rewrite existing rows except as specified (LLR-4.18); every migration has an upgrade test run against a copy of a pre-migration database</t>
+        </is>
+      </c>
+      <c r="E200" s="8" t="inlineStr">
+        <is>
+          <t>Built &amp; tested</t>
+        </is>
+      </c>
+      <c r="F200" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G200" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H200" s="8" t="inlineStr"/>
+      <c r="I200" s="8" t="inlineStr"/>
+      <c r="J200" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D9</t>
+        </is>
+      </c>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D201" s="8" t="inlineStr">
+        <is>
+          <t>Uploaded files are stored outside any public web folder with random names, served only through the BFF, and count against a 2 GB soft limit on the droplet (warning shown); moving to object storage later changes no requirement</t>
+        </is>
+      </c>
+      <c r="E201" s="8" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="F201" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G201" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H201" s="8" t="inlineStr"/>
+      <c r="I201" s="8" t="inlineStr"/>
+      <c r="J201" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D10</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D202" s="8" t="inlineStr">
+        <is>
+          <t>Search over notes, contacts and files returns in ≤ 300 ms for 5,000 items</t>
+        </is>
+      </c>
+      <c r="E202" s="8" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="F202" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G202" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H202" s="8" t="inlineStr"/>
+      <c r="I202" s="8" t="inlineStr"/>
+      <c r="J202" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D11</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D203" s="8" t="inlineStr">
+        <is>
+          <t>Every read endpoint has a test that a silent task leaves no trace (item, count or aggregate) in its response without the passcode</t>
+        </is>
+      </c>
+      <c r="E203" s="8" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="F203" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G203" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H203" s="8" t="inlineStr"/>
+      <c r="I203" s="8" t="inlineStr"/>
+      <c r="J203" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J193"/>
+  <autoFilter ref="A4:J203"/>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E393" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E403" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Built &amp; tested,Built (manual test),Planned,Next,Out of scope"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F393" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F403" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Must,Should,Could,Won't (now)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14697,7 +15384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14783,143 +15470,143 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.1–12.9; BR-R27–R30; LLR-8.13</t>
+          <t>LLR-13.1–13.8; BR-R31</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>/rewards*</t>
+          <t>/categories*, /areas*, PATCH /tasks/{id}</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>test_idea_needs_only_title, test_ideas_silent_by_default, test_idea_never_unlocks_or_counts, test_activate_idea_keeps_details_and_evaluates, test_close_and_reopen_idea, test_filter_by_for_whom, test_cover_photo_signed_link_and_cleanup, test_ideas_in_search, test_migration_defaults_existing_rewards</t>
+          <t>test_switch_off_areas_gives_the_tile_one_hidden_area, test_a_new_tile_can_start_without_areas, test_cannot_switch_off_while_the_tile_has_areas, test_tasks_on_a_tile_without_areas_show_the_tile_name, test_switching_areas_back_on, test_starter_set_leaves_a_tile_without_areas_alone, test_move_a_task_keeps_completions_and_reward_links; tile screen, redirects and the switch verified in the browser</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.1–11.13; BR-R22–R26; LLR-8.12</t>
+          <t>LLR-12.1–12.9; BR-R27–R30; LLR-8.13</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>tasks, rewards, /dashboard/summary</t>
+          <t>/rewards*</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>test_task_planning_fields_round_trip, test_overdue_rules, test_due_filters_milestones_and_sort, test_milestone_reward_needs_all_milestones, test_dashboard_overdue_and_milestones, test_migration_defaults_existing_tasks; quiet completion and celebrations verified in the browser; ⏳ test_silent_tasks_invisible_without_passcode comes with the passcode</t>
+          <t>test_idea_needs_only_title, test_ideas_silent_by_default, test_idea_never_unlocks_or_counts, test_activate_idea_keeps_details_and_evaluates, test_close_and_reopen_idea, test_filter_by_for_whom, test_cover_photo_signed_link_and_cleanup, test_ideas_in_search, test_migration_defaults_existing_rewards</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.1–10.12; BR-R20–R21; LLR-8.11</t>
+          <t>LLR-11.1–11.13; BR-R22–R26; LLR-8.12</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>details, files, /search</t>
+          <t>tasks, rewards, /dashboard/summary</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>test_details_grouped_by_topic_with_last_executive, test_tile_level_details_for_home_wide_services, test_contact_validation, test_edit_and_delete_items, test_file_upload_rules_and_signed_download, test_search_matches_names_topics_and_phone_digits, test_deleting_owner_removes_details_and_files, test_export_import_includes_details; read-only view test comes with the passcode work</t>
+          <t>test_task_planning_fields_round_trip, test_overdue_rules, test_due_filters_milestones_and_sort, test_milestone_reward_needs_all_milestones, test_dashboard_overdue_and_milestones, test_migration_defaults_existing_tasks; quiet completion and celebrations verified in the browser; ⏳ test_silent_tasks_invisible_without_passcode comes with the passcode</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.1, 2.3–2.5, 2.8, 2.9</t>
+          <t>LLR-10.1–10.12; BR-R20–R21; LLR-8.11</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>POST /areas/{id}/tasks, GET /areas/{id}/tasks, PATCH /tasks/{id}, GET /tasks</t>
+          <t>details, files, /search</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>test_create_filter_and_reprioritise_tasks</t>
+          <t>test_details_grouped_by_topic_with_last_executive, test_tile_level_details_for_home_wide_services, test_contact_validation, test_edit_and_delete_items, test_file_upload_rules_and_signed_download, test_search_matches_names_topics_and_phone_digits, test_deleting_owner_removes_details_and_files, test_export_import_includes_details; read-only view test comes with the passcode work</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.10</t>
+          <t>LLR-2.1, 2.3–2.5, 2.8, 2.9</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>PATCH /tasks/{id}, DELETE /tasks/{id}</t>
+          <t>POST /areas/{id}/tasks, GET /areas/{id}/tasks, PATCH /tasks/{id}, GET /tasks</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>test_edit_and_delete_task</t>
+          <t>test_create_filter_and_reprioritise_tasks</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.1, 3.6, 3.7; BR-R2–R4</t>
+          <t>LLR-2.10</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/complete, GET /tasks/{id}/activity, GET /tasks/{id}</t>
+          <t>PATCH /tasks/{id}, DELETE /tasks/{id}</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>test_completions_build_streak_and_activity_log, test_daily_streak, test_weekly_streak</t>
+          <t>test_edit_and_delete_task</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.3–3.5; BR-R4, R5</t>
+          <t>LLR-3.1, 3.6, 3.7; BR-R2–R4</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/complete</t>
+          <t>POST /tasks/{id}/complete, GET /tasks/{id}/activity, GET /tasks/{id}</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>test_completion_rules, test_one_off_streak_is_done_or_not</t>
+          <t>test_completions_build_streak_and_activity_log, test_daily_streak, test_weekly_streak</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.1, 4.2, 4.6, 4.7; BR-R7, R9, R10</t>
+          <t>LLR-3.3–3.5; BR-R4, R5</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>/rewards*</t>
+          <t>POST /tasks/{id}/complete</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>test_reward_unlocks_on_completion_count_then_claim, test_reward_already_met_unlocks_on_create_and_rejects_unknown_tasks, test_completions_rule_progress</t>
+          <t>test_completion_rules, test_one_off_streak_is_done_or_not</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>BR-R8</t>
+          <t>LLR-4.1, 4.2, 4.6, 4.7; BR-R7, R9, R10</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -14929,141 +15616,158 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>test_streak_reward_uses_best_current_streak_across_tasks, test_streak_rule_progress</t>
+          <t>test_reward_unlocks_on_completion_count_then_claim, test_reward_already_met_unlocks_on_create_and_rejects_unknown_tasks, test_completions_rule_progress</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>BR-R11</t>
+          <t>BR-R8</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/rewards*</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>test_unlocked_reward_stays_complete_after_streak_breaks</t>
+          <t>test_streak_reward_uses_best_current_streak_across_tasks, test_streak_rule_progress</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.1, 5.9, 5.10</t>
+          <t>BR-R11</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>GET /dashboard/summary</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>test_dashboard_summary_is_flat_snake_case</t>
+          <t>test_unlocked_reward_stays_complete_after_streak_breaks</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.1</t>
+          <t>LLR-5.1, 5.9, 5.10</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>GET /dashboard/summary</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>test_requires_demo_token</t>
+          <t>test_dashboard_summary_is_flat_snake_case</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.x, 5.2–5.8</t>
+          <t>LLR-8.1</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>all</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Manual E2E (browser, 375 px); planned Playwright smoke</t>
+          <t>test_requires_demo_token</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.x</t>
+          <t>LLR-7.x, 5.2–5.8</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>planned: adapter tests with FakeVisionAdapter, fallback tests</t>
+          <t>Manual E2E (browser, 375 px); planned Playwright smoke</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.9–4.17; LLR-8.7, 8.8</t>
+          <t>LLR-6.x</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>/rewards*, /rewards/{id}/tasks/{taskId}</t>
+          <t>⏳</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>test_reward_needs_only_a_title, test_area_rewards_are_kept_in_an_area_but_link_anywhere, test_link_any_task_to_any_reward, test_linked_task_counts_unlock_the_reward, test_linking_tasks_already_done_enough_unlocks_immediately, test_rewards_outlive_tiles_areas_and_tasks, test_delete_reward_keeps_tasks, test_older_all_tasks_in_area_rewards_keep_counting</t>
+          <t>planned: adapter tests with FakeVisionAdapter, fallback tests</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.9; NFR-D8</t>
+          <t>LLR-4.9–4.17; LLR-8.7, 8.8</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>startup migrations, app.backup</t>
+          <t>/rewards*, /rewards/{id}/tasks/{taskId}</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>test_models_match_migrations, test_pre_migration_database_is_stamped_not_rebuilt, test_migrate_is_idempotent, test_export_import_round_trip, test_import_refuses_non_empty_target_without_replace</t>
+          <t>test_reward_needs_only_a_title, test_area_rewards_are_kept_in_an_area_but_link_anywhere, test_link_any_task_to_any_reward, test_linked_task_counts_unlock_the_reward, test_linking_tasks_already_done_enough_unlocks_immediately, test_rewards_outlive_tiles_areas_and_tasks, test_delete_reward_keeps_tasks, test_older_all_tasks_in_area_rewards_keep_counting</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>LLR-8.9; NFR-D8</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>startup migrations, app.backup</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>test_models_match_migrations, test_pre_migration_database_is_stamped_not_rebuilt, test_migrate_is_idempotent, test_export_import_round_trip, test_import_refuses_non_empty_target_without_replace</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>LLR-4.18; BR-R16</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>migration 0003_reward_scope</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>test_migration_infers_scope_and_keeps_data (runs against a database at 0002_details)</t>
         </is>
@@ -15080,7 +15784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15156,27 +15860,27 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A5,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A5,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A5)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A5)</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A5,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A5,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A5,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A5,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A5,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A5,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A5,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A5,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H5" s="9">
@@ -15191,27 +15895,27 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A6,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A6,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A6)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A6)</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A6,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A6,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A6,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A6,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A6,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A6,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A6,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A6,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H6" s="9">
@@ -15226,27 +15930,27 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A7,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A7,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C7" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A7)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A7)</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A7,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A7,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A7,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A7,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A7,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A7,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A7,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A7,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H7" s="9">
@@ -15261,27 +15965,27 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A8,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A8,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C8" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A8)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A8,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A8,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A8,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A8,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A8,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A8,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A8,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A8,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H8" s="9">
@@ -15296,27 +16000,27 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A9,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A9,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C9" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A9)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A9,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A9,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A9,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A9,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A9,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A9,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A9,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A9,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H9" s="9">
@@ -15331,27 +16035,27 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A10,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A10,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A10)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A10,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A10,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A10,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A10,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A10,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A10,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A10,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A10,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H10" s="9">
@@ -15366,27 +16070,27 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A11,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A11,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A11)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A11,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A11,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A11,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A11,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A11,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A11,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A11,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A11,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H11" s="9">
@@ -15401,27 +16105,27 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A12,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A12,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A12)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A12,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A12,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A12,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A12,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A12,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A12,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A12,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A12,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H12" s="9">
@@ -15436,27 +16140,27 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A13,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A13,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A13)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A13,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A13,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A13,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A13,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A13,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A13,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A13,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A13,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H13" s="9">
@@ -15471,27 +16175,27 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A14,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A14,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A14)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A14,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A14,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A14,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A14,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A14,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A14,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A14,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A14,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H14" s="9">
@@ -15506,27 +16210,27 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A15,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A15,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C15" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A15)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A15)</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A15,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A15,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A15,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A15,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A15,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A15,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A15,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A15,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H15" s="9">
@@ -15541,27 +16245,27 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$393,MATCH(A16,'Requirements Register'!$A$5:$A$393,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A16,'Requirements Register'!$A$5:$A$403,0)),"")</f>
         <v/>
       </c>
       <c r="C16" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$393,A16)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A16)</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A16,'Requirements Register'!$E$5:$E$393,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A16,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A16,'Requirements Register'!$E$5:$E$393,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A16,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A16,'Requirements Register'!$E$5:$E$393,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A16,'Requirements Register'!$E$5:$E$403,"Next")</f>
         <v/>
       </c>
       <c r="G16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$393,A16,'Requirements Register'!$E$5:$E$393,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A16,'Requirements Register'!$E$5:$E$403,"Planned")</f>
         <v/>
       </c>
       <c r="H16" s="9">
@@ -15570,34 +16274,69 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>HLR-13</t>
+        </is>
+      </c>
+      <c r="B17" s="7">
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A17,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="7">
+        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="7">
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A17,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <v/>
+      </c>
+      <c r="E17" s="7">
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A17,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <v/>
+      </c>
+      <c r="F17" s="7">
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A17,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <v/>
+      </c>
+      <c r="G17" s="7">
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A17,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <v/>
+      </c>
+      <c r="H17" s="9">
+        <f>IF(C17=0,"-",(D17+E17)/C17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10">
-        <f>SUM(C5:C16)</f>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10">
+        <f>SUM(C5:C17)</f>
         <v/>
       </c>
-      <c r="D17" s="10">
-        <f>SUM(D5:D16)</f>
+      <c r="D18" s="10">
+        <f>SUM(D5:D17)</f>
         <v/>
       </c>
-      <c r="E17" s="10">
-        <f>SUM(E5:E16)</f>
+      <c r="E18" s="10">
+        <f>SUM(E5:E17)</f>
         <v/>
       </c>
-      <c r="F17" s="10">
-        <f>SUM(F5:F16)</f>
+      <c r="F18" s="10">
+        <f>SUM(F5:F17)</f>
         <v/>
       </c>
-      <c r="G17" s="10">
-        <f>SUM(G5:G16)</f>
+      <c r="G18" s="10">
+        <f>SUM(G5:G17)</f>
         <v/>
       </c>
-      <c r="H17" s="11">
-        <f>IF(C17=0,"-",(D17+E17)/C17)</f>
+      <c r="H18" s="11">
+        <f>IF(C18=0,"-",(D18+E18)/C18)</f>
         <v/>
       </c>
     </row>
@@ -15673,7 +16412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -16140,92 +16879,114 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>PO review (2026-10-02)</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Some parts of life have no natural sub-areas: in Career / Office / Work, things like "Connect with Amex Project - BA" are tasks, not places, so an extra area level only adds taps</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>A tile can switch areas off and hold its tasks, rewards and notes directly (HLR-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
           <t>D10</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PO review of MVP (2026-09-28)</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Rewards float free of the tile/area structure: a reward can be tagged to any task anywhere, so it isn't clear which part of life a reward belongs to</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Rewards use the same tiles and areas as tasks, and are matched to tasks inside that scope (HLR-9)</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>2.4 Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>• A1. Single user for the MVP; data is personal and low volume (&lt; 1k tasks, &lt; 50k completions).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>• A2. The user's calendar is one timezone (Asia/Kolkata by default).</t>
+          <t>• A1. Single user for the MVP; data is personal and low volume (&lt; 1k tasks, &lt; 50k completions).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>• A3. Rewards are self-fulfilled. There's no purchasing or payment integration.</t>
+          <t>• A2. The user's calendar is one timezone (Asia/Kolkata by default).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
+          <t>• A3. Rewards are self-fulfilled. There's no purchasing or payment integration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
           <t>• A4. The host site remains Vite + React 19 with hash routing.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>2.5 Constraints</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>• C1. Existing Vercel deployment of the host must keep building (npm run build → dist).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>• C2. Solo developer, capstone timeline; prefer managed or zero-ops components.</t>
+          <t>• C1. Existing Vercel deployment of the host must keep building (npm run build → dist).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>• C3. AI API keys must never reach the browser.</t>
+          <t>• C2. Solo developer, capstone timeline; prefer managed or zero-ops components.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>• C3. AI API keys must never reach the browser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>• C4. Out of scope: Android build, real auth, multi-user, other microfrontends, WhatsApp/Apify/Snowflake integrations.</t>
         </is>
@@ -16475,7 +17236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -17142,29 +17903,29 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3g</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Deploy the MFE + BFF; set the host's remote URL; merge to main</t>
+          <t>Tiles without areas (HLR-13), shipped as a data-preserving migration (0006_tile_without_areas)</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅ (branch)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Integration services: vision → events/outbox → reminders</t>
+          <t>Deploy the MFE + BFF; set the host's remote URL; merge to main</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -17176,23 +17937,40 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Integration services: vision → events/outbox → reminders</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Mobile BFF surface; Android client</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>⏳ future</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>No data migration from Neo4j is planned. The old feature held no production data worth carrying over (its auth gate was disabled and the new model differs). Confirm before T4.</t>
         </is>
@@ -17320,7 +18098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -17700,22 +18478,22 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>HLR-5</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Insights dashboard</t>
+          <t>Tiles without areas</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Aggregates, filters, cached reads, claim from dashboard</t>
+          <t>A tile can switch areas off (e.g. Career / Office / Work): it then opens straight to Tasks, Rewards and Notes &amp; contacts, and tasks can be moved between tiles and areas</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.x</t>
+          <t>LLR-13.x</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -17727,223 +18505,250 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>HLR-6</t>
+          <t>HLR-5</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>AI task suggestions</t>
+          <t>Insights dashboard</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Photos → suggestions → decisions → tasks; non-blocking</t>
+          <t>Aggregates, filters, cached reads, claim from dashboard</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.x</t>
+          <t>LLR-5.x</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>HLR-7</t>
+          <t>HLR-6</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Module composition</t>
+          <t>AI task suggestions</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Independently delivered MFE with host fallback</t>
+          <t>Photos → suggestions → decisions → tasks; non-blocking</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.x</t>
+          <t>LLR-6.x</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>⏳</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
+          <t>HLR-7</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Module composition</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Independently delivered MFE with host fallback</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>LLR-7.x</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
           <t>HLR-8</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>API (BFF)</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Versionable, documented, client-shaped API with demo auth</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>LLR-8.x</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>6.3 High-level non-functional requirements</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Requirement</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>HNFR-1</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Usability</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Mobile-first; every primary action reachable in ≤ 3 taps from the area screen</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>HNFR-2</t>
+          <t>HNFR-1</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Resilience</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>No single dependency failure (remote, BFF, AI) blanks the host page</t>
+          <t>Mobile-first; every primary action reachable in ≤ 3 taps from the area screen</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>HNFR-3</t>
+          <t>HNFR-2</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Resilience</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Rewards screen interactive ≤ 2 s on local/broadband; dashboard cached reads</t>
+          <t>No single dependency failure (remote, BFF, AI) blanks the host page</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>HNFR-4</t>
+          <t>HNFR-3</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Secrets server-side only; CORS allow-list; private photo storage</t>
+          <t>Rewards screen interactive ≤ 2 s on local/broadband; dashboard cached reads</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>HNFR-5</t>
+          <t>HNFR-4</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>WCAG 2.2 AA intent: labels, focus, live regions, contrast, reduced motion</t>
+          <t>Secrets server-side only; CORS allow-list; private photo storage</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>HNFR-6</t>
+          <t>HNFR-5</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Typed contracts; pure, unit-tested business rules; ≥ 1 test per business rule</t>
+          <t>WCAG 2.2 AA intent: labels, focus, live regions, contrast, reduced motion</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
+          <t>HNFR-6</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Typed contracts; pure, unit-tested business rules; ≥ 1 test per business rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
           <t>HNFR-7</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Portability</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>HTTP/JSON only between tiers; storage swappable (SQLite → Postgres)</t>
         </is>

--- a/docs/rewards/Rewards_HLRD_LLRD.xlsx
+++ b/docs/rewards/Rewards_HLRD_LLRD.xlsx
@@ -29,7 +29,7 @@
     <sheet name="LLRD 7. Traceability matrix" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements Register'!$A$4:$J$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements Register'!$A$4:$J$208</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-02 from docs/rewards/HLRD.md and docs/rewards/LLRD.md.</t>
+          <t>Generated 2026-10-03 from docs/rewards/HLRD.md and docs/rewards/LLRD.md.</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1116,6 +1116,13 @@
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>• (HLR-13) Career / Office / Work has areas switched off: opening it shows its tasks straight away ("Connect with Amex Project - BA", "Learning", …), and a new task is added right there with no area to pick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>• (HLR-2, D16) In Household › Kitchen, drag "Wipe the counters" from the bottom to the top: it stays first after a reload, on the phone too, and appears first under Kitchen on the Tasks screen. A newly added task appears at the bottom.</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C305"/>
+  <dimension ref="A1:C316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -2697,7 +2704,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Create a task with title (1–200 characters, required), notes (≤ 2000), priority (high/medium/low, default medium) and frequency (daily/weekly/one_off, default weekly). Source = manual; status = active; relevance = relevant</t>
+          <t>Create a task with title (1–200 characters, required), notes (≤ 2000) and frequency (daily/weekly/one_off, default weekly). Source = manual; status = active; relevance = relevant. No priority is asked for: a new task goes to the bottom of its area's list (D16, BR-R32)</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -2714,7 +2721,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>After creating a task, the form keeps the chosen priority and frequency for the next entry and clears the title and notes</t>
+          <t>After creating a task, the form keeps the chosen frequency for the next entry and clears the title and notes</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -2731,7 +2738,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>An area's task list is sorted by priority (high → low), then by creation time</t>
+          <t>An area's (or a tile without areas') task list is in the user's own order: top = most important, bottom = least (BR-R32)</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -2748,7 +2755,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Filter by priority, status and relevance, singly or combined. The default view is status = active</t>
+          <t>Filter by status, relevance, milestone and due (overdue / today / this week), singly or combined. The default view is status = active. The priority filter is removed</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -2765,7 +2772,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Reprioritise from the list (inline select) or from task detail</t>
+          <t>Drag to reorder: each task row has a ⠿ handle that works with mouse and touch (phone); the new order is saved at once (PUT /areas/{id}/tasks/order). Keyboard and screen-reader users get *Move up* / *Move down* on the handle (arrow keys). Replaces the inline High/Med/Low select</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -2845,12 +2852,12 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.10</t>
+          <t>LLR-2.11</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Edit a task from task detail (✎): title and notes. Delete a task (🗑) after a confirmation that names its completion count; its completions and reward tags go with it, the rewards themselves stay (DELETE /tasks/{id})</t>
+          <t>Dragging is available only in the default view (active tasks, no filters, *My order*). With a filter or *Sort by due date* on, the list shows a note "Clear filters to reorder" and has no handles, so the saved order is never changed by accident</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -2859,194 +2866,154 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>LLR-2.12</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>The order is shared by every list of the area's tasks: the area tab, the Tasks screen (each area group in its own order, areas in tile › area order) and the Link screen's task picker</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>AC-2.3</t>
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>LLR-2.13</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>A task moved to another tile or area (LLR-13.7) goes to the bottom there. A done or archived task keeps its place; if reactivated it reappears where it was</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a low-priority task created before a high-priority one *when* the list loads *then* the high one is first.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>AC-2.4</t>
-        </is>
-      </c>
-    </row>
+          <t>LLR-2.14</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Existing data is kept: migration adds tasks.sort_order, initialised per area from today's order (priority high → low, then creation time), with a backup first. The old priority value stays in the database and the JSON export but is no longer shown or used</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>LLR-2.10</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Edit a task from task detail (✎): title and notes. Delete a task (🗑) after a confirmation that names its completion count; its completions and reward tags go with it, the rewards themselves stay (DELETE /tasks/{id})</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* one task is archived *when* filtering status = active *then* only the other task shows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>AC-2.3 / 2.5 (D16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* tasks A, B, C in that order *when* the user drags C above A *then* the list shows C, A, B, and still does after a reload and on another device.</t>
+        </is>
+      </c>
+    </row>
     <row r="55">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>LLR-3 Completion, activity log and streaks (HLR-3)</t>
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* the same area *when* the user adds task D *then* D is last.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* *Sort by due date* is on *then* there are no drag handles and the saved order is unchanged.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.1</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Complete an active task, optionally with a note (≤ 1000) and a time (completedAt). If no time is given, the time is now</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>LLR-3.2</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Logging uses a month calendar: days the task was done are marked (with a count when more than once), today is outlined, future days are disabled, and ‹ › move between months. Tap a day, adjust the time (defaults to now), add an optional note and log. A time later than now is clamped to now</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-    </row>
+          <t>• *Given* an existing area whose tasks were High, Low, Medium (created in that order) *when* the migration runs *then* the order is High, Medium, Low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>LLR-3.3</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>A completion more than 1 minute in the future is rejected (422)</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>AC-2.4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.4</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Completing a one-off task sets it to done. Further completions are rejected (409)</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>LLR-3.5</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Completing a done or archived task is rejected with a message naming its status (409)</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
+          <t>• *Given* one task is archived *when* filtering status = active *then* only the other task shows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>LLR-3.6</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>The activity log lists completions newest first, with local date/time and note</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>Business rules: task order (D16)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>LLR-3.7</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Each task shows completion count, current streak, best streak and last completion time</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Rule</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.8</t>
+          <t>BR-R32</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>The area list offers a one-tap ✓ complete (now) for active tasks</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
+          <t>Each area (or tile without areas) has one task order, set only by the user: top = most important. Nothing reorders tasks automatically: not adding (goes last), completing, editing, filtering or sorting by due date. A reorder must list every active task of the area exactly once</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3021,7 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>Business rules: streaks</t>
+          <t>LLR-3 Completion, activity log and streaks (HLR-3)</t>
         </is>
       </c>
     </row>
@@ -3066,276 +3033,276 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>BR-R1</t>
+          <t>LLR-3.1</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>A period is a local calendar day (daily) or a Monday–Sunday week (weekly) in BFF_TIMEZONE</t>
+          <t>Complete an active task, optionally with a note (≤ 1000) and a time (completedAt). If no time is given, the time is now</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>BR-R2</t>
+          <t>LLR-3.2</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Several completions in one period count once towards the streak (they all count towards completion count)</t>
+          <t>Logging uses a month calendar: days the task was done are marked (with a count when more than once), today is outlined, future days are disabled, and ‹ › move between months. Tap a day, adjust the time (defaults to now), add an optional note and log. A time later than now is clamped to now</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>BR-R3</t>
+          <t>LLR-3.3</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Best streak = longest run of consecutive periods with ≥ 1 completion</t>
+          <t>A completion more than 1 minute in the future is rejected (422)</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>BR-R4</t>
+          <t>LLR-3.4</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Current streak = the run ending at the latest completed period, if that period is the current or the previous one; otherwise 0</t>
+          <t>Completing a one-off task sets it to done. Further completions are rejected (409)</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>BR-R5</t>
+          <t>LLR-3.5</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>One-off tasks: streak = 1 once completed, else 0 (not shown as an active streak)</t>
+          <t>Completing a done or archived task is rejected with a message naming its status (409)</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>BR-R6</t>
+          <t>LLR-3.6</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Streaks are derived from the activity log on every read (never stored)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
+          <t>The activity log lists completions newest first, with local date/time and note</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>LLR-3.7</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Each task shows completion count, current streak, best streak and last completion time</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
-        <is>
-          <t>AC-3 (streak)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* a daily task *when* completed yesterday and then today *then* current = 2 and best = 2.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>LLR-3.8</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>The area list offers a one-tap ✓ complete (now) for active tasks</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
     <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* the same task completed again today *then* current stays 2 and completion count becomes 3.</t>
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>Business rules: streaks</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* last completion 2 days ago (none yesterday) *then* current = 0 and best keeps its value.</t>
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Rule</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a weekly task done this Monday and last Sunday *then* current = 2 (different weeks).</t>
-        </is>
-      </c>
-    </row>
-    <row r="80"/>
+          <t>BR-R1</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>A period is a local calendar day (daily) or a Monday–Sunday week (weekly) in BFF_TIMEZONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>BR-R2</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Several completions in one period count once towards the streak (they all count towards completion count)</t>
+        </is>
+      </c>
+    </row>
     <row r="81">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>LLR-4 Rewards (HLR-4)</t>
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>BR-R3</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Best streak = longest run of consecutive periods with ≥ 1 completion</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>BR-R4</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Current streak = the run ending at the latest completed period, if that period is the current or the previous one; otherwise 0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.1</t>
+          <t>BR-R5</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Create a reward: title (1–200, required), description (≤ 2000), image URL (≤ 500, optional), rule type (completions or streak), threshold N (1–365), tagged tasks (optional)</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>One-off tasks: streak = 1 once completed, else 0 (not shown as an active streak)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.2</t>
+          <t>BR-R6</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Tag or untag tasks as a full replacement of the set. Unknown task ids are rejected (422)</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>LLR-4.3</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Tag a task to a locked reward from the task detail screen</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-    </row>
+          <t>Streaks are derived from the activity log on every read (never stored)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85"/>
     <row r="86">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>LLR-4.4</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Show each reward's rule text, progress (current / target, %), status and tagged tasks</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>AC-3 (streak)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.5</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Filter the rewards list by status</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* a daily task *when* completed yesterday and then today *then* current = 2 and best = 2.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.6</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>Claim is only possible when the status is unlocked. Claiming a locked reward is rejected (409). Claiming an already claimed reward changes nothing</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* the same task completed again today *then* current stays 2 and completion count becomes 3.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.7</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>When a completion unlocks a reward, the completion response includes it and the UI shows a celebration toast</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* last completion 2 days ago (none yesterday) *then* current = 0 and best keeps its value.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.8</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Editing a reward's tasks is only offered while it's locked</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
+          <t>• *Given* a weekly task done this Monday and last Sunday *then* current = 2 (different weeks).</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3310,7 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>Rewards, areas and links (HLR-9, revised 2026-09-30) ✅</t>
+          <t>LLR-4 Rewards (HLR-4)</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3334,12 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.9</t>
+          <t>LLR-4.1</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>Rewards stand alone. A reward needs only a title and N (default 5); a note and picture link are optional. It can optionally be kept in an area (to organise it; its tile comes from the area), but that never limits which tasks it can be linked to</t>
+          <t>Create a reward: title (1–200, required), description (≤ 2000), image URL (≤ 500, optional), rule type (completions or streak), threshold N (1–365), tagged tasks (optional)</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
@@ -3384,12 +3351,12 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.10</t>
+          <t>LLR-4.2</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Links are many-to-many and unrestricted: any task (from any tile or area) can be linked to any reward; one task can count for several rewards. Unlock rule for now: task count, the linked tasks done N times in total. (Older rewards that counted "all tasks in an area" keep working)</t>
+          <t>Tag or untag tasks as a full replacement of the set. Unknown task ids are rejected (422)</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -3401,29 +3368,29 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.11</t>
+          <t>LLR-4.3</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>Linking twice is harmless; unlinking an unlocked or claimed reward doesn't lock it again (BR-R10); deleting a task, area or tile removes only its links, and rewards stay. Deleting a tile does delete rewards kept in it (BR-R18)</t>
+          <t>Tag a task to a locked reward from the task detail screen</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.12</t>
+          <t>LLR-4.4</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>The Link screen (#/rewards/link, top menu *Link*) lists all tasks (grouped by tile › area, with how often each was done and how many rewards it counts for) and all rewards (with area, N and status), each searchable. Pick a task and a reward, then Link (or Unlink if they already are). *Current links* lists each linked reward with its tasks, each with ✕ to unlink. Opens with a task or reward already picked from the task or reward screens</t>
+          <t>Show each reward's rule text, progress (current / target, %), status and tagged tasks</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -3435,12 +3402,12 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.13</t>
+          <t>LLR-4.5</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>The top menu is Tiles | Tasks | Rewards | Link. *Tasks* lists every task grouped by tile › area (status filter, default Active; search; each row shows frequency, completions, streak 🔥 and rewards 🎁, with a quick ✓). *Rewards* lists every reward grouped by the area it's kept in (tile › area order, *Not in an area* last; status filter; search; + New with an optional area). The Link screen's two lists use the same grouping. A tile shows only its areas; an area has tabs Tasks | Rewards | Notes &amp; contacts, and its Rewards tab lists and adds the rewards kept there but doesn't link tasks</t>
+          <t>Filter the rewards list by status</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
@@ -3452,12 +3419,12 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.14</t>
+          <t>LLR-4.6</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>A reward's screen (#/rewards/r/{id}) shows its rule, progress and linked tasks (✕ to unlink), *+ Link tasks* (Link screen with this reward picked), *Claim 🎁* when unlocked, and ✎ / 🗑 to edit (title, N while locked, area, note, picture) or delete it (tasks and history stay)</t>
+          <t>Claim is only possible when the status is unlocked. Claiming a locked reward is rejected (409). Claiming an already claimed reward changes nothing</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -3469,12 +3436,12 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.15</t>
+          <t>LLR-4.7</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>On task detail, the *Rewards* card lists the rewards the task counts for (links to each reward) and *+ Link to a reward* opens the Link screen with this task picked</t>
+          <t>When a completion unlocks a reward, the completion response includes it and the UI shows a celebration toast</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
@@ -3486,771 +3453,771 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.16</t>
+          <t>LLR-4.8</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>N can be changed only while the reward is locked; lowering it re-checks the rule at once. A reward whose linked tasks already meet N unlocks as soon as it's linked</t>
+          <t>Editing a reward's tasks is only offered while it's locked</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
+          <t>🟡</t>
+        </is>
+      </c>
+    </row>
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" s="13" t="inlineStr">
+        <is>
+          <t>Rewards, areas and links (HLR-9, revised 2026-09-30) ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>LLR-4.9</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Rewards stand alone. A reward needs only a title and N (default 5); a note and picture link are optional. It can optionally be kept in an area (to organise it; its tile comes from the area), but that never limits which tasks it can be linked to</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
           <t>✅</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>LLR-4.17</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Moving a reward to another area, or out of any area, never changes its links</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>LLR-4.10</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Links are many-to-many and unrestricted: any task (from any tile or area) can be linked to any reward; one task can count for several rewards. Unlock rule for now: task count, the linked tasks done N times in total. (Older rewards that counted "all tasks in an area" keep working)</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t>LLR-4.18</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>Existing rewards are migrated without data loss (schema migration with automatic pre-upgrade backup): if all tagged tasks share one area, scope = that area; else if they share one tile, scope = that tile; otherwise (no tags, or tags across tiles) the reward keeps its tags and is marked *Needs a tile* until the user picks one. No reward, tag, completion or status is deleted</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105">
-      <c r="A105" s="13" t="inlineStr">
-        <is>
-          <t>Business rules: rewards</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>Rule</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>BR-R7</t>
+          <t>LLR-4.11</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>*Completions* rule progress = total completions of all tagged tasks (all-time)</t>
+          <t>Linking twice is harmless; unlinking an unlocked or claimed reward doesn't lock it again (BR-R10); deleting a task, area or tile removes only its links, and rewards stay. Deleting a tile does delete rewards kept in it (BR-R18)</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>BR-R8</t>
+          <t>LLR-4.12</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>*Streak* rule progress = the highest current streak among tagged tasks</t>
+          <t>The Link screen (#/rewards/link, top menu *Link*) lists all tasks (grouped by tile › area, with how often each was done and how many rewards it counts for) and all rewards (with area, N and status), each searchable. Pick a task and a reward, then Link (or Unlink if they already are). *Current links* lists each linked reward with its tasks, each with ✕ to unlink. Opens with a task or reward already picked from the task or reward screens</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>BR-R9</t>
+          <t>LLR-4.13</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>The unlock check runs on task completion, reward creation, reward update and tag change</t>
+          <t>The top menu is Tiles | Tasks | Rewards | Link. *Tasks* lists every task grouped by tile › area (status filter, default Active; search; each row shows frequency, completions, streak 🔥 and rewards 🎁, with a quick ✓). *Rewards* lists every reward grouped by the area it's kept in (tile › area order, *Not in an area* last; status filter; search; + New with an optional area). The Link screen's two lists use the same grouping. A tile shows only its areas; an area has tabs Tasks | Rewards | Notes &amp; contacts, and its Rewards tab lists and adds the rewards kept there but doesn't link tasks</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>BR-R10</t>
+          <t>LLR-4.14</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>Status flow locked → unlocked → claimed only; there's no path back</t>
+          <t>A reward's screen (#/rewards/r/{id}) shows its rule, progress and linked tasks (✕ to unlink), *+ Link tasks* (Link screen with this reward picked), *Claim 🎁* when unlocked, and ✎ / 🗑 to edit (title, N while locked, area, note, picture) or delete it (tasks and history stay)</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>BR-R11</t>
+          <t>LLR-4.15</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Unlocked and claimed rewards always show 100 %</t>
+          <t>On task detail, the *Rewards* card lists the rewards the task counts for (links to each reward) and *+ Link to a reward* opens the Link screen with this task picked</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>BR-R12</t>
+          <t>LLR-4.16</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>Scope containment. A task is in a reward's scope when the task's area belongs to the reward's tile and, if the reward has an area, the task's area *is* that area</t>
+          <t>N can be changed only while the reward is locked; lowering it re-checks the rule at once. A reward whose linked tasks already meet N unlocks as soon as it's linked</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>BR-R13</t>
+          <t>LLR-4.17</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Matched tasks. *Selected tasks*: the tagged tasks (all in scope). *All tasks in scope*: every task in scope whose status isn't archived. BR-R7 and BR-R8 compute progress over the matched tasks</t>
+          <t>Moving a reward to another area, or out of any area, never changes its links</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>BR-R14</t>
+          <t>LLR-4.18</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>In *All tasks in scope* mode, tags are ignored for progress (they're kept, so switching back to *Selected tasks* restores them)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="7" t="inlineStr">
-        <is>
-          <t>BR-R15</t>
-        </is>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>The unlock check (BR-R9) on completion evaluates every locked reward that matches the completed task, whether tagged or by scope</t>
-        </is>
-      </c>
-    </row>
+          <t>Existing rewards are migrated without data loss (schema migration with automatic pre-upgrade backup): if all tagged tasks share one area, scope = that area; else if they share one tile, scope = that tile; otherwise (no tags, or tags across tiles) the reward keeps its tags and is marked *Needs a tile* until the user picks one. No reward, tag, completion or status is deleted</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="115"/>
     <row r="116">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t>BR-R16</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>A reward marked *Needs a tile* (LLR-4.18) still shows progress from its tags, but can't be edited until a tile is chosen. It never unlocks from tasks outside the tile the user then picks</t>
-        </is>
-      </c>
-    </row>
-    <row r="117"/>
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>Business rules: rewards</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+    </row>
     <row r="118">
-      <c r="A118" s="13" t="inlineStr">
-        <is>
-          <t>AC-4b (scope and matching)</t>
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>BR-R7</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>*Completions* rule progress = total completions of all tagged tasks (all-time)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a reward scoped to Household › Kitchen *when* the user tries to tag the Laundry task *then* it's rejected: "“Wash whites” isn't in Household › Kitchen" (422).</t>
+          <t>BR-R8</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>*Streak* rule progress = the highest current streak among tagged tasks</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a reward "Weekend brunch" scoped to Household with *All tasks in scope*, 3 completions *when* the user completes any Household task (Kitchen or Laundry) *then* progress counts it without tagging. A Career task never counts.</t>
+          <t>BR-R9</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>The unlock check runs on task completion, reward creation, reward update and tag change</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a new Kitchen task is created after the reward *when* it's completed *then* it counts towards the Household reward immediately.</t>
+          <t>BR-R10</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>Status flow locked → unlocked → claimed only; there's no path back</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the Kitchen area screen *then* "Rewards you can earn here" lists rewards scoped to Household › Kitchen and to Household, not Fun or Household › Laundry.</t>
+          <t>BR-R11</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>Unlocked and claimed rewards always show 100 %</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>• *Given* an existing reward tagged only to Kitchen tasks *when* the migration runs *then* its scope becomes Household › Kitchen, and its tags, progress and status are unchanged.</t>
+          <t>BR-R12</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>Scope containment. A task is in a reward's scope when the task's area belongs to the reward's tile and, if the reward has an area, the task's area *is* that area</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the Kitchen area is deleted *then* a reward scoped to Household › Kitchen becomes scoped to Household and keeps its status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125"/>
+          <t>BR-R13</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>Matched tasks. *Selected tasks*: the tagged tasks (all in scope). *All tasks in scope*: every task in scope whose status isn't archived. BR-R7 and BR-R8 compute progress over the matched tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>BR-R14</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>In *All tasks in scope* mode, tags are ignored for progress (they're kept, so switching back to *Selected tasks* restores them)</t>
+        </is>
+      </c>
+    </row>
     <row r="126">
-      <c r="A126" s="13" t="inlineStr">
-        <is>
-          <t>AC-4 (demo flow)</t>
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>BR-R15</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>The unlock check (BR-R9) on completion evaluates every locked reward that matches the completed task, whether tagged or by scope</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a task with 2 completions and a locked "3 completions" reward *when* the reward is tagged to the task *then* progress = 2/3 (67 %).</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="7" t="inlineStr">
-        <is>
-          <t>• *When* the task is completed once more *then* the response lists the reward as unlocked and the UI shows "🎉 Reward unlocked: &lt;title&gt;".</t>
-        </is>
-      </c>
-    </row>
+          <t>BR-R16</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>A reward marked *Needs a tile* (LLR-4.18) still shows progress from its tags, but can't be edited until a tile is chosen. It never unlocks from tasks outside the tile the user then picks</t>
+        </is>
+      </c>
+    </row>
+    <row r="128"/>
     <row r="129">
-      <c r="A129" s="7" t="inlineStr">
-        <is>
-          <t>• *When* the user claims it *then* the status is claimed and claimedAt is set.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130"/>
+      <c r="A129" s="13" t="inlineStr">
+        <is>
+          <t>AC-4b (scope and matching)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* a reward scoped to Household › Kitchen *when* the user tries to tag the Laundry task *then* it's rejected: "“Wash whites” isn't in Household › Kitchen" (422).</t>
+        </is>
+      </c>
+    </row>
     <row r="131">
-      <c r="A131" s="13" t="inlineStr">
-        <is>
-          <t>LLR-5 Insights dashboard (HLR-5)</t>
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* a reward "Weekend brunch" scoped to Household with *All tasks in scope*, 3 completions *when* the user completes any Household task (Kitchen or Laundry) *then* progress counts it without tagging. A Career task never counts.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* a new Kitchen task is created after the reward *when* it's completed *then* it counts towards the Household reward immediately.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.1</t>
-        </is>
-      </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>Reads only GET /dashboard/summary; never the database</t>
-        </is>
-      </c>
-      <c r="C133" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* the Kitchen area screen *then* "Rewards you can earn here" lists rewards scoped to Household › Kitchen and to Household, not Fun or Household › Laundry.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.2</t>
-        </is>
-      </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>KPIs: completions (window), active tasks, active streaks, unlocked + claimed rewards, AI acceptance rate (— when undefined)</t>
-        </is>
-      </c>
-      <c r="C134" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
+          <t>• *Given* an existing reward tagged only to Kitchen tasks *when* the migration runs *then* its scope becomes Household › Kitchen, and its tags, progress and status are unchanged.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.3</t>
-        </is>
-      </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>Charts: completions by tile, by area (filterable by tile) and per day (empty days shown as gaps). Hover tooltips on every mark</t>
-        </is>
-      </c>
-      <c r="C135" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>LLR-5.4</t>
-        </is>
-      </c>
-      <c r="B136" s="7" t="inlineStr">
-        <is>
-          <t>Tables: active streaks (filterable by tile); reward progress with a progress bar</t>
-        </is>
-      </c>
-      <c r="C136" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-    </row>
+          <t>• *Given* the Kitchen area is deleted *then* a reward scoped to Household › Kitchen becomes scoped to Household and keeps its status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136"/>
     <row r="137">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>LLR-5.5</t>
-        </is>
-      </c>
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>Filters: window (7/30/90 days/all time) and tile. They survive reruns (session_state)</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
+      <c r="A137" s="13" t="inlineStr">
+        <is>
+          <t>AC-4 (demo flow)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.6</t>
-        </is>
-      </c>
-      <c r="B138" s="7" t="inlineStr">
-        <is>
-          <t>Responses are cached 30 s per window. *Refresh now* clears the cache</t>
-        </is>
-      </c>
-      <c r="C138" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
+          <t>• *Given* a task with 2 completions and a locked "3 completions" reward *when* the reward is tagged to the task *then* progress = 2/3 (67 %).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.7</t>
-        </is>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
-        <is>
-          <t>Unlocked rewards can be claimed from the dashboard. After claiming, the cache is cleared and the page shows fresh data</t>
-        </is>
-      </c>
-      <c r="C139" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
+          <t>• *When* the task is completed once more *then* the response lists the reward as unlocked and the UI shows "🎉 Reward unlocked: &lt;title&gt;".</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.8</t>
-        </is>
-      </c>
-      <c r="B140" s="7" t="inlineStr">
-        <is>
-          <t>If the BFF is unreachable, show the error and *Try again* (no stack traces)</t>
-        </is>
-      </c>
-      <c r="C140" s="7" t="inlineStr">
+          <t>• *When* the user claims it *then* the status is claimed and claimedAt is set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141"/>
+    <row r="142">
+      <c r="A142" s="13" t="inlineStr">
+        <is>
+          <t>LLR-5 Insights dashboard (HLR-5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>LLR-5.1</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>Reads only GET /dashboard/summary; never the database</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>LLR-5.2</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>KPIs: completions (window), active tasks, active streaks, unlocked + claimed rewards, AI acceptance rate (— when undefined)</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>LLR-5.9</t>
-        </is>
-      </c>
-      <c r="B141" s="7" t="inlineStr">
-        <is>
-          <t>Streaks and rewards ignore the window; completion aggregates respect it</t>
-        </is>
-      </c>
-      <c r="C141" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>LLR-5.10</t>
-        </is>
-      </c>
-      <c r="B142" s="7" t="inlineStr">
-        <is>
-          <t>Summary payload is flat snake_case records; React endpoints are camelCase (per-client shaping)</t>
-        </is>
-      </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t>LLR-5.11</t>
-        </is>
-      </c>
-      <c r="B143" s="7" t="inlineStr">
-        <is>
-          <t>Reward progress rows include the reward's tile and area; the dashboard's tile filter applies to rewards as well as completions and streaks</t>
-        </is>
-      </c>
-      <c r="C143" s="7" t="inlineStr">
-        <is>
-          <t>⏳ (HLR-9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144"/>
-    <row r="145">
-      <c r="A145" s="13" t="inlineStr">
-        <is>
-          <t>LLR-6 AI task suggestions (HLR-6) ⏳</t>
-        </is>
-      </c>
-    </row>
     <row r="146">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>Requirement</t>
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>LLR-5.3</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>Charts: completions by tile, by area (filterable by tile) and per day (empty days shown as gaps). Hover tooltips on every mark</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.1</t>
+          <t>LLR-5.4</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>Attach 1–5 photos per run to an area (JPEG/PNG/WebP, ≤ 5 MB each; type checked by content, not extension)</t>
+          <t>Tables: active streaks (filterable by tile); reward progress with a progress bar</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.2</t>
+          <t>LLR-5.5</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>Photos are stored privately with random names and are never publicly addressable</t>
+          <t>Filters: window (7/30/90 days/all time) and tile. They survive reruns (session_state)</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.3</t>
+          <t>LLR-5.6</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>Starting a suggestion run returns immediately (202) with a run id; the UI shows a loading state</t>
+          <t>Responses are cached 30 s per window. *Refresh now* clears the cache</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.4</t>
+          <t>LLR-5.7</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>While a run is in progress, the manual *Add a task* form stays fully usable</t>
+          <t>Unlocked rewards can be claimed from the dashboard. After claiming, the cache is cleared and the page shows fresh data</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.5</t>
+          <t>LLR-5.8</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>Each suggestion has a title (≤ 200), why (≤ 500), priority and frequency, validated against a strict schema</t>
+          <t>If the BFF is unreachable, show the error and *Try again* (no stack traces)</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.6</t>
+          <t>LLR-5.9</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>The user marks each suggestion Relevant / Not relevant / Ignore. Relevant creates a task with source = ai. A decision is final (409 on re-decide)</t>
+          <t>Streaks and rewards ignore the window; completion aggregates respect it</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.7</t>
+          <t>LLR-5.10</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>On timeout (30 s), invalid output or missing API key: retry once where sensible, then show "AI suggestions unavailable, add tasks manually". The page never breaks</t>
+          <t>Summary payload is flat snake_case records; React endpoints are camelCase (per-client shaping)</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.8</t>
+          <t>LLR-5.11</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>The API key exists only in BFF environment variables</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>LLR-6.9</t>
-        </is>
-      </c>
-      <c r="B155" s="7" t="inlineStr">
-        <is>
-          <t>Decisions feed the dashboard acceptance rate (relevant ÷ decided)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156"/>
+          <t>Reward progress rows include the reward's tile and area; the dashboard's tile filter applies to rewards as well as completions and streaks</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>⏳ (HLR-9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155"/>
+    <row r="156">
+      <c r="A156" s="13" t="inlineStr">
+        <is>
+          <t>LLR-6 AI task suggestions (HLR-6) ⏳</t>
+        </is>
+      </c>
+    </row>
     <row r="157">
-      <c r="A157" s="13" t="inlineStr">
-        <is>
-          <t>LLR-7 Module composition (HLR-7)</t>
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>Requirement</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>LLR-6.1</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>Attach 1–5 photos per run to an area (JPEG/PNG/WebP, ≤ 5 MB each; type checked by content, not extension)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.1</t>
+          <t>LLR-6.2</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>The MFE is built separately and exposes ./RewardsApp via remoteEntry.js</t>
-        </is>
-      </c>
-      <c r="C159" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>Photos are stored privately with random names and are never publicly addressable</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.2</t>
+          <t>LLR-6.3</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>The host mounts it on #/rewards and every #/rewards/*. The nav item stays active on sub-routes</t>
-        </is>
-      </c>
-      <c r="C160" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
+          <t>Starting a suggestion run returns immediately (202) with a run id; the UI shows a loading state</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.3</t>
+          <t>LLR-6.4</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>Host and remote share one React instance; the remote bundles no React</t>
-        </is>
-      </c>
-      <c r="C161" s="7" t="inlineStr">
-        <is>
-          <t>🟡 (verified in browser)</t>
+          <t>While a run is in progress, the manual *Add a task* form stays fully usable</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.4</t>
+          <t>LLR-6.5</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>If the remote fails to load, the host shows "Rewards is unavailable right now" and a reload button. Other pages are unaffected</t>
-        </is>
-      </c>
-      <c r="C162" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
+          <t>Each suggestion has a title (≤ 200), why (≤ 500), priority and frequency, validated against a strict schema</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.5</t>
+          <t>LLR-6.6</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>MFE styles are scoped (.rw-app) and don't alter host styles</t>
-        </is>
-      </c>
-      <c r="C163" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
+          <t>The user marks each suggestion Relevant / Not relevant / Ignore. Relevant creates a task with source = ai. A decision is final (409 on re-decide)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.6</t>
+          <t>LLR-6.7</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
         <is>
-          <t>The remote URL is configurable per environment (VITE_REWARDS_REMOTE_URL)</t>
-        </is>
-      </c>
-      <c r="C164" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>On timeout (30 s), invalid output or missing API key: retry once where sensible, then show "AI suggestions unavailable, add tasks manually". The page never breaks</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.7</t>
+          <t>LLR-6.8</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>The MFE runs standalone for development (npm run dev)</t>
-        </is>
-      </c>
-      <c r="C165" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
+          <t>The API key exists only in BFF environment variables</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.8</t>
+          <t>LLR-6.9</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
         <is>
-          <t>Every screen has loading, error (with retry) and empty states</t>
-        </is>
-      </c>
-      <c r="C166" s="7" t="inlineStr">
-        <is>
-          <t>🟡</t>
+          <t>Decisions feed the dashboard acceptance rate (relevant ÷ decided)</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4225,7 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>LLR-8 BFF API (HLR-8)</t>
+          <t>LLR-7 Module composition (HLR-7)</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4249,12 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.1</t>
+          <t>LLR-7.1</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>Every endpoint except /health needs Authorization: Bearer &lt;demo token&gt;; otherwise 401</t>
+          <t>The MFE is built separately and exposes ./RewardsApp via remoteEntry.js</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
@@ -4299,80 +4266,80 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.2</t>
+          <t>LLR-7.2</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>CORS allows only the configured origins</t>
+          <t>The host mounts it on #/rewards and every #/rewards/*. The nav item stays active on sub-routes</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.3</t>
+          <t>LLR-7.3</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t>OpenAPI documentation is served at /docs</t>
+          <t>Host and remote share one React instance; the remote bundles no React</t>
         </is>
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🟡 (verified in browser)</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.4</t>
+          <t>LLR-7.4</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>Errors use {detail} with status codes 401, 404, 409 and 422 as catalogued in LLD §3.3</t>
+          <t>If the remote fails to load, the host shows "Rewards is unavailable right now" and a reload button. Other pages are unaffected</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.5</t>
+          <t>LLR-7.5</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
         <is>
-          <t>Request bodies accept camelCase or snake_case. React responses are camelCase; dashboard responses are snake_case</t>
+          <t>MFE styles are scoped (.rw-app) and don't alter host styles</t>
         </is>
       </c>
       <c r="C174" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.6</t>
+          <t>LLR-7.6</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>Timestamps are ISO-8601 UTC in responses</t>
+          <t>The remote URL is configurable per environment (VITE_REWARDS_REMOTE_URL)</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
@@ -4384,97 +4351,71 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.7</t>
+          <t>LLR-7.7</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>POST /rewards needs only title (optional threshold = N, default 5, areaId, description, imageUrl, taskIds). GET /rewards (?status=, ?areaId=), GET / PATCH / DELETE /rewards/{id} (PATCH edits title, N, note, picture, areaId or null). POST / DELETE /rewards/{id}/tasks/{taskId} link and unlink one task; PUT /rewards/{id}/tasks replaces all links. Responses include the optional categoryId, categoryName, categoryIcon, areaId, areaName, plus tasks, connected and matchedTaskCount</t>
+          <t>The MFE runs standalone for development (npm run dev)</t>
         </is>
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🟡</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.8</t>
+          <t>LLR-7.8</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>Task detail's rewards lists every reward the task counts for, with how (tagged = linked, or scope for older all-tasks-in-an-area rewards)</t>
+          <t>Every screen has loading, error (with retry) and empty states</t>
         </is>
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="7" t="inlineStr">
-        <is>
-          <t>LLR-8.9</t>
-        </is>
-      </c>
-      <c r="B178" s="7" t="inlineStr">
-        <is>
-          <t>Schema changes are applied by versioned migrations on startup, never by dropping and recreating tables; a backup of the database file is written before each upgrade (Q14)</t>
-        </is>
-      </c>
-      <c r="C178" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
+          <t>🟡</t>
+        </is>
+      </c>
+    </row>
+    <row r="178"/>
     <row r="179">
-      <c r="A179" s="7" t="inlineStr">
-        <is>
-          <t>LLR-8.10</t>
-        </is>
-      </c>
-      <c r="B179" s="7" t="inlineStr">
-        <is>
-          <t>Tile endpoints: POST /categories, PATCH /categories/{id} (name, icon), DELETE /categories/{id}, PUT /categories/order and PUT /categories/{id}/areas/order, POST /categories/starter (LLR-1.8, returns what was added)</t>
-        </is>
-      </c>
-      <c r="C179" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A179" s="13" t="inlineStr">
+        <is>
+          <t>LLR-8 BFF API (HLR-8)</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="7" t="inlineStr">
-        <is>
-          <t>LLR-8.12</t>
-        </is>
-      </c>
-      <c r="B180" s="7" t="inlineStr">
-        <is>
-          <t>Task create/update accept isMilestone, visibility (announced | silent), dueAt (ISO date-time, optional) and targetDays (optional); GET /areas/{id}/tasks adds filters milestone=true and due=overdue|today|week and sort=due. Responses served without the passcode omit silent tasks entirely (BR-R23)</t>
-        </is>
-      </c>
-      <c r="C180" s="7" t="inlineStr">
-        <is>
-          <t>✅ (hiding silent tasks from visitors comes with the passcode)</t>
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.13</t>
+          <t>LLR-8.1</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>POST /rewards accepts status: "idea", forWhom, visibility, link and whereSeen; POST /rewards/{id}/activate (ruleType, threshold), /close (outcome: bought | dropped) and /reopen; PUT / DELETE /rewards/{id}/cover (multipart photo; served by a signed link like files); GET /rewards filters status=idea|closed and forWhom=; GET /rewards-people lists everyone for suggestions; ideas can't be linked or claimed (409)</t>
+          <t>Every endpoint except /health needs Authorization: Bearer &lt;demo token&gt;; otherwise 401</t>
         </is>
       </c>
       <c r="C181" s="7" t="inlineStr">
@@ -4486,12 +4427,12 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.11</t>
+          <t>LLR-8.2</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
         <is>
-          <t>Details endpoints for both owners (/categories/{id} and /areas/{id}): …/details (grouped by topic), …/notes, …/contacts, …/files (multipart upload); PATCH/DELETE on /notes/{id}, /contacts/{id}, /files/{id}; GET /files/{id}/download; GET /search?q=</t>
+          <t>CORS allows only the configured origins</t>
         </is>
       </c>
       <c r="C182" s="7" t="inlineStr">
@@ -4500,55 +4441,117 @@
         </is>
       </c>
     </row>
-    <row r="183"/>
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t>LLR-8.3</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>OpenAPI documentation is served at /docs</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
     <row r="184">
-      <c r="A184" s="13" t="inlineStr">
-        <is>
-          <t>LLR-10 Notes, contacts and files (HLR-10) ✅</t>
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t>LLR-8.4</t>
+        </is>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>Errors use {detail} with status codes 401, 404, 409 and 422 as catalogued in LLD §3.3</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="12" t="inlineStr">
-        <is>
-          <t>Each tile and each area has a *Notes &amp; contacts* section (Q16, Q18). Every note, contact and file can carry an optional topic (e.g. "Bosch Dishwasher", "Pest Control") that groups related items.</t>
-        </is>
-      </c>
-    </row>
-    <row r="186"/>
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>LLR-8.5</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>Request bodies accept camelCase or snake_case. React responses are camelCase; dashboard responses are snake_case</t>
+        </is>
+      </c>
+      <c r="C185" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>LLR-8.6</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>Timestamps are ISO-8601 UTC in responses</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
     <row r="187">
-      <c r="A187" s="13" t="inlineStr">
-        <is>
-          <t>LLR-10 Notes, contacts and files (HLR-10) ✅</t>
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>LLR-8.7</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>POST /rewards needs only title (optional threshold = N, default 5, areaId, description, imageUrl, taskIds). GET /rewards (?status=, ?areaId=), GET / PATCH / DELETE /rewards/{id} (PATCH edits title, N, note, picture, areaId or null). POST / DELETE /rewards/{id}/tasks/{taskId} link and unlink one task; PUT /rewards/{id}/tasks replaces all links. Responses include the optional categoryId, categoryName, categoryIcon, areaId, areaName, plus tasks, connected and matchedTaskCount</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t>LLR-8.8</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>Task detail's rewards lists every reward the task counts for, with how (tagged = linked, or scope for older all-tasks-in-an-area rewards)</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.1</t>
+          <t>LLR-8.9</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
         <is>
-          <t>The area screen has a Notes &amp; contacts tab (tiles no longer have their own tabs; older tile-level items stay stored and searchable) next to their main content. It lists topics as groups (items without a topic under "General"), each showing its contacts, files and notes</t>
+          <t>Schema changes are applied by versioned migrations on startup, never by dropping and recreating tables; a backup of the database file is written before each upgrade (Q14)</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
@@ -4560,12 +4563,12 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.2</t>
+          <t>LLR-8.10</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>Topic is free text (1–60 characters), optional, and offers existing topics from the same tile or area as suggestions, so "Bosch Dishwasher" isn't typed three different ways</t>
+          <t>Tile endpoints: POST /categories, PATCH /categories/{id} (name, icon), DELETE /categories/{id}, PUT /categories/order and PUT /categories/{id}/areas/order, POST /categories/starter (LLR-1.8, returns what was added)</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
@@ -4577,29 +4580,29 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.3</t>
+          <t>LLR-8.12</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
         <is>
-          <t>Contact: name (required, 1–80); organisation or brand (e.g. Bosch, Kent, IFB, LG); role (*Customer care*, *Service executive*, *Technician*, *Vendor or shop*, *Other*); up to 3 phone numbers with labels (mobile, toll-free, WhatsApp); email; website; last visit or contact date; notes (≤ 1000); topic</t>
+          <t>Task create/update accept isMilestone, visibility (announced | silent), dueAt (ISO date-time, optional) and targetDays (optional); GET /areas/{id}/tasks adds filters milestone=true and due=overdue|today|week and sort=due. Responses served without the passcode omit silent tasks entirely (BR-R23)</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>✅ (hiding silent tasks from visitors comes with the passcode)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.4</t>
+          <t>LLR-8.13</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t>Phone numbers are stored as entered and shown with actions: Call (tel:), WhatsApp (wa.me, for numbers marked WhatsApp) and Copy. Email gets Email (mailto:). All actions are one tap on a phone</t>
+          <t>POST /rewards accepts status: "idea", forWhom, visibility, link and whereSeen; POST /rewards/{id}/activate (ruleType, threshold), /close (outcome: bought | dropped) and /reopen; PUT / DELETE /rewards/{id}/cover (multipart photo; served by a signed link like files); GET /rewards filters status=idea|closed and forWhom=; GET /rewards-people lists everyone for suggestions; ideas can't be linked or claimed (409)</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
@@ -4611,12 +4614,12 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.5</t>
+          <t>LLR-8.11</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
         <is>
-          <t>Past executives: within a topic, contacts with the role *Service executive* or *Technician* are listed newest last-visit first. The topic header shows the last executive (name, date, call button)</t>
+          <t>Details endpoints for both owners (/categories/{id} and /areas/{id}): …/details (grouped by topic), …/notes, …/contacts, …/files (multipart upload); PATCH/DELETE on /notes/{id}, /contacts/{id}, /files/{id}; GET /files/{id}/download; GET /search?q=</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
@@ -4625,267 +4628,327 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="7" t="inlineStr">
-        <is>
-          <t>LLR-10.6</t>
-        </is>
-      </c>
-      <c r="B194" s="7" t="inlineStr">
-        <is>
-          <t>Note: text 1–5000 characters, optional title and topic; shows created and last-edited time; newest first</t>
-        </is>
-      </c>
-      <c r="C194" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
+    <row r="194"/>
     <row r="195">
-      <c r="A195" s="7" t="inlineStr">
-        <is>
-          <t>LLR-10.7</t>
-        </is>
-      </c>
-      <c r="B195" s="7" t="inlineStr">
-        <is>
-          <t>File (bills, invoices, warranty cards, manuals): PDF, JPG, PNG, WebP or HEIC, up to 10 MB each, checked by content; title (required), optional date, amount (₹) and topic. Files open in the browser or download; images show a thumbnail</t>
-        </is>
-      </c>
-      <c r="C195" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A195" s="13" t="inlineStr">
+        <is>
+          <t>LLR-10 Notes, contacts and files (HLR-10) ✅</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="7" t="inlineStr">
-        <is>
-          <t>LLR-10.8</t>
-        </is>
-      </c>
-      <c r="B196" s="7" t="inlineStr">
-        <is>
-          <t>Notes, contacts and files can be edited and deleted (with confirmation), and moved between topics by editing the topic</t>
-        </is>
-      </c>
-      <c r="C196" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="7" t="inlineStr">
-        <is>
-          <t>LLR-10.9</t>
-        </is>
-      </c>
-      <c r="B197" s="7" t="inlineStr">
-        <is>
-          <t>Search across every tile and area by contact name, organisation, topic, phone digits (spaces and dashes ignored), note text and file title. Results show where each hit lives (e.g. "Household › Kitchen › Bosch Dishwasher") and link to it</t>
-        </is>
-      </c>
-      <c r="C197" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
+      <c r="A196" s="12" t="inlineStr">
+        <is>
+          <t>Each tile and each area has a *Notes &amp; contacts* section (Q16, Q18). Every note, contact and file can carry an optional topic (e.g. "Bosch Dishwasher", "Pest Control") that groups related items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197"/>
     <row r="198">
-      <c r="A198" s="7" t="inlineStr">
-        <is>
-          <t>LLR-10.10</t>
-        </is>
-      </c>
-      <c r="B198" s="7" t="inlineStr">
-        <is>
-          <t>Deleting an area or tile deletes its notes, contacts and files, and the confirmation counts them (LLR-1.12). Stored files are removed only after the database change commits</t>
-        </is>
-      </c>
-      <c r="C198" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A198" s="13" t="inlineStr">
+        <is>
+          <t>LLR-10 Notes, contacts and files (HLR-10) ✅</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="7" t="inlineStr">
-        <is>
-          <t>LLR-10.11</t>
-        </is>
-      </c>
-      <c r="B199" s="7" t="inlineStr">
-        <is>
-          <t>Visibility follows the rewards setting (Q17): readable in the read-only view when public reads are on; creating, editing, deleting and uploading need the owner passcode</t>
-        </is>
-      </c>
-      <c r="C199" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.12</t>
+          <t>LLR-10.1</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
         <is>
-          <t>The JSON export (app.backup) includes notes and contacts, and lists files by title and stored name; the server backup covers the files folder as well as the database</t>
+          <t>The area screen has a Notes &amp; contacts tab (tiles no longer have their own tabs; older tile-level items stay stored and searchable) next to their main content. It lists topics as groups (items without a topic under "General"), each showing its contacts, files and notes</t>
         </is>
       </c>
       <c r="C200" s="7" t="inlineStr">
         <is>
-          <t>🟡 export built; server backup of the files folder comes with hosting</t>
-        </is>
-      </c>
-    </row>
-    <row r="201"/>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>LLR-10.2</t>
+        </is>
+      </c>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>Topic is free text (1–60 characters), optional, and offers existing topics from the same tile or area as suggestions, so "Bosch Dishwasher" isn't typed three different ways</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
     <row r="202">
-      <c r="A202" s="13" t="inlineStr">
-        <is>
-          <t>Business rules: tiles and details</t>
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>LLR-10.3</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>Contact: name (required, 1–80); organisation or brand (e.g. Bosch, Kent, IFB, LG); role (*Customer care*, *Service executive*, *Technician*, *Vendor or shop*, *Other*); up to 3 phone numbers with labels (mobile, toll-free, WhatsApp); email; website; last visit or contact date; notes (≤ 1000); topic</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B203" s="6" t="inlineStr">
-        <is>
-          <t>Rule</t>
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>LLR-10.4</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>Phone numbers are stored as entered and shown with actions: Call (tel:), WhatsApp (wa.me, for numbers marked WhatsApp) and Copy. Email gets Email (mailto:). All actions are one tap on a phone</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>BR-R17</t>
+          <t>LLR-10.5</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
         <is>
-          <t>Tile names are unique ignoring case; area names are unique within their tile ignoring case</t>
+          <t>Past executives: within a topic, contacts with the role *Service executive* or *Technician* are listed newest last-visit first. The topic header shows the last executive (name, date, call button)</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>BR-R18</t>
+          <t>LLR-10.6</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
         <is>
-          <t>Deleting a tile removes everything under it (areas, tasks, completions, rewards scoped to it, notes, contacts, files) in one transaction, after a database snapshot is saved to data/backups/</t>
+          <t>Note: text 1–5000 characters, optional title and topic; shows created and last-edited time; newest first</t>
+        </is>
+      </c>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>BR-R19</t>
+          <t>LLR-10.7</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
         <is>
-          <t>The starter set only adds tiles and areas whose names are missing; it never renames, merges or deletes</t>
+          <t>File (bills, invoices, warranty cards, manuals): PDF, JPG, PNG, WebP or HEIC, up to 10 MB each, checked by content; title (required), optional date, amount (₹) and topic. Files open in the browser or download; images show a thumbnail</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>BR-R20</t>
+          <t>LLR-10.8</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
         <is>
-          <t>Details belong to exactly one owner: a tile or an area. Moving an area to another tile isn't supported, so details never change tile</t>
+          <t>Notes, contacts and files can be edited and deleted (with confirmation), and moved between topics by editing the topic</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>BR-R21</t>
+          <t>LLR-10.9</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
         <is>
-          <t>The "last executive" of a topic is the *Service executive* or *Technician* contact in that topic with the latest last-visit date; contacts without a date come after dated ones</t>
-        </is>
-      </c>
-    </row>
-    <row r="209"/>
+          <t>Search across every tile and area by contact name, organisation, topic, phone digits (spaces and dashes ignored), note text and file title. Results show where each hit lives (e.g. "Household › Kitchen › Bosch Dishwasher") and link to it</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>LLR-10.10</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>Deleting an area or tile deletes its notes, contacts and files, and the confirmation counts them (LLR-1.12). Stored files are removed only after the database change commits</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
     <row r="210">
-      <c r="A210" s="13" t="inlineStr">
-        <is>
-          <t>AC-10 (your examples)</t>
+      <c r="A210" s="7" t="inlineStr">
+        <is>
+          <t>LLR-10.11</t>
+        </is>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t>Visibility follows the rewards setting (Q17): readable in the read-only view when public reads are on; creating, editing, deleting and uploading need the owner passcode</t>
+        </is>
+      </c>
+      <c r="C210" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>• *Given* Household › Kitchen *when* the user adds contacts "Bosch Customer Care" (Customer care, toll-free number) and "Ramesh" (Service executive, last visit 12 Aug 2026), both with topic "Bosch Dishwasher", uploads the installation bill and adds a note "Filter cleaned; next service due in 6 months" *then* the Bosch Dishwasher topic shows all four, with Ramesh as the last executive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* a topic "Kent Water Purifier" with executives visiting in March and August *then* the August executive is shown as the last executive, and both appear under past executives.</t>
-        </is>
-      </c>
-    </row>
+          <t>LLR-10.12</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>The JSON export (app.backup) includes notes and contacts, and lists files by title and stored name; the server backup covers the files folder as well as the database</t>
+        </is>
+      </c>
+      <c r="C211" s="7" t="inlineStr">
+        <is>
+          <t>🟡 export built; server backup of the files folder comes with hosting</t>
+        </is>
+      </c>
+    </row>
+    <row r="212"/>
     <row r="213">
-      <c r="A213" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* "IFB Washing Machine" (Laundry), "LG Fridge" (Kitchen) and "Pigeon Net" (Balcony) contacts *when* the user searches "IFB" *then* the result shows "Household › Laundry › IFB Washing Machine".</t>
+      <c r="A213" s="13" t="inlineStr">
+        <is>
+          <t>Business rules: tiles and details</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* Household (tile level) with topic "Pest Control" *then* its last executive shows on the Household tile's Notes &amp; contacts tab, not under any area.</t>
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>Rule</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a saved number "98450 12345" *when* the user searches "9845012345" *then* the contact is found, and tapping Call on a phone dials it.</t>
+          <t>BR-R17</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>Tile names are unique ignoring case; area names are unique within their tile ignoring case</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the read-only view (no passcode) *then* notes, contacts and files are visible, but the add, edit, delete and upload controls are hidden (Q17).</t>
-        </is>
-      </c>
-    </row>
-    <row r="217"/>
+          <t>BR-R18</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>Deleting a tile removes everything under it (areas, tasks, completions, rewards scoped to it, notes, contacts, files) in one transaction, after a database snapshot is saved to data/backups/</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr">
+        <is>
+          <t>BR-R19</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t>The starter set only adds tiles and areas whose names are missing; it never renames, merges or deletes</t>
+        </is>
+      </c>
+    </row>
     <row r="218">
-      <c r="A218" s="13" t="inlineStr">
-        <is>
-          <t>LLR-11 Task planning and visibility (HLR-11) ✅</t>
+      <c r="A218" s="7" t="inlineStr">
+        <is>
+          <t>BR-R20</t>
+        </is>
+      </c>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t>Details belong to exactly one owner: a tile or an area. Moving an area to another tile isn't supported, so details never change tile</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="12" t="inlineStr">
-        <is>
-          <t>Four new, optional task attributes (Q19 to Q22). They sit under More options in the add form, so adding a quick task on a phone stays one field and one tap.</t>
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t>BR-R21</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>The "last executive" of a topic is the *Service executive* or *Technician* contact in that topic with the latest last-visit date; contacts without a date come after dated ones</t>
         </is>
       </c>
     </row>
@@ -4893,223 +4956,101 @@
     <row r="221">
       <c r="A221" s="13" t="inlineStr">
         <is>
-          <t>LLR-11 Task planning and visibility (HLR-11) ✅</t>
+          <t>AC-10 (your examples)</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B222" s="6" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C222" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* Household › Kitchen *when* the user adds contacts "Bosch Customer Care" (Customer care, toll-free number) and "Ramesh" (Service executive, last visit 12 Aug 2026), both with topic "Bosch Dishwasher", uploads the installation bill and adds a note "Filter cleaned; next service due in 6 months" *then* the Bosch Dishwasher topic shows all four, with Ramesh as the last executive.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.1</t>
-        </is>
-      </c>
-      <c r="B223" s="7" t="inlineStr">
-        <is>
-          <t>Milestone: yes/no (default no), set when creating or editing a task</t>
-        </is>
-      </c>
-      <c r="C223" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* a topic "Kent Water Purifier" with executives visiting in March and August *then* the August executive is shown as the last executive, and both appear under past executives.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.2</t>
-        </is>
-      </c>
-      <c r="B224" s="7" t="inlineStr">
-        <is>
-          <t>Milestones show a 🏁 badge on task rows (area list, Tasks list, Link screen) and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
-        </is>
-      </c>
-      <c r="C224" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* "IFB Washing Machine" (Laundry), "LG Fridge" (Kitchen) and "Pigeon Net" (Balcony) contacts *when* the user searches "IFB" *then* the result shows "Household › Laundry › IFB Washing Machine".</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.3</t>
-        </is>
-      </c>
-      <c r="B225" s="7" t="inlineStr">
-        <is>
-          <t>Completing an announced milestone shows the milestone celebration: a larger, longer celebration than a normal completion (respects reduced motion), with its own share prompt</t>
-        </is>
-      </c>
-      <c r="C225" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* Household (tile level) with topic "Pest Control" *then* its last executive shows on the Household tile's Notes &amp; contacts tab, not under any area.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.4</t>
-        </is>
-      </c>
-      <c r="B226" s="7" t="inlineStr">
-        <is>
-          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task linked to it has at least one completion (BR-R25). With no milestone linked yet it shows 0 of 0 and never unlocks (tasks are linked later, on the Link screen)</t>
-        </is>
-      </c>
-      <c r="C226" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* a saved number "98450 12345" *when* the user searches "9845012345" *then* the contact is found, and tapping Call on a phone dials it.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.5</t>
-        </is>
-      </c>
-      <c r="B227" s="7" t="inlineStr">
-        <is>
-          <t>Announce or keep silent: each task is *Announced* (default) or *Silent*, set when creating or editing it (Q20, Q22)</t>
-        </is>
-      </c>
-      <c r="C227" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="7" t="inlineStr">
-        <is>
-          <t>LLR-11.6</t>
-        </is>
-      </c>
-      <c r="B228" s="7" t="inlineStr">
-        <is>
-          <t>Silent tasks and their completions never appear in anything served without the owner passcode: lists, counts, streaks, activity, dashboard aggregates or reward task lists (BR-R23). With the passcode they're shown with a 🔕 marker</t>
-        </is>
-      </c>
-      <c r="C228" s="7" t="inlineStr">
-        <is>
-          <t>🟡 🔕 marker and quiet completion built; hiding from visitors comes with the owner passcode (hosting)</t>
-        </is>
-      </c>
-    </row>
+          <t>• *Given* the read-only view (no passcode) *then* notes, contacts and files are visible, but the add, edit, delete and upload controls are hidden (Q17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228"/>
     <row r="229">
-      <c r="A229" s="7" t="inlineStr">
-        <is>
-          <t>LLR-11.7</t>
-        </is>
-      </c>
-      <c r="B229" s="7" t="inlineStr">
-        <is>
-          <t>Completing an announced task shows the celebration toast and a Share on WhatsApp prompt (prefilled text, e.g. "Done: Wipe counters 🔥 3-day streak"). Completing a silent task shows only a quiet "Logged" confirmation, with no share prompt (BR-R24)</t>
-        </is>
-      </c>
-      <c r="C229" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A229" s="13" t="inlineStr">
+        <is>
+          <t>LLR-11 Task planning and visibility (HLR-11) ✅</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="7" t="inlineStr">
-        <is>
-          <t>LLR-11.8</t>
-        </is>
-      </c>
-      <c r="B230" s="7" t="inlineStr">
-        <is>
-          <t>Due date and time (optional): a local date and time, stored in UTC. Tasks show a chip: *Overdue* (red), *Due today*, *Due in N days* (within 7 days) or the date. The area list can be filtered by *Overdue*, *Due today* and *Due this week*, and sorted by due date</t>
-        </is>
-      </c>
-      <c r="C230" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="7" t="inlineStr">
-        <is>
-          <t>LLR-11.9</t>
-        </is>
-      </c>
-      <c r="B231" s="7" t="inlineStr">
-        <is>
-          <t>Days to complete (optional): a whole number from 1 to 3650, shown as "Planned: N days". Task detail also shows "Day X of N", counted from the task's creation date</t>
-        </is>
-      </c>
-      <c r="C231" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
+      <c r="A230" s="12" t="inlineStr">
+        <is>
+          <t>Four new, optional task attributes (Q19 to Q22). They sit under More options in the add form, so adding a quick task on a phone stays one field and one tap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231"/>
     <row r="232">
-      <c r="A232" s="7" t="inlineStr">
-        <is>
-          <t>LLR-11.10</t>
-        </is>
-      </c>
-      <c r="B232" s="7" t="inlineStr">
-        <is>
-          <t>Due date and days to complete are independent: changing one never changes the other, and they may disagree (Q21, BR-R26)</t>
-        </is>
-      </c>
-      <c r="C232" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A232" s="13" t="inlineStr">
+        <is>
+          <t>LLR-11 Task planning and visibility (HLR-11) ✅</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="7" t="inlineStr">
-        <is>
-          <t>LLR-11.11</t>
-        </is>
-      </c>
-      <c r="B233" s="7" t="inlineStr">
-        <is>
-          <t>All four attributes can be edited on task detail at any time. A due date in the past is allowed (the task is simply overdue)</t>
-        </is>
-      </c>
-      <c r="C233" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.12</t>
+          <t>LLR-11.1</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
         <is>
-          <t>Existing tasks are migrated without data loss: milestone = no, visibility = announced, no due date, no days to complete. Nothing else changes</t>
+          <t>Milestone: yes/no (default no), set when creating or editing a task</t>
         </is>
       </c>
       <c r="C234" s="7" t="inlineStr">
@@ -5121,12 +5062,12 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.13</t>
+          <t>LLR-11.2</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
         <is>
-          <t>The dashboard adds an Overdue KPI and the *Milestones* table (LLR-11.2); the owner-only dashboard includes silent tasks, marked 🔕</t>
+          <t>Milestones show a 🏁 badge on task rows (area list, Tasks list, Link screen) and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
         </is>
       </c>
       <c r="C235" s="7" t="inlineStr">
@@ -5135,620 +5076,646 @@
         </is>
       </c>
     </row>
-    <row r="236"/>
+    <row r="236">
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t>LLR-11.3</t>
+        </is>
+      </c>
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>Completing an announced milestone shows the milestone celebration: a larger, longer celebration than a normal completion (respects reduced motion), with its own share prompt</t>
+        </is>
+      </c>
+      <c r="C236" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
     <row r="237">
-      <c r="A237" s="13" t="inlineStr">
-        <is>
-          <t>Business rules: task planning and visibility</t>
+      <c r="A237" s="7" t="inlineStr">
+        <is>
+          <t>LLR-11.4</t>
+        </is>
+      </c>
+      <c r="B237" s="7" t="inlineStr">
+        <is>
+          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task linked to it has at least one completion (BR-R25). With no milestone linked yet it shows 0 of 0 and never unlocks (tasks are linked later, on the Link screen)</t>
+        </is>
+      </c>
+      <c r="C237" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B238" s="6" t="inlineStr">
-        <is>
-          <t>Rule</t>
+      <c r="A238" s="7" t="inlineStr">
+        <is>
+          <t>LLR-11.5</t>
+        </is>
+      </c>
+      <c r="B238" s="7" t="inlineStr">
+        <is>
+          <t>Announce or keep silent: each task is *Announced* (default) or *Silent*, set when creating or editing it (Q20, Q22)</t>
+        </is>
+      </c>
+      <c r="C238" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>BR-R22</t>
+          <t>LLR-11.6</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
         <is>
-          <t>A task is overdue when it's active, has a due date, and the due date is before now. Done and archived tasks are never overdue</t>
+          <t>Silent tasks and their completions never appear in anything served without the owner passcode: lists, counts, streaks, activity, dashboard aggregates or reward task lists (BR-R23). With the passcode they're shown with a 🔕 marker</t>
+        </is>
+      </c>
+      <c r="C239" s="7" t="inlineStr">
+        <is>
+          <t>🟡 🔕 marker and quiet completion built; hiding from visitors comes with the owner passcode (hosting)</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>BR-R23</t>
+          <t>LLR-11.7</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
         <is>
-          <t>Silent means invisible without the passcode: silent tasks, their completions, streaks and activity are excluded from every response to a caller without the owner passcode, including counts and aggregates, so their existence can't be inferred</t>
+          <t>Completing an announced task shows the celebration toast and a Share on WhatsApp prompt (prefilled text, e.g. "Done: Wipe counters 🔥 3-day streak"). Completing a silent task shows only a quiet "Logged" confirmation, with no share prompt (BR-R24)</t>
+        </is>
+      </c>
+      <c r="C240" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>BR-R24</t>
+          <t>LLR-11.8</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
         <is>
-          <t>Celebrations and share prompts happen only for announced tasks. A reward unlocked by a silent task's completion is unlocked quietly (no share prompt); the reward itself stays visible</t>
+          <t>Due date and time (optional): a local date and time, stored in UTC. Tasks show a chip: *Overdue* (red), *Due today*, *Due in N days* (within 7 days) or the date. The area list can be filtered by *Overdue*, *Due today* and *Due this week*, and sorted by due date</t>
+        </is>
+      </c>
+      <c r="C241" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>BR-R25</t>
+          <t>LLR-11.9</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
         <is>
-          <t>A Milestone completed reward unlocks when every milestone task it matches (tagged, or in scope with *All tasks in scope*) has ≥ 1 completion. Non-milestone tasks tagged to it don't count. Progress = milestones completed ÷ milestones matched</t>
+          <t>Days to complete (optional): a whole number from 1 to 3650, shown as "Planned: N days". Task detail also shows "Day X of N", counted from the task's creation date</t>
+        </is>
+      </c>
+      <c r="C242" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>BR-R26</t>
+          <t>LLR-11.10</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
         <is>
-          <t>Due date and days to complete are never derived from each other or from the frequency</t>
-        </is>
-      </c>
-    </row>
-    <row r="244"/>
+          <t>Due date and days to complete are independent: changing one never changes the other, and they may disagree (Q21, BR-R26)</t>
+        </is>
+      </c>
+      <c r="C243" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="7" t="inlineStr">
+        <is>
+          <t>LLR-11.11</t>
+        </is>
+      </c>
+      <c r="B244" s="7" t="inlineStr">
+        <is>
+          <t>All four attributes can be edited on task detail at any time. A due date in the past is allowed (the task is simply overdue)</t>
+        </is>
+      </c>
+      <c r="C244" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
     <row r="245">
-      <c r="A245" s="13" t="inlineStr">
-        <is>
-          <t>AC-11 (your examples)</t>
+      <c r="A245" s="7" t="inlineStr">
+        <is>
+          <t>LLR-11.12</t>
+        </is>
+      </c>
+      <c r="B245" s="7" t="inlineStr">
+        <is>
+          <t>Existing tasks are migrated without data loss: milestone = no, visibility = announced, no due date, no days to complete. Nothing else changes</t>
+        </is>
+      </c>
+      <c r="C245" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the add form *when* the user opens More options, ticks Milestone, sets due "31 Oct 2026, 6:00 pm" and days to complete "30" *then* the task shows 🏁, "Due 31 Oct" and "Planned: 30 days", and task detail shows "Day 1 of 30".</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* a reward "New laptop bag" with the rule Milestone completed tagged to the milestone "Finish React course" *when* that task is completed *then* the reward unlocks and the milestone celebration plays.</t>
-        </is>
-      </c>
-    </row>
+          <t>LLR-11.13</t>
+        </is>
+      </c>
+      <c r="B246" s="7" t="inlineStr">
+        <is>
+          <t>The dashboard adds an Overdue KPI and the *Milestones* table (LLR-11.2); the owner-only dashboard includes silent tasks, marked 🔕</t>
+        </is>
+      </c>
+      <c r="C246" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="247"/>
     <row r="248">
-      <c r="A248" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* two milestone tasks tagged to one milestone reward *when* only one is completed *then* progress shows 1 of 2 and it stays locked (BR-R25, O7).</t>
+      <c r="A248" s="13" t="inlineStr">
+        <is>
+          <t>Business rules: task planning and visibility</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* a silent task "Therapy session" *when* a visitor opens the read-only view *then* it isn't listed, the area's active count doesn't include it, and dashboard totals exclude it; with the passcode it's shown with 🔕.</t>
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B249" s="6" t="inlineStr">
+        <is>
+          <t>Rule</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the user completes a silent task *then* only "Logged" appears: no toast and no share prompt.</t>
+          <t>BR-R22</t>
+        </is>
+      </c>
+      <c r="B250" s="7" t="inlineStr">
+        <is>
+          <t>A task is overdue when it's active, has a due date, and the due date is before now. Done and archived tasks are never overdue</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a task due yesterday that's still active *then* it shows *Overdue*; when it's completed or archived the chip disappears.</t>
+          <t>BR-R23</t>
+        </is>
+      </c>
+      <c r="B251" s="7" t="inlineStr">
+        <is>
+          <t>Silent means invisible without the passcode: silent tasks, their completions, streaks and activity are excluded from every response to a caller without the owner passcode, including counts and aggregates, so their existence can't be inferred</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>• *Given* a task with due date 10 Oct and days to complete 30 *when* the due date is moved to 20 Oct *then* days to complete stays 30.</t>
-        </is>
-      </c>
-    </row>
-    <row r="253"/>
+          <t>BR-R24</t>
+        </is>
+      </c>
+      <c r="B252" s="7" t="inlineStr">
+        <is>
+          <t>Celebrations and share prompts happen only for announced tasks. A reward unlocked by a silent task's completion is unlocked quietly (no share prompt); the reward itself stays visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="7" t="inlineStr">
+        <is>
+          <t>BR-R25</t>
+        </is>
+      </c>
+      <c r="B253" s="7" t="inlineStr">
+        <is>
+          <t>A Milestone completed reward unlocks when every milestone task it matches (tagged, or in scope with *All tasks in scope*) has ≥ 1 completion. Non-milestone tasks tagged to it don't count. Progress = milestones completed ÷ milestones matched</t>
+        </is>
+      </c>
+    </row>
     <row r="254">
-      <c r="A254" s="13" t="inlineStr">
-        <is>
-          <t>LLR-12 Reward ideas and wishlist (HLR-12) ✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="12" t="inlineStr">
-        <is>
-          <t>A reward can start life as an idea: something you might get later, captured before any rule or task exists (Q23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="256"/>
+      <c r="A254" s="7" t="inlineStr">
+        <is>
+          <t>BR-R26</t>
+        </is>
+      </c>
+      <c r="B254" s="7" t="inlineStr">
+        <is>
+          <t>Due date and days to complete are never derived from each other or from the frequency</t>
+        </is>
+      </c>
+    </row>
+    <row r="255"/>
+    <row r="256">
+      <c r="A256" s="13" t="inlineStr">
+        <is>
+          <t>AC-11 (your examples)</t>
+        </is>
+      </c>
+    </row>
     <row r="257">
-      <c r="A257" s="13" t="inlineStr">
-        <is>
-          <t>LLR-12 Reward ideas and wishlist (HLR-12) ✅</t>
+      <c r="A257" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* the add form *when* the user opens More options, ticks Milestone, sets due "31 Oct 2026, 6:00 pm" and days to complete "30" *then* the task shows 🏁, "Due 31 Oct" and "Planned: 30 days", and task detail shows "Day 1 of 30".</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B258" s="6" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C258" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A258" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* a reward "New laptop bag" with the rule Milestone completed tagged to the milestone "Finish React course" *when* that task is completed *then* the reward unlocks and the milestone celebration plays.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.1</t>
-        </is>
-      </c>
-      <c r="B259" s="7" t="inlineStr">
-        <is>
-          <t>Quick capture: "💡 + Idea" on the Rewards screen and on every area's Rewards tab opens a short form: title (required), for whom (default Me) and a one-tap cover photo (camera or gallery; JPG, PNG, WebP or HEIC up to 10 MB); *More* adds where seen, link, note and (on the Rewards screen) an optional area. Saving needs only the title</t>
-        </is>
-      </c>
-      <c r="C259" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* two milestone tasks tagged to one milestone reward *when* only one is completed *then* progress shows 1 of 2 and it stays locked (BR-R25, O7).</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.2</t>
-        </is>
-      </c>
-      <c r="B260" s="7" t="inlineStr">
-        <is>
-          <t>For whom on every reward and idea: free text (1–40) with suggestions from earlier entries; default "Me" (Q25)</t>
-        </is>
-      </c>
-      <c r="C260" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* a silent task "Therapy session" *when* a visitor opens the read-only view *then* it isn't listed, the area's active count doesn't include it, and dashboard totals exclude it; with the passcode it's shown with 🔕.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.3</t>
-        </is>
-      </c>
-      <c r="B261" s="7" t="inlineStr">
-        <is>
-          <t>Ideas have status Idea: no rule, no progress and no tasks, and they never unlock or appear in progress counts (BR-R27)</t>
-        </is>
-      </c>
-      <c r="C261" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* the user completes a silent task *then* only "Logged" appears: no toast and no share prompt.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.4</t>
-        </is>
-      </c>
-      <c r="B262" s="7" t="inlineStr">
-        <is>
-          <t>The Rewards screen filters by status (💡 Ideas, Locked, Unlocked, Claimed, Closed) and by for whom (e.g. *Shiragi*), plus search; closed ideas are hidden unless *Closed* is chosen. An area's Rewards tab lists its ideas with its rewards. Ideas are never offered on the Link screen</t>
-        </is>
-      </c>
-      <c r="C262" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* a task due yesterday that's still active *then* it shows *Overdue*; when it's completed or archived the chip disappears.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.5</t>
-        </is>
-      </c>
-      <c r="B263" s="7" t="inlineStr">
-        <is>
-          <t>Turn into reward: on an idea, pick how it unlocks (task count with N, or milestone completed). It becomes a normal *locked* reward with the same id, keeping title, photo, link, note, where seen, area and for whom; tasks are then linked on the Link screen (BR-R28)</t>
-        </is>
-      </c>
-      <c r="C263" s="7" t="inlineStr">
+          <t>• *Given* a task with due date 10 Oct and days to complete 30 *when* the due date is moved to 20 Oct *then* days to complete stays 30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264"/>
+    <row r="265">
+      <c r="A265" s="13" t="inlineStr">
+        <is>
+          <t>LLR-12 Reward ideas and wishlist (HLR-12) ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="12" t="inlineStr">
+        <is>
+          <t>A reward can start life as an idea: something you might get later, captured before any rule or task exists (Q23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="267"/>
+    <row r="268">
+      <c r="A268" s="13" t="inlineStr">
+        <is>
+          <t>LLR-12 Reward ideas and wishlist (HLR-12) ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="7" t="inlineStr">
+        <is>
+          <t>LLR-12.1</t>
+        </is>
+      </c>
+      <c r="B270" s="7" t="inlineStr">
+        <is>
+          <t>Quick capture: "💡 + Idea" on the Rewards screen and on every area's Rewards tab opens a short form: title (required), for whom (default Me) and a one-tap cover photo (camera or gallery; JPG, PNG, WebP or HEIC up to 10 MB); *More* adds where seen, link, note and (on the Rewards screen) an optional area. Saving needs only the title</t>
+        </is>
+      </c>
+      <c r="C270" s="7" t="inlineStr">
         <is>
           <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="7" t="inlineStr">
-        <is>
-          <t>LLR-12.6</t>
-        </is>
-      </c>
-      <c r="B264" s="7" t="inlineStr">
-        <is>
-          <t>Close an idea as *Bought* (got it without a rule) or *Dropped* (no longer wanted). Closed ideas leave the Ideas list, stay under *Closed* with the date and outcome, and can be reopened (BR-R29)</t>
-        </is>
-      </c>
-      <c r="C264" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="7" t="inlineStr">
-        <is>
-          <t>LLR-12.7</t>
-        </is>
-      </c>
-      <c r="B265" s="7" t="inlineStr">
-        <is>
-          <t>Ideas are Silent by default (hidden from the read-only view) and can be switched to *Announced*; ordinary rewards default to *Announced*. Visibility follows the silent rules of BR-R23 (Q24)</t>
-        </is>
-      </c>
-      <c r="C265" s="7" t="inlineStr">
-        <is>
-          <t>🟡 private by default with a 🔕 marker; hiding from visitors comes with the owner passcode (hosting)</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="7" t="inlineStr">
-        <is>
-          <t>LLR-12.8</t>
-        </is>
-      </c>
-      <c r="B266" s="7" t="inlineStr">
-        <is>
-          <t>Ideas are included in search (LLR-10.9) by title, notes, for whom and where seen</t>
-        </is>
-      </c>
-      <c r="C266" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="7" t="inlineStr">
-        <is>
-          <t>LLR-12.9</t>
-        </is>
-      </c>
-      <c r="B267" s="7" t="inlineStr">
-        <is>
-          <t>Existing rewards are migrated without data loss: for whom = "Me", visibility = announced; their status, rule, tasks and progress are unchanged</t>
-        </is>
-      </c>
-      <c r="C267" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="268"/>
-    <row r="269">
-      <c r="A269" s="13" t="inlineStr">
-        <is>
-          <t>Business rules: ideas</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B270" s="6" t="inlineStr">
-        <is>
-          <t>Rule</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>BR-R27</t>
+          <t>LLR-12.2</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
         <is>
-          <t>An *Idea* has no rule and no progress. It can't unlock or be claimed, and it isn't counted in reward totals or progress on the dashboard (the dashboard shows an *Ideas* count per person)</t>
+          <t>For whom on every reward and idea: free text (1–40) with suggestions from earlier entries; default "Me" (Q25)</t>
+        </is>
+      </c>
+      <c r="C271" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>BR-R28</t>
+          <t>LLR-12.3</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
         <is>
-          <t>Turning an idea into a reward requires a rule and a threshold (except *milestone completed*); a tile isn't required since rewards stand alone. The idea's id is kept, so links and photos stay attached</t>
+          <t>Ideas have status Idea: no rule, no progress and no tasks, and they never unlock or appear in progress counts (BR-R27)</t>
+        </is>
+      </c>
+      <c r="C272" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>BR-R29</t>
+          <t>LLR-12.4</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
         <is>
-          <t>Closing is only for ideas; a reward that already has a rule is claimed, not closed. Reopening a closed idea returns it to *Idea*</t>
+          <t>The Rewards screen filters by status (💡 Ideas, Locked, Unlocked, Claimed, Closed) and by for whom (e.g. *Shiragi*), plus search; closed ideas are hidden unless *Closed* is chosen. An area's Rewards tab lists its ideas with its rewards. Ideas are never offered on the Link screen</t>
+        </is>
+      </c>
+      <c r="C273" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>BR-R30</t>
+          <t>LLR-12.5</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
         <is>
-          <t>*For whom* is a label: it groups and filters rewards, but never changes who can see or edit them (visibility rules decide that)</t>
-        </is>
-      </c>
-    </row>
-    <row r="275"/>
+          <t>Turn into reward: on an idea, pick how it unlocks (task count with N, or milestone completed). It becomes a normal *locked* reward with the same id, keeping title, photo, link, note, where seen, area and for whom; tasks are then linked on the Link screen (BR-R28)</t>
+        </is>
+      </c>
+      <c r="C274" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="7" t="inlineStr">
+        <is>
+          <t>LLR-12.6</t>
+        </is>
+      </c>
+      <c r="B275" s="7" t="inlineStr">
+        <is>
+          <t>Close an idea as *Bought* (got it without a rule) or *Dropped* (no longer wanted). Closed ideas leave the Ideas list, stay under *Closed* with the date and outcome, and can be reopened (BR-R29)</t>
+        </is>
+      </c>
+      <c r="C275" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
     <row r="276">
-      <c r="A276" s="13" t="inlineStr">
-        <is>
-          <t>AC-12 (your example)</t>
+      <c r="A276" s="7" t="inlineStr">
+        <is>
+          <t>LLR-12.7</t>
+        </is>
+      </c>
+      <c r="B276" s="7" t="inlineStr">
+        <is>
+          <t>Ideas are Silent by default (hidden from the read-only view) and can be switched to *Announced*; ordinary rewards default to *Announced*. Visibility follows the silent rules of BR-R23 (Q24)</t>
+        </is>
+      </c>
+      <c r="C276" s="7" t="inlineStr">
+        <is>
+          <t>🟡 private by default with a 🔕 marker; hiding from visitors comes with the owner passcode (hosting)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the user is at the library *when* they tap "+ Idea", type "101 Hilarious Jokes", choose for whom "Shiragi", take a photo of the cover and save *then* it appears under Rewards › Ideas with the photo, for "Shiragi", saved in under 10 seconds on a phone.</t>
+          <t>LLR-12.8</t>
+        </is>
+      </c>
+      <c r="B277" s="7" t="inlineStr">
+        <is>
+          <t>Ideas are included in search (LLR-10.9) by title, notes, for whom and where seen</t>
+        </is>
+      </c>
+      <c r="C277" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the idea *when* a visitor opens the read-only view *then* it isn't shown (silent by default); with the passcode it's listed with 🔕.</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* the idea *when* the user turns it into a reward for Household › Books with the rule "streak of 7" tagged to Shiragi's task "Read 20 minutes" *then* it's a locked reward at 0 %, still with its photo, link and for whom "Shiragi".</t>
-        </is>
-      </c>
-    </row>
+          <t>LLR-12.9</t>
+        </is>
+      </c>
+      <c r="B278" s="7" t="inlineStr">
+        <is>
+          <t>Existing rewards are migrated without data loss: for whom = "Me", visibility = announced; their status, rule, tasks and progress are unchanged</t>
+        </is>
+      </c>
+      <c r="C278" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="279"/>
     <row r="280">
-      <c r="A280" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* the user simply buys the book *when* they close the idea as *Bought* *then* it moves to *Closed* with today's date.</t>
+      <c r="A280" s="13" t="inlineStr">
+        <is>
+          <t>Business rules: ideas</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="7" t="inlineStr">
-        <is>
-          <t>• *Given* the Rewards tab filtered to "Shiragi" *then* only her ideas and rewards are shown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="282"/>
+      <c r="A281" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B281" s="6" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="7" t="inlineStr">
+        <is>
+          <t>BR-R27</t>
+        </is>
+      </c>
+      <c r="B282" s="7" t="inlineStr">
+        <is>
+          <t>An *Idea* has no rule and no progress. It can't unlock or be claimed, and it isn't counted in reward totals or progress on the dashboard (the dashboard shows an *Ideas* count per person)</t>
+        </is>
+      </c>
+    </row>
     <row r="283">
-      <c r="A283" s="13" t="inlineStr">
-        <is>
-          <t>LLR-13 Tiles without areas (HLR-13) ✅</t>
+      <c r="A283" s="7" t="inlineStr">
+        <is>
+          <t>BR-R28</t>
+        </is>
+      </c>
+      <c r="B283" s="7" t="inlineStr">
+        <is>
+          <t>Turning an idea into a reward requires a rule and a threshold (except *milestone completed*); a tile isn't required since rewards stand alone. The idea's id is kept, so links and photos stay attached</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="12" t="inlineStr">
-        <is>
-          <t>Some tiles have no natural sub-areas (D15). Such a tile holds its tasks, rewards and notes directly. Internally it keeps exactly one hidden area, so tasks, completions, rewards and notes work unchanged; every screen shows the tile in its place.</t>
-        </is>
-      </c>
-    </row>
-    <row r="285"/>
-    <row r="286">
-      <c r="A286" s="13" t="inlineStr">
-        <is>
-          <t>LLR-13 Tiles without areas (HLR-13) ✅</t>
-        </is>
-      </c>
-    </row>
+      <c r="A284" s="7" t="inlineStr">
+        <is>
+          <t>BR-R29</t>
+        </is>
+      </c>
+      <c r="B284" s="7" t="inlineStr">
+        <is>
+          <t>Closing is only for ideas; a reward that already has a rule is claimed, not closed. Reopening a closed idea returns it to *Idea*</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="7" t="inlineStr">
+        <is>
+          <t>BR-R30</t>
+        </is>
+      </c>
+      <c r="B285" s="7" t="inlineStr">
+        <is>
+          <t>*For whom* is a label: it groups and filters rewards, but never changes who can see or edit them (visibility rules decide that)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286"/>
     <row r="287">
-      <c r="A287" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B287" s="6" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C287" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A287" s="13" t="inlineStr">
+        <is>
+          <t>AC-12 (your example)</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.1</t>
-        </is>
-      </c>
-      <c r="B288" s="7" t="inlineStr">
-        <is>
-          <t>The tile form (new tile and ✎ edit) has a Use areas switch, on by default. POST /categories and PATCH /categories/{id} accept useAreas; every tile in GET /categories returns useAreas, and each area returns hidden</t>
-        </is>
-      </c>
-      <c r="C288" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* the user is at the library *when* they tap "+ Idea", type "101 Hilarious Jokes", choose for whom "Shiragi", take a photo of the cover and save *then* it appears under Rewards › Ideas with the photo, for "Shiragi", saved in under 10 seconds on a phone.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.2</t>
-        </is>
-      </c>
-      <c r="B289" s="7" t="inlineStr">
-        <is>
-          <t>Switching areas off is only possible while the tile has no areas; otherwise the switch is disabled with "move or delete its N areas first" and the API answers 409 (BR-R31)</t>
-        </is>
-      </c>
-      <c r="C289" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* the idea *when* a visitor opens the read-only view *then* it isn't shown (silent by default); with the passcode it's listed with 🔕.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.3</t>
-        </is>
-      </c>
-      <c r="B290" s="7" t="inlineStr">
-        <is>
-          <t>A tile without areas opens straight to Tasks | Rewards | Notes &amp; contacts at #/rewards/c/{tile} (/rewards, /details), with the tile's name, icon and its ✎ / 🗑 buttons. Old links to its hidden area open the tile instead</t>
-        </is>
-      </c>
-      <c r="C290" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* the idea *when* the user turns it into a reward for Household › Books with the rule "streak of 7" tagged to Shiragi's task "Read 20 minutes" *then* it's a locked reward at 0 %, still with its photo, link and for whom "Shiragi".</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.4</t>
-        </is>
-      </c>
-      <c r="B291" s="7" t="inlineStr">
-        <is>
-          <t>Tiles screen shows "N active tasks" without an area count; the Tasks, Rewards and Link screens, area pickers, search results and the dashboard show such tasks and rewards under the tile name alone (e.g. "💼 Career / Office / Work", never "› General")</t>
-        </is>
-      </c>
-      <c r="C291" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>• *Given* the user simply buys the book *when* they close the idea as *Bought* *then* it moves to *Closed* with today's date.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.5</t>
-        </is>
-      </c>
-      <c r="B292" s="7" t="inlineStr">
-        <is>
-          <t>No areas can be added to, and the hidden area can't be renamed or deleted on, a tile without areas (409); the starter set never adds areas to it</t>
-        </is>
-      </c>
-      <c r="C292" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="7" t="inlineStr">
-        <is>
-          <t>LLR-13.6</t>
-        </is>
-      </c>
-      <c r="B293" s="7" t="inlineStr">
-        <is>
-          <t>Switching areas back on: if the tile holds anything, its hidden area becomes a normal area called General with everything in it; if it's empty, it simply goes</t>
-        </is>
-      </c>
-      <c r="C293" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
+          <t>• *Given* the Rewards tab filtered to "Shiragi" *then* only her ideas and rewards are shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293"/>
     <row r="294">
-      <c r="A294" s="7" t="inlineStr">
-        <is>
-          <t>LLR-13.7</t>
-        </is>
-      </c>
-      <c r="B294" s="7" t="inlineStr">
-        <is>
-          <t>Move a task: the task's edit form has a *Tile or area* picker (PATCH /tasks/{id} with areaId). Completions, streaks and reward links move with it</t>
-        </is>
-      </c>
-      <c r="C294" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A294" s="13" t="inlineStr">
+        <is>
+          <t>LLR-13 Tiles without areas (HLR-13) ✅</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="7" t="inlineStr">
-        <is>
-          <t>LLR-13.8</t>
-        </is>
-      </c>
-      <c r="B295" s="7" t="inlineStr">
-        <is>
-          <t>Existing data is kept: migration 0006_tile_without_areas adds areas.hidden (false for every existing area), with a backup first</t>
-        </is>
-      </c>
-      <c r="C295" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="A295" s="12" t="inlineStr">
+        <is>
+          <t>Some tiles have no natural sub-areas (D15). Such a tile holds its tasks, rewards and notes directly. Internally it keeps exactly one hidden area, so tasks, completions, rewards and notes work unchanged; every screen shows the tile in its place.</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5723,7 @@
     <row r="297">
       <c r="A297" s="13" t="inlineStr">
         <is>
-          <t>Business rules: tiles without areas</t>
+          <t>LLR-13 Tiles without areas (HLR-13) ✅</t>
         </is>
       </c>
     </row>
@@ -5768,53 +5735,214 @@
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>BR-R31</t>
+          <t>LLR-13.1</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
         <is>
-          <t>A tile either uses areas or holds everything itself, never both. Areas can only be switched off on a tile with no areas, so nothing is hidden or lost by the switch</t>
-        </is>
-      </c>
-    </row>
-    <row r="300"/>
+          <t>The tile form (new tile and ✎ edit) has a Use areas switch, on by default. POST /categories and PATCH /categories/{id} accept useAreas; every tile in GET /categories returns useAreas, and each area returns hidden</t>
+        </is>
+      </c>
+      <c r="C299" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.2</t>
+        </is>
+      </c>
+      <c r="B300" s="7" t="inlineStr">
+        <is>
+          <t>Switching areas off is only possible while the tile has no areas; otherwise the switch is disabled with "move or delete its N areas first" and the API answers 409 (BR-R31)</t>
+        </is>
+      </c>
+      <c r="C300" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
     <row r="301">
-      <c r="A301" s="13" t="inlineStr">
-        <is>
-          <t>AC-13 (your example)</t>
+      <c r="A301" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.3</t>
+        </is>
+      </c>
+      <c r="B301" s="7" t="inlineStr">
+        <is>
+          <t>A tile without areas opens straight to Tasks | Rewards | Notes &amp; contacts at #/rewards/c/{tile} (/rewards, /details), with the tile's name, icon and its ✎ / 🗑 buttons. Old links to its hidden area open the tile instead</t>
+        </is>
+      </c>
+      <c r="C301" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>• *Given* Career / Office / Work with areas switched off *when* the user opens it *then* the task list and an *Add a task* form are shown straight away, with no area step.</t>
+          <t>LLR-13.4</t>
+        </is>
+      </c>
+      <c r="B302" s="7" t="inlineStr">
+        <is>
+          <t>Tiles screen shows "N active tasks" without an area count; the Tasks, Rewards and Link screens, area pickers, search results and the dashboard show such tasks and rewards under the tile name alone (e.g. "💼 Career / Office / Work", never "› General")</t>
+        </is>
+      </c>
+      <c r="C302" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the Tasks screen *then* those tasks are grouped under "💼 Career / Office / Work", not under an area.</t>
+          <t>LLR-13.5</t>
+        </is>
+      </c>
+      <c r="B303" s="7" t="inlineStr">
+        <is>
+          <t>No areas can be added to, and the hidden area can't be renamed or deleted on, a tile without areas (409); the starter set never adds areas to it</t>
+        </is>
+      </c>
+      <c r="C303" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="7" t="inlineStr">
         <is>
-          <t>• *Given* the Fun tile with 2 areas *when* the user edits it *then* *Use areas* can't be switched off and says to move or delete its 2 areas first.</t>
+          <t>LLR-13.6</t>
+        </is>
+      </c>
+      <c r="B304" s="7" t="inlineStr">
+        <is>
+          <t>Switching areas back on: if the tile holds anything, its hidden area becomes a normal area called General with everything in it; if it's empty, it simply goes</t>
+        </is>
+      </c>
+      <c r="C304" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.7</t>
+        </is>
+      </c>
+      <c r="B305" s="7" t="inlineStr">
+        <is>
+          <t>Move a task: the task's edit form has a *Tile or area* picker (PATCH /tasks/{id} with areaId). Completions, streaks and reward links move with it</t>
+        </is>
+      </c>
+      <c r="C305" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="7" t="inlineStr">
+        <is>
+          <t>LLR-13.8</t>
+        </is>
+      </c>
+      <c r="B306" s="7" t="inlineStr">
+        <is>
+          <t>Existing data is kept: migration 0006_tile_without_areas adds areas.hidden (false for every existing area), with a backup first</t>
+        </is>
+      </c>
+      <c r="C306" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="307"/>
+    <row r="308">
+      <c r="A308" s="13" t="inlineStr">
+        <is>
+          <t>Business rules: tiles without areas</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B309" s="6" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="7" t="inlineStr">
+        <is>
+          <t>BR-R31</t>
+        </is>
+      </c>
+      <c r="B310" s="7" t="inlineStr">
+        <is>
+          <t>A tile either uses areas or holds everything itself, never both. Areas can only be switched off on a tile with no areas, so nothing is hidden or lost by the switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="311"/>
+    <row r="312">
+      <c r="A312" s="13" t="inlineStr">
+        <is>
+          <t>AC-13 (your example)</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* Career / Office / Work with areas switched off *when* the user opens it *then* the task list and an *Add a task* form are shown straight away, with no area step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* the Tasks screen *then* those tasks are grouped under "💼 Career / Office / Work", not under an area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="7" t="inlineStr">
+        <is>
+          <t>• *Given* the Fun tile with 2 areas *when* the user edits it *then* *Use areas* can't be switched off and says to move or delete its 2 areas first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="7" t="inlineStr">
         <is>
           <t>• *Given* the task "Micro-frontend Rewards Deployment" with 1 completion and a linked reward *when* it's moved to another tile *then* its completion and reward link stay.</t>
         </is>
@@ -5943,7 +6071,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Breadcrumb; active count; add form (⏳ with More options: milestone, announce/silent, due date and time, days to complete); filters (collapsible; ⏳ milestones, overdue/due today/this week, sort by due); task rows (title, frequency, source, status, streak 🔥, priority select, ✓; ⏳ 🏁 milestone, due chip, 🔕 silent); ⏳ "Rewards you can earn here" (matching rewards with progress)</t>
+          <t>Breadcrumb; active count; add form (⏳ with More options: milestone, announce/silent, due date and time, days to complete); filters (collapsible; ⏳ milestones, overdue/due today/this week, sort by due); task rows (⠿ drag handle; title, frequency, source, status, streak 🔥, ✓; ⏳ 🏁 milestone, due chip, 🔕 silent); ⏳ "Rewards you can earn here" (matching rewards with progress)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -5953,7 +6081,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>add task, filter, reprioritise, quick complete, open task; ⏳ create reward for this area</t>
+          <t>add task, filter, drag to reorder, quick complete, open task; ⏳ create reward for this area</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J203"/>
+  <dimension ref="A1:J208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6934,7 +7062,7 @@
       <c r="C11" s="7" t="inlineStr"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Task management: Create, prioritise, filter, change status/frequency/relevance</t>
+          <t>Task management: Create, order by importance (drag; top = most important), filter, change status/frequency/relevance</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -8298,7 +8426,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Create a task with title (1–200 characters, required), notes (≤ 2000), priority (high/medium/low, default medium) and frequency (daily/weekly/one_off, default weekly). Source = manual; status = active; relevance = relevant</t>
+          <t>Create a task with title (1–200 characters, required), notes (≤ 2000) and frequency (daily/weekly/one_off, default weekly). Source = manual; status = active; relevance = relevant. No priority is asked for: a new task goes to the bottom of its area's list (D16, BR-R32)</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -8342,7 +8470,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>After creating a task, the form keeps the chosen priority and frequency for the next entry and clears the title and notes</t>
+          <t>After creating a task, the form keeps the chosen frequency for the next entry and clears the title and notes</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -8386,7 +8514,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>An area's task list is sorted by priority (high → low), then by creation time</t>
+          <t>An area's (or a tile without areas') task list is in the user's own order: top = most important, bottom = least (BR-R32)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -8430,7 +8558,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Filter by priority, status and relevance, singly or combined. The default view is status = active</t>
+          <t>Filter by status, relevance, milestone and due (overdue / today / this week), singly or combined. The default view is status = active. The priority filter is removed</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -8474,7 +8602,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Reprioritise from the list (inline select) or from task detail</t>
+          <t>Drag to reorder: each task row has a ⠿ handle that works with mouse and touch (phone); the new order is saved at once (PUT /areas/{id}/tasks/order). Keyboard and screen-reader users get *Move up* / *Move down* on the handle (arrow keys). Replaces the inline High/Med/Low select</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -8723,7 +8851,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.1</t>
+          <t>LLR-2.11</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -8733,12 +8861,12 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-2</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Complete an active task, optionally with a note (≤ 1000) and a time (completedAt). If no time is given, the time is now</t>
+          <t>Dragging is available only in the default view (active tasks, no filters, *My order*). With a filter or *Sort by due date* on, the list shows a note "Clear filters to reorder" and has no handles, so the saved order is never changed by accident</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -8767,7 +8895,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.2</t>
+          <t>LLR-2.12</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -8777,17 +8905,17 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-2</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Logging uses a month calendar: days the task was done are marked (with a count when more than once), today is outlined, future days are disabled, and ‹ › move between months. Tap a day, adjust the time (defaults to now), add an optional note and log. A time later than now is clamped to now</t>
+          <t>The order is shared by every list of the area's tasks: the area tab, the Tasks screen (each area group in its own order, areas in tile › area order) and the Link screen's task picker</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -8811,7 +8939,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.3</t>
+          <t>LLR-2.13</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -8821,12 +8949,12 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-2</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>A completion more than 1 minute in the future is rejected (422)</t>
+          <t>A task moved to another tile or area (LLR-13.7) goes to the bottom there. A done or archived task keeps its place; if reactivated it reappears where it was</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -8855,7 +8983,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.4</t>
+          <t>LLR-2.14</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -8865,12 +8993,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-2</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Completing a one-off task sets it to done. Further completions are rejected (409)</t>
+          <t>Existing data is kept: migration adds tasks.sort_order, initialised per area from today's order (priority high → low, then creation time), with a backup first. The old priority value stays in the database and the JSON export but is no longer shown or used</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -8899,7 +9027,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.5</t>
+          <t>LLR-3.1</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -8914,7 +9042,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Completing a done or archived task is rejected with a message naming its status (409)</t>
+          <t>Complete an active task, optionally with a note (≤ 1000) and a time (completedAt). If no time is given, the time is now</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -8943,7 +9071,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.6</t>
+          <t>LLR-3.2</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -8958,12 +9086,12 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>The activity log lists completions newest first, with local date/time and note</t>
+          <t>Logging uses a month calendar: days the task was done are marked (with a count when more than once), today is outlined, future days are disabled, and ‹ › move between months. Tap a day, adjust the time (defaults to now), add an optional note and log. A time later than now is clamped to now</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -8987,7 +9115,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.7</t>
+          <t>LLR-3.3</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -9002,7 +9130,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Each task shows completion count, current streak, best streak and last completion time</t>
+          <t>A completion more than 1 minute in the future is rejected (422)</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -9031,7 +9159,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.8</t>
+          <t>LLR-3.4</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -9046,12 +9174,12 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>The area list offers a one-tap ✓ complete (now) for active tasks</t>
+          <t>Completing a one-off task sets it to done. Further completions are rejected (409)</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -9075,7 +9203,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.1</t>
+          <t>LLR-3.5</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -9085,12 +9213,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Create a reward: title (1–200, required), description (≤ 2000), image URL (≤ 500, optional), rule type (completions or streak), threshold N (1–365), tagged tasks (optional)</t>
+          <t>Completing a done or archived task is rejected with a message naming its status (409)</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -9119,7 +9247,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.2</t>
+          <t>LLR-3.6</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -9129,12 +9257,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Tag or untag tasks as a full replacement of the set. Unknown task ids are rejected (422)</t>
+          <t>The activity log lists completions newest first, with local date/time and note</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -9163,7 +9291,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.3</t>
+          <t>LLR-3.7</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -9173,17 +9301,17 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Tag a task to a locked reward from the task detail screen</t>
+          <t>Each task shows completion count, current streak, best streak and last completion time</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -9207,7 +9335,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.4</t>
+          <t>LLR-3.8</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -9217,17 +9345,17 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Show each reward's rule text, progress (current / target, %), status and tagged tasks</t>
+          <t>The area list offers a one-tap ✓ complete (now) for active tasks</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -9251,7 +9379,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.5</t>
+          <t>LLR-4.1</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -9266,7 +9394,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Filter the rewards list by status</t>
+          <t>Create a reward: title (1–200, required), description (≤ 2000), image URL (≤ 500, optional), rule type (completions or streak), threshold N (1–365), tagged tasks (optional)</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -9295,7 +9423,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.6</t>
+          <t>LLR-4.2</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -9310,7 +9438,7 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Claim is only possible when the status is unlocked. Claiming a locked reward is rejected (409). Claiming an already claimed reward changes nothing</t>
+          <t>Tag or untag tasks as a full replacement of the set. Unknown task ids are rejected (422)</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -9339,7 +9467,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.7</t>
+          <t>LLR-4.3</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -9354,12 +9482,12 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>When a completion unlocks a reward, the completion response includes it and the UI shows a celebration toast</t>
+          <t>Tag a task to a locked reward from the task detail screen</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -9383,7 +9511,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.8</t>
+          <t>LLR-4.4</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -9398,12 +9526,12 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Editing a reward's tasks is only offered while it's locked</t>
+          <t>Show each reward's rule text, progress (current / target, %), status and tagged tasks</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -9427,7 +9555,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.9</t>
+          <t>LLR-4.5</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -9437,12 +9565,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Rewards stand alone. A reward needs only a title and N (default 5); a note and picture link are optional. It can optionally be kept in an area (to organise it; its tile comes from the area), but that never limits which tasks it can be linked to</t>
+          <t>Filter the rewards list by status</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -9471,7 +9599,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.10</t>
+          <t>LLR-4.6</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -9481,12 +9609,12 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Links are many-to-many and unrestricted: any task (from any tile or area) can be linked to any reward; one task can count for several rewards. Unlock rule for now: task count, the linked tasks done N times in total. (Older rewards that counted "all tasks in an area" keep working)</t>
+          <t>Claim is only possible when the status is unlocked. Claiming a locked reward is rejected (409). Claiming an already claimed reward changes nothing</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -9515,7 +9643,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.11</t>
+          <t>LLR-4.7</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -9525,12 +9653,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Linking twice is harmless; unlinking an unlocked or claimed reward doesn't lock it again (BR-R10); deleting a task, area or tile removes only its links, and rewards stay. Deleting a tile does delete rewards kept in it (BR-R18)</t>
+          <t>When a completion unlocks a reward, the completion response includes it and the UI shows a celebration toast</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -9559,7 +9687,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.12</t>
+          <t>LLR-4.8</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -9569,17 +9697,17 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>The Link screen (#/rewards/link, top menu *Link*) lists all tasks (grouped by tile › area, with how often each was done and how many rewards it counts for) and all rewards (with area, N and status), each searchable. Pick a task and a reward, then Link (or Unlink if they already are). *Current links* lists each linked reward with its tasks, each with ✕ to unlink. Opens with a task or reward already picked from the task or reward screens</t>
+          <t>Editing a reward's tasks is only offered while it's locked</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -9603,7 +9731,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.13</t>
+          <t>LLR-4.9</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -9618,7 +9746,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>The top menu is Tiles | Tasks | Rewards | Link. *Tasks* lists every task grouped by tile › area (status filter, default Active; search; each row shows frequency, completions, streak 🔥 and rewards 🎁, with a quick ✓). *Rewards* lists every reward grouped by the area it's kept in (tile › area order, *Not in an area* last; status filter; search; + New with an optional area). The Link screen's two lists use the same grouping. A tile shows only its areas; an area has tabs Tasks | Rewards | Notes &amp; contacts, and its Rewards tab lists and adds the rewards kept there but doesn't link tasks</t>
+          <t>Rewards stand alone. A reward needs only a title and N (default 5); a note and picture link are optional. It can optionally be kept in an area (to organise it; its tile comes from the area), but that never limits which tasks it can be linked to</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -9647,7 +9775,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.14</t>
+          <t>LLR-4.10</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9662,7 +9790,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>A reward's screen (#/rewards/r/{id}) shows its rule, progress and linked tasks (✕ to unlink), *+ Link tasks* (Link screen with this reward picked), *Claim 🎁* when unlocked, and ✎ / 🗑 to edit (title, N while locked, area, note, picture) or delete it (tasks and history stay)</t>
+          <t>Links are many-to-many and unrestricted: any task (from any tile or area) can be linked to any reward; one task can count for several rewards. Unlock rule for now: task count, the linked tasks done N times in total. (Older rewards that counted "all tasks in an area" keep working)</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -9691,7 +9819,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.15</t>
+          <t>LLR-4.11</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -9706,7 +9834,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>On task detail, the *Rewards* card lists the rewards the task counts for (links to each reward) and *+ Link to a reward* opens the Link screen with this task picked</t>
+          <t>Linking twice is harmless; unlinking an unlocked or claimed reward doesn't lock it again (BR-R10); deleting a task, area or tile removes only its links, and rewards stay. Deleting a tile does delete rewards kept in it (BR-R18)</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -9735,7 +9863,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.16</t>
+          <t>LLR-4.12</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9750,7 +9878,7 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>N can be changed only while the reward is locked; lowering it re-checks the rule at once. A reward whose linked tasks already meet N unlocks as soon as it's linked</t>
+          <t>The Link screen (#/rewards/link, top menu *Link*) lists all tasks (grouped by tile › area, with how often each was done and how many rewards it counts for) and all rewards (with area, N and status), each searchable. Pick a task and a reward, then Link (or Unlink if they already are). *Current links* lists each linked reward with its tasks, each with ✕ to unlink. Opens with a task or reward already picked from the task or reward screens</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -9779,7 +9907,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.17</t>
+          <t>LLR-4.13</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -9794,7 +9922,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Moving a reward to another area, or out of any area, never changes its links</t>
+          <t>The top menu is Tiles | Tasks | Rewards | Link. *Tasks* lists every task grouped by tile › area (status filter, default Active; search; each row shows frequency, completions, streak 🔥 and rewards 🎁, with a quick ✓). *Rewards* lists every reward grouped by the area it's kept in (tile › area order, *Not in an area* last; status filter; search; + New with an optional area). The Link screen's two lists use the same grouping. A tile shows only its areas; an area has tabs Tasks | Rewards | Notes &amp; contacts, and its Rewards tab lists and adds the rewards kept there but doesn't link tasks</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -9823,7 +9951,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.18</t>
+          <t>LLR-4.14</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9838,7 +9966,7 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Existing rewards are migrated without data loss (schema migration with automatic pre-upgrade backup): if all tagged tasks share one area, scope = that area; else if they share one tile, scope = that tile; otherwise (no tags, or tags across tiles) the reward keeps its tags and is marked *Needs a tile* until the user picks one. No reward, tag, completion or status is deleted</t>
+          <t>A reward's screen (#/rewards/r/{id}) shows its rule, progress and linked tasks (✕ to unlink), *+ Link tasks* (Link screen with this reward picked), *Claim 🎁* when unlocked, and ✎ / 🗑 to edit (title, N while locked, area, note, picture) or delete it (tasks and history stay)</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -9867,7 +9995,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.1</t>
+          <t>LLR-4.15</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -9877,12 +10005,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>HLR-5</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Reads only GET /dashboard/summary; never the database</t>
+          <t>On task detail, the *Rewards* card lists the rewards the task counts for (links to each reward) and *+ Link to a reward* opens the Link screen with this task picked</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -9911,7 +10039,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.2</t>
+          <t>LLR-4.16</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9921,17 +10049,17 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>HLR-5</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>KPIs: completions (window), active tasks, active streaks, unlocked + claimed rewards, AI acceptance rate (— when undefined)</t>
+          <t>N can be changed only while the reward is locked; lowering it re-checks the rule at once. A reward whose linked tasks already meet N unlocks as soon as it's linked</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -9955,7 +10083,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.3</t>
+          <t>LLR-4.17</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -9965,17 +10093,17 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>HLR-5</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Charts: completions by tile, by area (filterable by tile) and per day (empty days shown as gaps). Hover tooltips on every mark</t>
+          <t>Moving a reward to another area, or out of any area, never changes its links</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -9999,7 +10127,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.4</t>
+          <t>LLR-4.18</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -10009,17 +10137,17 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>HLR-5</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Tables: active streaks (filterable by tile); reward progress with a progress bar</t>
+          <t>Existing rewards are migrated without data loss (schema migration with automatic pre-upgrade backup): if all tagged tasks share one area, scope = that area; else if they share one tile, scope = that tile; otherwise (no tags, or tags across tiles) the reward keeps its tags and is marked *Needs a tile* until the user picks one. No reward, tag, completion or status is deleted</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -10043,7 +10171,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.5</t>
+          <t>LLR-5.1</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -10058,12 +10186,12 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Filters: window (7/30/90 days/all time) and tile. They survive reruns (session_state)</t>
+          <t>Reads only GET /dashboard/summary; never the database</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -10087,7 +10215,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.6</t>
+          <t>LLR-5.2</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -10102,7 +10230,7 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Responses are cached 30 s per window. *Refresh now* clears the cache</t>
+          <t>KPIs: completions (window), active tasks, active streaks, unlocked + claimed rewards, AI acceptance rate (— when undefined)</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -10131,7 +10259,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.7</t>
+          <t>LLR-5.3</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -10146,7 +10274,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Unlocked rewards can be claimed from the dashboard. After claiming, the cache is cleared and the page shows fresh data</t>
+          <t>Charts: completions by tile, by area (filterable by tile) and per day (empty days shown as gaps). Hover tooltips on every mark</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -10175,7 +10303,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.8</t>
+          <t>LLR-5.4</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -10190,7 +10318,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>If the BFF is unreachable, show the error and *Try again* (no stack traces)</t>
+          <t>Tables: active streaks (filterable by tile); reward progress with a progress bar</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -10219,7 +10347,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.9</t>
+          <t>LLR-5.5</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -10234,12 +10362,12 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Streaks and rewards ignore the window; completion aggregates respect it</t>
+          <t>Filters: window (7/30/90 days/all time) and tile. They survive reruns (session_state)</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -10263,7 +10391,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.10</t>
+          <t>LLR-5.6</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -10278,12 +10406,12 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Summary payload is flat snake_case records; React endpoints are camelCase (per-client shaping)</t>
+          <t>Responses are cached 30 s per window. *Refresh now* clears the cache</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -10307,7 +10435,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.11</t>
+          <t>LLR-5.7</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -10322,12 +10450,12 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Reward progress rows include the reward's tile and area; the dashboard's tile filter applies to rewards as well as completions and streaks</t>
+          <t>Unlocked rewards can be claimed from the dashboard. After claiming, the cache is cleared and the page shows fresh data</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -10351,7 +10479,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.1</t>
+          <t>LLR-5.8</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -10361,22 +10489,22 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>HLR-6</t>
+          <t>HLR-5</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Attach 1–5 photos per run to an area (JPEG/PNG/WebP, ≤ 5 MB each; type checked by content, not extension)</t>
+          <t>If the BFF is unreachable, show the error and *Try again* (no stack traces)</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
@@ -10395,7 +10523,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.2</t>
+          <t>LLR-5.9</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -10405,22 +10533,22 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>HLR-6</t>
+          <t>HLR-5</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Photos are stored privately with random names and are never publicly addressable</t>
+          <t>Streaks and rewards ignore the window; completion aggregates respect it</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -10439,7 +10567,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.3</t>
+          <t>LLR-5.10</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -10449,22 +10577,22 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>HLR-6</t>
+          <t>HLR-5</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Starting a suggestion run returns immediately (202) with a run id; the UI shows a loading state</t>
+          <t>Summary payload is flat snake_case records; React endpoints are camelCase (per-client shaping)</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
@@ -10483,7 +10611,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.4</t>
+          <t>LLR-5.11</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -10493,22 +10621,22 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>HLR-6</t>
+          <t>HLR-5</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>While a run is in progress, the manual *Add a task* form stays fully usable</t>
+          <t>Reward progress rows include the reward's tile and area; the dashboard's tile filter applies to rewards as well as completions and streaks</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
@@ -10527,7 +10655,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.5</t>
+          <t>LLR-6.1</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10542,7 +10670,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Each suggestion has a title (≤ 200), why (≤ 500), priority and frequency, validated against a strict schema</t>
+          <t>Attach 1–5 photos per run to an area (JPEG/PNG/WebP, ≤ 5 MB each; type checked by content, not extension)</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -10571,7 +10699,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.6</t>
+          <t>LLR-6.2</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -10586,7 +10714,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>The user marks each suggestion Relevant / Not relevant / Ignore. Relevant creates a task with source = ai. A decision is final (409 on re-decide)</t>
+          <t>Photos are stored privately with random names and are never publicly addressable</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -10615,7 +10743,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.7</t>
+          <t>LLR-6.3</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -10630,7 +10758,7 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>On timeout (30 s), invalid output or missing API key: retry once where sensible, then show "AI suggestions unavailable, add tasks manually". The page never breaks</t>
+          <t>Starting a suggestion run returns immediately (202) with a run id; the UI shows a loading state</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -10659,7 +10787,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.8</t>
+          <t>LLR-6.4</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -10674,7 +10802,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>The API key exists only in BFF environment variables</t>
+          <t>While a run is in progress, the manual *Add a task* form stays fully usable</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -10703,7 +10831,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.9</t>
+          <t>LLR-6.5</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -10718,7 +10846,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Decisions feed the dashboard acceptance rate (relevant ÷ decided)</t>
+          <t>Each suggestion has a title (≤ 200), why (≤ 500), priority and frequency, validated against a strict schema</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -10747,7 +10875,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.1</t>
+          <t>LLR-6.6</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -10757,22 +10885,22 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>HLR-7</t>
+          <t>HLR-6</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>The MFE is built separately and exposes ./RewardsApp via remoteEntry.js</t>
+          <t>The user marks each suggestion Relevant / Not relevant / Ignore. Relevant creates a task with source = ai. A decision is final (409 on re-decide)</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -10791,7 +10919,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.2</t>
+          <t>LLR-6.7</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -10801,22 +10929,22 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>HLR-7</t>
+          <t>HLR-6</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>The host mounts it on #/rewards and every #/rewards/*. The nav item stays active on sub-routes</t>
+          <t>On timeout (30 s), invalid output or missing API key: retry once where sensible, then show "AI suggestions unavailable, add tasks manually". The page never breaks</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
@@ -10835,7 +10963,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.3</t>
+          <t>LLR-6.8</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -10845,22 +10973,22 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>HLR-7</t>
+          <t>HLR-6</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Host and remote share one React instance; the remote bundles no React</t>
+          <t>The API key exists only in BFF environment variables</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -10879,7 +11007,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.4</t>
+          <t>LLR-6.9</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -10889,22 +11017,22 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>HLR-7</t>
+          <t>HLR-6</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>If the remote fails to load, the host shows "Rewards is unavailable right now" and a reload button. Other pages are unaffected</t>
+          <t>Decisions feed the dashboard acceptance rate (relevant ÷ decided)</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
@@ -10923,7 +11051,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.5</t>
+          <t>LLR-7.1</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -10938,12 +11066,12 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>MFE styles are scoped (.rw-app) and don't alter host styles</t>
+          <t>The MFE is built separately and exposes ./RewardsApp via remoteEntry.js</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -10967,7 +11095,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.6</t>
+          <t>LLR-7.2</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -10982,12 +11110,12 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>The remote URL is configurable per environment (VITE_REWARDS_REMOTE_URL)</t>
+          <t>The host mounts it on #/rewards and every #/rewards/*. The nav item stays active on sub-routes</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
@@ -11011,7 +11139,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.7</t>
+          <t>LLR-7.3</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -11026,7 +11154,7 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>The MFE runs standalone for development (npm run dev)</t>
+          <t>Host and remote share one React instance; the remote bundles no React</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -11055,7 +11183,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.8</t>
+          <t>LLR-7.4</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -11070,7 +11198,7 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Every screen has loading, error (with retry) and empty states</t>
+          <t>If the remote fails to load, the host shows "Rewards is unavailable right now" and a reload button. Other pages are unaffected</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -11099,7 +11227,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.1</t>
+          <t>LLR-7.5</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -11109,17 +11237,17 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>HLR-8</t>
+          <t>HLR-7</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Every endpoint except /health needs Authorization: Bearer &lt;demo token&gt;; otherwise 401</t>
+          <t>MFE styles are scoped (.rw-app) and don't alter host styles</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
@@ -11143,7 +11271,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.2</t>
+          <t>LLR-7.6</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -11153,12 +11281,12 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>HLR-8</t>
+          <t>HLR-7</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>CORS allows only the configured origins</t>
+          <t>The remote URL is configurable per environment (VITE_REWARDS_REMOTE_URL)</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -11187,7 +11315,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.3</t>
+          <t>LLR-7.7</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -11197,17 +11325,17 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>HLR-8</t>
+          <t>HLR-7</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>OpenAPI documentation is served at /docs</t>
+          <t>The MFE runs standalone for development (npm run dev)</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
@@ -11231,7 +11359,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.4</t>
+          <t>LLR-7.8</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -11241,17 +11369,17 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>HLR-8</t>
+          <t>HLR-7</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Errors use {detail} with status codes 401, 404, 409 and 422 as catalogued in LLD §3.3</t>
+          <t>Every screen has loading, error (with retry) and empty states</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr">
@@ -11275,7 +11403,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.5</t>
+          <t>LLR-8.1</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -11290,7 +11418,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Request bodies accept camelCase or snake_case. React responses are camelCase; dashboard responses are snake_case</t>
+          <t>Every endpoint except /health needs Authorization: Bearer &lt;demo token&gt;; otherwise 401</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -11319,7 +11447,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.6</t>
+          <t>LLR-8.2</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -11334,7 +11462,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Timestamps are ISO-8601 UTC in responses</t>
+          <t>CORS allows only the configured origins</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -11363,7 +11491,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.7</t>
+          <t>LLR-8.3</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -11373,12 +11501,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-8</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>POST /rewards needs only title (optional threshold = N, default 5, areaId, description, imageUrl, taskIds). GET /rewards (?status=, ?areaId=), GET / PATCH / DELETE /rewards/{id} (PATCH edits title, N, note, picture, areaId or null). POST / DELETE /rewards/{id}/tasks/{taskId} link and unlink one task; PUT /rewards/{id}/tasks replaces all links. Responses include the optional categoryId, categoryName, categoryIcon, areaId, areaName, plus tasks, connected and matchedTaskCount</t>
+          <t>OpenAPI documentation is served at /docs</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -11407,7 +11535,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.8</t>
+          <t>LLR-8.4</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -11417,12 +11545,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-8</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Task detail's rewards lists every reward the task counts for, with how (tagged = linked, or scope for older all-tasks-in-an-area rewards)</t>
+          <t>Errors use {detail} with status codes 401, 404, 409 and 422 as catalogued in LLD §3.3</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -11451,7 +11579,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.9</t>
+          <t>LLR-8.5</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -11466,7 +11594,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Schema changes are applied by versioned migrations on startup, never by dropping and recreating tables; a backup of the database file is written before each upgrade (Q14)</t>
+          <t>Request bodies accept camelCase or snake_case. React responses are camelCase; dashboard responses are snake_case</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -11495,7 +11623,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.10</t>
+          <t>LLR-8.6</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -11505,12 +11633,12 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>HLR-1</t>
+          <t>HLR-8</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Tile endpoints: POST /categories, PATCH /categories/{id} (name, icon), DELETE /categories/{id}, PUT /categories/order and PUT /categories/{id}/areas/order, POST /categories/starter (LLR-1.8, returns what was added)</t>
+          <t>Timestamps are ISO-8601 UTC in responses</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -11539,7 +11667,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.11</t>
+          <t>LLR-8.7</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -11549,12 +11677,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Details endpoints for both owners (/categories/{id} and /areas/{id}): …/details (grouped by topic), …/notes, …/contacts, …/files (multipart upload); PATCH/DELETE on /notes/{id}, /contacts/{id}, /files/{id}; GET /files/{id}/download; GET /search?q=</t>
+          <t>POST /rewards needs only title (optional threshold = N, default 5, areaId, description, imageUrl, taskIds). GET /rewards (?status=, ?areaId=), GET / PATCH / DELETE /rewards/{id} (PATCH edits title, N, note, picture, areaId or null). POST / DELETE /rewards/{id}/tasks/{taskId} link and unlink one task; PUT /rewards/{id}/tasks replaces all links. Responses include the optional categoryId, categoryName, categoryIcon, areaId, areaName, plus tasks, connected and matchedTaskCount</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -11583,7 +11711,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.12</t>
+          <t>LLR-8.8</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -11593,12 +11721,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Task create/update accept isMilestone, visibility (announced | silent), dueAt (ISO date-time, optional) and targetDays (optional); GET /areas/{id}/tasks adds filters milestone=true and due=overdue|today|week and sort=due. Responses served without the passcode omit silent tasks entirely (BR-R23)</t>
+          <t>Task detail's rewards lists every reward the task counts for, with how (tagged = linked, or scope for older all-tasks-in-an-area rewards)</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -11627,7 +11755,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.13</t>
+          <t>LLR-8.9</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -11637,12 +11765,12 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-8</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>POST /rewards accepts status: "idea", forWhom, visibility, link and whereSeen; POST /rewards/{id}/activate (ruleType, threshold), /close (outcome: bought | dropped) and /reopen; PUT / DELETE /rewards/{id}/cover (multipart photo; served by a signed link like files); GET /rewards filters status=idea|closed and forWhom=; GET /rewards-people lists everyone for suggestions; ideas can't be linked or claimed (409)</t>
+          <t>Schema changes are applied by versioned migrations on startup, never by dropping and recreating tables; a backup of the database file is written before each upgrade (Q14)</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -11671,7 +11799,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.1</t>
+          <t>LLR-8.10</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -11681,12 +11809,12 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-1</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>The area screen has a Notes &amp; contacts tab (tiles no longer have their own tabs; older tile-level items stay stored and searchable) next to their main content. It lists topics as groups (items without a topic under "General"), each showing its contacts, files and notes</t>
+          <t>Tile endpoints: POST /categories, PATCH /categories/{id} (name, icon), DELETE /categories/{id}, PUT /categories/order and PUT /categories/{id}/areas/order, POST /categories/starter (LLR-1.8, returns what was added)</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -11715,7 +11843,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.2</t>
+          <t>LLR-8.11</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -11730,7 +11858,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Topic is free text (1–60 characters), optional, and offers existing topics from the same tile or area as suggestions, so "Bosch Dishwasher" isn't typed three different ways</t>
+          <t>Details endpoints for both owners (/categories/{id} and /areas/{id}): …/details (grouped by topic), …/notes, …/contacts, …/files (multipart upload); PATCH/DELETE on /notes/{id}, /contacts/{id}, /files/{id}; GET /files/{id}/download; GET /search?q=</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -11759,7 +11887,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.3</t>
+          <t>LLR-8.12</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -11769,12 +11897,12 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Contact: name (required, 1–80); organisation or brand (e.g. Bosch, Kent, IFB, LG); role (*Customer care*, *Service executive*, *Technician*, *Vendor or shop*, *Other*); up to 3 phone numbers with labels (mobile, toll-free, WhatsApp); email; website; last visit or contact date; notes (≤ 1000); topic</t>
+          <t>Task create/update accept isMilestone, visibility (announced | silent), dueAt (ISO date-time, optional) and targetDays (optional); GET /areas/{id}/tasks adds filters milestone=true and due=overdue|today|week and sort=due. Responses served without the passcode omit silent tasks entirely (BR-R23)</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
@@ -11803,7 +11931,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.4</t>
+          <t>LLR-8.13</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -11813,12 +11941,12 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Phone numbers are stored as entered and shown with actions: Call (tel:), WhatsApp (wa.me, for numbers marked WhatsApp) and Copy. Email gets Email (mailto:). All actions are one tap on a phone</t>
+          <t>POST /rewards accepts status: "idea", forWhom, visibility, link and whereSeen; POST /rewards/{id}/activate (ruleType, threshold), /close (outcome: bought | dropped) and /reopen; PUT / DELETE /rewards/{id}/cover (multipart photo; served by a signed link like files); GET /rewards filters status=idea|closed and forWhom=; GET /rewards-people lists everyone for suggestions; ideas can't be linked or claimed (409)</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -11847,7 +11975,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.5</t>
+          <t>LLR-10.1</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -11862,7 +11990,7 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Past executives: within a topic, contacts with the role *Service executive* or *Technician* are listed newest last-visit first. The topic header shows the last executive (name, date, call button)</t>
+          <t>The area screen has a Notes &amp; contacts tab (tiles no longer have their own tabs; older tile-level items stay stored and searchable) next to their main content. It lists topics as groups (items without a topic under "General"), each showing its contacts, files and notes</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
@@ -11891,7 +12019,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.6</t>
+          <t>LLR-10.2</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -11906,7 +12034,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Note: text 1–5000 characters, optional title and topic; shows created and last-edited time; newest first</t>
+          <t>Topic is free text (1–60 characters), optional, and offers existing topics from the same tile or area as suggestions, so "Bosch Dishwasher" isn't typed three different ways</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -11935,7 +12063,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.7</t>
+          <t>LLR-10.3</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -11950,7 +12078,7 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>File (bills, invoices, warranty cards, manuals): PDF, JPG, PNG, WebP or HEIC, up to 10 MB each, checked by content; title (required), optional date, amount (₹) and topic. Files open in the browser or download; images show a thumbnail</t>
+          <t>Contact: name (required, 1–80); organisation or brand (e.g. Bosch, Kent, IFB, LG); role (*Customer care*, *Service executive*, *Technician*, *Vendor or shop*, *Other*); up to 3 phone numbers with labels (mobile, toll-free, WhatsApp); email; website; last visit or contact date; notes (≤ 1000); topic</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
@@ -11979,7 +12107,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.8</t>
+          <t>LLR-10.4</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -11994,7 +12122,7 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Notes, contacts and files can be edited and deleted (with confirmation), and moved between topics by editing the topic</t>
+          <t>Phone numbers are stored as entered and shown with actions: Call (tel:), WhatsApp (wa.me, for numbers marked WhatsApp) and Copy. Email gets Email (mailto:). All actions are one tap on a phone</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -12023,7 +12151,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.9</t>
+          <t>LLR-10.5</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -12038,7 +12166,7 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Search across every tile and area by contact name, organisation, topic, phone digits (spaces and dashes ignored), note text and file title. Results show where each hit lives (e.g. "Household › Kitchen › Bosch Dishwasher") and link to it</t>
+          <t>Past executives: within a topic, contacts with the role *Service executive* or *Technician* are listed newest last-visit first. The topic header shows the last executive (name, date, call button)</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
@@ -12067,7 +12195,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.10</t>
+          <t>LLR-10.6</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -12082,7 +12210,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>Deleting an area or tile deletes its notes, contacts and files, and the confirmation counts them (LLR-1.12). Stored files are removed only after the database change commits</t>
+          <t>Note: text 1–5000 characters, optional title and topic; shows created and last-edited time; newest first</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -12111,7 +12239,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.11</t>
+          <t>LLR-10.7</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -12126,7 +12254,7 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Visibility follows the rewards setting (Q17): readable in the read-only view when public reads are on; creating, editing, deleting and uploading need the owner passcode</t>
+          <t>File (bills, invoices, warranty cards, manuals): PDF, JPG, PNG, WebP or HEIC, up to 10 MB each, checked by content; title (required), optional date, amount (₹) and topic. Files open in the browser or download; images show a thumbnail</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
@@ -12155,7 +12283,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>LLR-10.12</t>
+          <t>LLR-10.8</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -12170,12 +12298,12 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>The JSON export (app.backup) includes notes and contacts, and lists files by title and stored name; the server backup covers the files folder as well as the database</t>
+          <t>Notes, contacts and files can be edited and deleted (with confirmation), and moved between topics by editing the topic</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
@@ -12199,7 +12327,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.1</t>
+          <t>LLR-10.9</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -12209,12 +12337,12 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Milestone: yes/no (default no), set when creating or editing a task</t>
+          <t>Search across every tile and area by contact name, organisation, topic, phone digits (spaces and dashes ignored), note text and file title. Results show where each hit lives (e.g. "Household › Kitchen › Bosch Dishwasher") and link to it</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
@@ -12243,7 +12371,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.2</t>
+          <t>LLR-10.10</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -12253,12 +12381,12 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Milestones show a 🏁 badge on task rows (area list, Tasks list, Link screen) and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
+          <t>Deleting an area or tile deletes its notes, contacts and files, and the confirmation counts them (LLR-1.12). Stored files are removed only after the database change commits</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -12287,7 +12415,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.3</t>
+          <t>LLR-10.11</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -12297,12 +12425,12 @@
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Completing an announced milestone shows the milestone celebration: a larger, longer celebration than a normal completion (respects reduced motion), with its own share prompt</t>
+          <t>Visibility follows the rewards setting (Q17): readable in the read-only view when public reads are on; creating, editing, deleting and uploading need the owner passcode</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
@@ -12331,7 +12459,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.4</t>
+          <t>LLR-10.12</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -12341,17 +12469,17 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task linked to it has at least one completion (BR-R25). With no milestone linked yet it shows 0 of 0 and never unlocks (tasks are linked later, on the Link screen)</t>
+          <t>The JSON export (app.backup) includes notes and contacts, and lists files by title and stored name; the server backup covers the files folder as well as the database</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
@@ -12375,7 +12503,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.5</t>
+          <t>LLR-11.1</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -12390,7 +12518,7 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Announce or keep silent: each task is *Announced* (default) or *Silent*, set when creating or editing it (Q20, Q22)</t>
+          <t>Milestone: yes/no (default no), set when creating or editing a task</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
@@ -12419,7 +12547,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.6</t>
+          <t>LLR-11.2</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -12434,12 +12562,12 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Silent tasks and their completions never appear in anything served without the owner passcode: lists, counts, streaks, activity, dashboard aggregates or reward task lists (BR-R23). With the passcode they're shown with a 🔕 marker</t>
+          <t>Milestones show a 🏁 badge on task rows (area list, Tasks list, Link screen) and task detail. The area task list has a Milestones only filter, and the dashboard has a *Milestones* table (title, tile › area, due, done / overdue / upcoming)</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
@@ -12463,7 +12591,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.7</t>
+          <t>LLR-11.3</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -12478,7 +12606,7 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Completing an announced task shows the celebration toast and a Share on WhatsApp prompt (prefilled text, e.g. "Done: Wipe counters 🔥 3-day streak"). Completing a silent task shows only a quiet "Logged" confirmation, with no share prompt (BR-R24)</t>
+          <t>Completing an announced milestone shows the milestone celebration: a larger, longer celebration than a normal completion (respects reduced motion), with its own share prompt</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
@@ -12507,7 +12635,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.8</t>
+          <t>LLR-11.4</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -12522,7 +12650,7 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Due date and time (optional): a local date and time, stored in UTC. Tasks show a chip: *Overdue* (red), *Due today*, *Due in N days* (within 7 days) or the date. The area list can be filtered by *Overdue*, *Due today* and *Due this week*, and sorted by due date</t>
+          <t>New reward rule Milestone completed (alongside *N completions* and *streak of N*). The reward unlocks when every milestone task linked to it has at least one completion (BR-R25). With no milestone linked yet it shows 0 of 0 and never unlocks (tasks are linked later, on the Link screen)</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -12551,7 +12679,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.9</t>
+          <t>LLR-11.5</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -12566,7 +12694,7 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Days to complete (optional): a whole number from 1 to 3650, shown as "Planned: N days". Task detail also shows "Day X of N", counted from the task's creation date</t>
+          <t>Announce or keep silent: each task is *Announced* (default) or *Silent*, set when creating or editing it (Q20, Q22)</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -12595,7 +12723,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.10</t>
+          <t>LLR-11.6</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -12610,12 +12738,12 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Due date and days to complete are independent: changing one never changes the other, and they may disagree (Q21, BR-R26)</t>
+          <t>Silent tasks and their completions never appear in anything served without the owner passcode: lists, counts, streaks, activity, dashboard aggregates or reward task lists (BR-R23). With the passcode they're shown with a 🔕 marker</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
@@ -12639,7 +12767,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.11</t>
+          <t>LLR-11.7</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -12654,7 +12782,7 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>All four attributes can be edited on task detail at any time. A due date in the past is allowed (the task is simply overdue)</t>
+          <t>Completing an announced task shows the celebration toast and a Share on WhatsApp prompt (prefilled text, e.g. "Done: Wipe counters 🔥 3-day streak"). Completing a silent task shows only a quiet "Logged" confirmation, with no share prompt (BR-R24)</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
@@ -12683,7 +12811,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.12</t>
+          <t>LLR-11.8</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -12698,7 +12826,7 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>Existing tasks are migrated without data loss: milestone = no, visibility = announced, no due date, no days to complete. Nothing else changes</t>
+          <t>Due date and time (optional): a local date and time, stored in UTC. Tasks show a chip: *Overdue* (red), *Due today*, *Due in N days* (within 7 days) or the date. The area list can be filtered by *Overdue*, *Due today* and *Due this week*, and sorted by due date</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -12727,7 +12855,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>LLR-11.13</t>
+          <t>LLR-11.9</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -12742,7 +12870,7 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>The dashboard adds an Overdue KPI and the *Milestones* table (LLR-11.2); the owner-only dashboard includes silent tasks, marked 🔕</t>
+          <t>Days to complete (optional): a whole number from 1 to 3650, shown as "Planned: N days". Task detail also shows "Day X of N", counted from the task's creation date</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
@@ -12771,7 +12899,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.1</t>
+          <t>LLR-11.10</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -12781,12 +12909,12 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Quick capture: "💡 + Idea" on the Rewards screen and on every area's Rewards tab opens a short form: title (required), for whom (default Me) and a one-tap cover photo (camera or gallery; JPG, PNG, WebP or HEIC up to 10 MB); *More* adds where seen, link, note and (on the Rewards screen) an optional area. Saving needs only the title</t>
+          <t>Due date and days to complete are independent: changing one never changes the other, and they may disagree (Q21, BR-R26)</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -12815,7 +12943,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.2</t>
+          <t>LLR-11.11</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -12825,12 +12953,12 @@
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>For whom on every reward and idea: free text (1–40) with suggestions from earlier entries; default "Me" (Q25)</t>
+          <t>All four attributes can be edited on task detail at any time. A due date in the past is allowed (the task is simply overdue)</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
@@ -12859,7 +12987,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.3</t>
+          <t>LLR-11.12</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -12869,12 +12997,12 @@
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>Ideas have status Idea: no rule, no progress and no tasks, and they never unlock or appear in progress counts (BR-R27)</t>
+          <t>Existing tasks are migrated without data loss: milestone = no, visibility = announced, no due date, no days to complete. Nothing else changes</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -12903,7 +13031,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.4</t>
+          <t>LLR-11.13</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -12913,12 +13041,12 @@
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>The Rewards screen filters by status (💡 Ideas, Locked, Unlocked, Claimed, Closed) and by for whom (e.g. *Shiragi*), plus search; closed ideas are hidden unless *Closed* is chosen. An area's Rewards tab lists its ideas with its rewards. Ideas are never offered on the Link screen</t>
+          <t>The dashboard adds an Overdue KPI and the *Milestones* table (LLR-11.2); the owner-only dashboard includes silent tasks, marked 🔕</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
@@ -12947,7 +13075,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.5</t>
+          <t>LLR-12.1</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -12962,7 +13090,7 @@
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Turn into reward: on an idea, pick how it unlocks (task count with N, or milestone completed). It becomes a normal *locked* reward with the same id, keeping title, photo, link, note, where seen, area and for whom; tasks are then linked on the Link screen (BR-R28)</t>
+          <t>Quick capture: "💡 + Idea" on the Rewards screen and on every area's Rewards tab opens a short form: title (required), for whom (default Me) and a one-tap cover photo (camera or gallery; JPG, PNG, WebP or HEIC up to 10 MB); *More* adds where seen, link, note and (on the Rewards screen) an optional area. Saving needs only the title</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -12991,7 +13119,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.6</t>
+          <t>LLR-12.2</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -13006,7 +13134,7 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Close an idea as *Bought* (got it without a rule) or *Dropped* (no longer wanted). Closed ideas leave the Ideas list, stay under *Closed* with the date and outcome, and can be reopened (BR-R29)</t>
+          <t>For whom on every reward and idea: free text (1–40) with suggestions from earlier entries; default "Me" (Q25)</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
@@ -13035,7 +13163,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.7</t>
+          <t>LLR-12.3</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -13050,12 +13178,12 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>Ideas are Silent by default (hidden from the read-only view) and can be switched to *Announced*; ordinary rewards default to *Announced*. Visibility follows the silent rules of BR-R23 (Q24)</t>
+          <t>Ideas have status Idea: no rule, no progress and no tasks, and they never unlock or appear in progress counts (BR-R27)</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Built (manual test)</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
@@ -13079,7 +13207,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.8</t>
+          <t>LLR-12.4</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -13094,7 +13222,7 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Ideas are included in search (LLR-10.9) by title, notes, for whom and where seen</t>
+          <t>The Rewards screen filters by status (💡 Ideas, Locked, Unlocked, Claimed, Closed) and by for whom (e.g. *Shiragi*), plus search; closed ideas are hidden unless *Closed* is chosen. An area's Rewards tab lists its ideas with its rewards. Ideas are never offered on the Link screen</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
@@ -13123,7 +13251,7 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>LLR-12.9</t>
+          <t>LLR-12.5</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -13138,7 +13266,7 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>Existing rewards are migrated without data loss: for whom = "Me", visibility = announced; their status, rule, tasks and progress are unchanged</t>
+          <t>Turn into reward: on an idea, pick how it unlocks (task count with N, or milestone completed). It becomes a normal *locked* reward with the same id, keeping title, photo, link, note, where seen, area and for whom; tasks are then linked on the Link screen (BR-R28)</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -13167,7 +13295,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.1</t>
+          <t>LLR-12.6</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -13177,12 +13305,12 @@
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>HLR-13</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>The tile form (new tile and ✎ edit) has a Use areas switch, on by default. POST /categories and PATCH /categories/{id} accept useAreas; every tile in GET /categories returns useAreas, and each area returns hidden</t>
+          <t>Close an idea as *Bought* (got it without a rule) or *Dropped* (no longer wanted). Closed ideas leave the Ideas list, stay under *Closed* with the date and outcome, and can be reopened (BR-R29)</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
@@ -13211,7 +13339,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.2</t>
+          <t>LLR-12.7</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -13221,17 +13349,17 @@
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>HLR-13</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>Switching areas off is only possible while the tile has no areas; otherwise the switch is disabled with "move or delete its N areas first" and the API answers 409 (BR-R31)</t>
+          <t>Ideas are Silent by default (hidden from the read-only view) and can be switched to *Announced*; ordinary rewards default to *Announced*. Visibility follows the silent rules of BR-R23 (Q24)</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Built &amp; tested</t>
+          <t>Built (manual test)</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr">
@@ -13255,7 +13383,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.3</t>
+          <t>LLR-12.8</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -13265,12 +13393,12 @@
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>HLR-13</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>A tile without areas opens straight to Tasks | Rewards | Notes &amp; contacts at #/rewards/c/{tile} (/rewards, /details), with the tile's name, icon and its ✎ / 🗑 buttons. Old links to its hidden area open the tile instead</t>
+          <t>Ideas are included in search (LLR-10.9) by title, notes, for whom and where seen</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
@@ -13299,7 +13427,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.4</t>
+          <t>LLR-12.9</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -13309,12 +13437,12 @@
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>HLR-13</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Tiles screen shows "N active tasks" without an area count; the Tasks, Rewards and Link screens, area pickers, search results and the dashboard show such tasks and rewards under the tile name alone (e.g. "💼 Career / Office / Work", never "› General")</t>
+          <t>Existing rewards are migrated without data loss: for whom = "Me", visibility = announced; their status, rule, tasks and progress are unchanged</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -13343,7 +13471,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.5</t>
+          <t>LLR-13.1</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -13358,7 +13486,7 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>No areas can be added to, and the hidden area can't be renamed or deleted on, a tile without areas (409); the starter set never adds areas to it</t>
+          <t>The tile form (new tile and ✎ edit) has a Use areas switch, on by default. POST /categories and PATCH /categories/{id} accept useAreas; every tile in GET /categories returns useAreas, and each area returns hidden</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
@@ -13387,7 +13515,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.6</t>
+          <t>LLR-13.2</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -13402,7 +13530,7 @@
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>Switching areas back on: if the tile holds anything, its hidden area becomes a normal area called General with everything in it; if it's empty, it simply goes</t>
+          <t>Switching areas off is only possible while the tile has no areas; otherwise the switch is disabled with "move or delete its N areas first" and the API answers 409 (BR-R31)</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -13431,7 +13559,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.7</t>
+          <t>LLR-13.3</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -13446,7 +13574,7 @@
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Move a task: the task's edit form has a *Tile or area* picker (PATCH /tasks/{id} with areaId). Completions, streaks and reward links move with it</t>
+          <t>A tile without areas opens straight to Tasks | Rewards | Notes &amp; contacts at #/rewards/c/{tile} (/rewards, /details), with the tile's name, icon and its ✎ / 🗑 buttons. Old links to its hidden area open the tile instead</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
@@ -13475,7 +13603,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>LLR-13.8</t>
+          <t>LLR-13.4</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -13490,7 +13618,7 @@
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>Existing data is kept: migration 0006_tile_without_areas adds areas.hidden (false for every existing area), with a backup first</t>
+          <t>Tiles screen shows "N active tasks" without an area count; the Tasks, Rewards and Link screens, area pickers, search results and the dashboard show such tasks and rewards under the tile name alone (e.g. "💼 Career / Office / Work", never "› General")</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -13519,22 +13647,22 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>BR-R1</t>
+          <t>LLR-13.5</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>A period is a local calendar day (daily) or a Monday–Sunday week (weekly) in BFF_TIMEZONE</t>
+          <t>No areas can be added to, and the hidden area can't be renamed or deleted on, a tile without areas (409); the starter set never adds areas to it</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
@@ -13563,22 +13691,22 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>BR-R2</t>
+          <t>LLR-13.6</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>Several completions in one period count once towards the streak (they all count towards completion count)</t>
+          <t>Switching areas back on: if the tile holds anything, its hidden area becomes a normal area called General with everything in it; if it's empty, it simply goes</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -13607,22 +13735,22 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>BR-R3</t>
+          <t>LLR-13.7</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Best streak = longest run of consecutive periods with ≥ 1 completion</t>
+          <t>Move a task: the task's edit form has a *Tile or area* picker (PATCH /tasks/{id} with areaId). Completions, streaks and reward links move with it</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
@@ -13651,22 +13779,22 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>BR-R4</t>
+          <t>LLR-13.8</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>Business rule</t>
+          <t>Functional (LLR)</t>
         </is>
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>HLR-3</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>Current streak = the run ending at the latest completed period, if that period is the current or the previous one; otherwise 0</t>
+          <t>Existing data is kept: migration 0006_tile_without_areas adds areas.hidden (false for every existing area), with a backup first</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -13695,7 +13823,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>BR-R5</t>
+          <t>BR-R1</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -13710,7 +13838,7 @@
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>One-off tasks: streak = 1 once completed, else 0 (not shown as an active streak)</t>
+          <t>A period is a local calendar day (daily) or a Monday–Sunday week (weekly) in BFF_TIMEZONE</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
@@ -13739,7 +13867,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>BR-R6</t>
+          <t>BR-R2</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -13754,7 +13882,7 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>Streaks are derived from the activity log on every read (never stored)</t>
+          <t>Several completions in one period count once towards the streak (they all count towards completion count)</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -13783,7 +13911,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>BR-R7</t>
+          <t>BR-R3</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -13793,12 +13921,12 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>*Completions* rule progress = total completions of all tagged tasks (all-time)</t>
+          <t>Best streak = longest run of consecutive periods with ≥ 1 completion</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
@@ -13827,7 +13955,7 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>BR-R8</t>
+          <t>BR-R4</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -13837,12 +13965,12 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t>*Streak* rule progress = the highest current streak among tagged tasks</t>
+          <t>Current streak = the run ending at the latest completed period, if that period is the current or the previous one; otherwise 0</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -13871,7 +13999,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>BR-R9</t>
+          <t>BR-R5</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -13881,12 +14009,12 @@
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>The unlock check runs on task completion, reward creation, reward update and tag change</t>
+          <t>One-off tasks: streak = 1 once completed, else 0 (not shown as an active streak)</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
@@ -13915,7 +14043,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>BR-R10</t>
+          <t>BR-R6</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -13925,12 +14053,12 @@
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>HLR-4</t>
+          <t>HLR-3</t>
         </is>
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>Status flow locked → unlocked → claimed only; there's no path back</t>
+          <t>Streaks are derived from the activity log on every read (never stored)</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -13959,7 +14087,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>BR-R11</t>
+          <t>BR-R7</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -13974,7 +14102,7 @@
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Unlocked and claimed rewards always show 100 %</t>
+          <t>*Completions* rule progress = total completions of all tagged tasks (all-time)</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
@@ -14003,7 +14131,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>BR-R12</t>
+          <t>BR-R8</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -14013,12 +14141,12 @@
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>Scope containment. A task is in a reward's scope when the task's area belongs to the reward's tile and, if the reward has an area, the task's area *is* that area</t>
+          <t>*Streak* rule progress = the highest current streak among tagged tasks</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -14047,7 +14175,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>BR-R13</t>
+          <t>BR-R9</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -14057,12 +14185,12 @@
       </c>
       <c r="C174" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Matched tasks. *Selected tasks*: the tagged tasks (all in scope). *All tasks in scope*: every task in scope whose status isn't archived. BR-R7 and BR-R8 compute progress over the matched tasks</t>
+          <t>The unlock check runs on task completion, reward creation, reward update and tag change</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
@@ -14091,7 +14219,7 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>BR-R14</t>
+          <t>BR-R10</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -14101,12 +14229,12 @@
       </c>
       <c r="C175" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>In *All tasks in scope* mode, tags are ignored for progress (they're kept, so switching back to *Selected tasks* restores them)</t>
+          <t>Status flow locked → unlocked → claimed only; there's no path back</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -14135,7 +14263,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>BR-R15</t>
+          <t>BR-R11</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -14145,12 +14273,12 @@
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>HLR-9</t>
+          <t>HLR-4</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>The unlock check (BR-R9) on completion evaluates every locked reward that matches the completed task, whether tagged or by scope</t>
+          <t>Unlocked and claimed rewards always show 100 %</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
@@ -14179,7 +14307,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>BR-R16</t>
+          <t>BR-R12</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -14194,7 +14322,7 @@
       </c>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t>A reward marked *Needs a tile* (LLR-4.18) still shows progress from its tags, but can't be edited until a tile is chosen. It never unlocks from tasks outside the tile the user then picks</t>
+          <t>Scope containment. A task is in a reward's scope when the task's area belongs to the reward's tile and, if the reward has an area, the task's area *is* that area</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -14223,7 +14351,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>BR-R17</t>
+          <t>BR-R13</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -14233,12 +14361,12 @@
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>HLR-1</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>Tile names are unique ignoring case; area names are unique within their tile ignoring case</t>
+          <t>Matched tasks. *Selected tasks*: the tagged tasks (all in scope). *All tasks in scope*: every task in scope whose status isn't archived. BR-R7 and BR-R8 compute progress over the matched tasks</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
@@ -14267,7 +14395,7 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>BR-R18</t>
+          <t>BR-R14</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -14277,12 +14405,12 @@
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>HLR-1</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>Deleting a tile removes everything under it (areas, tasks, completions, rewards scoped to it, notes, contacts, files) in one transaction, after a database snapshot is saved to data/backups/</t>
+          <t>In *All tasks in scope* mode, tags are ignored for progress (they're kept, so switching back to *Selected tasks* restores them)</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -14311,7 +14439,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>BR-R19</t>
+          <t>BR-R15</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -14321,12 +14449,12 @@
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>HLR-1</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>The starter set only adds tiles and areas whose names are missing; it never renames, merges or deletes</t>
+          <t>The unlock check (BR-R9) on completion evaluates every locked reward that matches the completed task, whether tagged or by scope</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
@@ -14355,7 +14483,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>BR-R20</t>
+          <t>BR-R16</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -14365,12 +14493,12 @@
       </c>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-9</t>
         </is>
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>Details belong to exactly one owner: a tile or an area. Moving an area to another tile isn't supported, so details never change tile</t>
+          <t>A reward marked *Needs a tile* (LLR-4.18) still shows progress from its tags, but can't be edited until a tile is chosen. It never unlocks from tasks outside the tile the user then picks</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -14399,7 +14527,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>BR-R21</t>
+          <t>BR-R17</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
@@ -14409,12 +14537,12 @@
       </c>
       <c r="C182" s="7" t="inlineStr">
         <is>
-          <t>HLR-10</t>
+          <t>HLR-1</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>The "last executive" of a topic is the *Service executive* or *Technician* contact in that topic with the latest last-visit date; contacts without a date come after dated ones</t>
+          <t>Tile names are unique ignoring case; area names are unique within their tile ignoring case</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
@@ -14443,7 +14571,7 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>BR-R22</t>
+          <t>BR-R18</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
@@ -14453,12 +14581,12 @@
       </c>
       <c r="C183" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-1</t>
         </is>
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>A task is overdue when it's active, has a due date, and the due date is before now. Done and archived tasks are never overdue</t>
+          <t>Deleting a tile removes everything under it (areas, tasks, completions, rewards scoped to it, notes, contacts, files) in one transaction, after a database snapshot is saved to data/backups/</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -14487,7 +14615,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>BR-R23</t>
+          <t>BR-R19</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
@@ -14497,12 +14625,12 @@
       </c>
       <c r="C184" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-1</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Silent means invisible without the passcode: silent tasks, their completions, streaks and activity are excluded from every response to a caller without the owner passcode, including counts and aggregates, so their existence can't be inferred</t>
+          <t>The starter set only adds tiles and areas whose names are missing; it never renames, merges or deletes</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
@@ -14531,7 +14659,7 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>BR-R24</t>
+          <t>BR-R20</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
@@ -14541,12 +14669,12 @@
       </c>
       <c r="C185" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>Celebrations and share prompts happen only for announced tasks. A reward unlocked by a silent task's completion is unlocked quietly (no share prompt); the reward itself stays visible</t>
+          <t>Details belong to exactly one owner: a tile or an area. Moving an area to another tile isn't supported, so details never change tile</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -14575,7 +14703,7 @@
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>BR-R25</t>
+          <t>BR-R21</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -14585,12 +14713,12 @@
       </c>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>HLR-11</t>
+          <t>HLR-10</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>A Milestone completed reward unlocks when every milestone task it matches (tagged, or in scope with *All tasks in scope*) has ≥ 1 completion. Non-milestone tasks tagged to it don't count. Progress = milestones completed ÷ milestones matched</t>
+          <t>The "last executive" of a topic is the *Service executive* or *Technician* contact in that topic with the latest last-visit date; contacts without a date come after dated ones</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
@@ -14619,7 +14747,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>BR-R26</t>
+          <t>BR-R22</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -14634,7 +14762,7 @@
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>Due date and days to complete are never derived from each other or from the frequency</t>
+          <t>A task is overdue when it's active, has a due date, and the due date is before now. Done and archived tasks are never overdue</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -14663,7 +14791,7 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>BR-R27</t>
+          <t>BR-R23</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -14673,12 +14801,12 @@
       </c>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>An *Idea* has no rule and no progress. It can't unlock or be claimed, and it isn't counted in reward totals or progress on the dashboard (the dashboard shows an *Ideas* count per person)</t>
+          <t>Silent means invisible without the passcode: silent tasks, their completions, streaks and activity are excluded from every response to a caller without the owner passcode, including counts and aggregates, so their existence can't be inferred</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
@@ -14707,7 +14835,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>BR-R28</t>
+          <t>BR-R24</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -14717,12 +14845,12 @@
       </c>
       <c r="C189" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>Turning an idea into a reward requires a rule and a threshold (except *milestone completed*); a tile isn't required since rewards stand alone. The idea's id is kept, so links and photos stay attached</t>
+          <t>Celebrations and share prompts happen only for announced tasks. A reward unlocked by a silent task's completion is unlocked quietly (no share prompt); the reward itself stays visible</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -14751,7 +14879,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>BR-R29</t>
+          <t>BR-R25</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -14761,12 +14889,12 @@
       </c>
       <c r="C190" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>Closing is only for ideas; a reward that already has a rule is claimed, not closed. Reopening a closed idea returns it to *Idea*</t>
+          <t>A Milestone completed reward unlocks when every milestone task it matches (tagged, or in scope with *All tasks in scope*) has ≥ 1 completion. Non-milestone tasks tagged to it don't count. Progress = milestones completed ÷ milestones matched</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
@@ -14795,7 +14923,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>BR-R30</t>
+          <t>BR-R26</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -14805,12 +14933,12 @@
       </c>
       <c r="C191" s="7" t="inlineStr">
         <is>
-          <t>HLR-12</t>
+          <t>HLR-11</t>
         </is>
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>*For whom* is a label: it groups and filters rewards, but never changes who can see or edit them (visibility rules decide that)</t>
+          <t>Due date and days to complete are never derived from each other or from the frequency</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -14839,7 +14967,7 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>BR-R31</t>
+          <t>BR-R27</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -14849,12 +14977,12 @@
       </c>
       <c r="C192" s="7" t="inlineStr">
         <is>
-          <t>HLR-13</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>A tile either uses areas or holds everything itself, never both. Areas can only be switched off on a tile with no areas, so nothing is hidden or lost by the switch</t>
+          <t>An *Idea* has no rule and no progress. It can't unlock or be claimed, and it isn't counted in reward totals or progress on the dashboard (the dashboard shows an *Ideas* count per person)</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
@@ -14883,22 +15011,22 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>NFR-D1</t>
+          <t>BR-R28</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>Remote exposed chunk ≤ 50 KB gzip (now ~11 KB)</t>
+          <t>Turning an idea into a reward requires a rule and a threshold (except *milestone completed*); a tile isn't required since rewards stand alone. The idea's id is kept, so links and photos stay attached</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -14920,29 +15048,29 @@
       <c r="I193" s="8" t="inlineStr"/>
       <c r="J193" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>NFR-D2</t>
+          <t>BR-R29</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C194" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>Remote load after navigating to #/rewards ≤ 500 ms locally (measured ~36 ms client-side nav, ~275 ms cold)</t>
+          <t>Closing is only for ideas; a reward that already has a rule is claimed, not closed. Reopening a closed idea returns it to *Idea*</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
@@ -14964,29 +15092,29 @@
       <c r="I194" s="8" t="inlineStr"/>
       <c r="J194" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>NFR-D3</t>
+          <t>BR-R30</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-12</t>
         </is>
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>Dashboard issues ≤ 1 BFF read per window per 30 s</t>
+          <t>*For whom* is a label: it groups and filters rewards, but never changes who can see or edit them (visibility rules decide that)</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -15008,29 +15136,29 @@
       <c r="I195" s="8" t="inlineStr"/>
       <c r="J195" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>NFR-D4</t>
+          <t>BR-R31</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C196" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-13</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>No horizontal scroll at 375 px width</t>
+          <t>A tile either uses areas or holds everything itself, never both. Areas can only be switched off on a tile with no areas, so nothing is hidden or lost by the switch</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
@@ -15052,29 +15180,29 @@
       <c r="I196" s="8" t="inlineStr"/>
       <c r="J196" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>NFR-D5</t>
+          <t>BR-R32</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
         <is>
-          <t>Non-functional (detailed)</t>
+          <t>Business rule</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>HLR-2</t>
         </is>
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>Stats for N tasks use one activity query (no N+1)</t>
+          <t>Each area (or tile without areas) has one task order, set only by the user: top = most important. Nothing reorders tasks automatically: not adding (goes last), completing, editing, filtering or sorting by due date. A reorder must list every active task of the area exactly once</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -15096,14 +15224,14 @@
       <c r="I197" s="8" t="inlineStr"/>
       <c r="J197" s="7" t="inlineStr">
         <is>
-          <t>LLRD › 6. Detailed non-functional requirements</t>
+          <t>LLRD › 3. Detailed functional requirements</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>NFR-D6</t>
+          <t>NFR-D1</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -15118,7 +15246,7 @@
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Every business rule BR-R1…R30 has ≥ 1 automated test</t>
+          <t>Remote exposed chunk ≤ 50 KB gzip (now ~11 KB)</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
@@ -15147,7 +15275,7 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>NFR-D7</t>
+          <t>NFR-D2</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
@@ -15162,7 +15290,7 @@
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>Naive datetimes never reach storage</t>
+          <t>Remote load after navigating to #/rewards ≤ 500 ms locally (measured ~36 ms client-side nav, ~275 ms cold)</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -15191,7 +15319,7 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>NFR-D8</t>
+          <t>NFR-D3</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -15206,7 +15334,7 @@
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>No schema change may delete or rewrite existing rows except as specified (LLR-4.18); every migration has an upgrade test run against a copy of a pre-migration database</t>
+          <t>Dashboard issues ≤ 1 BFF read per window per 30 s</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
@@ -15235,7 +15363,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>NFR-D9</t>
+          <t>NFR-D4</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -15250,12 +15378,12 @@
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>Uploaded files are stored outside any public web folder with random names, served only through the BFF, and count against a 2 GB soft limit on the droplet (warning shown); moving to object storage later changes no requirement</t>
+          <t>No horizontal scroll at 375 px width</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F201" s="8" t="inlineStr">
@@ -15279,7 +15407,7 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>NFR-D10</t>
+          <t>NFR-D5</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -15294,12 +15422,12 @@
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Search over notes, contacts and files returns in ≤ 300 ms for 5,000 items</t>
+          <t>Stats for N tasks use one activity query (no N+1)</t>
         </is>
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F202" s="8" t="inlineStr">
@@ -15323,7 +15451,7 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>NFR-D11</t>
+          <t>NFR-D6</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -15338,12 +15466,12 @@
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>Every read endpoint has a test that a silent task leaves no trace (item, count or aggregate) in its response without the passcode</t>
+          <t>Every business rule BR-R1…R30 has ≥ 1 automated test</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Built &amp; tested</t>
         </is>
       </c>
       <c r="F203" s="8" t="inlineStr">
@@ -15364,13 +15492,233 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D7</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D204" s="8" t="inlineStr">
+        <is>
+          <t>Naive datetimes never reach storage</t>
+        </is>
+      </c>
+      <c r="E204" s="8" t="inlineStr">
+        <is>
+          <t>Built &amp; tested</t>
+        </is>
+      </c>
+      <c r="F204" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G204" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H204" s="8" t="inlineStr"/>
+      <c r="I204" s="8" t="inlineStr"/>
+      <c r="J204" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D8</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D205" s="8" t="inlineStr">
+        <is>
+          <t>No schema change may delete or rewrite existing rows except as specified (LLR-4.18); every migration has an upgrade test run against a copy of a pre-migration database</t>
+        </is>
+      </c>
+      <c r="E205" s="8" t="inlineStr">
+        <is>
+          <t>Built &amp; tested</t>
+        </is>
+      </c>
+      <c r="F205" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G205" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H205" s="8" t="inlineStr"/>
+      <c r="I205" s="8" t="inlineStr"/>
+      <c r="J205" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D9</t>
+        </is>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D206" s="8" t="inlineStr">
+        <is>
+          <t>Uploaded files are stored outside any public web folder with random names, served only through the BFF, and count against a 2 GB soft limit on the droplet (warning shown); moving to object storage later changes no requirement</t>
+        </is>
+      </c>
+      <c r="E206" s="8" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="F206" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G206" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H206" s="8" t="inlineStr"/>
+      <c r="I206" s="8" t="inlineStr"/>
+      <c r="J206" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D10</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D207" s="8" t="inlineStr">
+        <is>
+          <t>Search over notes, contacts and files returns in ≤ 300 ms for 5,000 items</t>
+        </is>
+      </c>
+      <c r="E207" s="8" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="F207" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G207" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H207" s="8" t="inlineStr"/>
+      <c r="I207" s="8" t="inlineStr"/>
+      <c r="J207" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>NFR-D11</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>Non-functional (detailed)</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D208" s="8" t="inlineStr">
+        <is>
+          <t>Every read endpoint has a test that a silent task leaves no trace (item, count or aggregate) in its response without the passcode</t>
+        </is>
+      </c>
+      <c r="E208" s="8" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="F208" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G208" s="8" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="H208" s="8" t="inlineStr"/>
+      <c r="I208" s="8" t="inlineStr"/>
+      <c r="J208" s="7" t="inlineStr">
+        <is>
+          <t>LLRD › 6. Detailed non-functional requirements</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J203"/>
+  <autoFilter ref="A4:J208"/>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E403" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E408" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Built &amp; tested,Built (manual test),Planned,Next,Out of scope"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F403" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F408" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Must,Should,Could,Won't (now)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15384,7 +15732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15548,82 +15896,82 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>test_create_filter_and_reprioritise_tasks</t>
+          <t>test_create_filter_and_order_tasks</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>LLR-2.10</t>
+          <t>LLR-2.11–2.14; BR-R32</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>PATCH /tasks/{id}, DELETE /tasks/{id}</t>
+          <t>PUT /areas/{id}/tasks/order, GET /areas/{id}/tasks, GET /tasks</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>test_edit_and_delete_task</t>
+          <t>test_new_task_goes_last, test_reorder_needs_every_active_task_once, test_done_tasks_keep_their_place, test_completing_editing_and_due_sort_never_reorder, test_order_shared_by_area_and_tasks_lists, test_moved_task_goes_last, test_migration_keeps_priority_order; mouse drag, keyboard reorder and the due-date view verified in the browser</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.1, 3.6, 3.7; BR-R2–R4</t>
+          <t>LLR-2.10</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/complete, GET /tasks/{id}/activity, GET /tasks/{id}</t>
+          <t>PATCH /tasks/{id}, DELETE /tasks/{id}</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>test_completions_build_streak_and_activity_log, test_daily_streak, test_weekly_streak</t>
+          <t>test_edit_and_delete_task</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>LLR-3.3–3.5; BR-R4, R5</t>
+          <t>LLR-3.1, 3.6, 3.7; BR-R2–R4</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/complete</t>
+          <t>POST /tasks/{id}/complete, GET /tasks/{id}/activity, GET /tasks/{id}</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>test_completion_rules, test_one_off_streak_is_done_or_not</t>
+          <t>test_completions_build_streak_and_activity_log, test_daily_streak, test_weekly_streak</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.1, 4.2, 4.6, 4.7; BR-R7, R9, R10</t>
+          <t>LLR-3.3–3.5; BR-R4, R5</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>/rewards*</t>
+          <t>POST /tasks/{id}/complete</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>test_reward_unlocks_on_completion_count_then_claim, test_reward_already_met_unlocks_on_create_and_rejects_unknown_tasks, test_completions_rule_progress</t>
+          <t>test_completion_rules, test_one_off_streak_is_done_or_not</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>BR-R8</t>
+          <t>LLR-4.1, 4.2, 4.6, 4.7; BR-R7, R9, R10</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -15633,141 +15981,158 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>test_streak_reward_uses_best_current_streak_across_tasks, test_streak_rule_progress</t>
+          <t>test_reward_unlocks_on_completion_count_then_claim, test_reward_already_met_unlocks_on_create_and_rejects_unknown_tasks, test_completions_rule_progress</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>BR-R11</t>
+          <t>BR-R8</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/rewards*</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>test_unlocked_reward_stays_complete_after_streak_breaks</t>
+          <t>test_streak_reward_uses_best_current_streak_across_tasks, test_streak_rule_progress</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>LLR-5.1, 5.9, 5.10</t>
+          <t>BR-R11</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>GET /dashboard/summary</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>test_dashboard_summary_is_flat_snake_case</t>
+          <t>test_unlocked_reward_stays_complete_after_streak_breaks</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.1</t>
+          <t>LLR-5.1, 5.9, 5.10</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>GET /dashboard/summary</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>test_requires_demo_token</t>
+          <t>test_dashboard_summary_is_flat_snake_case</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>LLR-7.x, 5.2–5.8</t>
+          <t>LLR-8.1</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>all</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Manual E2E (browser, 375 px); planned Playwright smoke</t>
+          <t>test_requires_demo_token</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>LLR-6.x</t>
+          <t>LLR-7.x, 5.2–5.8</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>planned: adapter tests with FakeVisionAdapter, fallback tests</t>
+          <t>Manual E2E (browser, 375 px); planned Playwright smoke</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>LLR-4.9–4.17; LLR-8.7, 8.8</t>
+          <t>LLR-6.x</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>/rewards*, /rewards/{id}/tasks/{taskId}</t>
+          <t>⏳</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>test_reward_needs_only_a_title, test_area_rewards_are_kept_in_an_area_but_link_anywhere, test_link_any_task_to_any_reward, test_linked_task_counts_unlock_the_reward, test_linking_tasks_already_done_enough_unlocks_immediately, test_rewards_outlive_tiles_areas_and_tasks, test_delete_reward_keeps_tasks, test_older_all_tasks_in_area_rewards_keep_counting</t>
+          <t>planned: adapter tests with FakeVisionAdapter, fallback tests</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>LLR-8.9; NFR-D8</t>
+          <t>LLR-4.9–4.17; LLR-8.7, 8.8</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>startup migrations, app.backup</t>
+          <t>/rewards*, /rewards/{id}/tasks/{taskId}</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>test_models_match_migrations, test_pre_migration_database_is_stamped_not_rebuilt, test_migrate_is_idempotent, test_export_import_round_trip, test_import_refuses_non_empty_target_without_replace</t>
+          <t>test_reward_needs_only_a_title, test_area_rewards_are_kept_in_an_area_but_link_anywhere, test_link_any_task_to_any_reward, test_linked_task_counts_unlock_the_reward, test_linking_tasks_already_done_enough_unlocks_immediately, test_rewards_outlive_tiles_areas_and_tasks, test_delete_reward_keeps_tasks, test_older_all_tasks_in_area_rewards_keep_counting</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
+          <t>LLR-8.9; NFR-D8</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>startup migrations, app.backup</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>test_models_match_migrations, test_pre_migration_database_is_stamped_not_rebuilt, test_migrate_is_idempotent, test_export_import_round_trip, test_import_refuses_non_empty_target_without_replace</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
           <t>LLR-4.18; BR-R16</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>migration 0003_reward_scope</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>test_migration_infers_scope_and_keeps_data (runs against a database at 0002_details)</t>
         </is>
@@ -15860,27 +16225,27 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A5,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A5,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A5)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A5)</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A5,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A5,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A5,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A5,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A5,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A5,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G5" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A5,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A5,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H5" s="9">
@@ -15895,27 +16260,27 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A6,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A6,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A6)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A6)</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A6,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A6,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A6,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A6,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A6,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A6,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G6" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A6,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A6,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H6" s="9">
@@ -15930,27 +16295,27 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A7,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A7,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C7" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A7)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A7)</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A7,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A7,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A7,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A7,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A7,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A7,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A7,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A7,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H7" s="9">
@@ -15965,27 +16330,27 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A8,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A8,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C8" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A8)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A8,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A8,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A8,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A8,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A8,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A8,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G8" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A8,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A8,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H8" s="9">
@@ -16000,27 +16365,27 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A9,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A9,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C9" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A9)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A9,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A9,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A9,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A9,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A9,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A9,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G9" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A9,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A9,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H9" s="9">
@@ -16035,27 +16400,27 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A10,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A10,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A10)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A10,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A10,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A10,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A10,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A10,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A10,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G10" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A10,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A10,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H10" s="9">
@@ -16070,27 +16435,27 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A11,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A11,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A11)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A11,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A11,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A11,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A11,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A11,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A11,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G11" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A11,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A11,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H11" s="9">
@@ -16105,27 +16470,27 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A12,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A12,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A12)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A12,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A12,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A12,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A12,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A12,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A12,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G12" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A12,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A12,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H12" s="9">
@@ -16140,27 +16505,27 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A13,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A13,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A13)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A13,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A13,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A13,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A13,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A13,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A13,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G13" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A13,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A13,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H13" s="9">
@@ -16175,27 +16540,27 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A14,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A14,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A14)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A14,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A14,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A14,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A14,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A14,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A14,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G14" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A14,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A14,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H14" s="9">
@@ -16210,27 +16575,27 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A15,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A15,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C15" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A15)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A15)</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A15,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A15,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A15,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A15,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A15,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A15,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G15" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A15,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A15,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H15" s="9">
@@ -16245,27 +16610,27 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A16,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A16,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C16" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A16)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A16)</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A16,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A16,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A16,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A16,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A16,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A16,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G16" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A16,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A16,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H16" s="9">
@@ -16280,27 +16645,27 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$403,MATCH(A17,'Requirements Register'!$A$5:$A$403,0)),"")</f>
+        <f>IFERROR(INDEX('Requirements Register'!$D$5:$D$408,MATCH(A17,'Requirements Register'!$A$5:$A$408,0)),"")</f>
         <v/>
       </c>
       <c r="C17" s="7">
-        <f>COUNTIF('Requirements Register'!$C$5:$C$403,A17)</f>
+        <f>COUNTIF('Requirements Register'!$C$5:$C$408,A17)</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A17,'Requirements Register'!$E$5:$E$403,"Built &amp; tested")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A17,'Requirements Register'!$E$5:$E$408,"Built &amp; tested")</f>
         <v/>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A17,'Requirements Register'!$E$5:$E$403,"Built (manual test)")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A17,'Requirements Register'!$E$5:$E$408,"Built (manual test)")</f>
         <v/>
       </c>
       <c r="F17" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A17,'Requirements Register'!$E$5:$E$403,"Next")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A17,'Requirements Register'!$E$5:$E$408,"Next")</f>
         <v/>
       </c>
       <c r="G17" s="7">
-        <f>COUNTIFS('Requirements Register'!$C$5:$C$403,A17,'Requirements Register'!$E$5:$E$403,"Planned")</f>
+        <f>COUNTIFS('Requirements Register'!$C$5:$C$408,A17,'Requirements Register'!$E$5:$E$408,"Planned")</f>
         <v/>
       </c>
       <c r="H17" s="9">
@@ -16412,7 +16777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -16901,92 +17266,114 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>PO review (2026-10-03)</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Three priority levels are too coarse: within "High" there is still a most and a least important task, and choosing a level for every task is friction</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Tasks are dragged into order: top = most important, bottom = least. The order replaces High/Med/Low; new tasks start at the bottom (HLR-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
           <t>D10</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PO review of MVP (2026-09-28)</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Rewards float free of the tile/area structure: a reward can be tagged to any task anywhere, so it isn't clear which part of life a reward belongs to</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Rewards use the same tiles and areas as tasks, and are matched to tasks inside that scope (HLR-9)</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>2.4 Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>• A1. Single user for the MVP; data is personal and low volume (&lt; 1k tasks, &lt; 50k completions).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>• A2. The user's calendar is one timezone (Asia/Kolkata by default).</t>
+          <t>• A1. Single user for the MVP; data is personal and low volume (&lt; 1k tasks, &lt; 50k completions).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>• A3. Rewards are self-fulfilled. There's no purchasing or payment integration.</t>
+          <t>• A2. The user's calendar is one timezone (Asia/Kolkata by default).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
+          <t>• A3. Rewards are self-fulfilled. There's no purchasing or payment integration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
           <t>• A4. The host site remains Vite + React 19 with hash routing.</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>2.5 Constraints</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>• C1. Existing Vercel deployment of the host must keep building (npm run build → dist).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>• C2. Solo developer, capstone timeline; prefer managed or zero-ops components.</t>
+          <t>• C1. Existing Vercel deployment of the host must keep building (npm run build → dist).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>• C3. AI API keys must never reach the browser.</t>
+          <t>• C2. Solo developer, capstone timeline; prefer managed or zero-ops components.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>• C3. AI API keys must never reach the browser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>• C4. Out of scope: Android build, real auth, multi-user, other microfrontends, WhatsApp/Apify/Snowflake integrations.</t>
         </is>
@@ -17236,7 +17623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -17470,7 +17857,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>High/Med/Low; filter by priority, status, relevance</t>
+          <t>Drag tasks into your own order (top = most important); filter by status, relevance, milestone, due</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -17920,29 +18307,29 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3h</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Deploy the MFE + BFF; set the host's remote URL; merge to main</t>
+          <t>Drag tasks into order instead of High/Med/Low (HLR-2 revision, D16), with a data-preserving migration (0007_task_order) that keeps today's order</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>✅ (branch)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Integration services: vision → events/outbox → reminders</t>
+          <t>Deploy the MFE + BFF; set the host's remote URL; merge to main</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -17954,23 +18341,40 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Integration services: vision → events/outbox → reminders</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Mobile BFF surface; Android client</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>⏳ future</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>No data migration from Neo4j is planned. The old feature held no production data worth carrying over (its auth gate was disabled and the new model differs). Confirm before T4.</t>
         </is>
@@ -18299,7 +18703,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Create, prioritise, filter, change status/frequency/relevance</t>
+          <t>Create, order by importance (drag; top = most important), filter, change status/frequency/relevance</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
